--- a/crm_dominus/apps/dados/backlog_ativacao.xlsx
+++ b/crm_dominus/apps/dados/backlog_ativacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32CB1B2-F661-4552-A459-6EA61FF1A0EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC39D773-336F-42A3-B6D6-B9C3D33F4E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1068BE8-6A04-4046-BF81-1D35DD95EA81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11798" uniqueCount="2362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12560" uniqueCount="2493">
   <si>
     <t>Cliente</t>
   </si>
@@ -6810,9 +6810,6 @@
     <t>NEUZA MARIA MACCARI JAGUSZESKI</t>
   </si>
   <si>
-    <t>Antônio Carlos Rosário</t>
-  </si>
-  <si>
     <t>Isabela Rodrigues goularte</t>
   </si>
   <si>
@@ -6888,9 +6885,6 @@
     <t>Blandine Dessakines</t>
   </si>
   <si>
-    <t>Jenifer De Oliveira</t>
-  </si>
-  <si>
     <t>GIRLAN ESTANISLAU DOS SANTOS</t>
   </si>
   <si>
@@ -7120,6 +7114,405 @@
   </si>
   <si>
     <t>PAR - COM - PSW - TORMEN INFORMATICA - GABRIELA P. GIRARDI</t>
+  </si>
+  <si>
+    <t>ANTÔNIO CARLOS CUSTODIO ROSÁRIO</t>
+  </si>
+  <si>
+    <t>Genifer De Oliveira</t>
+  </si>
+  <si>
+    <t>Fernanda Siqueira Souza E Silva</t>
+  </si>
+  <si>
+    <t>CLAUDINEIA APARECIDA BIANCHINI REIS</t>
+  </si>
+  <si>
+    <t>Adelar Stoll</t>
+  </si>
+  <si>
+    <t>LAURI FORTES</t>
+  </si>
+  <si>
+    <t>GABRIELA FIGUEIREDO DA SILVA</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Almeida Pinto</t>
+  </si>
+  <si>
+    <t>DOUGLAS MACHADO PINTO</t>
+  </si>
+  <si>
+    <t>Thiago Perin</t>
+  </si>
+  <si>
+    <t>Marcos Antônio Giaretta</t>
+  </si>
+  <si>
+    <t>IRACEMA RIVA</t>
+  </si>
+  <si>
+    <t>Zenaira Streit de campos</t>
+  </si>
+  <si>
+    <t>CLAUDIA DE ALMEIDA MELO</t>
+  </si>
+  <si>
+    <t>Castorino Galvao Filho</t>
+  </si>
+  <si>
+    <t>MARCIO EMANUEL DORNELAS</t>
+  </si>
+  <si>
+    <t>EDILANAR MACIEL LOURENÇO</t>
+  </si>
+  <si>
+    <t>ANA FLAVIA FELIX</t>
+  </si>
+  <si>
+    <t>Sueli De Oliveira</t>
+  </si>
+  <si>
+    <t>ALISSON FELIPE PEDRA HUME</t>
+  </si>
+  <si>
+    <t>Dalvina Fortes da Silva</t>
+  </si>
+  <si>
+    <t>maria leopoldina rodrigues rocha</t>
+  </si>
+  <si>
+    <t>ELEN WOLOSZYN TOMAZ</t>
+  </si>
+  <si>
+    <t>Regiane de Mello costa</t>
+  </si>
+  <si>
+    <t>DIONATAN RODRIGUES CHAVES</t>
+  </si>
+  <si>
+    <t>Edna rosa Marques</t>
+  </si>
+  <si>
+    <t>Lucas Dilan Esteven</t>
+  </si>
+  <si>
+    <t>EDIMARILDA DELFINO LEAL DA SILVA</t>
+  </si>
+  <si>
+    <t>SANDRA ZENATTI</t>
+  </si>
+  <si>
+    <t>CLUBE RECREATIVO E CULTURAL UNIAO DA GLORIA</t>
+  </si>
+  <si>
+    <t>THAIS APARECIDA PEREIRA</t>
+  </si>
+  <si>
+    <t>Alessa Rafaelle Amaral Ferreira</t>
+  </si>
+  <si>
+    <t>ELEN SOARES BARBOSA</t>
+  </si>
+  <si>
+    <t>Leticia de Jesus Cruz</t>
+  </si>
+  <si>
+    <t>Célia Jacinta Carneiro</t>
+  </si>
+  <si>
+    <t>nelcindda Pereira da Silva</t>
+  </si>
+  <si>
+    <t>Andreia Vigano Pires</t>
+  </si>
+  <si>
+    <t>maria ivone ribeiro tegami</t>
+  </si>
+  <si>
+    <t>Ismary Flores</t>
+  </si>
+  <si>
+    <t>CLEIDE DAIANE RODRIGUES</t>
+  </si>
+  <si>
+    <t>Luciana Paula Menezes</t>
+  </si>
+  <si>
+    <t>CASSIA LILIANE VIEIRA FRANCESCHI</t>
+  </si>
+  <si>
+    <t>Mateus Genani Kovalski</t>
+  </si>
+  <si>
+    <t>DEBORA SILVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>LUCIANO FELIPPE BAGATINI</t>
+  </si>
+  <si>
+    <t>CLAUDINEI RAZERA</t>
+  </si>
+  <si>
+    <t>Ademir Fátima Barbosa</t>
+  </si>
+  <si>
+    <t>LARISSA BURIN MACHADO</t>
+  </si>
+  <si>
+    <t>ENDRIGO DOS SANTOS RIBAS</t>
+  </si>
+  <si>
+    <t>Geison Gedeão trindade</t>
+  </si>
+  <si>
+    <t>VALDEMAR BILHAR GODINHO</t>
+  </si>
+  <si>
+    <t>ALINE CRISTINA SEMCHECHEM</t>
+  </si>
+  <si>
+    <t>Joarez Bernanrdes</t>
+  </si>
+  <si>
+    <t>STEFANNY THALLYA MAIA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Juliano da Silva paz</t>
+  </si>
+  <si>
+    <t>SUELÉM BEATRIZ DA SILVA</t>
+  </si>
+  <si>
+    <t>Augusto de Campos Vieira da Rosa</t>
+  </si>
+  <si>
+    <t>RONOALDO MONTALVÃO</t>
+  </si>
+  <si>
+    <t>Erasmo Carlos Monteiro</t>
+  </si>
+  <si>
+    <t>DAIANE FLORES GONÇALVES</t>
+  </si>
+  <si>
+    <t>JONATAN ALEXANDRE SANTOS CASTRO</t>
+  </si>
+  <si>
+    <t>Lidiane de Almeida Herbstrith</t>
+  </si>
+  <si>
+    <t>JOSIANE RODRIGUES LIMA</t>
+  </si>
+  <si>
+    <t>GRACIELE APARECIDA DE FREITAS</t>
+  </si>
+  <si>
+    <t>CIBELA REBECA FERNANDES BENTO</t>
+  </si>
+  <si>
+    <t>Laís Favero</t>
+  </si>
+  <si>
+    <t>RAMON PACHECO</t>
+  </si>
+  <si>
+    <t>LUCILENE DANIEL PADILHA MENDES</t>
+  </si>
+  <si>
+    <t>Carlos Eduardo Rosa Cardia</t>
+  </si>
+  <si>
+    <t>Antônio Anderson Costa Santos</t>
+  </si>
+  <si>
+    <t>ISABELLA CHRISTINE GONÇALVES APPE</t>
+  </si>
+  <si>
+    <t>RODRIGO DA SILVA</t>
+  </si>
+  <si>
+    <t>NATANAEL LEMES HORST</t>
+  </si>
+  <si>
+    <t>FELIPE DINEL CANTINI</t>
+  </si>
+  <si>
+    <t>Dara Aparecida Amaral Ribeiro</t>
+  </si>
+  <si>
+    <t>MIRIAM ARAUJO COSTA</t>
+  </si>
+  <si>
+    <t>Roseli Da Silva Oliveira</t>
+  </si>
+  <si>
+    <t>NARENICE LOPES SILVA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>MICHELE PEREIRA GODINHO</t>
+  </si>
+  <si>
+    <t>Erick Gabriel da Luz</t>
+  </si>
+  <si>
+    <t>Rosecleia Matte</t>
+  </si>
+  <si>
+    <t>Raiane Cristina dos Santos Betim</t>
+  </si>
+  <si>
+    <t>Cleiton Luis Engelman</t>
+  </si>
+  <si>
+    <t>Elisandra Ortiz</t>
+  </si>
+  <si>
+    <t>Ana Carolina Machado Nunes</t>
+  </si>
+  <si>
+    <t>Cícera Claudia de sousa</t>
+  </si>
+  <si>
+    <t>Neila Da Silva Flores</t>
+  </si>
+  <si>
+    <t>Daiane Cristina Ribeiro</t>
+  </si>
+  <si>
+    <t>Tainara Daniela Carvalho</t>
+  </si>
+  <si>
+    <t>Tainá Corrêa Fontes</t>
+  </si>
+  <si>
+    <t>Larice machado de Oliveira</t>
+  </si>
+  <si>
+    <t>Carlos Alberto Dos Santos</t>
+  </si>
+  <si>
+    <t>Marcelo De Lima Rocha</t>
+  </si>
+  <si>
+    <t>CRISTIANE BALDEZ DIAS</t>
+  </si>
+  <si>
+    <t>EDUARDA APARECIDA SCHISSLER DA SILVA</t>
+  </si>
+  <si>
+    <t>Franciele Zanchet</t>
+  </si>
+  <si>
+    <t>Gilberto José Kipper</t>
+  </si>
+  <si>
+    <t>Aldenise Mendes da Silva</t>
+  </si>
+  <si>
+    <t>Jenifer Wiland</t>
+  </si>
+  <si>
+    <t>Jose Renato Pallota Vaz</t>
+  </si>
+  <si>
+    <t>Jesus Enrique Luque Pérez</t>
+  </si>
+  <si>
+    <t>FERNANDA RITZEL MARTINS PADILHA SOUZA</t>
+  </si>
+  <si>
+    <t>JURANDIR REMOALDO</t>
+  </si>
+  <si>
+    <t>MARIANI VAZ DE ALMEIDA SANTOS</t>
+  </si>
+  <si>
+    <t>GERALDO CASSIMIRRO FERREIRA</t>
+  </si>
+  <si>
+    <t>Maria Vitoria bueno whestphal</t>
+  </si>
+  <si>
+    <t>ALCEU SILVEIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>JAIR DA COSTA</t>
+  </si>
+  <si>
+    <t>Ronize Barpi</t>
+  </si>
+  <si>
+    <t>ELISANDRA PRITSCH</t>
+  </si>
+  <si>
+    <t>Juliana de Amorim Mello</t>
+  </si>
+  <si>
+    <t>Marcos Giovane Almada da Silva</t>
+  </si>
+  <si>
+    <t>João Felipe Pereira Da Silva</t>
+  </si>
+  <si>
+    <t>MARIA IVETE TEIXEIRA</t>
+  </si>
+  <si>
+    <t>BIANCA MARIA JAQUES</t>
+  </si>
+  <si>
+    <t>Naidjanaira Magalhães Trindade</t>
+  </si>
+  <si>
+    <t>Elias Balles</t>
+  </si>
+  <si>
+    <t>Fabiana Oliveira de Paula</t>
+  </si>
+  <si>
+    <t>Letícia Fortes Ferreira</t>
+  </si>
+  <si>
+    <t>Teresinha Elisabeth rosa martineli</t>
+  </si>
+  <si>
+    <t>Thamiris Lima da Silva</t>
+  </si>
+  <si>
+    <t>Gustavo Messias Fraporti Miotto</t>
+  </si>
+  <si>
+    <t>Ereni de Fátima Ebert</t>
+  </si>
+  <si>
+    <t>Viviane da Silva dos Santos</t>
+  </si>
+  <si>
+    <t>Elizabete Isnarde</t>
+  </si>
+  <si>
+    <t>Greicielle Santos Silva</t>
+  </si>
+  <si>
+    <t>Jorge Luiz Brito de Oliveira</t>
+  </si>
+  <si>
+    <t>COM - PBC - LUCAS DE MELO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>PAR - SOC - COM - ALMAVIVA EXPERIENCE - MARCOS V. DE CASTRO</t>
+  </si>
+  <si>
+    <t>COM - ERE - CLEONICE MARIA BUCHI</t>
+  </si>
+  <si>
+    <t>O&amp;M - PGO - TEC - RUAN EDELBERG COELHO</t>
+  </si>
+  <si>
+    <t>COM - VAI - JULIA GABRIELA DE QUADRA BARBOSA</t>
+  </si>
+  <si>
+    <t>COM - KDK - CAMILLY BUCHHORN BATISTA</t>
   </si>
 </sst>
 </file>
@@ -7543,7 +7936,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBE226-2569-43EF-8B89-51B7526D69A9}">
-  <dimension ref="A1:H1966"/>
+  <dimension ref="A1:H2093"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -7621,7 +8014,7 @@
         <v>96</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H3" s="13" t="s">
         <v>87</v>
@@ -7673,7 +8066,7 @@
         <v>94</v>
       </c>
       <c r="G5" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H5" s="13" t="s">
         <v>87</v>
@@ -7725,7 +8118,7 @@
         <v>94</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>87</v>
@@ -7933,7 +8326,7 @@
         <v>118</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H15" s="13" t="s">
         <v>87</v>
@@ -8089,7 +8482,7 @@
         <v>94</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>87</v>
@@ -8115,7 +8508,7 @@
         <v>94</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H22" s="8" t="s">
         <v>87</v>
@@ -8167,7 +8560,7 @@
         <v>94</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H24" s="8" t="s">
         <v>87</v>
@@ -8271,7 +8664,7 @@
         <v>94</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H28" s="8" t="s">
         <v>87</v>
@@ -8427,7 +8820,7 @@
         <v>118</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H34" s="8" t="s">
         <v>87</v>
@@ -8505,7 +8898,7 @@
         <v>89</v>
       </c>
       <c r="G37" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H37" s="13" t="s">
         <v>87</v>
@@ -8531,7 +8924,7 @@
         <v>89</v>
       </c>
       <c r="G38" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H38" s="8" t="s">
         <v>87</v>
@@ -8557,7 +8950,7 @@
         <v>85</v>
       </c>
       <c r="G39" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H39" s="13" t="s">
         <v>87</v>
@@ -8609,7 +9002,7 @@
         <v>89</v>
       </c>
       <c r="G41" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H41" s="13" t="s">
         <v>87</v>
@@ -9103,7 +9496,7 @@
         <v>89</v>
       </c>
       <c r="G60" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H60" s="8" t="s">
         <v>87</v>
@@ -9441,7 +9834,7 @@
         <v>109</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H73" s="13" t="s">
         <v>87</v>
@@ -9493,7 +9886,7 @@
         <v>85</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H75" s="13" t="s">
         <v>87</v>
@@ -9519,7 +9912,7 @@
         <v>109</v>
       </c>
       <c r="G76" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H76" s="8" t="s">
         <v>87</v>
@@ -9597,7 +9990,7 @@
         <v>94</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H79" s="13" t="s">
         <v>87</v>
@@ -9857,7 +10250,7 @@
         <v>89</v>
       </c>
       <c r="G89" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H89" s="13" t="s">
         <v>87</v>
@@ -9883,7 +10276,7 @@
         <v>85</v>
       </c>
       <c r="G90" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H90" s="8" t="s">
         <v>87</v>
@@ -10117,7 +10510,7 @@
         <v>94</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H99" s="13" t="s">
         <v>87</v>
@@ -10195,7 +10588,7 @@
         <v>89</v>
       </c>
       <c r="G102" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H102" s="8" t="s">
         <v>87</v>
@@ -10221,7 +10614,7 @@
         <v>109</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H103" s="13" t="s">
         <v>87</v>
@@ -10403,7 +10796,7 @@
         <v>118</v>
       </c>
       <c r="G110" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H110" s="8" t="s">
         <v>87</v>
@@ -10429,7 +10822,7 @@
         <v>94</v>
       </c>
       <c r="G111" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H111" s="13" t="s">
         <v>87</v>
@@ -10455,7 +10848,7 @@
         <v>89</v>
       </c>
       <c r="G112" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H112" s="8" t="s">
         <v>87</v>
@@ -10611,7 +11004,7 @@
         <v>109</v>
       </c>
       <c r="G118" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H118" s="8" t="s">
         <v>87</v>
@@ -10663,7 +11056,7 @@
         <v>109</v>
       </c>
       <c r="G120" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H120" s="8" t="s">
         <v>87</v>
@@ -10689,7 +11082,7 @@
         <v>109</v>
       </c>
       <c r="G121" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H121" s="13" t="s">
         <v>87</v>
@@ -11521,7 +11914,7 @@
         <v>118</v>
       </c>
       <c r="G153" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H153" s="13" t="s">
         <v>87</v>
@@ -11677,7 +12070,7 @@
         <v>109</v>
       </c>
       <c r="G159" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H159" s="13" t="s">
         <v>87</v>
@@ -11781,7 +12174,7 @@
         <v>94</v>
       </c>
       <c r="G163" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H163" s="13" t="s">
         <v>87</v>
@@ -12275,7 +12668,7 @@
         <v>109</v>
       </c>
       <c r="G182" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H182" s="8" t="s">
         <v>87</v>
@@ -12925,7 +13318,7 @@
         <v>109</v>
       </c>
       <c r="G207" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H207" s="13" t="s">
         <v>87</v>
@@ -13029,7 +13422,7 @@
         <v>109</v>
       </c>
       <c r="G211" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H211" s="13" t="s">
         <v>87</v>
@@ -13211,7 +13604,7 @@
         <v>96</v>
       </c>
       <c r="G218" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H218" s="8" t="s">
         <v>87</v>
@@ -13263,7 +13656,7 @@
         <v>89</v>
       </c>
       <c r="G220" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H220" s="8" t="s">
         <v>87</v>
@@ -13289,7 +13682,7 @@
         <v>109</v>
       </c>
       <c r="G221" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H221" s="13" t="s">
         <v>87</v>
@@ -13315,7 +13708,7 @@
         <v>94</v>
       </c>
       <c r="G222" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H222" s="8" t="s">
         <v>87</v>
@@ -13341,7 +13734,7 @@
         <v>118</v>
       </c>
       <c r="G223" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H223" s="13" t="s">
         <v>87</v>
@@ -13419,7 +13812,7 @@
         <v>94</v>
       </c>
       <c r="G226" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H226" s="8" t="s">
         <v>87</v>
@@ -13445,7 +13838,7 @@
         <v>109</v>
       </c>
       <c r="G227" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H227" s="13" t="s">
         <v>87</v>
@@ -14069,7 +14462,7 @@
         <v>89</v>
       </c>
       <c r="G251" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H251" s="13" t="s">
         <v>87</v>
@@ -15083,7 +15476,7 @@
         <v>109</v>
       </c>
       <c r="G290" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H290" s="8" t="s">
         <v>87</v>
@@ -15109,7 +15502,7 @@
         <v>94</v>
       </c>
       <c r="G291" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H291" s="13" t="s">
         <v>87</v>
@@ -15213,7 +15606,7 @@
         <v>109</v>
       </c>
       <c r="G295" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H295" s="13" t="s">
         <v>87</v>
@@ -16019,7 +16412,7 @@
         <v>123</v>
       </c>
       <c r="G326" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H326" s="8" t="s">
         <v>87</v>
@@ -16201,7 +16594,7 @@
         <v>109</v>
       </c>
       <c r="G333" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H333" s="13" t="s">
         <v>87</v>
@@ -16253,7 +16646,7 @@
         <v>118</v>
       </c>
       <c r="G335" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H335" s="13" t="s">
         <v>87</v>
@@ -16721,7 +17114,7 @@
         <v>109</v>
       </c>
       <c r="G353" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H353" s="13" t="s">
         <v>87</v>
@@ -16851,7 +17244,7 @@
         <v>109</v>
       </c>
       <c r="G358" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H358" s="8" t="s">
         <v>87</v>
@@ -16929,7 +17322,7 @@
         <v>118</v>
       </c>
       <c r="G361" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H361" s="13" t="s">
         <v>87</v>
@@ -17735,7 +18128,7 @@
         <v>94</v>
       </c>
       <c r="G392" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H392" s="8" t="s">
         <v>87</v>
@@ -17995,7 +18388,7 @@
         <v>109</v>
       </c>
       <c r="G402" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H402" s="8" t="s">
         <v>87</v>
@@ -18047,7 +18440,7 @@
         <v>94</v>
       </c>
       <c r="G404" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H404" s="8" t="s">
         <v>87</v>
@@ -18099,7 +18492,7 @@
         <v>94</v>
       </c>
       <c r="G406" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H406" s="8" t="s">
         <v>87</v>
@@ -18333,7 +18726,7 @@
         <v>89</v>
       </c>
       <c r="G415" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H415" s="13" t="s">
         <v>87</v>
@@ -18437,7 +18830,7 @@
         <v>85</v>
       </c>
       <c r="G419" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H419" s="13" t="s">
         <v>87</v>
@@ -18567,7 +18960,7 @@
         <v>109</v>
       </c>
       <c r="G424" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H424" s="8" t="s">
         <v>87</v>
@@ -18983,7 +19376,7 @@
         <v>94</v>
       </c>
       <c r="G440" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H440" s="8" t="s">
         <v>87</v>
@@ -19373,7 +19766,7 @@
         <v>109</v>
       </c>
       <c r="G455" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H455" s="13" t="s">
         <v>87</v>
@@ -19399,7 +19792,7 @@
         <v>109</v>
       </c>
       <c r="G456" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H456" s="8" t="s">
         <v>87</v>
@@ -19607,7 +20000,7 @@
         <v>85</v>
       </c>
       <c r="G464" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H464" s="8" t="s">
         <v>87</v>
@@ -19685,7 +20078,7 @@
         <v>109</v>
       </c>
       <c r="G467" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H467" s="13" t="s">
         <v>87</v>
@@ -19919,7 +20312,7 @@
         <v>94</v>
       </c>
       <c r="G476" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H476" s="8" t="s">
         <v>87</v>
@@ -20179,7 +20572,7 @@
         <v>89</v>
       </c>
       <c r="G486" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H486" s="8" t="s">
         <v>87</v>
@@ -20465,7 +20858,7 @@
         <v>109</v>
       </c>
       <c r="G497" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H497" s="13" t="s">
         <v>87</v>
@@ -21063,7 +21456,7 @@
         <v>192</v>
       </c>
       <c r="G520" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H520" s="8" t="s">
         <v>87</v>
@@ -21167,7 +21560,7 @@
         <v>192</v>
       </c>
       <c r="G524" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H524" s="8" t="s">
         <v>87</v>
@@ -21323,7 +21716,7 @@
         <v>109</v>
       </c>
       <c r="G530" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H530" s="8" t="s">
         <v>87</v>
@@ -21427,7 +21820,7 @@
         <v>85</v>
       </c>
       <c r="G534" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H534" s="8" t="s">
         <v>87</v>
@@ -21661,7 +22054,7 @@
         <v>85</v>
       </c>
       <c r="G543" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H543" s="13" t="s">
         <v>87</v>
@@ -21739,7 +22132,7 @@
         <v>109</v>
       </c>
       <c r="G546" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H546" s="8" t="s">
         <v>87</v>
@@ -21999,7 +22392,7 @@
         <v>94</v>
       </c>
       <c r="G556" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H556" s="8" t="s">
         <v>87</v>
@@ -22051,7 +22444,7 @@
         <v>118</v>
       </c>
       <c r="G558" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H558" s="8" t="s">
         <v>87</v>
@@ -22259,7 +22652,7 @@
         <v>85</v>
       </c>
       <c r="G566" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H566" s="8" t="s">
         <v>87</v>
@@ -22337,7 +22730,7 @@
         <v>85</v>
       </c>
       <c r="G569" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H569" s="13" t="s">
         <v>87</v>
@@ -22935,7 +23328,7 @@
         <v>109</v>
       </c>
       <c r="G592" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H592" s="8" t="s">
         <v>87</v>
@@ -22961,7 +23354,7 @@
         <v>109</v>
       </c>
       <c r="G593" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H593" s="13" t="s">
         <v>87</v>
@@ -23091,7 +23484,7 @@
         <v>96</v>
       </c>
       <c r="G598" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H598" s="8" t="s">
         <v>87</v>
@@ -23221,7 +23614,7 @@
         <v>109</v>
       </c>
       <c r="G603" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H603" s="13" t="s">
         <v>87</v>
@@ -23325,7 +23718,7 @@
         <v>109</v>
       </c>
       <c r="G607" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H607" s="13" t="s">
         <v>87</v>
@@ -23455,7 +23848,7 @@
         <v>192</v>
       </c>
       <c r="G612" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H612" s="8" t="s">
         <v>87</v>
@@ -23949,7 +24342,7 @@
         <v>89</v>
       </c>
       <c r="G631" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H631" s="13" t="s">
         <v>87</v>
@@ -23975,7 +24368,7 @@
         <v>96</v>
       </c>
       <c r="G632" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H632" s="8" t="s">
         <v>87</v>
@@ -24157,7 +24550,7 @@
         <v>109</v>
       </c>
       <c r="G639" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H639" s="13" t="s">
         <v>87</v>
@@ -24235,7 +24628,7 @@
         <v>192</v>
       </c>
       <c r="G642" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H642" s="8" t="s">
         <v>87</v>
@@ -24833,7 +25226,7 @@
         <v>89</v>
       </c>
       <c r="G665" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H665" s="13" t="s">
         <v>87</v>
@@ -25717,7 +26110,7 @@
         <v>89</v>
       </c>
       <c r="G699" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H699" s="13" t="s">
         <v>87</v>
@@ -26185,7 +26578,7 @@
         <v>94</v>
       </c>
       <c r="G717" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H717" s="13" t="s">
         <v>87</v>
@@ -26991,7 +27384,7 @@
         <v>109</v>
       </c>
       <c r="G748" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H748" s="8" t="s">
         <v>87</v>
@@ -27511,7 +27904,7 @@
         <v>118</v>
       </c>
       <c r="G768" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H768" s="8" t="s">
         <v>87</v>
@@ -27615,7 +28008,7 @@
         <v>94</v>
       </c>
       <c r="G772" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H772" s="8" t="s">
         <v>87</v>
@@ -27927,7 +28320,7 @@
         <v>109</v>
       </c>
       <c r="G784" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H784" s="8" t="s">
         <v>87</v>
@@ -27953,7 +28346,7 @@
         <v>94</v>
       </c>
       <c r="G785" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H785" s="13" t="s">
         <v>87</v>
@@ -27979,7 +28372,7 @@
         <v>109</v>
       </c>
       <c r="G786" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H786" s="8" t="s">
         <v>87</v>
@@ -28161,7 +28554,7 @@
         <v>94</v>
       </c>
       <c r="G793" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H793" s="13" t="s">
         <v>87</v>
@@ -28265,7 +28658,7 @@
         <v>109</v>
       </c>
       <c r="G797" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H797" s="13" t="s">
         <v>87</v>
@@ -28317,7 +28710,7 @@
         <v>89</v>
       </c>
       <c r="G799" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H799" s="13" t="s">
         <v>87</v>
@@ -28655,7 +29048,7 @@
         <v>94</v>
       </c>
       <c r="G812" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H812" s="8" t="s">
         <v>87</v>
@@ -28837,7 +29230,7 @@
         <v>109</v>
       </c>
       <c r="G819" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H819" s="13" t="s">
         <v>87</v>
@@ -29071,7 +29464,7 @@
         <v>96</v>
       </c>
       <c r="G828" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H828" s="8" t="s">
         <v>87</v>
@@ -29097,7 +29490,7 @@
         <v>85</v>
       </c>
       <c r="G829" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H829" s="13" t="s">
         <v>87</v>
@@ -29357,7 +29750,7 @@
         <v>94</v>
       </c>
       <c r="G839" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H839" s="13" t="s">
         <v>87</v>
@@ -29383,7 +29776,7 @@
         <v>109</v>
       </c>
       <c r="G840" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H840" s="8" t="s">
         <v>87</v>
@@ -29513,7 +29906,7 @@
         <v>89</v>
       </c>
       <c r="G845" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H845" s="13" t="s">
         <v>87</v>
@@ -29591,7 +29984,7 @@
         <v>109</v>
       </c>
       <c r="G848" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H848" s="8" t="s">
         <v>87</v>
@@ -29721,7 +30114,7 @@
         <v>109</v>
       </c>
       <c r="G853" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H853" s="13" t="s">
         <v>87</v>
@@ -29825,7 +30218,7 @@
         <v>94</v>
       </c>
       <c r="G857" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H857" s="13" t="s">
         <v>87</v>
@@ -29877,7 +30270,7 @@
         <v>85</v>
       </c>
       <c r="G859" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H859" s="13" t="s">
         <v>87</v>
@@ -29929,7 +30322,7 @@
         <v>109</v>
       </c>
       <c r="G861" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H861" s="13" t="s">
         <v>87</v>
@@ -30059,7 +30452,7 @@
         <v>85</v>
       </c>
       <c r="G866" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H866" s="8" t="s">
         <v>87</v>
@@ -30527,7 +30920,7 @@
         <v>96</v>
       </c>
       <c r="G884" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H884" s="8" t="s">
         <v>87</v>
@@ -30579,7 +30972,7 @@
         <v>109</v>
       </c>
       <c r="G886" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H886" s="8" t="s">
         <v>87</v>
@@ -30995,7 +31388,7 @@
         <v>94</v>
       </c>
       <c r="G902" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H902" s="8" t="s">
         <v>87</v>
@@ -31021,7 +31414,7 @@
         <v>85</v>
       </c>
       <c r="G903" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H903" s="13" t="s">
         <v>87</v>
@@ -31047,7 +31440,7 @@
         <v>109</v>
       </c>
       <c r="G904" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H904" s="8" t="s">
         <v>87</v>
@@ -31307,7 +31700,7 @@
         <v>85</v>
       </c>
       <c r="G914" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H914" s="8" t="s">
         <v>87</v>
@@ -31567,7 +31960,7 @@
         <v>94</v>
       </c>
       <c r="G924" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H924" s="8" t="s">
         <v>87</v>
@@ -31931,7 +32324,7 @@
         <v>94</v>
       </c>
       <c r="G938" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H938" s="8" t="s">
         <v>87</v>
@@ -32087,7 +32480,7 @@
         <v>89</v>
       </c>
       <c r="G944" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H944" s="8" t="s">
         <v>87</v>
@@ -32113,7 +32506,7 @@
         <v>109</v>
       </c>
       <c r="G945" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H945" s="13" t="s">
         <v>87</v>
@@ -32165,7 +32558,7 @@
         <v>89</v>
       </c>
       <c r="G947" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H947" s="13" t="s">
         <v>87</v>
@@ -32269,7 +32662,7 @@
         <v>118</v>
       </c>
       <c r="G951" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H951" s="13" t="s">
         <v>87</v>
@@ -32295,7 +32688,7 @@
         <v>85</v>
       </c>
       <c r="G952" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H952" s="8" t="s">
         <v>87</v>
@@ -32373,7 +32766,7 @@
         <v>109</v>
       </c>
       <c r="G955" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H955" s="13" t="s">
         <v>87</v>
@@ -32451,7 +32844,7 @@
         <v>85</v>
       </c>
       <c r="G958" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H958" s="8" t="s">
         <v>87</v>
@@ -32581,7 +32974,7 @@
         <v>109</v>
       </c>
       <c r="G963" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H963" s="13" t="s">
         <v>87</v>
@@ -32659,7 +33052,7 @@
         <v>85</v>
       </c>
       <c r="G966" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H966" s="8" t="s">
         <v>87</v>
@@ -32737,7 +33130,7 @@
         <v>89</v>
       </c>
       <c r="G969" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H969" s="13" t="s">
         <v>87</v>
@@ -32815,7 +33208,7 @@
         <v>94</v>
       </c>
       <c r="G972" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H972" s="8" t="s">
         <v>87</v>
@@ -33205,7 +33598,7 @@
         <v>192</v>
       </c>
       <c r="G987" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H987" s="13" t="s">
         <v>87</v>
@@ -33335,7 +33728,7 @@
         <v>94</v>
       </c>
       <c r="G992" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H992" s="8" t="s">
         <v>87</v>
@@ -33595,7 +33988,7 @@
         <v>89</v>
       </c>
       <c r="G1002" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1002" s="8" t="s">
         <v>87</v>
@@ -33881,7 +34274,7 @@
         <v>109</v>
       </c>
       <c r="G1013" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1013" s="13" t="s">
         <v>87</v>
@@ -33959,7 +34352,7 @@
         <v>94</v>
       </c>
       <c r="G1016" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1016" s="8" t="s">
         <v>87</v>
@@ -34037,7 +34430,7 @@
         <v>94</v>
       </c>
       <c r="G1019" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1019" s="13" t="s">
         <v>87</v>
@@ -34401,7 +34794,7 @@
         <v>94</v>
       </c>
       <c r="G1033" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1033" s="13" t="s">
         <v>87</v>
@@ -34479,7 +34872,7 @@
         <v>109</v>
       </c>
       <c r="G1036" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1036" s="8" t="s">
         <v>87</v>
@@ -34583,7 +34976,7 @@
         <v>94</v>
       </c>
       <c r="G1040" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1040" s="8" t="s">
         <v>87</v>
@@ -34739,7 +35132,7 @@
         <v>109</v>
       </c>
       <c r="G1046" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1046" s="8" t="s">
         <v>87</v>
@@ -34765,7 +35158,7 @@
         <v>109</v>
       </c>
       <c r="G1047" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1047" s="13" t="s">
         <v>87</v>
@@ -34791,7 +35184,7 @@
         <v>94</v>
       </c>
       <c r="G1048" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1048" s="8" t="s">
         <v>87</v>
@@ -35285,7 +35678,7 @@
         <v>109</v>
       </c>
       <c r="G1067" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1067" s="13" t="s">
         <v>87</v>
@@ -35571,7 +35964,7 @@
         <v>109</v>
       </c>
       <c r="G1078" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1078" s="8" t="s">
         <v>87</v>
@@ -35597,7 +35990,7 @@
         <v>94</v>
       </c>
       <c r="G1079" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1079" s="13" t="s">
         <v>87</v>
@@ -35831,7 +36224,7 @@
         <v>85</v>
       </c>
       <c r="G1088" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1088" s="8" t="s">
         <v>87</v>
@@ -35935,7 +36328,7 @@
         <v>109</v>
       </c>
       <c r="G1092" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1092" s="8" t="s">
         <v>87</v>
@@ -36143,7 +36536,7 @@
         <v>94</v>
       </c>
       <c r="G1100" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1100" s="8" t="s">
         <v>87</v>
@@ -37053,7 +37446,7 @@
         <v>94</v>
       </c>
       <c r="G1135" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1135" s="13" t="s">
         <v>87</v>
@@ -37365,7 +37758,7 @@
         <v>94</v>
       </c>
       <c r="G1147" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1147" s="13" t="s">
         <v>87</v>
@@ -37469,7 +37862,7 @@
         <v>94</v>
       </c>
       <c r="G1151" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1151" s="13" t="s">
         <v>87</v>
@@ -37573,7 +37966,7 @@
         <v>94</v>
       </c>
       <c r="G1155" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1155" s="13" t="s">
         <v>87</v>
@@ -37703,7 +38096,7 @@
         <v>109</v>
       </c>
       <c r="G1160" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1160" s="8" t="s">
         <v>87</v>
@@ -37781,7 +38174,7 @@
         <v>109</v>
       </c>
       <c r="G1163" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1163" s="13" t="s">
         <v>87</v>
@@ -37989,7 +38382,7 @@
         <v>94</v>
       </c>
       <c r="G1171" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1171" s="13" t="s">
         <v>87</v>
@@ -38015,7 +38408,7 @@
         <v>94</v>
       </c>
       <c r="G1172" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1172" s="8" t="s">
         <v>87</v>
@@ -38171,7 +38564,7 @@
         <v>109</v>
       </c>
       <c r="G1178" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1178" s="8" t="s">
         <v>87</v>
@@ -38223,7 +38616,7 @@
         <v>89</v>
       </c>
       <c r="G1180" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1180" s="8" t="s">
         <v>87</v>
@@ -38275,7 +38668,7 @@
         <v>96</v>
       </c>
       <c r="G1182" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1182" s="8" t="s">
         <v>87</v>
@@ -38301,7 +38694,7 @@
         <v>89</v>
       </c>
       <c r="G1183" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1183" s="13" t="s">
         <v>87</v>
@@ -38405,7 +38798,7 @@
         <v>85</v>
       </c>
       <c r="G1187" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1187" s="13" t="s">
         <v>87</v>
@@ -38483,7 +38876,7 @@
         <v>85</v>
       </c>
       <c r="G1190" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1190" s="8" t="s">
         <v>87</v>
@@ -38691,7 +39084,7 @@
         <v>109</v>
       </c>
       <c r="G1198" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1198" s="8" t="s">
         <v>87</v>
@@ -38847,7 +39240,7 @@
         <v>94</v>
       </c>
       <c r="G1204" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1204" s="8" t="s">
         <v>87</v>
@@ -38873,7 +39266,7 @@
         <v>109</v>
       </c>
       <c r="G1205" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1205" s="13" t="s">
         <v>87</v>
@@ -38899,7 +39292,7 @@
         <v>89</v>
       </c>
       <c r="G1206" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1206" s="8" t="s">
         <v>87</v>
@@ -39003,7 +39396,7 @@
         <v>109</v>
       </c>
       <c r="G1210" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1210" s="8" t="s">
         <v>87</v>
@@ -39055,7 +39448,7 @@
         <v>94</v>
       </c>
       <c r="G1212" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1212" s="8" t="s">
         <v>87</v>
@@ -39081,7 +39474,7 @@
         <v>94</v>
       </c>
       <c r="G1213" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1213" s="13" t="s">
         <v>87</v>
@@ -39107,7 +39500,7 @@
         <v>109</v>
       </c>
       <c r="G1214" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1214" s="8" t="s">
         <v>87</v>
@@ -39211,7 +39604,7 @@
         <v>118</v>
       </c>
       <c r="G1218" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1218" s="8" t="s">
         <v>87</v>
@@ -39237,7 +39630,7 @@
         <v>109</v>
       </c>
       <c r="G1219" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1219" s="13" t="s">
         <v>87</v>
@@ -39445,7 +39838,7 @@
         <v>89</v>
       </c>
       <c r="G1227" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1227" s="13" t="s">
         <v>87</v>
@@ -39549,7 +39942,7 @@
         <v>109</v>
       </c>
       <c r="G1231" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1231" s="13" t="s">
         <v>87</v>
@@ -39575,7 +39968,7 @@
         <v>94</v>
       </c>
       <c r="G1232" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1232" s="8" t="s">
         <v>87</v>
@@ -39627,7 +40020,7 @@
         <v>89</v>
       </c>
       <c r="G1234" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1234" s="8" t="s">
         <v>87</v>
@@ -39913,7 +40306,7 @@
         <v>109</v>
       </c>
       <c r="G1245" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1245" s="13" t="s">
         <v>87</v>
@@ -40017,7 +40410,7 @@
         <v>94</v>
       </c>
       <c r="G1249" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1249" s="13" t="s">
         <v>87</v>
@@ -40199,7 +40592,7 @@
         <v>89</v>
       </c>
       <c r="G1256" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1256" s="8" t="s">
         <v>87</v>
@@ -40355,7 +40748,7 @@
         <v>89</v>
       </c>
       <c r="G1262" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1262" s="8" t="s">
         <v>87</v>
@@ -40693,7 +41086,7 @@
         <v>109</v>
       </c>
       <c r="G1275" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1275" s="13" t="s">
         <v>87</v>
@@ -40901,7 +41294,7 @@
         <v>109</v>
       </c>
       <c r="G1283" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1283" s="13" t="s">
         <v>87</v>
@@ -40927,7 +41320,7 @@
         <v>85</v>
       </c>
       <c r="G1284" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1284" s="8" t="s">
         <v>87</v>
@@ -41421,7 +41814,7 @@
         <v>109</v>
       </c>
       <c r="G1303" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1303" s="13" t="s">
         <v>87</v>
@@ -41447,7 +41840,7 @@
         <v>109</v>
       </c>
       <c r="G1304" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1304" s="8" t="s">
         <v>87</v>
@@ -41499,7 +41892,7 @@
         <v>109</v>
       </c>
       <c r="G1306" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1306" s="8" t="s">
         <v>87</v>
@@ -41551,7 +41944,7 @@
         <v>94</v>
       </c>
       <c r="G1308" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1308" s="8" t="s">
         <v>87</v>
@@ -41655,7 +42048,7 @@
         <v>96</v>
       </c>
       <c r="G1312" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1312" s="8" t="s">
         <v>87</v>
@@ -41733,7 +42126,7 @@
         <v>109</v>
       </c>
       <c r="G1315" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1315" s="13" t="s">
         <v>87</v>
@@ -41993,7 +42386,7 @@
         <v>85</v>
       </c>
       <c r="G1325" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1325" s="13" t="s">
         <v>87</v>
@@ -42175,7 +42568,7 @@
         <v>94</v>
       </c>
       <c r="G1332" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1332" s="8" t="s">
         <v>87</v>
@@ -42383,7 +42776,7 @@
         <v>85</v>
       </c>
       <c r="G1340" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1340" s="8" t="s">
         <v>87</v>
@@ -42591,7 +42984,7 @@
         <v>94</v>
       </c>
       <c r="G1348" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1348" s="8" t="s">
         <v>87</v>
@@ -42773,7 +43166,7 @@
         <v>118</v>
       </c>
       <c r="G1355" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1355" s="13" t="s">
         <v>87</v>
@@ -42799,7 +43192,7 @@
         <v>94</v>
       </c>
       <c r="G1356" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1356" s="8" t="s">
         <v>87</v>
@@ -42851,7 +43244,7 @@
         <v>109</v>
       </c>
       <c r="G1358" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1358" s="8" t="s">
         <v>87</v>
@@ -43189,7 +43582,7 @@
         <v>89</v>
       </c>
       <c r="G1371" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1371" s="13" t="s">
         <v>87</v>
@@ -43241,7 +43634,7 @@
         <v>109</v>
       </c>
       <c r="G1373" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1373" s="13" t="s">
         <v>87</v>
@@ -43267,7 +43660,7 @@
         <v>94</v>
       </c>
       <c r="G1374" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1374" s="8" t="s">
         <v>87</v>
@@ -43319,7 +43712,7 @@
         <v>109</v>
       </c>
       <c r="G1376" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1376" s="8" t="s">
         <v>87</v>
@@ -43475,7 +43868,7 @@
         <v>94</v>
       </c>
       <c r="G1382" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1382" s="8" t="s">
         <v>87</v>
@@ -43605,7 +43998,7 @@
         <v>89</v>
       </c>
       <c r="G1387" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1387" s="13" t="s">
         <v>87</v>
@@ -43735,7 +44128,7 @@
         <v>94</v>
       </c>
       <c r="G1392" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1392" s="8" t="s">
         <v>87</v>
@@ -43839,7 +44232,7 @@
         <v>89</v>
       </c>
       <c r="G1396" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1396" s="8" t="s">
         <v>87</v>
@@ -43891,7 +44284,7 @@
         <v>89</v>
       </c>
       <c r="G1398" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1398" s="8" t="s">
         <v>87</v>
@@ -43917,7 +44310,7 @@
         <v>109</v>
       </c>
       <c r="G1399" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1399" s="13" t="s">
         <v>87</v>
@@ -43943,7 +44336,7 @@
         <v>94</v>
       </c>
       <c r="G1400" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1400" s="8" t="s">
         <v>87</v>
@@ -44047,7 +44440,7 @@
         <v>85</v>
       </c>
       <c r="G1404" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1404" s="8" t="s">
         <v>87</v>
@@ -44151,7 +44544,7 @@
         <v>96</v>
       </c>
       <c r="G1408" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1408" s="8" t="s">
         <v>87</v>
@@ -44229,7 +44622,7 @@
         <v>89</v>
       </c>
       <c r="G1411" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1411" s="13" t="s">
         <v>87</v>
@@ -44307,7 +44700,7 @@
         <v>192</v>
       </c>
       <c r="G1414" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1414" s="8" t="s">
         <v>87</v>
@@ -44359,7 +44752,7 @@
         <v>94</v>
       </c>
       <c r="G1416" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1416" s="8" t="s">
         <v>87</v>
@@ -44385,7 +44778,7 @@
         <v>94</v>
       </c>
       <c r="G1417" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1417" s="13" t="s">
         <v>87</v>
@@ -44463,7 +44856,7 @@
         <v>109</v>
       </c>
       <c r="G1420" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1420" s="8" t="s">
         <v>87</v>
@@ -44619,7 +45012,7 @@
         <v>85</v>
       </c>
       <c r="G1426" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1426" s="8" t="s">
         <v>87</v>
@@ -44801,7 +45194,7 @@
         <v>109</v>
       </c>
       <c r="G1433" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1433" s="13" t="s">
         <v>87</v>
@@ -44983,7 +45376,7 @@
         <v>85</v>
       </c>
       <c r="G1440" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1440" s="8" t="s">
         <v>87</v>
@@ -45009,7 +45402,7 @@
         <v>109</v>
       </c>
       <c r="G1441" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1441" s="13" t="s">
         <v>87</v>
@@ -45035,7 +45428,7 @@
         <v>94</v>
       </c>
       <c r="G1442" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1442" s="8" t="s">
         <v>87</v>
@@ -45165,7 +45558,7 @@
         <v>94</v>
       </c>
       <c r="G1447" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1447" s="13" t="s">
         <v>87</v>
@@ -45243,7 +45636,7 @@
         <v>96</v>
       </c>
       <c r="G1450" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1450" s="8" t="s">
         <v>87</v>
@@ -45321,7 +45714,7 @@
         <v>96</v>
       </c>
       <c r="G1453" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1453" s="13" t="s">
         <v>87</v>
@@ -45347,7 +45740,7 @@
         <v>96</v>
       </c>
       <c r="G1454" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1454" s="8" t="s">
         <v>87</v>
@@ -45399,7 +45792,7 @@
         <v>89</v>
       </c>
       <c r="G1456" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1456" s="8" t="s">
         <v>87</v>
@@ -45451,7 +45844,7 @@
         <v>94</v>
       </c>
       <c r="G1458" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1458" s="8" t="s">
         <v>87</v>
@@ -45555,7 +45948,7 @@
         <v>109</v>
       </c>
       <c r="G1462" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1462" s="8" t="s">
         <v>87</v>
@@ -45607,7 +46000,7 @@
         <v>123</v>
       </c>
       <c r="G1464" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1464" s="8" t="s">
         <v>87</v>
@@ -45789,7 +46182,7 @@
         <v>94</v>
       </c>
       <c r="G1471" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1471" s="13" t="s">
         <v>87</v>
@@ -45815,7 +46208,7 @@
         <v>109</v>
       </c>
       <c r="G1472" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1472" s="8" t="s">
         <v>87</v>
@@ -46075,7 +46468,7 @@
         <v>109</v>
       </c>
       <c r="G1482" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1482" s="8" t="s">
         <v>87</v>
@@ -46101,7 +46494,7 @@
         <v>118</v>
       </c>
       <c r="G1483" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1483" s="13" t="s">
         <v>87</v>
@@ -46179,7 +46572,7 @@
         <v>89</v>
       </c>
       <c r="G1486" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1486" s="8" t="s">
         <v>87</v>
@@ -46439,7 +46832,7 @@
         <v>109</v>
       </c>
       <c r="G1496" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1496" s="8" t="s">
         <v>87</v>
@@ -46621,7 +47014,7 @@
         <v>85</v>
       </c>
       <c r="G1503" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1503" s="13" t="s">
         <v>87</v>
@@ -46699,7 +47092,7 @@
         <v>94</v>
       </c>
       <c r="G1506" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1506" s="8" t="s">
         <v>87</v>
@@ -46751,7 +47144,7 @@
         <v>89</v>
       </c>
       <c r="G1508" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1508" s="8" t="s">
         <v>87</v>
@@ -46829,7 +47222,7 @@
         <v>94</v>
       </c>
       <c r="G1511" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1511" s="13" t="s">
         <v>87</v>
@@ -46933,7 +47326,7 @@
         <v>94</v>
       </c>
       <c r="G1515" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1515" s="13" t="s">
         <v>87</v>
@@ -47011,7 +47404,7 @@
         <v>94</v>
       </c>
       <c r="G1518" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1518" s="8" t="s">
         <v>87</v>
@@ -47037,7 +47430,7 @@
         <v>85</v>
       </c>
       <c r="G1519" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1519" s="13" t="s">
         <v>87</v>
@@ -47063,7 +47456,7 @@
         <v>94</v>
       </c>
       <c r="G1520" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1520" s="8" t="s">
         <v>87</v>
@@ -47271,7 +47664,7 @@
         <v>109</v>
       </c>
       <c r="G1528" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1528" s="8" t="s">
         <v>87</v>
@@ -47323,7 +47716,7 @@
         <v>109</v>
       </c>
       <c r="G1530" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1530" s="8" t="s">
         <v>87</v>
@@ -47453,7 +47846,7 @@
         <v>109</v>
       </c>
       <c r="G1535" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1535" s="13" t="s">
         <v>87</v>
@@ -47895,7 +48288,7 @@
         <v>94</v>
       </c>
       <c r="G1552" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1552" s="8" t="s">
         <v>87</v>
@@ -47973,7 +48366,7 @@
         <v>89</v>
       </c>
       <c r="G1555" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1555" s="13" t="s">
         <v>87</v>
@@ -47999,7 +48392,7 @@
         <v>109</v>
       </c>
       <c r="G1556" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1556" s="8" t="s">
         <v>87</v>
@@ -48103,7 +48496,7 @@
         <v>89</v>
       </c>
       <c r="G1560" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1560" s="8" t="s">
         <v>87</v>
@@ -48207,7 +48600,7 @@
         <v>85</v>
       </c>
       <c r="G1564" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1564" s="8" t="s">
         <v>87</v>
@@ -48285,7 +48678,7 @@
         <v>109</v>
       </c>
       <c r="G1567" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1567" s="13" t="s">
         <v>87</v>
@@ -48311,7 +48704,7 @@
         <v>94</v>
       </c>
       <c r="G1568" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1568" s="8" t="s">
         <v>87</v>
@@ -48415,7 +48808,7 @@
         <v>109</v>
       </c>
       <c r="G1572" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1572" s="8" t="s">
         <v>87</v>
@@ -48441,7 +48834,7 @@
         <v>109</v>
       </c>
       <c r="G1573" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1573" s="13" t="s">
         <v>87</v>
@@ -48493,7 +48886,7 @@
         <v>94</v>
       </c>
       <c r="G1575" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1575" s="13" t="s">
         <v>87</v>
@@ -48623,7 +49016,7 @@
         <v>85</v>
       </c>
       <c r="G1580" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1580" s="8" t="s">
         <v>87</v>
@@ -48831,7 +49224,7 @@
         <v>109</v>
       </c>
       <c r="G1588" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1588" s="8" t="s">
         <v>87</v>
@@ -49117,7 +49510,7 @@
         <v>109</v>
       </c>
       <c r="G1599" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1599" s="13" t="s">
         <v>87</v>
@@ -49169,7 +49562,7 @@
         <v>85</v>
       </c>
       <c r="G1601" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1601" s="13" t="s">
         <v>87</v>
@@ -49429,7 +49822,7 @@
         <v>89</v>
       </c>
       <c r="G1611" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1611" s="13" t="s">
         <v>87</v>
@@ -49611,7 +50004,7 @@
         <v>192</v>
       </c>
       <c r="G1618" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1618" s="8" t="s">
         <v>87</v>
@@ -49637,7 +50030,7 @@
         <v>109</v>
       </c>
       <c r="G1619" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1619" s="13" t="s">
         <v>87</v>
@@ -49663,7 +50056,7 @@
         <v>89</v>
       </c>
       <c r="G1620" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1620" s="8" t="s">
         <v>87</v>
@@ -49845,7 +50238,7 @@
         <v>109</v>
       </c>
       <c r="G1627" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1627" s="13" t="s">
         <v>87</v>
@@ -49949,7 +50342,7 @@
         <v>94</v>
       </c>
       <c r="G1631" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1631" s="13" t="s">
         <v>87</v>
@@ -50131,7 +50524,7 @@
         <v>85</v>
       </c>
       <c r="G1638" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1638" s="8" t="s">
         <v>87</v>
@@ -50339,7 +50732,7 @@
         <v>109</v>
       </c>
       <c r="G1646" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1646" s="8" t="s">
         <v>87</v>
@@ -50443,7 +50836,7 @@
         <v>94</v>
       </c>
       <c r="G1650" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1650" s="8" t="s">
         <v>87</v>
@@ -50859,7 +51252,7 @@
         <v>126</v>
       </c>
       <c r="G1666" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1666" s="8" t="s">
         <v>87</v>
@@ -51197,7 +51590,7 @@
         <v>94</v>
       </c>
       <c r="G1679" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1679" s="13" t="s">
         <v>87</v>
@@ -51249,7 +51642,7 @@
         <v>85</v>
       </c>
       <c r="G1681" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1681" s="13" t="s">
         <v>87</v>
@@ -51457,7 +51850,7 @@
         <v>109</v>
       </c>
       <c r="G1689" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1689" s="13" t="s">
         <v>87</v>
@@ -51561,7 +51954,7 @@
         <v>94</v>
       </c>
       <c r="G1693" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1693" s="13" t="s">
         <v>87</v>
@@ -51795,7 +52188,7 @@
         <v>94</v>
       </c>
       <c r="G1702" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1702" s="8" t="s">
         <v>87</v>
@@ -51821,7 +52214,7 @@
         <v>118</v>
       </c>
       <c r="G1703" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1703" s="13" t="s">
         <v>87</v>
@@ -51873,7 +52266,7 @@
         <v>94</v>
       </c>
       <c r="G1705" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1705" s="13" t="s">
         <v>87</v>
@@ -51899,7 +52292,7 @@
         <v>109</v>
       </c>
       <c r="G1706" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1706" s="8" t="s">
         <v>87</v>
@@ -51951,7 +52344,7 @@
         <v>126</v>
       </c>
       <c r="G1708" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1708" s="8" t="s">
         <v>87</v>
@@ -51977,7 +52370,7 @@
         <v>192</v>
       </c>
       <c r="G1709" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1709" s="13" t="s">
         <v>87</v>
@@ -52029,7 +52422,7 @@
         <v>85</v>
       </c>
       <c r="G1711" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1711" s="13" t="s">
         <v>87</v>
@@ -52107,7 +52500,7 @@
         <v>96</v>
       </c>
       <c r="G1714" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1714" s="8" t="s">
         <v>87</v>
@@ -52185,7 +52578,7 @@
         <v>109</v>
       </c>
       <c r="G1717" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1717" s="13" t="s">
         <v>87</v>
@@ -52211,7 +52604,7 @@
         <v>123</v>
       </c>
       <c r="G1718" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1718" s="8" t="s">
         <v>87</v>
@@ -52237,7 +52630,7 @@
         <v>109</v>
       </c>
       <c r="G1719" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1719" s="13" t="s">
         <v>87</v>
@@ -52263,7 +52656,7 @@
         <v>123</v>
       </c>
       <c r="G1720" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1720" s="8" t="s">
         <v>87</v>
@@ -52315,7 +52708,7 @@
         <v>89</v>
       </c>
       <c r="G1722" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1722" s="8" t="s">
         <v>87</v>
@@ -52393,7 +52786,7 @@
         <v>123</v>
       </c>
       <c r="G1725" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1725" s="13" t="s">
         <v>87</v>
@@ -52439,7 +52832,7 @@
         <v>870377</v>
       </c>
       <c r="E1727" s="5" t="s">
-        <v>2348</v>
+        <v>2346</v>
       </c>
       <c r="F1727" s="5" t="s">
         <v>96</v>
@@ -52523,7 +52916,7 @@
         <v>94</v>
       </c>
       <c r="G1730" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1730" s="8" t="s">
         <v>87</v>
@@ -52601,7 +52994,7 @@
         <v>94</v>
       </c>
       <c r="G1733" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1733" s="13" t="s">
         <v>87</v>
@@ -52783,7 +53176,7 @@
         <v>94</v>
       </c>
       <c r="G1740" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1740" s="8" t="s">
         <v>87</v>
@@ -52887,7 +53280,7 @@
         <v>94</v>
       </c>
       <c r="G1744" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1744" s="8" t="s">
         <v>87</v>
@@ -52991,7 +53384,7 @@
         <v>89</v>
       </c>
       <c r="G1748" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1748" s="8" t="s">
         <v>87</v>
@@ -53277,7 +53670,7 @@
         <v>94</v>
       </c>
       <c r="G1759" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1759" s="13" t="s">
         <v>87</v>
@@ -53355,7 +53748,7 @@
         <v>109</v>
       </c>
       <c r="G1762" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1762" s="8" t="s">
         <v>87</v>
@@ -53693,7 +54086,7 @@
         <v>109</v>
       </c>
       <c r="G1775" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1775" s="13" t="s">
         <v>87</v>
@@ -53719,7 +54112,7 @@
         <v>109</v>
       </c>
       <c r="G1776" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1776" s="8" t="s">
         <v>87</v>
@@ -53791,10 +54184,10 @@
         <v>608931</v>
       </c>
       <c r="E1779" s="5" t="s">
-        <v>2349</v>
+        <v>2347</v>
       </c>
       <c r="F1779" s="5" t="s">
-        <v>2350</v>
+        <v>2348</v>
       </c>
       <c r="G1779" s="10" t="s">
         <v>90</v>
@@ -53921,13 +54314,13 @@
         <v>114283</v>
       </c>
       <c r="E1784" s="5" t="s">
-        <v>2351</v>
+        <v>2349</v>
       </c>
       <c r="F1784" s="5" t="s">
         <v>94</v>
       </c>
       <c r="G1784" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1784" s="8" t="s">
         <v>87</v>
@@ -54213,7 +54606,7 @@
         <v>94</v>
       </c>
       <c r="G1795" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1795" s="13" t="s">
         <v>87</v>
@@ -54239,7 +54632,7 @@
         <v>94</v>
       </c>
       <c r="G1796" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1796" s="8" t="s">
         <v>87</v>
@@ -54337,7 +54730,7 @@
         <v>730513</v>
       </c>
       <c r="E1800" s="5" t="s">
-        <v>2352</v>
+        <v>2350</v>
       </c>
       <c r="F1800" s="5" t="s">
         <v>94</v>
@@ -54421,7 +54814,7 @@
         <v>118</v>
       </c>
       <c r="G1803" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1803" s="13" t="s">
         <v>87</v>
@@ -54577,7 +54970,7 @@
         <v>85</v>
       </c>
       <c r="G1809" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1809" s="13" t="s">
         <v>87</v>
@@ -54655,7 +55048,7 @@
         <v>94</v>
       </c>
       <c r="G1812" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1812" s="8" t="s">
         <v>87</v>
@@ -54727,7 +55120,7 @@
         <v>873645</v>
       </c>
       <c r="E1815" s="5" t="s">
-        <v>2353</v>
+        <v>2351</v>
       </c>
       <c r="F1815" s="5" t="s">
         <v>96</v>
@@ -55019,7 +55412,7 @@
         <v>109</v>
       </c>
       <c r="G1826" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1826" s="8" t="s">
         <v>87</v>
@@ -55123,7 +55516,7 @@
         <v>94</v>
       </c>
       <c r="G1830" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1830" s="8" t="s">
         <v>87</v>
@@ -55305,7 +55698,7 @@
         <v>94</v>
       </c>
       <c r="G1837" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1837" s="13" t="s">
         <v>87</v>
@@ -55331,7 +55724,7 @@
         <v>109</v>
       </c>
       <c r="G1838" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1838" s="8" t="s">
         <v>87</v>
@@ -55383,7 +55776,7 @@
         <v>118</v>
       </c>
       <c r="G1840" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1840" s="8" t="s">
         <v>87</v>
@@ -55409,7 +55802,7 @@
         <v>109</v>
       </c>
       <c r="G1841" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1841" s="13" t="s">
         <v>87</v>
@@ -55435,7 +55828,7 @@
         <v>94</v>
       </c>
       <c r="G1842" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1842" s="8" t="s">
         <v>87</v>
@@ -55513,7 +55906,7 @@
         <v>94</v>
       </c>
       <c r="G1845" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1845" s="13" t="s">
         <v>87</v>
@@ -55539,7 +55932,7 @@
         <v>94</v>
       </c>
       <c r="G1846" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1846" s="8" t="s">
         <v>87</v>
@@ -55559,7 +55952,7 @@
         <v>882361</v>
       </c>
       <c r="E1847" s="5" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="F1847" s="5" t="s">
         <v>96</v>
@@ -55591,7 +55984,7 @@
         <v>109</v>
       </c>
       <c r="G1848" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1848" s="8" t="s">
         <v>87</v>
@@ -55637,7 +56030,7 @@
         <v>882361</v>
       </c>
       <c r="E1850" s="5" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="F1850" s="5" t="s">
         <v>96</v>
@@ -55955,7 +56348,7 @@
         <v>85</v>
       </c>
       <c r="G1862" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1862" s="8" t="s">
         <v>87</v>
@@ -55975,7 +56368,7 @@
         <v>880349</v>
       </c>
       <c r="E1863" s="5" t="s">
-        <v>2355</v>
+        <v>2353</v>
       </c>
       <c r="F1863" s="5" t="s">
         <v>96</v>
@@ -56131,7 +56524,7 @@
         <v>878856</v>
       </c>
       <c r="E1869" s="5" t="s">
-        <v>2356</v>
+        <v>2354</v>
       </c>
       <c r="F1869" s="5" t="s">
         <v>96</v>
@@ -56163,7 +56556,7 @@
         <v>94</v>
       </c>
       <c r="G1870" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1870" s="8" t="s">
         <v>87</v>
@@ -56215,7 +56608,7 @@
         <v>96</v>
       </c>
       <c r="G1872" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1872" s="8" t="s">
         <v>87</v>
@@ -56241,7 +56634,7 @@
         <v>109</v>
       </c>
       <c r="G1873" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1873" s="13" t="s">
         <v>87</v>
@@ -56319,7 +56712,7 @@
         <v>109</v>
       </c>
       <c r="G1876" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1876" s="8" t="s">
         <v>87</v>
@@ -56371,7 +56764,7 @@
         <v>85</v>
       </c>
       <c r="G1878" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1878" s="8" t="s">
         <v>87</v>
@@ -56379,7 +56772,7 @@
     </row>
     <row r="1879" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1879" s="9" t="s">
-        <v>2258</v>
+        <v>2360</v>
       </c>
       <c r="B1879" s="10" t="s">
         <v>19</v>
@@ -56405,7 +56798,7 @@
     </row>
     <row r="1880" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1880" s="4" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B1880" s="5" t="s">
         <v>15</v>
@@ -56431,7 +56824,7 @@
     </row>
     <row r="1881" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1881" s="9" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B1881" s="10" t="s">
         <v>37</v>
@@ -56457,7 +56850,7 @@
     </row>
     <row r="1882" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1882" s="4" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B1882" s="5" t="s">
         <v>43</v>
@@ -56483,7 +56876,7 @@
     </row>
     <row r="1883" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1883" s="9" t="s">
-        <v>2262</v>
+        <v>2261</v>
       </c>
       <c r="B1883" s="10" t="s">
         <v>43</v>
@@ -56495,7 +56888,7 @@
         <v>830617</v>
       </c>
       <c r="E1883" s="5" t="s">
-        <v>2357</v>
+        <v>2355</v>
       </c>
       <c r="F1883" s="5" t="s">
         <v>94</v>
@@ -56509,7 +56902,7 @@
     </row>
     <row r="1884" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1884" s="4" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B1884" s="5" t="s">
         <v>8</v>
@@ -56535,7 +56928,7 @@
     </row>
     <row r="1885" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1885" s="9" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B1885" s="10" t="s">
         <v>9</v>
@@ -56561,7 +56954,7 @@
     </row>
     <row r="1886" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1886" s="4" t="s">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B1886" s="5" t="s">
         <v>42</v>
@@ -56587,7 +56980,7 @@
     </row>
     <row r="1887" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1887" s="9" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B1887" s="10" t="s">
         <v>31</v>
@@ -56613,7 +57006,7 @@
     </row>
     <row r="1888" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1888" s="4" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B1888" s="5" t="s">
         <v>632</v>
@@ -56639,7 +57032,7 @@
     </row>
     <row r="1889" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1889" s="9" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B1889" s="10" t="s">
         <v>40</v>
@@ -56651,13 +57044,13 @@
         <v>875521</v>
       </c>
       <c r="E1889" s="5" t="s">
-        <v>2358</v>
+        <v>2356</v>
       </c>
       <c r="F1889" s="5" t="s">
         <v>94</v>
       </c>
       <c r="G1889" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1889" s="13" t="s">
         <v>87</v>
@@ -56665,7 +57058,7 @@
     </row>
     <row r="1890" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1890" s="4" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="B1890" s="5" t="s">
         <v>11</v>
@@ -56683,7 +57076,7 @@
         <v>94</v>
       </c>
       <c r="G1890" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1890" s="8" t="s">
         <v>87</v>
@@ -56691,7 +57084,7 @@
     </row>
     <row r="1891" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1891" s="9" t="s">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="B1891" s="10" t="s">
         <v>19</v>
@@ -56717,7 +57110,7 @@
     </row>
     <row r="1892" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1892" s="4" t="s">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="B1892" s="5" t="s">
         <v>8</v>
@@ -56743,7 +57136,7 @@
     </row>
     <row r="1893" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1893" s="9" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B1893" s="10" t="s">
         <v>51</v>
@@ -56761,7 +57154,7 @@
         <v>96</v>
       </c>
       <c r="G1893" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1893" s="13" t="s">
         <v>87</v>
@@ -56769,7 +57162,7 @@
     </row>
     <row r="1894" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1894" s="4" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="B1894" s="5" t="s">
         <v>13</v>
@@ -56795,7 +57188,7 @@
     </row>
     <row r="1895" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1895" s="9" t="s">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="B1895" s="10" t="s">
         <v>20</v>
@@ -56821,7 +57214,7 @@
     </row>
     <row r="1896" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1896" s="4" t="s">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="B1896" s="5" t="s">
         <v>31</v>
@@ -56847,7 +57240,7 @@
     </row>
     <row r="1897" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1897" s="9" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="B1897" s="10" t="s">
         <v>717</v>
@@ -56873,7 +57266,7 @@
     </row>
     <row r="1898" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1898" s="4" t="s">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="B1898" s="5" t="s">
         <v>31</v>
@@ -56899,7 +57292,7 @@
     </row>
     <row r="1899" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1899" s="9" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="B1899" s="10" t="s">
         <v>30</v>
@@ -56925,7 +57318,7 @@
     </row>
     <row r="1900" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1900" s="4" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="B1900" s="5" t="s">
         <v>8</v>
@@ -56951,7 +57344,7 @@
     </row>
     <row r="1901" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1901" s="9" t="s">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="B1901" s="10" t="s">
         <v>806</v>
@@ -56977,7 +57370,7 @@
     </row>
     <row r="1902" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1902" s="4" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="B1902" s="5" t="s">
         <v>16</v>
@@ -57003,7 +57396,7 @@
     </row>
     <row r="1903" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1903" s="9" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B1903" s="10" t="s">
         <v>34</v>
@@ -57029,7 +57422,7 @@
     </row>
     <row r="1904" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1904" s="4" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="B1904" s="5" t="s">
         <v>1488</v>
@@ -57047,7 +57440,7 @@
         <v>94</v>
       </c>
       <c r="G1904" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1904" s="8" t="s">
         <v>87</v>
@@ -57055,7 +57448,7 @@
     </row>
     <row r="1905" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1905" s="9" t="s">
-        <v>2284</v>
+        <v>2361</v>
       </c>
       <c r="B1905" s="10" t="s">
         <v>19</v>
@@ -57081,7 +57474,7 @@
     </row>
     <row r="1906" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1906" s="4" t="s">
-        <v>2285</v>
+        <v>2283</v>
       </c>
       <c r="B1906" s="5" t="s">
         <v>15</v>
@@ -57107,7 +57500,7 @@
     </row>
     <row r="1907" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1907" s="9" t="s">
-        <v>2286</v>
+        <v>2284</v>
       </c>
       <c r="B1907" s="10" t="s">
         <v>46</v>
@@ -57119,7 +57512,7 @@
         <v>882361</v>
       </c>
       <c r="E1907" s="5" t="s">
-        <v>2354</v>
+        <v>2352</v>
       </c>
       <c r="F1907" s="5" t="s">
         <v>96</v>
@@ -57133,7 +57526,7 @@
     </row>
     <row r="1908" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1908" s="4" t="s">
-        <v>2287</v>
+        <v>2285</v>
       </c>
       <c r="B1908" s="5" t="s">
         <v>17</v>
@@ -57159,7 +57552,7 @@
     </row>
     <row r="1909" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1909" s="9" t="s">
-        <v>2288</v>
+        <v>2286</v>
       </c>
       <c r="B1909" s="10" t="s">
         <v>19</v>
@@ -57185,7 +57578,7 @@
     </row>
     <row r="1910" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1910" s="4" t="s">
-        <v>2289</v>
+        <v>2287</v>
       </c>
       <c r="B1910" s="5" t="s">
         <v>1085</v>
@@ -57203,7 +57596,7 @@
         <v>109</v>
       </c>
       <c r="G1910" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1910" s="8" t="s">
         <v>87</v>
@@ -57211,10 +57604,10 @@
     </row>
     <row r="1911" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1911" s="9" t="s">
-        <v>2290</v>
+        <v>2288</v>
       </c>
       <c r="B1911" s="10" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C1911" s="11">
         <v>45842</v>
@@ -57229,7 +57622,7 @@
         <v>85</v>
       </c>
       <c r="G1911" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1911" s="13" t="s">
         <v>87</v>
@@ -57237,7 +57630,7 @@
     </row>
     <row r="1912" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1912" s="4" t="s">
-        <v>2292</v>
+        <v>2290</v>
       </c>
       <c r="B1912" s="5" t="s">
         <v>8</v>
@@ -57263,7 +57656,7 @@
     </row>
     <row r="1913" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1913" s="9" t="s">
-        <v>2293</v>
+        <v>2291</v>
       </c>
       <c r="B1913" s="10" t="s">
         <v>14</v>
@@ -57289,7 +57682,7 @@
     </row>
     <row r="1914" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1914" s="4" t="s">
-        <v>2294</v>
+        <v>2292</v>
       </c>
       <c r="B1914" s="5" t="s">
         <v>22</v>
@@ -57307,7 +57700,7 @@
         <v>109</v>
       </c>
       <c r="G1914" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1914" s="8" t="s">
         <v>87</v>
@@ -57315,7 +57708,7 @@
     </row>
     <row r="1915" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1915" s="9" t="s">
-        <v>2295</v>
+        <v>2293</v>
       </c>
       <c r="B1915" s="10" t="s">
         <v>19</v>
@@ -57341,7 +57734,7 @@
     </row>
     <row r="1916" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1916" s="4" t="s">
-        <v>2296</v>
+        <v>2294</v>
       </c>
       <c r="B1916" s="5" t="s">
         <v>15</v>
@@ -57393,7 +57786,7 @@
     </row>
     <row r="1918" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1918" s="4" t="s">
-        <v>2297</v>
+        <v>2295</v>
       </c>
       <c r="B1918" s="5" t="s">
         <v>17</v>
@@ -57419,7 +57812,7 @@
     </row>
     <row r="1919" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1919" s="9" t="s">
-        <v>2298</v>
+        <v>2296</v>
       </c>
       <c r="B1919" s="10" t="s">
         <v>15</v>
@@ -57445,7 +57838,7 @@
     </row>
     <row r="1920" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1920" s="4" t="s">
-        <v>2299</v>
+        <v>2297</v>
       </c>
       <c r="B1920" s="5" t="s">
         <v>19</v>
@@ -57471,7 +57864,7 @@
     </row>
     <row r="1921" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1921" s="9" t="s">
-        <v>2300</v>
+        <v>2298</v>
       </c>
       <c r="B1921" s="10" t="s">
         <v>11</v>
@@ -57483,13 +57876,13 @@
         <v>878851</v>
       </c>
       <c r="E1921" s="5" t="s">
-        <v>2359</v>
+        <v>2357</v>
       </c>
       <c r="F1921" s="5" t="s">
         <v>96</v>
       </c>
       <c r="G1921" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1921" s="13" t="s">
         <v>87</v>
@@ -57497,7 +57890,7 @@
     </row>
     <row r="1922" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1922" s="4" t="s">
-        <v>2301</v>
+        <v>2299</v>
       </c>
       <c r="B1922" s="5" t="s">
         <v>15</v>
@@ -57523,7 +57916,7 @@
     </row>
     <row r="1923" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1923" s="9" t="s">
-        <v>2302</v>
+        <v>2300</v>
       </c>
       <c r="B1923" s="10" t="s">
         <v>714</v>
@@ -57549,7 +57942,7 @@
     </row>
     <row r="1924" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1924" s="4" t="s">
-        <v>2303</v>
+        <v>2301</v>
       </c>
       <c r="B1924" s="5" t="s">
         <v>8</v>
@@ -57575,7 +57968,7 @@
     </row>
     <row r="1925" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1925" s="9" t="s">
-        <v>2304</v>
+        <v>2302</v>
       </c>
       <c r="B1925" s="10" t="s">
         <v>714</v>
@@ -57587,7 +57980,7 @@
         <v>859994</v>
       </c>
       <c r="E1925" s="5" t="s">
-        <v>2360</v>
+        <v>2358</v>
       </c>
       <c r="F1925" s="5" t="s">
         <v>94</v>
@@ -57601,7 +57994,7 @@
     </row>
     <row r="1926" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1926" s="4" t="s">
-        <v>2305</v>
+        <v>2303</v>
       </c>
       <c r="B1926" s="5" t="s">
         <v>1488</v>
@@ -57619,7 +58012,7 @@
         <v>85</v>
       </c>
       <c r="G1926" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1926" s="8" t="s">
         <v>87</v>
@@ -57627,7 +58020,7 @@
     </row>
     <row r="1927" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1927" s="9" t="s">
-        <v>2306</v>
+        <v>2304</v>
       </c>
       <c r="B1927" s="10" t="s">
         <v>27</v>
@@ -57653,7 +58046,7 @@
     </row>
     <row r="1928" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1928" s="4" t="s">
-        <v>2307</v>
+        <v>2305</v>
       </c>
       <c r="B1928" s="5" t="s">
         <v>28</v>
@@ -57679,7 +58072,7 @@
     </row>
     <row r="1929" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1929" s="9" t="s">
-        <v>2308</v>
+        <v>2306</v>
       </c>
       <c r="B1929" s="10" t="s">
         <v>8</v>
@@ -57705,7 +58098,7 @@
     </row>
     <row r="1930" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1930" s="4" t="s">
-        <v>2309</v>
+        <v>2307</v>
       </c>
       <c r="B1930" s="5" t="s">
         <v>37</v>
@@ -57731,7 +58124,7 @@
     </row>
     <row r="1931" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1931" s="9" t="s">
-        <v>2310</v>
+        <v>2308</v>
       </c>
       <c r="B1931" s="10" t="s">
         <v>30</v>
@@ -57757,7 +58150,7 @@
     </row>
     <row r="1932" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1932" s="4" t="s">
-        <v>2311</v>
+        <v>2309</v>
       </c>
       <c r="B1932" s="5" t="s">
         <v>16</v>
@@ -57783,7 +58176,7 @@
     </row>
     <row r="1933" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1933" s="9" t="s">
-        <v>2312</v>
+        <v>2310</v>
       </c>
       <c r="B1933" s="10" t="s">
         <v>25</v>
@@ -57809,7 +58202,7 @@
     </row>
     <row r="1934" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1934" s="4" t="s">
-        <v>2313</v>
+        <v>2311</v>
       </c>
       <c r="B1934" s="5" t="s">
         <v>632</v>
@@ -57835,7 +58228,7 @@
     </row>
     <row r="1935" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1935" s="9" t="s">
-        <v>2314</v>
+        <v>2312</v>
       </c>
       <c r="B1935" s="10" t="s">
         <v>9</v>
@@ -57861,7 +58254,7 @@
     </row>
     <row r="1936" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1936" s="4" t="s">
-        <v>2315</v>
+        <v>2313</v>
       </c>
       <c r="B1936" s="5" t="s">
         <v>15</v>
@@ -57887,7 +58280,7 @@
     </row>
     <row r="1937" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1937" s="9" t="s">
-        <v>2316</v>
+        <v>2314</v>
       </c>
       <c r="B1937" s="10" t="s">
         <v>59</v>
@@ -57905,7 +58298,7 @@
         <v>109</v>
       </c>
       <c r="G1937" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1937" s="13" t="s">
         <v>87</v>
@@ -57913,7 +58306,7 @@
     </row>
     <row r="1938" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1938" s="4" t="s">
-        <v>2317</v>
+        <v>2315</v>
       </c>
       <c r="B1938" s="5" t="s">
         <v>17</v>
@@ -57939,7 +58332,7 @@
     </row>
     <row r="1939" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1939" s="9" t="s">
-        <v>2318</v>
+        <v>2316</v>
       </c>
       <c r="B1939" s="10" t="s">
         <v>26</v>
@@ -57951,13 +58344,13 @@
         <v>843508</v>
       </c>
       <c r="E1939" s="5" t="s">
-        <v>2361</v>
+        <v>2359</v>
       </c>
       <c r="F1939" s="5" t="s">
         <v>89</v>
       </c>
       <c r="G1939" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1939" s="13" t="s">
         <v>87</v>
@@ -57965,7 +58358,7 @@
     </row>
     <row r="1940" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1940" s="4" t="s">
-        <v>2319</v>
+        <v>2317</v>
       </c>
       <c r="B1940" s="5" t="s">
         <v>17</v>
@@ -57991,7 +58384,7 @@
     </row>
     <row r="1941" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1941" s="9" t="s">
-        <v>2320</v>
+        <v>2318</v>
       </c>
       <c r="B1941" s="10" t="s">
         <v>840</v>
@@ -58017,7 +58410,7 @@
     </row>
     <row r="1942" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1942" s="4" t="s">
-        <v>2321</v>
+        <v>2319</v>
       </c>
       <c r="B1942" s="5" t="s">
         <v>1715</v>
@@ -58043,7 +58436,7 @@
     </row>
     <row r="1943" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1943" s="9" t="s">
-        <v>2322</v>
+        <v>2320</v>
       </c>
       <c r="B1943" s="10" t="s">
         <v>63</v>
@@ -58069,7 +58462,7 @@
     </row>
     <row r="1944" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1944" s="4" t="s">
-        <v>2323</v>
+        <v>2321</v>
       </c>
       <c r="B1944" s="5" t="s">
         <v>22</v>
@@ -58087,7 +58480,7 @@
         <v>109</v>
       </c>
       <c r="G1944" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1944" s="8" t="s">
         <v>87</v>
@@ -58095,7 +58488,7 @@
     </row>
     <row r="1945" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1945" s="9" t="s">
-        <v>2324</v>
+        <v>2322</v>
       </c>
       <c r="B1945" s="10" t="s">
         <v>722</v>
@@ -58113,7 +58506,7 @@
         <v>85</v>
       </c>
       <c r="G1945" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1945" s="13" t="s">
         <v>87</v>
@@ -58121,7 +58514,7 @@
     </row>
     <row r="1946" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1946" s="4" t="s">
-        <v>2325</v>
+        <v>2323</v>
       </c>
       <c r="B1946" s="5" t="s">
         <v>32</v>
@@ -58147,7 +58540,7 @@
     </row>
     <row r="1947" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1947" s="9" t="s">
-        <v>2326</v>
+        <v>2324</v>
       </c>
       <c r="B1947" s="10" t="s">
         <v>1488</v>
@@ -58165,7 +58558,7 @@
         <v>94</v>
       </c>
       <c r="G1947" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1947" s="13" t="s">
         <v>87</v>
@@ -58173,7 +58566,7 @@
     </row>
     <row r="1948" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1948" s="4" t="s">
-        <v>2327</v>
+        <v>2325</v>
       </c>
       <c r="B1948" s="5" t="s">
         <v>22</v>
@@ -58191,7 +58584,7 @@
         <v>109</v>
       </c>
       <c r="G1948" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1948" s="8" t="s">
         <v>87</v>
@@ -58199,7 +58592,7 @@
     </row>
     <row r="1949" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1949" s="9" t="s">
-        <v>2328</v>
+        <v>2326</v>
       </c>
       <c r="B1949" s="10" t="s">
         <v>1853</v>
@@ -58225,7 +58618,7 @@
     </row>
     <row r="1950" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1950" s="4" t="s">
-        <v>2329</v>
+        <v>2327</v>
       </c>
       <c r="B1950" s="5" t="s">
         <v>15</v>
@@ -58251,7 +58644,7 @@
     </row>
     <row r="1951" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1951" s="9" t="s">
-        <v>2330</v>
+        <v>2328</v>
       </c>
       <c r="B1951" s="10" t="s">
         <v>19</v>
@@ -58277,7 +58670,7 @@
     </row>
     <row r="1952" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1952" s="4" t="s">
-        <v>2331</v>
+        <v>2329</v>
       </c>
       <c r="B1952" s="5" t="s">
         <v>17</v>
@@ -58303,7 +58696,7 @@
     </row>
     <row r="1953" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1953" s="9" t="s">
-        <v>2332</v>
+        <v>2330</v>
       </c>
       <c r="B1953" s="10" t="s">
         <v>1288</v>
@@ -58329,10 +58722,10 @@
     </row>
     <row r="1954" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1954" s="4" t="s">
-        <v>2333</v>
+        <v>2331</v>
       </c>
       <c r="B1954" s="5" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C1954" s="6">
         <v>45842</v>
@@ -58347,7 +58740,7 @@
         <v>96</v>
       </c>
       <c r="G1954" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1954" s="8" t="s">
         <v>87</v>
@@ -58355,10 +58748,10 @@
     </row>
     <row r="1955" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1955" s="9" t="s">
-        <v>2334</v>
+        <v>2332</v>
       </c>
       <c r="B1955" s="10" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C1955" s="11">
         <v>45842</v>
@@ -58373,7 +58766,7 @@
         <v>96</v>
       </c>
       <c r="G1955" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1955" s="13" t="s">
         <v>87</v>
@@ -58381,7 +58774,7 @@
     </row>
     <row r="1956" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1956" s="4" t="s">
-        <v>2335</v>
+        <v>2333</v>
       </c>
       <c r="B1956" s="5" t="s">
         <v>840</v>
@@ -58407,7 +58800,7 @@
     </row>
     <row r="1957" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1957" s="9" t="s">
-        <v>2336</v>
+        <v>2334</v>
       </c>
       <c r="B1957" s="10" t="s">
         <v>19</v>
@@ -58433,7 +58826,7 @@
     </row>
     <row r="1958" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1958" s="4" t="s">
-        <v>2337</v>
+        <v>2335</v>
       </c>
       <c r="B1958" s="5" t="s">
         <v>37</v>
@@ -58459,7 +58852,7 @@
     </row>
     <row r="1959" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1959" s="9" t="s">
-        <v>2338</v>
+        <v>2336</v>
       </c>
       <c r="B1959" s="10" t="s">
         <v>28</v>
@@ -58485,7 +58878,7 @@
     </row>
     <row r="1960" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1960" s="4" t="s">
-        <v>2339</v>
+        <v>2337</v>
       </c>
       <c r="B1960" s="5" t="s">
         <v>56</v>
@@ -58503,7 +58896,7 @@
         <v>109</v>
       </c>
       <c r="G1960" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1960" s="8" t="s">
         <v>87</v>
@@ -58511,7 +58904,7 @@
     </row>
     <row r="1961" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1961" s="9" t="s">
-        <v>2340</v>
+        <v>2338</v>
       </c>
       <c r="B1961" s="10" t="s">
         <v>840</v>
@@ -58537,7 +58930,7 @@
     </row>
     <row r="1962" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1962" s="4" t="s">
-        <v>2341</v>
+        <v>2339</v>
       </c>
       <c r="B1962" s="5" t="s">
         <v>31</v>
@@ -58563,7 +58956,7 @@
     </row>
     <row r="1963" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1963" s="9" t="s">
-        <v>2342</v>
+        <v>2340</v>
       </c>
       <c r="B1963" s="10" t="s">
         <v>30</v>
@@ -58589,7 +58982,7 @@
     </row>
     <row r="1964" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1964" s="4" t="s">
-        <v>2343</v>
+        <v>2341</v>
       </c>
       <c r="B1964" s="5" t="s">
         <v>714</v>
@@ -58615,10 +59008,10 @@
     </row>
     <row r="1965" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1965" s="9" t="s">
-        <v>2344</v>
+        <v>2342</v>
       </c>
       <c r="B1965" s="10" t="s">
-        <v>2345</v>
+        <v>2343</v>
       </c>
       <c r="C1965" s="11">
         <v>45842</v>
@@ -58633,7 +59026,7 @@
         <v>94</v>
       </c>
       <c r="G1965" s="10" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1965" s="13" t="s">
         <v>87</v>
@@ -58641,10 +59034,10 @@
     </row>
     <row r="1966" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1966" s="4" t="s">
-        <v>2346</v>
+        <v>2344</v>
       </c>
       <c r="B1966" s="5" t="s">
-        <v>2291</v>
+        <v>2289</v>
       </c>
       <c r="C1966" s="6">
         <v>45842</v>
@@ -58659,9 +59052,3311 @@
         <v>96</v>
       </c>
       <c r="G1966" s="5" t="s">
-        <v>2347</v>
+        <v>2345</v>
       </c>
       <c r="H1966" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1967" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1967" s="9" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B1967" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1967" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1967" s="12">
+        <v>787456</v>
+      </c>
+      <c r="E1967" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="F1967" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1967" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1967" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1968" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1968" s="4" t="s">
+        <v>2363</v>
+      </c>
+      <c r="B1968" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C1968" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1968" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E1968" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1968" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1968" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1968" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1969" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1969" s="9" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1969" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1969" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1969" s="12">
+        <v>382096</v>
+      </c>
+      <c r="E1969" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F1969" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1969" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1969" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1970" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1970" s="4" t="s">
+        <v>2365</v>
+      </c>
+      <c r="B1970" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1970" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1970" s="7">
+        <v>864414</v>
+      </c>
+      <c r="E1970" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F1970" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1970" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1970" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1971" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1971" s="9" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B1971" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1971" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1971" s="12">
+        <v>878918</v>
+      </c>
+      <c r="E1971" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1971" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1971" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1971" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1972" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1972" s="4" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1972" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1972" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1972" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E1972" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1972" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1972" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H1972" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1973" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1973" s="9" t="s">
+        <v>2368</v>
+      </c>
+      <c r="B1973" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1973" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1973" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E1973" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1973" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1973" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1973" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1974" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1974" s="4" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B1974" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1974" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1974" s="7">
+        <v>885298</v>
+      </c>
+      <c r="E1974" s="5" t="s">
+        <v>2487</v>
+      </c>
+      <c r="F1974" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1974" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1974" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1975" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1975" s="9" t="s">
+        <v>2370</v>
+      </c>
+      <c r="B1975" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1975" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1975" s="12">
+        <v>666428</v>
+      </c>
+      <c r="E1975" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F1975" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1975" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1975" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1976" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1976" s="4" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B1976" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C1976" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1976" s="7">
+        <v>883580</v>
+      </c>
+      <c r="E1976" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F1976" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1976" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1976" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1977" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1977" s="9" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1977" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C1977" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1977" s="12">
+        <v>86784</v>
+      </c>
+      <c r="E1977" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1977" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1977" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1977" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1978" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1978" s="4" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B1978" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1978" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1978" s="7">
+        <v>405</v>
+      </c>
+      <c r="E1978" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1978" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1978" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1978" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1979" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1979" s="9" t="s">
+        <v>2374</v>
+      </c>
+      <c r="B1979" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C1979" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1979" s="12">
+        <v>368409</v>
+      </c>
+      <c r="E1979" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1979" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1979" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1979" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1980" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1980" s="4" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1980" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C1980" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1980" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E1980" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F1980" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1980" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1980" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1981" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1981" s="9" t="s">
+        <v>2376</v>
+      </c>
+      <c r="B1981" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1981" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1981" s="12">
+        <v>637113</v>
+      </c>
+      <c r="E1981" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F1981" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1981" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H1981" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1982" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1982" s="4" t="s">
+        <v>2377</v>
+      </c>
+      <c r="B1982" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1982" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1982" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E1982" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1982" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1982" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1982" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1983" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1983" s="9" t="s">
+        <v>2378</v>
+      </c>
+      <c r="B1983" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1983" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1983" s="12">
+        <v>876395</v>
+      </c>
+      <c r="E1983" s="5" t="s">
+        <v>1570</v>
+      </c>
+      <c r="F1983" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1983" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1983" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1984" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1984" s="4" t="s">
+        <v>2379</v>
+      </c>
+      <c r="B1984" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1984" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1984" s="7">
+        <v>785577</v>
+      </c>
+      <c r="E1984" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F1984" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1984" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1984" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1985" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1985" s="9" t="s">
+        <v>2380</v>
+      </c>
+      <c r="B1985" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C1985" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1985" s="12">
+        <v>884826</v>
+      </c>
+      <c r="E1985" s="5" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F1985" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1985" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1985" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="1986" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1986" s="4" t="s">
+        <v>2381</v>
+      </c>
+      <c r="B1986" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1986" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1986" s="7">
+        <v>825133</v>
+      </c>
+      <c r="E1986" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F1986" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1986" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1986" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1987" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1987" s="9" t="s">
+        <v>2382</v>
+      </c>
+      <c r="B1987" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1987" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1987" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E1987" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1987" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1987" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1987" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1988" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1988" s="4" t="s">
+        <v>2383</v>
+      </c>
+      <c r="B1988" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1988" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1988" s="7">
+        <v>883827</v>
+      </c>
+      <c r="E1988" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1988" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1988" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1988" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1989" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1989" s="9" t="s">
+        <v>2384</v>
+      </c>
+      <c r="B1989" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1989" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1989" s="12">
+        <v>883815</v>
+      </c>
+      <c r="E1989" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F1989" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1989" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1989" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="1990" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1990" s="4" t="s">
+        <v>2385</v>
+      </c>
+      <c r="B1990" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1990" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1990" s="7">
+        <v>610972</v>
+      </c>
+      <c r="E1990" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1990" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1990" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1990" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1991" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1991" s="9" t="s">
+        <v>2386</v>
+      </c>
+      <c r="B1991" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1991" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1991" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E1991" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F1991" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1991" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1991" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1992" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1992" s="4" t="s">
+        <v>2387</v>
+      </c>
+      <c r="B1992" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C1992" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1992" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E1992" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F1992" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G1992" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H1992" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1993" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1993" s="9" t="s">
+        <v>2388</v>
+      </c>
+      <c r="B1993" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1993" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1993" s="12">
+        <v>741461</v>
+      </c>
+      <c r="E1993" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1993" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G1993" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H1993" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1994" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1994" s="4" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B1994" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1994" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1994" s="7">
+        <v>405</v>
+      </c>
+      <c r="E1994" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F1994" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1994" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1994" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="1995" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1995" s="9" t="s">
+        <v>2390</v>
+      </c>
+      <c r="B1995" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1995" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1995" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E1995" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1995" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1995" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1995" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1996" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1996" s="4" t="s">
+        <v>2391</v>
+      </c>
+      <c r="B1996" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1996" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1996" s="7">
+        <v>829353</v>
+      </c>
+      <c r="E1996" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F1996" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1996" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1996" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1997" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1997" s="9" t="s">
+        <v>2392</v>
+      </c>
+      <c r="B1997" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1997" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1997" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E1997" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1997" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1997" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1997" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1998" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1998" s="4" t="s">
+        <v>2393</v>
+      </c>
+      <c r="B1998" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1998" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D1998" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E1998" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F1998" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G1998" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1998" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="1999" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1999" s="9" t="s">
+        <v>2394</v>
+      </c>
+      <c r="B1999" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1999" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D1999" s="12">
+        <v>860321</v>
+      </c>
+      <c r="E1999" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="F1999" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1999" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1999" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2000" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2000" s="4" t="s">
+        <v>2395</v>
+      </c>
+      <c r="B2000" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2000" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2000" s="7">
+        <v>562578</v>
+      </c>
+      <c r="E2000" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2000" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2000" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2000" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2001" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2001" s="9" t="s">
+        <v>2396</v>
+      </c>
+      <c r="B2001" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2001" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2001" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2001" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2001" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2001" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2001" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2002" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2002" s="4" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B2002" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2002" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2002" s="7">
+        <v>886911</v>
+      </c>
+      <c r="E2002" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F2002" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2002" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2002" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2003" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2003" s="9" t="s">
+        <v>2398</v>
+      </c>
+      <c r="B2003" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2003" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2003" s="12">
+        <v>680982</v>
+      </c>
+      <c r="E2003" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2003" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2003" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2003" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2004" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2004" s="4" t="s">
+        <v>2397</v>
+      </c>
+      <c r="B2004" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2004" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2004" s="7">
+        <v>886911</v>
+      </c>
+      <c r="E2004" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F2004" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2004" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2004" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2005" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2005" s="9" t="s">
+        <v>2399</v>
+      </c>
+      <c r="B2005" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2005" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2005" s="12">
+        <v>811237</v>
+      </c>
+      <c r="E2005" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="F2005" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2005" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2005" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2006" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2006" s="4" t="s">
+        <v>2400</v>
+      </c>
+      <c r="B2006" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2006" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2006" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2006" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2006" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2006" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2006" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2007" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2007" s="9" t="s">
+        <v>2401</v>
+      </c>
+      <c r="B2007" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2007" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2007" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2007" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2007" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2007" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2007" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2008" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2008" s="4" t="s">
+        <v>2402</v>
+      </c>
+      <c r="B2008" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2008" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2008" s="7">
+        <v>713743</v>
+      </c>
+      <c r="E2008" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="F2008" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2008" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2008" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2009" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2009" s="9" t="s">
+        <v>2403</v>
+      </c>
+      <c r="B2009" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2009" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2009" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2009" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2009" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2009" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2009" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2010" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2010" s="4" t="s">
+        <v>2404</v>
+      </c>
+      <c r="B2010" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2010" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2010" s="7">
+        <v>864414</v>
+      </c>
+      <c r="E2010" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F2010" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2010" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2010" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2011" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2011" s="9" t="s">
+        <v>2405</v>
+      </c>
+      <c r="B2011" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2011" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2011" s="12">
+        <v>636843</v>
+      </c>
+      <c r="E2011" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F2011" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2011" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2011" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2012" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2012" s="4" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B2012" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C2012" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2012" s="7">
+        <v>882361</v>
+      </c>
+      <c r="E2012" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F2012" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2012" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2012" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2013" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2013" s="9" t="s">
+        <v>2407</v>
+      </c>
+      <c r="B2013" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2013" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2013" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2013" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2013" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2013" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2013" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2014" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2014" s="4" t="s">
+        <v>2408</v>
+      </c>
+      <c r="B2014" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2014" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2014" s="7">
+        <v>405</v>
+      </c>
+      <c r="E2014" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2014" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2014" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2014" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2015" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2015" s="9" t="s">
+        <v>2409</v>
+      </c>
+      <c r="B2015" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2015" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2015" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2015" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2015" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2015" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2015" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2016" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2016" s="4" t="s">
+        <v>2410</v>
+      </c>
+      <c r="B2016" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2016" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2016" s="7">
+        <v>567578</v>
+      </c>
+      <c r="E2016" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="F2016" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2016" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2016" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2017" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2017" s="9" t="s">
+        <v>2411</v>
+      </c>
+      <c r="B2017" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2017" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2017" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2017" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2017" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2017" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2017" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2018" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2018" s="4" t="s">
+        <v>2412</v>
+      </c>
+      <c r="B2018" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2018" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2018" s="7">
+        <v>619784</v>
+      </c>
+      <c r="E2018" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2018" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2018" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2018" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2019" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2019" s="9" t="s">
+        <v>2413</v>
+      </c>
+      <c r="B2019" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2019" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2019" s="12">
+        <v>882331</v>
+      </c>
+      <c r="E2019" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2019" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2019" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2019" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2020" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2020" s="4" t="s">
+        <v>2414</v>
+      </c>
+      <c r="B2020" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2020" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2020" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2020" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2020" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2020" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2020" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2021" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2021" s="9" t="s">
+        <v>2415</v>
+      </c>
+      <c r="B2021" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2021" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2021" s="12">
+        <v>741456</v>
+      </c>
+      <c r="E2021" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2021" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2021" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2021" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2022" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2022" s="4" t="s">
+        <v>2416</v>
+      </c>
+      <c r="B2022" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2022" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2022" s="7">
+        <v>236724</v>
+      </c>
+      <c r="E2022" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2022" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2022" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2022" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2023" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2023" s="9" t="s">
+        <v>2417</v>
+      </c>
+      <c r="B2023" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2023" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2023" s="12">
+        <v>810976</v>
+      </c>
+      <c r="E2023" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F2023" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2023" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2023" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2024" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2024" s="4" t="s">
+        <v>2418</v>
+      </c>
+      <c r="B2024" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2024" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2024" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2024" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2024" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2024" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2024" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2025" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2025" s="9" t="s">
+        <v>2419</v>
+      </c>
+      <c r="B2025" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2025" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2025" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E2025" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2025" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2025" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2025" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2026" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2026" s="4" t="s">
+        <v>2420</v>
+      </c>
+      <c r="B2026" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2026" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2026" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2026" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2026" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2026" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2026" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2027" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2027" s="9" t="s">
+        <v>2421</v>
+      </c>
+      <c r="B2027" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2027" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2027" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E2027" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2027" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2027" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2027" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2028" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2028" s="4" t="s">
+        <v>2422</v>
+      </c>
+      <c r="B2028" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2028" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2028" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2028" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2028" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2028" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2028" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2029" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2029" s="9" t="s">
+        <v>2423</v>
+      </c>
+      <c r="B2029" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2029" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2029" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2029" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2029" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2029" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2029" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2030" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2030" s="4" t="s">
+        <v>2424</v>
+      </c>
+      <c r="B2030" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2030" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2030" s="7">
+        <v>822704</v>
+      </c>
+      <c r="E2030" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2030" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2030" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2030" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2031" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2031" s="9" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B2031" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2031" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2031" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2031" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2031" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2031" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2031" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2032" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2032" s="4" t="s">
+        <v>2426</v>
+      </c>
+      <c r="B2032" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2032" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2032" s="7">
+        <v>857350</v>
+      </c>
+      <c r="E2032" s="5" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F2032" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2032" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2032" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2033" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2033" s="9" t="s">
+        <v>2427</v>
+      </c>
+      <c r="B2033" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2033" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2033" s="12">
+        <v>777905</v>
+      </c>
+      <c r="E2033" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2033" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2033" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2033" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2034" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2034" s="4" t="s">
+        <v>2428</v>
+      </c>
+      <c r="B2034" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2034" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2034" s="7">
+        <v>879127</v>
+      </c>
+      <c r="E2034" s="5" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F2034" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2034" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2034" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2035" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2035" s="9" t="s">
+        <v>2429</v>
+      </c>
+      <c r="B2035" s="10" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C2035" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2035" s="12">
+        <v>878856</v>
+      </c>
+      <c r="E2035" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F2035" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2035" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2035" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2036" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2036" s="4" t="s">
+        <v>2430</v>
+      </c>
+      <c r="B2036" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2036" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2036" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2036" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2036" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2036" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2036" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2037" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2037" s="9" t="s">
+        <v>2431</v>
+      </c>
+      <c r="B2037" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2037" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2037" s="12">
+        <v>822704</v>
+      </c>
+      <c r="E2037" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2037" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2037" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2037" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2038" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2038" s="4" t="s">
+        <v>2432</v>
+      </c>
+      <c r="B2038" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2038" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2038" s="7">
+        <v>866566</v>
+      </c>
+      <c r="E2038" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2038" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2038" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2038" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2039" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2039" s="9" t="s">
+        <v>2433</v>
+      </c>
+      <c r="B2039" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2039" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2039" s="12">
+        <v>833948</v>
+      </c>
+      <c r="E2039" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2039" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2039" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2039" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2040" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2040" s="4" t="s">
+        <v>2434</v>
+      </c>
+      <c r="B2040" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2040" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2040" s="7">
+        <v>882361</v>
+      </c>
+      <c r="E2040" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F2040" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2040" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2040" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2041" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2041" s="9" t="s">
+        <v>2435</v>
+      </c>
+      <c r="B2041" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2041" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2041" s="12">
+        <v>824664</v>
+      </c>
+      <c r="E2041" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F2041" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2041" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2041" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2042" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2042" s="4" t="s">
+        <v>2436</v>
+      </c>
+      <c r="B2042" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2042" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2042" s="7">
+        <v>177442</v>
+      </c>
+      <c r="E2042" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2042" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2042" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2042" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2043" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2043" s="9" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B2043" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2043" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2043" s="12">
+        <v>824664</v>
+      </c>
+      <c r="E2043" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F2043" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2043" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2043" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2044" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2044" s="4" t="s">
+        <v>2438</v>
+      </c>
+      <c r="B2044" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2044" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2044" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2044" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2044" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2044" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2044" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2045" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2045" s="9" t="s">
+        <v>2439</v>
+      </c>
+      <c r="B2045" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2045" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2045" s="12">
+        <v>736256</v>
+      </c>
+      <c r="E2045" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2045" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2045" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2045" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2046" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2046" s="4" t="s">
+        <v>2440</v>
+      </c>
+      <c r="B2046" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2046" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2046" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E2046" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2046" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2046" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2046" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2047" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2047" s="9" t="s">
+        <v>2441</v>
+      </c>
+      <c r="B2047" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2047" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2047" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2047" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2047" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2047" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2047" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2048" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2048" s="4" t="s">
+        <v>2442</v>
+      </c>
+      <c r="B2048" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2048" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2048" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2048" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2048" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2048" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2048" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2049" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2049" s="9" t="s">
+        <v>2443</v>
+      </c>
+      <c r="B2049" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2049" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2049" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2049" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2049" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2049" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2049" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2050" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2050" s="4" t="s">
+        <v>2444</v>
+      </c>
+      <c r="B2050" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2050" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2050" s="7">
+        <v>653931</v>
+      </c>
+      <c r="E2050" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2050" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2050" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2050" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2051" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2051" s="9" t="s">
+        <v>2445</v>
+      </c>
+      <c r="B2051" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2051" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2051" s="12">
+        <v>882296</v>
+      </c>
+      <c r="E2051" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2051" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2051" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2051" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2052" s="4" t="s">
+        <v>2446</v>
+      </c>
+      <c r="B2052" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2052" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2052" s="7">
+        <v>653931</v>
+      </c>
+      <c r="E2052" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2052" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2052" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2052" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2053" s="9" t="s">
+        <v>2447</v>
+      </c>
+      <c r="B2053" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2053" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2053" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E2053" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2053" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2053" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2053" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2054" s="4" t="s">
+        <v>2448</v>
+      </c>
+      <c r="B2054" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2054" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2054" s="7">
+        <v>884801</v>
+      </c>
+      <c r="E2054" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2054" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2054" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2054" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2055" s="9" t="s">
+        <v>2449</v>
+      </c>
+      <c r="B2055" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2055" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2055" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E2055" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2055" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2055" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2055" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2056" s="4" t="s">
+        <v>2450</v>
+      </c>
+      <c r="B2056" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2056" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2056" s="7">
+        <v>882357</v>
+      </c>
+      <c r="E2056" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2056" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2056" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2056" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2057" s="9" t="s">
+        <v>2451</v>
+      </c>
+      <c r="B2057" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2057" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2057" s="12">
+        <v>878787</v>
+      </c>
+      <c r="E2057" s="5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F2057" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2057" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2057" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2058" s="4" t="s">
+        <v>2452</v>
+      </c>
+      <c r="B2058" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2058" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2058" s="7">
+        <v>790437</v>
+      </c>
+      <c r="E2058" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F2058" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2058" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2058" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2059" s="9" t="s">
+        <v>2453</v>
+      </c>
+      <c r="B2059" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2059" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2059" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2059" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2059" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2059" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2059" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2060" s="4" t="s">
+        <v>2454</v>
+      </c>
+      <c r="B2060" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2060" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2060" s="7">
+        <v>869886</v>
+      </c>
+      <c r="E2060" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F2060" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2060" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2060" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2061" s="9" t="s">
+        <v>2455</v>
+      </c>
+      <c r="B2061" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2061" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2061" s="12">
+        <v>698940</v>
+      </c>
+      <c r="E2061" s="5" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F2061" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2061" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2061" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2062" s="4" t="s">
+        <v>2456</v>
+      </c>
+      <c r="B2062" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2062" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2062" s="7">
+        <v>884801</v>
+      </c>
+      <c r="E2062" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2062" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2062" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2062" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2063" s="9" t="s">
+        <v>2457</v>
+      </c>
+      <c r="B2063" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2063" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2063" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2063" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2063" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2063" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2063" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2064" s="4" t="s">
+        <v>2458</v>
+      </c>
+      <c r="B2064" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2064" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2064" s="7">
+        <v>878249</v>
+      </c>
+      <c r="E2064" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="F2064" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2064" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2064" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2065" s="9" t="s">
+        <v>2459</v>
+      </c>
+      <c r="B2065" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2065" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2065" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E2065" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2065" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2065" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2065" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2066" s="4" t="s">
+        <v>2460</v>
+      </c>
+      <c r="B2066" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2066" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2066" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2066" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2066" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2066" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2066" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2067" s="9" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B2067" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2067" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2067" s="12">
+        <v>857350</v>
+      </c>
+      <c r="E2067" s="5" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F2067" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2067" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2067" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2068" s="4" t="s">
+        <v>2462</v>
+      </c>
+      <c r="B2068" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2068" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2068" s="7">
+        <v>741461</v>
+      </c>
+      <c r="E2068" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2068" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2068" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2068" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2069" s="9" t="s">
+        <v>2463</v>
+      </c>
+      <c r="B2069" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2069" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2069" s="12">
+        <v>213687</v>
+      </c>
+      <c r="E2069" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2069" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2069" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2069" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2070" s="4" t="s">
+        <v>2464</v>
+      </c>
+      <c r="B2070" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2070" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2070" s="7">
+        <v>878851</v>
+      </c>
+      <c r="E2070" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F2070" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2070" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2070" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2071" s="9" t="s">
+        <v>2465</v>
+      </c>
+      <c r="B2071" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2071" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2071" s="12">
+        <v>858855</v>
+      </c>
+      <c r="E2071" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F2071" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2071" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2071" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2072" s="4" t="s">
+        <v>2466</v>
+      </c>
+      <c r="B2072" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2072" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2072" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2072" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2072" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2072" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2072" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2073" s="9" t="s">
+        <v>2467</v>
+      </c>
+      <c r="B2073" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2073" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2073" s="12">
+        <v>834515</v>
+      </c>
+      <c r="E2073" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F2073" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2073" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2073" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2074" s="4" t="s">
+        <v>2468</v>
+      </c>
+      <c r="B2074" s="5" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C2074" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2074" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E2074" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2074" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2074" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2074" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2075" s="9" t="s">
+        <v>2469</v>
+      </c>
+      <c r="B2075" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2075" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2075" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2075" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2075" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2075" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2075" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2076" s="4" t="s">
+        <v>2470</v>
+      </c>
+      <c r="B2076" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2076" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2076" s="7">
+        <v>653931</v>
+      </c>
+      <c r="E2076" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2076" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2076" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2076" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2077" s="9" t="s">
+        <v>2471</v>
+      </c>
+      <c r="B2077" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2077" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2077" s="12">
+        <v>547683</v>
+      </c>
+      <c r="E2077" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2077" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2077" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2077" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2078" s="4" t="s">
+        <v>2472</v>
+      </c>
+      <c r="B2078" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2078" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2078" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E2078" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2078" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2078" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2078" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2079" s="9" t="s">
+        <v>2473</v>
+      </c>
+      <c r="B2079" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2079" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2079" s="12">
+        <v>696769</v>
+      </c>
+      <c r="E2079" s="5" t="s">
+        <v>2489</v>
+      </c>
+      <c r="F2079" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2079" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2079" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2080" s="4" t="s">
+        <v>2474</v>
+      </c>
+      <c r="B2080" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2080" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2080" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2080" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2080" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2080" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2080" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2081" s="9" t="s">
+        <v>2475</v>
+      </c>
+      <c r="B2081" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2081" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2081" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2081" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2081" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2081" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2081" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2082" s="4" t="s">
+        <v>2476</v>
+      </c>
+      <c r="B2082" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2082" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2082" s="7">
+        <v>791714</v>
+      </c>
+      <c r="E2082" s="5" t="s">
+        <v>2490</v>
+      </c>
+      <c r="F2082" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2082" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2082" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2083" s="9" t="s">
+        <v>2477</v>
+      </c>
+      <c r="B2083" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2083" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2083" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2083" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2083" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2083" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2083" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2084" s="4" t="s">
+        <v>2478</v>
+      </c>
+      <c r="B2084" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2084" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2084" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2084" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2084" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2084" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2084" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2085" s="9" t="s">
+        <v>2479</v>
+      </c>
+      <c r="B2085" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2085" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2085" s="12">
+        <v>872253</v>
+      </c>
+      <c r="E2085" s="5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F2085" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2085" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2085" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2086" s="4" t="s">
+        <v>2480</v>
+      </c>
+      <c r="B2086" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2086" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2086" s="7">
+        <v>766248</v>
+      </c>
+      <c r="E2086" s="5" t="s">
+        <v>2492</v>
+      </c>
+      <c r="F2086" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2086" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2086" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2087" s="9" t="s">
+        <v>2481</v>
+      </c>
+      <c r="B2087" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2087" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2087" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2087" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2087" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2087" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2087" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2088" s="4" t="s">
+        <v>2482</v>
+      </c>
+      <c r="B2088" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2088" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2088" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2088" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2088" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2088" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2088" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2089" s="9" t="s">
+        <v>764</v>
+      </c>
+      <c r="B2089" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2089" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2089" s="12">
+        <v>725067</v>
+      </c>
+      <c r="E2089" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2089" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2089" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2089" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2090" s="4" t="s">
+        <v>2483</v>
+      </c>
+      <c r="B2090" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2090" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2090" s="7">
+        <v>867361</v>
+      </c>
+      <c r="E2090" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2090" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2090" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2090" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2091" s="9" t="s">
+        <v>2484</v>
+      </c>
+      <c r="B2091" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2091" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2091" s="12">
+        <v>870487</v>
+      </c>
+      <c r="E2091" s="5" t="s">
+        <v>2094</v>
+      </c>
+      <c r="F2091" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2091" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2091" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2092" s="4" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B2092" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2092" s="6">
+        <v>45843</v>
+      </c>
+      <c r="D2092" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2092" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2092" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2092" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2092" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2093" s="9" t="s">
+        <v>2486</v>
+      </c>
+      <c r="B2093" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2093" s="11">
+        <v>45843</v>
+      </c>
+      <c r="D2093" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2093" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2093" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2093" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2093" s="13" t="s">
         <v>87</v>
       </c>
     </row>

--- a/crm_dominus/apps/dados/backlog_ativacao.xlsx
+++ b/crm_dominus/apps/dados/backlog_ativacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC39D773-336F-42A3-B6D6-B9C3D33F4E3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387895B8-35C9-4F44-8EE3-93D719AFCEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1068BE8-6A04-4046-BF81-1D35DD95EA81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12560" uniqueCount="2493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13772" uniqueCount="2694">
   <si>
     <t>Cliente</t>
   </si>
@@ -7513,6 +7513,609 @@
   </si>
   <si>
     <t>COM - KDK - CAMILLY BUCHHORN BATISTA</t>
+  </si>
+  <si>
+    <t>DANIEL IMHOFF</t>
+  </si>
+  <si>
+    <t>PABLO ANTONIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>LUIZ OTAVIO DE CASTRO MEIRELLES</t>
+  </si>
+  <si>
+    <t>Nicolas nagel</t>
+  </si>
+  <si>
+    <t>Cleiton Ponsalces Fagundes</t>
+  </si>
+  <si>
+    <t>LEANDRO CORADI DA SILVA</t>
+  </si>
+  <si>
+    <t>Thyago José Santana Santos</t>
+  </si>
+  <si>
+    <t>Raissa dos Santos iovanovichi</t>
+  </si>
+  <si>
+    <t>FG MAQUINAS AGRICOLAS LTDA</t>
+  </si>
+  <si>
+    <t>MARLEIDE FRITSCH</t>
+  </si>
+  <si>
+    <t>ADENILZA BERNARDES</t>
+  </si>
+  <si>
+    <t>Matheus Henrique de Oliveira</t>
+  </si>
+  <si>
+    <t>Felipe Silva de Oliveira</t>
+  </si>
+  <si>
+    <t>Kaylan de Jesus Mendes da Rocha</t>
+  </si>
+  <si>
+    <t>Davi assis da silva</t>
+  </si>
+  <si>
+    <t>Jesus Alegando González Fuentes</t>
+  </si>
+  <si>
+    <t>João Vitor Alvares Peixoto</t>
+  </si>
+  <si>
+    <t>Roseli Correa de Almeida</t>
+  </si>
+  <si>
+    <t>Tatianne De Souza Franco</t>
+  </si>
+  <si>
+    <t>Sandra Márcia Palermo</t>
+  </si>
+  <si>
+    <t>OLIANNYS ALEJANDRA GONZALEZ JIMENEZ</t>
+  </si>
+  <si>
+    <t>Carlos Fasolo</t>
+  </si>
+  <si>
+    <t>Fabio Junior Alves</t>
+  </si>
+  <si>
+    <t>ELIEGE DE OLIVEIRA DA ROSA</t>
+  </si>
+  <si>
+    <t>SUZANA MENEGHINI</t>
+  </si>
+  <si>
+    <t>MARGARETE CRUZ DE FREITAS</t>
+  </si>
+  <si>
+    <t>Marcio snak de Lima</t>
+  </si>
+  <si>
+    <t>Ketlin Eduarda Paz dos Santos</t>
+  </si>
+  <si>
+    <t>Lucas Tiago leite</t>
+  </si>
+  <si>
+    <t>SILMARA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Sabrina Toillier de Andrade</t>
+  </si>
+  <si>
+    <t>JOCELAINE CORREIA DA SILVA</t>
+  </si>
+  <si>
+    <t>Paulo Alexandre loureiro Lopes</t>
+  </si>
+  <si>
+    <t>EVLY APARECIDA MESQUITA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Denize Aparecida Nunes</t>
+  </si>
+  <si>
+    <t>CATERINE ALVES DIAS</t>
+  </si>
+  <si>
+    <t>FERNANDA SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>Dirlei Coelli</t>
+  </si>
+  <si>
+    <t>Alexsandra Gomes Rossi</t>
+  </si>
+  <si>
+    <t>Antônio Bordin Neto</t>
+  </si>
+  <si>
+    <t>Sidnei Osório Rosa Alves</t>
+  </si>
+  <si>
+    <t>Carina correa Figueiredo</t>
+  </si>
+  <si>
+    <t>MARINETE ROVEDA</t>
+  </si>
+  <si>
+    <t>Jerônimo Marquez de Macedo Neto</t>
+  </si>
+  <si>
+    <t>ARESTIDES TURIN</t>
+  </si>
+  <si>
+    <t>TIAGO DA SILVA SOUSA</t>
+  </si>
+  <si>
+    <t>Leni Terezinha de Mello</t>
+  </si>
+  <si>
+    <t>Karoline Franck Falcão</t>
+  </si>
+  <si>
+    <t>GLORIA VIRGINIA BENDER</t>
+  </si>
+  <si>
+    <t>Larissa Andrade Martins</t>
+  </si>
+  <si>
+    <t>Taciane Schwab Bini</t>
+  </si>
+  <si>
+    <t>Mayra dos santos</t>
+  </si>
+  <si>
+    <t>Liciane Anelize Oliveira Melo</t>
+  </si>
+  <si>
+    <t>CELESTE LUISANNIS LUNA MEJIAS</t>
+  </si>
+  <si>
+    <t>Bruna Tuani Vieira Alves</t>
+  </si>
+  <si>
+    <t>Hellen cristini monteiro Rodrigues</t>
+  </si>
+  <si>
+    <t>BR - ADRIEL FERNANDO DE MATOS BUENO</t>
+  </si>
+  <si>
+    <t>José Luis Irala de Freitas</t>
+  </si>
+  <si>
+    <t>Levi Xavier Da Cunha Junior</t>
+  </si>
+  <si>
+    <t>Diego de Oliveira Marochi</t>
+  </si>
+  <si>
+    <t>ronaldo rodrigo dos santos</t>
+  </si>
+  <si>
+    <t>Orlando Ucero</t>
+  </si>
+  <si>
+    <t>NAIELI RICARTE</t>
+  </si>
+  <si>
+    <t>VINICIUS MARINOSKI</t>
+  </si>
+  <si>
+    <t>Silvia Letícia De Morais</t>
+  </si>
+  <si>
+    <t>MARIA HELENA NORONHA</t>
+  </si>
+  <si>
+    <t>Wilmar Orso</t>
+  </si>
+  <si>
+    <t>Ercina de azeredo</t>
+  </si>
+  <si>
+    <t>Marina Izabel De França</t>
+  </si>
+  <si>
+    <t>Kyoshiro Massaharo Marinho Kawamoto</t>
+  </si>
+  <si>
+    <t>LEONIR FAGUNDES DA SILVA</t>
+  </si>
+  <si>
+    <t>RUBENS MIEUELETI BUENO</t>
+  </si>
+  <si>
+    <t>EDUARDO PICOLI</t>
+  </si>
+  <si>
+    <t>MARIA APARECIDA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Vilson de Mello</t>
+  </si>
+  <si>
+    <t>Danilo Ivo Brassanini</t>
+  </si>
+  <si>
+    <t>Marcia Roberta dos Santos Baron</t>
+  </si>
+  <si>
+    <t>LUAN COSTA NUNES</t>
+  </si>
+  <si>
+    <t>Emily Augusta do Nascimento Carnauba</t>
+  </si>
+  <si>
+    <t>OTAVIA LUCIA SKIERZYNSKI BETTANIN</t>
+  </si>
+  <si>
+    <t>BRUNA DE OLIVEIRA PIENTENCOSKI</t>
+  </si>
+  <si>
+    <t>LEONARDO DE MELLO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>EDUARDO DE ARAÚJO FERNANDES</t>
+  </si>
+  <si>
+    <t>Adriana Maria dos Santos Silva</t>
+  </si>
+  <si>
+    <t>Rogerio Lemos Ribeiro</t>
+  </si>
+  <si>
+    <t>Pio Balduino Quilante</t>
+  </si>
+  <si>
+    <t>Neiva Maria de Andrade</t>
+  </si>
+  <si>
+    <t>Vanessa Martins Barbosa</t>
+  </si>
+  <si>
+    <t>ALEXIS ENRIGUE AZOCAR ACUNA</t>
+  </si>
+  <si>
+    <t>Ricardo Sampaio Cordeiro eventos - Me</t>
+  </si>
+  <si>
+    <t>Ederson lírio</t>
+  </si>
+  <si>
+    <t>MARIA CLARA TABACZENISKI DA SILVA</t>
+  </si>
+  <si>
+    <t>Edson ferreira de Moraes</t>
+  </si>
+  <si>
+    <t>GABRIEL KIESLARCKI CASTAGNEL</t>
+  </si>
+  <si>
+    <t>Angela Maria geraldo</t>
+  </si>
+  <si>
+    <t>Willyam Juan de Almeida Florentino Pontes</t>
+  </si>
+  <si>
+    <t>EDUARDO NAUE ALVES DA ROSA</t>
+  </si>
+  <si>
+    <t>Sandryelle Millena Marcon</t>
+  </si>
+  <si>
+    <t>ALDO SCHILLO</t>
+  </si>
+  <si>
+    <t>Joice Feijó</t>
+  </si>
+  <si>
+    <t>MARIA DORETI MOREIRA</t>
+  </si>
+  <si>
+    <t>Jocelita Tobera</t>
+  </si>
+  <si>
+    <t>LUCAS SEGHETTO AIRES</t>
+  </si>
+  <si>
+    <t>DELESIA MARIA FELIPINI MASSAROTO</t>
+  </si>
+  <si>
+    <t>lucimar Cursino da Silva</t>
+  </si>
+  <si>
+    <t>Raikeli Josefina Amaya Villasana</t>
+  </si>
+  <si>
+    <t>YELITZA DEL VALLE FIGUEROA JAIME</t>
+  </si>
+  <si>
+    <t>Luis Cleber da Silva Azevedo</t>
+  </si>
+  <si>
+    <t>Larissa Fontoura de Freitas</t>
+  </si>
+  <si>
+    <t>Franciele Aparecida de Oliveira</t>
+  </si>
+  <si>
+    <t>JWK Construtora</t>
+  </si>
+  <si>
+    <t>Neusa Maria ribeiro</t>
+  </si>
+  <si>
+    <t>João Walter Castilho bohrer</t>
+  </si>
+  <si>
+    <t>Edilaine Aparecida Garcia da Silva</t>
+  </si>
+  <si>
+    <t>Lidia Madureira</t>
+  </si>
+  <si>
+    <t>ALESSANDRO AURELIO</t>
+  </si>
+  <si>
+    <t>Tatiane Cruz Keche</t>
+  </si>
+  <si>
+    <t>Jandira Da Rosa Fernandes</t>
+  </si>
+  <si>
+    <t>APMF COLEGIO ESTADUAL SAO FRANCISCO DE ASSIS FNDE/PDDE-QUALIDADE ESCOLA CONECTADA</t>
+  </si>
+  <si>
+    <t>GABRIEL SEVERO DANDOLINI</t>
+  </si>
+  <si>
+    <t>IVAN JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>FERNANDA RIBEIRO TOMAIZ</t>
+  </si>
+  <si>
+    <t>Sandra Maria Sibirino</t>
+  </si>
+  <si>
+    <t>SAULO HENRIQUE CALIXTO</t>
+  </si>
+  <si>
+    <t>Maria Eduarda Torres Ferreira</t>
+  </si>
+  <si>
+    <t>Gonçalo Leal Ramos</t>
+  </si>
+  <si>
+    <t>Volmir Antônio Ávila</t>
+  </si>
+  <si>
+    <t>LEONIR LOPES</t>
+  </si>
+  <si>
+    <t>DELANE BORGES MARTINS</t>
+  </si>
+  <si>
+    <t>ANDRE LUIZ CANDIDO</t>
+  </si>
+  <si>
+    <t>Larissa Abi-Zaid</t>
+  </si>
+  <si>
+    <t>GABRIEL APARECIDO NASCIMENTO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>GILBERTO BUTI</t>
+  </si>
+  <si>
+    <t>Anderson lemes de Oliveira</t>
+  </si>
+  <si>
+    <t>Cassia Patrícia Barizon de Andrade</t>
+  </si>
+  <si>
+    <t>Carlos Eri Fontoura da silveira</t>
+  </si>
+  <si>
+    <t>AMANDA STÉFANI DA SILVA MACIEL</t>
+  </si>
+  <si>
+    <t>ANTONIO GELSON DE PAULA</t>
+  </si>
+  <si>
+    <t>Maria Júlia Soares Pinheiro</t>
+  </si>
+  <si>
+    <t>Wellington Almeida de Oliveira</t>
+  </si>
+  <si>
+    <t>Franciele Custodio Boldt</t>
+  </si>
+  <si>
+    <t>PAULA TILLWRITZ</t>
+  </si>
+  <si>
+    <t>PATRICIA FARIAS BRANDE</t>
+  </si>
+  <si>
+    <t>Ester Vital do Nascimento</t>
+  </si>
+  <si>
+    <t>Luciana Santos Da Silva</t>
+  </si>
+  <si>
+    <t>Elis Regina Pereira Ribeiro Da Silva</t>
+  </si>
+  <si>
+    <t>Rodrigo Pereira Ribeiro</t>
+  </si>
+  <si>
+    <t>Nelci Aparecida Pontes</t>
+  </si>
+  <si>
+    <t>Gabriel Cardoso da Silva</t>
+  </si>
+  <si>
+    <t>ANTONIO CARLOS CAMARGO</t>
+  </si>
+  <si>
+    <t>Caroline Ferreira De Lima</t>
+  </si>
+  <si>
+    <t>Ana Beatriz De Mello</t>
+  </si>
+  <si>
+    <t>Antônio Marcos Ferreira</t>
+  </si>
+  <si>
+    <t>valdir da rosa pereira junior</t>
+  </si>
+  <si>
+    <t>Daniela Santos Mengue</t>
+  </si>
+  <si>
+    <t>Otilia Beatriz Silva de Oliveira</t>
+  </si>
+  <si>
+    <t>DANIELA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Emerson Zanardi</t>
+  </si>
+  <si>
+    <t>Dreice Oliveira bortolotti</t>
+  </si>
+  <si>
+    <t>Rafael Krever</t>
+  </si>
+  <si>
+    <t>ADRIANA ALVES FERREIRA</t>
+  </si>
+  <si>
+    <t>SAO JOSE DAS PALMEIRAS/PR</t>
+  </si>
+  <si>
+    <t>Ana Carolina Gonçalves Obrusnik</t>
+  </si>
+  <si>
+    <t>Eduardo Spricigo de Souza</t>
+  </si>
+  <si>
+    <t>Grazielly Martins Tobaldini</t>
+  </si>
+  <si>
+    <t>ENI VITORIA LIMA DE LIMA</t>
+  </si>
+  <si>
+    <t>Patrícia da Silva</t>
+  </si>
+  <si>
+    <t>EVANDRO GOMES FAGUNDES DA CUNHA</t>
+  </si>
+  <si>
+    <t>Mafalda Basso Fiorini</t>
+  </si>
+  <si>
+    <t>TEREZA IANEGITZ</t>
+  </si>
+  <si>
+    <t>Nilva Bencke</t>
+  </si>
+  <si>
+    <t>Carlos Henrique Antunes</t>
+  </si>
+  <si>
+    <t>ersulina dos passos gomes</t>
+  </si>
+  <si>
+    <t>Mariete Claro Nunes</t>
+  </si>
+  <si>
+    <t>ACADEMIA EFAPI FIT LTDA</t>
+  </si>
+  <si>
+    <t>ELIEL MATIAS PEREIRA</t>
+  </si>
+  <si>
+    <t>INPULSE FASHION LTDA</t>
+  </si>
+  <si>
+    <t>Roniele Carniel</t>
+  </si>
+  <si>
+    <t>Ana Luiza Severo Dos Santos</t>
+  </si>
+  <si>
+    <t>Francys Júnior Gonçalves Braga</t>
+  </si>
+  <si>
+    <t>Mikaelly de Souza Lima</t>
+  </si>
+  <si>
+    <t>Helena Rodrigues</t>
+  </si>
+  <si>
+    <t>Erick Willi Ribas Castanha</t>
+  </si>
+  <si>
+    <t>JOCIANE APARECIDA DA FONSECA RAQUEL MACHADO</t>
+  </si>
+  <si>
+    <t>MARCIANO LAUTERIO DA SILVA</t>
+  </si>
+  <si>
+    <t>LUIZ CARLOS VIEIRA FILHO</t>
+  </si>
+  <si>
+    <t>ADRIANA DA COSTA ALVES</t>
+  </si>
+  <si>
+    <t>Altamiro Pereira Dos Santos</t>
+  </si>
+  <si>
+    <t>JUSLAINE NUNES BARRZO</t>
+  </si>
+  <si>
+    <t>William Wingelmann</t>
+  </si>
+  <si>
+    <t>GABRIEL HENRIQUE SEHNEM</t>
+  </si>
+  <si>
+    <t>SANDRA MARA DE JESUS ORCHEL SANTANA</t>
+  </si>
+  <si>
+    <t>Dirceu Martins Padilha</t>
+  </si>
+  <si>
+    <t>Miriam salcedo Corrêa</t>
+  </si>
+  <si>
+    <t>VINICIUS MOTTA DA ROSA</t>
+  </si>
+  <si>
+    <t>Samuel Wagner Henschel</t>
+  </si>
+  <si>
+    <t>EZEQUIEL QUEIROZ</t>
+  </si>
+  <si>
+    <t>COM - CDA - JESSICA MAIARA DIAS DA SILVA</t>
+  </si>
+  <si>
+    <t>COM - CAN - THAIANE NATASHA VARGAS DA SILVA</t>
+  </si>
+  <si>
+    <t>COM - IXI - LORENA ANTONIA TROMBETTA</t>
+  </si>
+  <si>
+    <t>ATN - IAI - ANA LUIZA PITALUGA KLEIN</t>
   </si>
 </sst>
 </file>
@@ -7936,7 +8539,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBE226-2569-43EF-8B89-51B7526D69A9}">
-  <dimension ref="A1:H2093"/>
+  <dimension ref="A1:H2295"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -62360,6 +62963,5258 @@
         <v>87</v>
       </c>
     </row>
+    <row r="2094" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2094" s="4" t="s">
+        <v>2493</v>
+      </c>
+      <c r="B2094" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2094" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2094" s="7">
+        <v>875515</v>
+      </c>
+      <c r="E2094" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F2094" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2094" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2094" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2095" s="9" t="s">
+        <v>2494</v>
+      </c>
+      <c r="B2095" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2095" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2095" s="12">
+        <v>637113</v>
+      </c>
+      <c r="E2095" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F2095" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2095" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2095" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2096" s="4" t="s">
+        <v>2495</v>
+      </c>
+      <c r="B2096" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2096" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2096" s="7">
+        <v>818285</v>
+      </c>
+      <c r="E2096" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2096" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2096" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2096" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2097" s="9" t="s">
+        <v>2496</v>
+      </c>
+      <c r="B2097" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2097" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2097" s="12">
+        <v>725067</v>
+      </c>
+      <c r="E2097" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2097" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2097" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2097" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2098" s="4" t="s">
+        <v>2497</v>
+      </c>
+      <c r="B2098" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2098" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2098" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2098" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2098" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2098" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2098" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2099" s="9" t="s">
+        <v>2498</v>
+      </c>
+      <c r="B2099" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2099" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2099" s="12">
+        <v>459336</v>
+      </c>
+      <c r="E2099" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2099" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2099" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2099" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2100" s="4" t="s">
+        <v>2499</v>
+      </c>
+      <c r="B2100" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2100" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2100" s="7">
+        <v>619784</v>
+      </c>
+      <c r="E2100" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2100" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2100" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2100" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2101" s="9" t="s">
+        <v>2500</v>
+      </c>
+      <c r="B2101" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2101" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2101" s="12">
+        <v>691859</v>
+      </c>
+      <c r="E2101" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="F2101" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2101" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2101" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2102" s="4" t="s">
+        <v>2501</v>
+      </c>
+      <c r="B2102" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2102" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2102" s="7">
+        <v>110</v>
+      </c>
+      <c r="E2102" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2102" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2102" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2102" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2103" s="9" t="s">
+        <v>2502</v>
+      </c>
+      <c r="B2103" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C2103" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2103" s="12">
+        <v>77299</v>
+      </c>
+      <c r="E2103" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F2103" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2103" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2103" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2104" s="4" t="s">
+        <v>2503</v>
+      </c>
+      <c r="B2104" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2104" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2104" s="7">
+        <v>837937</v>
+      </c>
+      <c r="E2104" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F2104" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2104" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2104" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2105" s="9" t="s">
+        <v>2504</v>
+      </c>
+      <c r="B2105" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2105" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2105" s="12">
+        <v>867522</v>
+      </c>
+      <c r="E2105" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2105" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2105" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2105" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2106" s="4" t="s">
+        <v>2505</v>
+      </c>
+      <c r="B2106" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2106" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2106" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2106" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2106" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2106" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2106" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2107" s="9" t="s">
+        <v>2506</v>
+      </c>
+      <c r="B2107" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2107" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2107" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2107" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2107" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2107" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2107" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2108" s="4" t="s">
+        <v>2507</v>
+      </c>
+      <c r="B2108" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2108" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2108" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2108" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2108" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2108" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2108" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2109" s="9" t="s">
+        <v>2508</v>
+      </c>
+      <c r="B2109" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2109" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2109" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2109" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2109" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2109" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2109" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2110" s="4" t="s">
+        <v>2509</v>
+      </c>
+      <c r="B2110" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2110" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2110" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2110" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2110" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2110" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2110" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2111" s="9" t="s">
+        <v>2510</v>
+      </c>
+      <c r="B2111" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2111" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2111" s="12">
+        <v>829353</v>
+      </c>
+      <c r="E2111" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2111" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2111" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2111" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2112" s="4" t="s">
+        <v>2511</v>
+      </c>
+      <c r="B2112" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2112" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2112" s="7">
+        <v>576159</v>
+      </c>
+      <c r="E2112" s="5" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F2112" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2112" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2112" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2113" s="9" t="s">
+        <v>2512</v>
+      </c>
+      <c r="B2113" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2113" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2113" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2113" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2113" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2113" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2113" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2114" s="4" t="s">
+        <v>2513</v>
+      </c>
+      <c r="B2114" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2114" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2114" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2114" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2114" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2114" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2114" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2115" s="9" t="s">
+        <v>2514</v>
+      </c>
+      <c r="B2115" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2115" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2115" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2115" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2115" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2115" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2115" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2116" s="4" t="s">
+        <v>2515</v>
+      </c>
+      <c r="B2116" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2116" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2116" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2116" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2116" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2116" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2116" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2117" s="9" t="s">
+        <v>2516</v>
+      </c>
+      <c r="B2117" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2117" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2117" s="12">
+        <v>529843</v>
+      </c>
+      <c r="E2117" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F2117" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2117" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2117" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2118" s="4" t="s">
+        <v>2517</v>
+      </c>
+      <c r="B2118" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2118" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2118" s="7">
+        <v>873823</v>
+      </c>
+      <c r="E2118" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="F2118" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2118" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2118" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2119" s="9" t="s">
+        <v>2518</v>
+      </c>
+      <c r="B2119" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2119" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2119" s="12">
+        <v>6060</v>
+      </c>
+      <c r="E2119" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F2119" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2119" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2119" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2120" s="4" t="s">
+        <v>2519</v>
+      </c>
+      <c r="B2120" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2120" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2120" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2120" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2120" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2120" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2120" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2121" s="9" t="s">
+        <v>2520</v>
+      </c>
+      <c r="B2121" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2121" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2121" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2121" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2121" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2121" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2121" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2122" s="4" t="s">
+        <v>2521</v>
+      </c>
+      <c r="B2122" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2122" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2122" s="7">
+        <v>867522</v>
+      </c>
+      <c r="E2122" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2122" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2122" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2122" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2123" s="9" t="s">
+        <v>2522</v>
+      </c>
+      <c r="B2123" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2123" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2123" s="12">
+        <v>819069</v>
+      </c>
+      <c r="E2123" s="5" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F2123" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2123" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2123" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2124" s="4" t="s">
+        <v>2523</v>
+      </c>
+      <c r="B2124" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2124" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2124" s="7">
+        <v>884801</v>
+      </c>
+      <c r="E2124" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2124" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2124" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2124" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2125" s="9" t="s">
+        <v>2524</v>
+      </c>
+      <c r="B2125" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2125" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2125" s="12">
+        <v>780589</v>
+      </c>
+      <c r="E2125" s="5" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F2125" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2125" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2125" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2126" s="4" t="s">
+        <v>2525</v>
+      </c>
+      <c r="B2126" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C2126" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2126" s="7">
+        <v>884826</v>
+      </c>
+      <c r="E2126" s="5" t="s">
+        <v>2089</v>
+      </c>
+      <c r="F2126" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2126" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2126" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2127" s="9" t="s">
+        <v>2526</v>
+      </c>
+      <c r="B2127" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2127" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2127" s="12">
+        <v>172141</v>
+      </c>
+      <c r="E2127" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2127" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2127" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2127" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2128" s="4" t="s">
+        <v>2527</v>
+      </c>
+      <c r="B2128" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2128" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2128" s="7">
+        <v>562578</v>
+      </c>
+      <c r="E2128" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2128" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2128" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2128" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2129" s="9" t="s">
+        <v>2528</v>
+      </c>
+      <c r="B2129" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2129" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2129" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E2129" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2129" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2129" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2129" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2130" s="4" t="s">
+        <v>2529</v>
+      </c>
+      <c r="B2130" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2130" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2130" s="7">
+        <v>262147</v>
+      </c>
+      <c r="E2130" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2130" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2130" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2130" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2131" s="9" t="s">
+        <v>2530</v>
+      </c>
+      <c r="B2131" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2131" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2131" s="12">
+        <v>876282</v>
+      </c>
+      <c r="E2131" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F2131" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2131" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2131" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2132" s="4" t="s">
+        <v>2531</v>
+      </c>
+      <c r="B2132" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2132" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2132" s="7">
+        <v>239381</v>
+      </c>
+      <c r="E2132" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2132" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2132" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2132" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2133" s="9" t="s">
+        <v>2532</v>
+      </c>
+      <c r="B2133" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2133" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2133" s="12">
+        <v>729970</v>
+      </c>
+      <c r="E2133" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2133" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2133" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2133" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2134" s="4" t="s">
+        <v>2533</v>
+      </c>
+      <c r="B2134" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2134" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2134" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2134" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2134" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2134" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2134" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2135" s="9" t="s">
+        <v>2534</v>
+      </c>
+      <c r="B2135" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2135" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2135" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2135" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2135" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2135" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2135" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2136" s="4" t="s">
+        <v>2535</v>
+      </c>
+      <c r="B2136" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="C2136" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2136" s="7">
+        <v>110</v>
+      </c>
+      <c r="E2136" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2136" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2136" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2136" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2137" s="9" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B2137" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2137" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2137" s="12">
+        <v>255780</v>
+      </c>
+      <c r="E2137" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2137" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2137" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2137" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2138" s="4" t="s">
+        <v>2537</v>
+      </c>
+      <c r="B2138" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2138" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2138" s="7">
+        <v>818285</v>
+      </c>
+      <c r="E2138" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2138" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2138" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2138" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2139" s="9" t="s">
+        <v>2538</v>
+      </c>
+      <c r="B2139" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2139" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2139" s="12">
+        <v>382096</v>
+      </c>
+      <c r="E2139" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F2139" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2139" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2139" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2140" s="4" t="s">
+        <v>2539</v>
+      </c>
+      <c r="B2140" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2140" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2140" s="7">
+        <v>529843</v>
+      </c>
+      <c r="E2140" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F2140" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2140" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2140" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2141" s="9" t="s">
+        <v>2540</v>
+      </c>
+      <c r="B2141" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2141" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2141" s="12">
+        <v>547683</v>
+      </c>
+      <c r="E2141" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F2141" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2141" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2141" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2142" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B2142" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2142" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2142" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2142" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2142" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2142" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2142" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2143" s="9" t="s">
+        <v>2542</v>
+      </c>
+      <c r="B2143" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2143" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2143" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2143" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2143" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2143" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2143" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2144" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B2144" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2144" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2144" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2144" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2144" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2144" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2144" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2145" s="9" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B2145" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2145" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2145" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2145" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2145" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2145" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2145" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2146" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B2146" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2146" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2146" s="7">
+        <v>236724</v>
+      </c>
+      <c r="E2146" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2146" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2146" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2146" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2147" s="9" t="s">
+        <v>2546</v>
+      </c>
+      <c r="B2147" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2147" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2147" s="12">
+        <v>822704</v>
+      </c>
+      <c r="E2147" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2147" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2147" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2147" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2148" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B2148" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2148" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2148" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E2148" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2148" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2148" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2148" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2149" s="9" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B2149" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2149" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2149" s="12">
+        <v>576121</v>
+      </c>
+      <c r="E2149" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2149" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2149" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2149" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2150" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B2150" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2150" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2150" s="7">
+        <v>883827</v>
+      </c>
+      <c r="E2150" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2150" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2150" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2150" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2151" s="9" t="s">
+        <v>2550</v>
+      </c>
+      <c r="B2151" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2151" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2151" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2151" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2151" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2151" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2151" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2152" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B2152" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2152" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2152" s="7">
+        <v>829353</v>
+      </c>
+      <c r="E2152" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2152" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2152" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2152" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2153" s="9" t="s">
+        <v>2548</v>
+      </c>
+      <c r="B2153" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2153" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2153" s="12">
+        <v>576121</v>
+      </c>
+      <c r="E2153" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2153" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2153" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2153" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2154" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="B2154" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2154" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2154" s="7">
+        <v>713743</v>
+      </c>
+      <c r="E2154" s="5" t="s">
+        <v>901</v>
+      </c>
+      <c r="F2154" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2154" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2154" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2155" s="9" t="s">
+        <v>2553</v>
+      </c>
+      <c r="B2155" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2155" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2155" s="12">
+        <v>879945</v>
+      </c>
+      <c r="E2155" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2155" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2155" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2155" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2156" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B2156" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2156" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2156" s="7">
+        <v>216565</v>
+      </c>
+      <c r="E2156" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2156" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2156" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2156" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2157" s="9" t="s">
+        <v>2555</v>
+      </c>
+      <c r="B2157" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2157" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2157" s="12">
+        <v>822704</v>
+      </c>
+      <c r="E2157" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2157" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2157" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2157" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2158" s="4" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B2158" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2158" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2158" s="7">
+        <v>872122</v>
+      </c>
+      <c r="E2158" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2158" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2158" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2158" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2159" s="9" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B2159" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2159" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2159" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E2159" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2159" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2159" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2159" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2160" s="4" t="s">
+        <v>2558</v>
+      </c>
+      <c r="B2160" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2160" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2160" s="7">
+        <v>885451</v>
+      </c>
+      <c r="E2160" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F2160" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2160" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2160" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2161" s="9" t="s">
+        <v>2559</v>
+      </c>
+      <c r="B2161" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2161" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2161" s="12">
+        <v>216565</v>
+      </c>
+      <c r="E2161" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2161" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2161" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2161" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2162" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B2162" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2162" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2162" s="7">
+        <v>873652</v>
+      </c>
+      <c r="E2162" s="5" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F2162" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2162" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2162" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2163" s="9" t="s">
+        <v>2561</v>
+      </c>
+      <c r="B2163" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2163" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2163" s="12">
+        <v>790437</v>
+      </c>
+      <c r="E2163" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F2163" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2163" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2163" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2164" s="4" t="s">
+        <v>2562</v>
+      </c>
+      <c r="B2164" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2164" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2164" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2164" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2164" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2164" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2164" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2165" s="9" t="s">
+        <v>2563</v>
+      </c>
+      <c r="B2165" s="10" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C2165" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2165" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2165" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2165" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2165" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2165" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2166" s="4" t="s">
+        <v>2564</v>
+      </c>
+      <c r="B2166" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2166" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2166" s="7">
+        <v>855523</v>
+      </c>
+      <c r="E2166" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2166" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2166" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2166" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2167" s="9" t="s">
+        <v>2565</v>
+      </c>
+      <c r="B2167" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2167" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2167" s="12">
+        <v>621514</v>
+      </c>
+      <c r="E2167" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2167" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2167" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2167" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2168" s="4" t="s">
+        <v>2566</v>
+      </c>
+      <c r="B2168" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2168" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2168" s="7">
+        <v>822704</v>
+      </c>
+      <c r="E2168" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2168" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2168" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2168" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2169" s="9" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B2169" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2169" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2169" s="12">
+        <v>437804</v>
+      </c>
+      <c r="E2169" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2169" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2169" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2169" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2170" s="4" t="s">
+        <v>2568</v>
+      </c>
+      <c r="B2170" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2170" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2170" s="7">
+        <v>729970</v>
+      </c>
+      <c r="E2170" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2170" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2170" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2170" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2171" s="9" t="s">
+        <v>2569</v>
+      </c>
+      <c r="B2171" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2171" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2171" s="12">
+        <v>825133</v>
+      </c>
+      <c r="E2171" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2171" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2171" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2171" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2172" s="4" t="s">
+        <v>2570</v>
+      </c>
+      <c r="B2172" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2172" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2172" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2172" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2172" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2172" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2172" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2173" s="9" t="s">
+        <v>2571</v>
+      </c>
+      <c r="B2173" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2173" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2173" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2173" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2173" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2173" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2173" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2174" s="4" t="s">
+        <v>2572</v>
+      </c>
+      <c r="B2174" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2174" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2174" s="7">
+        <v>255780</v>
+      </c>
+      <c r="E2174" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2174" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2174" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2174" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2175" s="9" t="s">
+        <v>2573</v>
+      </c>
+      <c r="B2175" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2175" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2175" s="12">
+        <v>775845</v>
+      </c>
+      <c r="E2175" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F2175" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2175" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2175" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2176" s="4" t="s">
+        <v>2574</v>
+      </c>
+      <c r="B2176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2176" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2176" s="7">
+        <v>165769</v>
+      </c>
+      <c r="E2176" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2176" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2176" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2176" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2177" s="9" t="s">
+        <v>2575</v>
+      </c>
+      <c r="B2177" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2177" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2177" s="12">
+        <v>874055</v>
+      </c>
+      <c r="E2177" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="F2177" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2177" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2177" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2178" s="4" t="s">
+        <v>2576</v>
+      </c>
+      <c r="B2178" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2178" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2178" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2178" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2178" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2178" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2178" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2179" s="9" t="s">
+        <v>2577</v>
+      </c>
+      <c r="B2179" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2179" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2179" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2179" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2179" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2179" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2179" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2180" s="4" t="s">
+        <v>2578</v>
+      </c>
+      <c r="B2180" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2180" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2180" s="7">
+        <v>834515</v>
+      </c>
+      <c r="E2180" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F2180" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2180" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2180" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2181" s="9" t="s">
+        <v>2579</v>
+      </c>
+      <c r="B2181" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2181" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2181" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2181" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2181" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2181" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2181" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2182" s="4" t="s">
+        <v>2580</v>
+      </c>
+      <c r="B2182" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2182" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2182" s="7">
+        <v>172141</v>
+      </c>
+      <c r="E2182" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2182" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2182" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2182" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2183" s="9" t="s">
+        <v>2581</v>
+      </c>
+      <c r="B2183" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2183" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2183" s="12">
+        <v>689070</v>
+      </c>
+      <c r="E2183" s="5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F2183" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2183" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2183" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2184" s="4" t="s">
+        <v>2582</v>
+      </c>
+      <c r="B2184" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2184" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2184" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2184" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2184" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2184" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2184" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2185" s="9" t="s">
+        <v>2583</v>
+      </c>
+      <c r="B2185" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2185" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2185" s="12">
+        <v>829353</v>
+      </c>
+      <c r="E2185" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2185" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2185" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2185" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2186" s="4" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B2186" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2186" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2186" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2186" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2186" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2186" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2186" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2187" s="9" t="s">
+        <v>2585</v>
+      </c>
+      <c r="B2187" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2187" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2187" s="12">
+        <v>875888</v>
+      </c>
+      <c r="E2187" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F2187" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2187" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2187" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2188" s="4" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B2188" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2188" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2188" s="7">
+        <v>683063</v>
+      </c>
+      <c r="E2188" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2188" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2188" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2188" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2189" s="9" t="s">
+        <v>2587</v>
+      </c>
+      <c r="B2189" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2189" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2189" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2189" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2189" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2189" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2189" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2190" s="4" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B2190" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2190" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2190" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E2190" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2190" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2190" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2190" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2191" s="9" t="s">
+        <v>2589</v>
+      </c>
+      <c r="B2191" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2191" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2191" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2191" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2191" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2191" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2191" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2192" s="4" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B2192" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2192" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2192" s="7">
+        <v>636843</v>
+      </c>
+      <c r="E2192" s="5" t="s">
+        <v>1553</v>
+      </c>
+      <c r="F2192" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2192" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2192" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2193" s="9" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B2193" s="10" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C2193" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2193" s="12">
+        <v>680982</v>
+      </c>
+      <c r="E2193" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2193" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2193" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2193" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2194" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="B2194" s="5" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C2194" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2194" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E2194" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2194" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2194" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2194" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2195" s="9" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B2195" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2195" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2195" s="12">
+        <v>867361</v>
+      </c>
+      <c r="E2195" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2195" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2195" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2195" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2196" s="4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="B2196" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2196" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2196" s="7">
+        <v>172141</v>
+      </c>
+      <c r="E2196" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2196" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2196" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2196" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2197" s="9" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B2197" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2197" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2197" s="12">
+        <v>619784</v>
+      </c>
+      <c r="E2197" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2197" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2197" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2197" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2198" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="B2198" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2198" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2198" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2198" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2198" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2198" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2198" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2199" s="9" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B2199" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2199" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2199" s="12">
+        <v>382096</v>
+      </c>
+      <c r="E2199" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F2199" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2199" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2199" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2200" s="4" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B2200" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2200" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2200" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2200" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2200" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2200" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2200" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2201" s="9" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B2201" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2201" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2201" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2201" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2201" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2201" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2201" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2202" s="4" t="s">
+        <v>2598</v>
+      </c>
+      <c r="B2202" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2202" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2202" s="7">
+        <v>883815</v>
+      </c>
+      <c r="E2202" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F2202" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2202" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2202" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2203" s="9" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B2203" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2203" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2203" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2203" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2203" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2203" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2203" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2204" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B2204" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2204" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2204" s="7">
+        <v>858817</v>
+      </c>
+      <c r="E2204" s="5" t="s">
+        <v>2693</v>
+      </c>
+      <c r="F2204" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2204" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2204" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2205" s="9" t="s">
+        <v>2601</v>
+      </c>
+      <c r="B2205" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2205" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2205" s="12">
+        <v>884801</v>
+      </c>
+      <c r="E2205" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2205" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2205" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2205" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2206" s="4" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B2206" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2206" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2206" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2206" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2206" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2206" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2206" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2207" s="9" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B2207" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2207" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2207" s="12">
+        <v>621514</v>
+      </c>
+      <c r="E2207" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2207" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2207" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2207" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2208" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="B2208" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2208" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2208" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E2208" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2208" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2208" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2208" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2209" s="9" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B2209" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2209" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2209" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2209" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2209" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2209" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2209" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2210" s="4" t="s">
+        <v>2606</v>
+      </c>
+      <c r="B2210" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2210" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2210" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2210" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2210" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2210" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2210" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2211" s="9" t="s">
+        <v>2607</v>
+      </c>
+      <c r="B2211" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2211" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2211" s="12">
+        <v>886641</v>
+      </c>
+      <c r="E2211" s="5" t="s">
+        <v>895</v>
+      </c>
+      <c r="F2211" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2211" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2211" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2212" s="4" t="s">
+        <v>2608</v>
+      </c>
+      <c r="B2212" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2212" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2212" s="7">
+        <v>833948</v>
+      </c>
+      <c r="E2212" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2212" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2212" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2212" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2213" s="9" t="s">
+        <v>2609</v>
+      </c>
+      <c r="B2213" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2213" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2213" s="12">
+        <v>825133</v>
+      </c>
+      <c r="E2213" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2213" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2213" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2213" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2214" s="4" t="s">
+        <v>2610</v>
+      </c>
+      <c r="B2214" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2214" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2214" s="7">
+        <v>878929</v>
+      </c>
+      <c r="E2214" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2214" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2214" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2214" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2215" s="9" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B2215" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2215" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2215" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2215" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2215" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2215" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2215" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2216" s="4" t="s">
+        <v>2612</v>
+      </c>
+      <c r="B2216" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2216" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2216" s="7">
+        <v>666428</v>
+      </c>
+      <c r="E2216" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F2216" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2216" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2216" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2217" s="9" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B2217" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2217" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2217" s="12">
+        <v>867522</v>
+      </c>
+      <c r="E2217" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F2217" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2217" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2217" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2218" s="4" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B2218" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2218" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2218" s="7">
+        <v>885451</v>
+      </c>
+      <c r="E2218" s="5" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F2218" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2218" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2218" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2219" s="9" t="s">
+        <v>2614</v>
+      </c>
+      <c r="B2219" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2219" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2219" s="12">
+        <v>810976</v>
+      </c>
+      <c r="E2219" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F2219" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2219" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2219" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2220" s="4" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B2220" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2220" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2220" s="7">
+        <v>869886</v>
+      </c>
+      <c r="E2220" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F2220" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2220" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2220" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2221" s="9" t="s">
+        <v>2616</v>
+      </c>
+      <c r="B2221" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2221" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2221" s="12">
+        <v>459336</v>
+      </c>
+      <c r="E2221" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2221" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2221" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2221" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2222" s="4" t="s">
+        <v>2617</v>
+      </c>
+      <c r="B2222" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2222" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2222" s="7">
+        <v>879127</v>
+      </c>
+      <c r="E2222" s="5" t="s">
+        <v>2488</v>
+      </c>
+      <c r="F2222" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2222" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2222" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2223" s="9" t="s">
+        <v>2618</v>
+      </c>
+      <c r="B2223" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2223" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2223" s="12">
+        <v>790437</v>
+      </c>
+      <c r="E2223" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F2223" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2223" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2223" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2224" s="4" t="s">
+        <v>2619</v>
+      </c>
+      <c r="B2224" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C2224" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2224" s="7">
+        <v>216565</v>
+      </c>
+      <c r="E2224" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2224" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2224" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2224" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2225" s="9" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B2225" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2225" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2225" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2225" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2225" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2225" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2225" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2226" s="4" t="s">
+        <v>2621</v>
+      </c>
+      <c r="B2226" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2226" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2226" s="7">
+        <v>878856</v>
+      </c>
+      <c r="E2226" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F2226" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2226" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2226" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2227" s="9" t="s">
+        <v>2622</v>
+      </c>
+      <c r="B2227" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2227" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2227" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2227" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2227" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2227" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2227" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2228" s="4" t="s">
+        <v>2623</v>
+      </c>
+      <c r="B2228" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2228" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2228" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2228" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2228" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2228" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2228" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2229" s="9" t="s">
+        <v>2624</v>
+      </c>
+      <c r="B2229" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C2229" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2229" s="12">
+        <v>77299</v>
+      </c>
+      <c r="E2229" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F2229" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2229" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2229" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2230" s="4" t="s">
+        <v>2625</v>
+      </c>
+      <c r="B2230" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2230" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2230" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2230" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2230" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2230" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2230" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2231" s="9" t="s">
+        <v>2626</v>
+      </c>
+      <c r="B2231" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2231" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2231" s="12">
+        <v>529843</v>
+      </c>
+      <c r="E2231" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F2231" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2231" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2231" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2232" s="4" t="s">
+        <v>2627</v>
+      </c>
+      <c r="B2232" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2232" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2232" s="7">
+        <v>870487</v>
+      </c>
+      <c r="E2232" s="5" t="s">
+        <v>2094</v>
+      </c>
+      <c r="F2232" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2232" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2232" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2233" s="9" t="s">
+        <v>2628</v>
+      </c>
+      <c r="B2233" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2233" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2233" s="12">
+        <v>729970</v>
+      </c>
+      <c r="E2233" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2233" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2233" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2233" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2234" s="4" t="s">
+        <v>2629</v>
+      </c>
+      <c r="B2234" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2234" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2234" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E2234" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2234" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2234" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2234" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2235" s="9" t="s">
+        <v>2630</v>
+      </c>
+      <c r="B2235" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2235" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2235" s="12">
+        <v>236724</v>
+      </c>
+      <c r="E2235" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="F2235" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2235" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2235" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2236" s="4" t="s">
+        <v>2631</v>
+      </c>
+      <c r="B2236" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2236" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2236" s="7">
+        <v>853036</v>
+      </c>
+      <c r="E2236" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="F2236" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2236" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2236" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2237" s="9" t="s">
+        <v>2632</v>
+      </c>
+      <c r="B2237" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2237" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2237" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2237" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2237" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2237" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2237" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2238" s="4" t="s">
+        <v>2633</v>
+      </c>
+      <c r="B2238" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2238" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2238" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2238" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2238" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2238" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2238" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2239" s="9" t="s">
+        <v>2634</v>
+      </c>
+      <c r="B2239" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2239" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2239" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2239" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2239" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2239" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2239" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2240" s="4" t="s">
+        <v>2635</v>
+      </c>
+      <c r="B2240" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2240" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2240" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2240" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2240" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2240" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2240" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2241" s="9" t="s">
+        <v>2636</v>
+      </c>
+      <c r="B2241" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2241" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2241" s="12">
+        <v>882361</v>
+      </c>
+      <c r="E2241" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F2241" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2241" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2241" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2242" s="4" t="s">
+        <v>2637</v>
+      </c>
+      <c r="B2242" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2242" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2242" s="7">
+        <v>653931</v>
+      </c>
+      <c r="E2242" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2242" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2242" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2242" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2243" s="9" t="s">
+        <v>2638</v>
+      </c>
+      <c r="B2243" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2243" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2243" s="12">
+        <v>781646</v>
+      </c>
+      <c r="E2243" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2243" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2243" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2243" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2244" s="4" t="s">
+        <v>2639</v>
+      </c>
+      <c r="B2244" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2244" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2244" s="7">
+        <v>781646</v>
+      </c>
+      <c r="E2244" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2244" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2244" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2244" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2245" s="9" t="s">
+        <v>2640</v>
+      </c>
+      <c r="B2245" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2245" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2245" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2245" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2245" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2245" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2245" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2246" s="4" t="s">
+        <v>2641</v>
+      </c>
+      <c r="B2246" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2246" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2246" s="7">
+        <v>725067</v>
+      </c>
+      <c r="E2246" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2246" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2246" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2246" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2247" s="9" t="s">
+        <v>2642</v>
+      </c>
+      <c r="B2247" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2247" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2247" s="12">
+        <v>870268</v>
+      </c>
+      <c r="E2247" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="F2247" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2247" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2247" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2248" s="4" t="s">
+        <v>2643</v>
+      </c>
+      <c r="B2248" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2248" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2248" s="7">
+        <v>40828</v>
+      </c>
+      <c r="E2248" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2248" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2248" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2248" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2249" s="9" t="s">
+        <v>2644</v>
+      </c>
+      <c r="B2249" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2249" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2249" s="12">
+        <v>177442</v>
+      </c>
+      <c r="E2249" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2249" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2249" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2249" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2250" s="4" t="s">
+        <v>2645</v>
+      </c>
+      <c r="B2250" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2250" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2250" s="7">
+        <v>529843</v>
+      </c>
+      <c r="E2250" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F2250" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2250" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2250" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2251" s="9" t="s">
+        <v>2646</v>
+      </c>
+      <c r="B2251" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2251" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2251" s="12">
+        <v>870012</v>
+      </c>
+      <c r="E2251" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F2251" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2251" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2251" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2252" s="4" t="s">
+        <v>2647</v>
+      </c>
+      <c r="B2252" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2252" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2252" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2252" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2252" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2252" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2252" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2253" s="9" t="s">
+        <v>2648</v>
+      </c>
+      <c r="B2253" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2253" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2253" s="12">
+        <v>725067</v>
+      </c>
+      <c r="E2253" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2253" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2253" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2253" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2254" s="4" t="s">
+        <v>2649</v>
+      </c>
+      <c r="B2254" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2254" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2254" s="7">
+        <v>882296</v>
+      </c>
+      <c r="E2254" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2254" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2254" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2254" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2255" s="9" t="s">
+        <v>2650</v>
+      </c>
+      <c r="B2255" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2255" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2255" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2255" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2255" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2255" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2255" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2256" s="4" t="s">
+        <v>2651</v>
+      </c>
+      <c r="B2256" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2256" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2256" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2256" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2256" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2256" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2256" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2257" s="9" t="s">
+        <v>2652</v>
+      </c>
+      <c r="B2257" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2257" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2257" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2257" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2257" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2257" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2257" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2258" s="4" t="s">
+        <v>2653</v>
+      </c>
+      <c r="B2258" s="5" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C2258" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2258" s="7">
+        <v>336158</v>
+      </c>
+      <c r="E2258" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F2258" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2258" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2258" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2259" s="9" t="s">
+        <v>2655</v>
+      </c>
+      <c r="B2259" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2259" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2259" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2259" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2259" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2259" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2259" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2260" s="4" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B2260" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2260" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2260" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2260" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2260" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2260" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2260" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2261" s="9" t="s">
+        <v>2657</v>
+      </c>
+      <c r="B2261" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2261" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2261" s="12">
+        <v>864414</v>
+      </c>
+      <c r="E2261" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F2261" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2261" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2261" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2262" s="4" t="s">
+        <v>2658</v>
+      </c>
+      <c r="B2262" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2262" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2262" s="7">
+        <v>608355</v>
+      </c>
+      <c r="E2262" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2262" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2262" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2262" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2263" s="9" t="s">
+        <v>2659</v>
+      </c>
+      <c r="B2263" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2263" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2263" s="12">
+        <v>822770</v>
+      </c>
+      <c r="E2263" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2263" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2263" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2263" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2264" s="4" t="s">
+        <v>2660</v>
+      </c>
+      <c r="B2264" s="5" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C2264" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2264" s="7">
+        <v>404528</v>
+      </c>
+      <c r="E2264" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="F2264" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2264" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2264" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2265" s="9" t="s">
+        <v>2661</v>
+      </c>
+      <c r="B2265" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2265" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2265" s="12">
+        <v>785577</v>
+      </c>
+      <c r="E2265" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F2265" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2265" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2265" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2266" s="4" t="s">
+        <v>2662</v>
+      </c>
+      <c r="B2266" s="5" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C2266" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2266" s="7">
+        <v>336158</v>
+      </c>
+      <c r="E2266" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F2266" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2266" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2266" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2267" s="9" t="s">
+        <v>2663</v>
+      </c>
+      <c r="B2267" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2267" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2267" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2267" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2267" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2267" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2267" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2268" s="4" t="s">
+        <v>2664</v>
+      </c>
+      <c r="B2268" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2268" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2268" s="7">
+        <v>884801</v>
+      </c>
+      <c r="E2268" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2268" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2268" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2268" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2269" s="9" t="s">
+        <v>2665</v>
+      </c>
+      <c r="B2269" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2269" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2269" s="12">
+        <v>870012</v>
+      </c>
+      <c r="E2269" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F2269" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2269" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2269" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2270" s="4" t="s">
+        <v>2666</v>
+      </c>
+      <c r="B2270" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2270" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2270" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2270" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2270" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2270" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2270" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2271" s="9" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B2271" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2271" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2271" s="12">
+        <v>666428</v>
+      </c>
+      <c r="E2271" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F2271" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2271" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2271" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2272" s="4" t="s">
+        <v>2667</v>
+      </c>
+      <c r="B2272" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2272" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2272" s="7">
+        <v>666428</v>
+      </c>
+      <c r="E2272" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F2272" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2272" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2272" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2273" s="9" t="s">
+        <v>2668</v>
+      </c>
+      <c r="B2273" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2273" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2273" s="12">
+        <v>452920</v>
+      </c>
+      <c r="E2273" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="F2273" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2273" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2273" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2274" s="4" t="s">
+        <v>2669</v>
+      </c>
+      <c r="B2274" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2274" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2274" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2274" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2274" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2274" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2274" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2275" s="9" t="s">
+        <v>2670</v>
+      </c>
+      <c r="B2275" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2275" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2275" s="12">
+        <v>237623</v>
+      </c>
+      <c r="E2275" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2275" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2275" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2275" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2276" s="4" t="s">
+        <v>2671</v>
+      </c>
+      <c r="B2276" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2276" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2276" s="7">
+        <v>716615</v>
+      </c>
+      <c r="E2276" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F2276" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2276" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2276" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2277" s="9" t="s">
+        <v>2672</v>
+      </c>
+      <c r="B2277" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2277" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2277" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2277" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2277" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2277" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2277" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2278" s="4" t="s">
+        <v>2673</v>
+      </c>
+      <c r="B2278" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2278" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2278" s="7">
+        <v>872155</v>
+      </c>
+      <c r="E2278" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2278" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2278" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2278" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2279" s="9" t="s">
+        <v>2674</v>
+      </c>
+      <c r="B2279" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2279" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2279" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2279" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2279" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2279" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2279" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2280" s="4" t="s">
+        <v>2675</v>
+      </c>
+      <c r="B2280" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2280" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2280" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2280" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2280" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2280" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2280" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2281" s="9" t="s">
+        <v>2676</v>
+      </c>
+      <c r="B2281" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2281" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2281" s="12">
+        <v>777905</v>
+      </c>
+      <c r="E2281" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F2281" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2281" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2281" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2282" s="4" t="s">
+        <v>2677</v>
+      </c>
+      <c r="B2282" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2282" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2282" s="7">
+        <v>290021</v>
+      </c>
+      <c r="E2282" s="5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F2282" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2282" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2282" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2283" s="9" t="s">
+        <v>2678</v>
+      </c>
+      <c r="B2283" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2283" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2283" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2283" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2283" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2283" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2283" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2284" s="4" t="s">
+        <v>2679</v>
+      </c>
+      <c r="B2284" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2284" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2284" s="7">
+        <v>165769</v>
+      </c>
+      <c r="E2284" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2284" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2284" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2284" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2285" s="9" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B2285" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C2285" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2285" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E2285" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2285" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2285" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2285" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2286" s="4" t="s">
+        <v>2681</v>
+      </c>
+      <c r="B2286" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2286" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2286" s="7">
+        <v>878851</v>
+      </c>
+      <c r="E2286" s="5" t="s">
+        <v>2357</v>
+      </c>
+      <c r="F2286" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2286" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2286" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2287" s="9" t="s">
+        <v>2682</v>
+      </c>
+      <c r="B2287" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2287" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2287" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2287" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2287" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2287" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2287" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2288" s="4" t="s">
+        <v>2683</v>
+      </c>
+      <c r="B2288" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2288" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2288" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2288" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2288" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2288" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2288" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2289" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2289" s="9" t="s">
+        <v>2684</v>
+      </c>
+      <c r="B2289" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2289" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2289" s="12">
+        <v>866566</v>
+      </c>
+      <c r="E2289" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="F2289" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2289" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2289" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2290" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2290" s="4" t="s">
+        <v>2685</v>
+      </c>
+      <c r="B2290" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2290" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2290" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2290" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2290" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2290" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2290" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2291" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2291" s="9" t="s">
+        <v>2686</v>
+      </c>
+      <c r="B2291" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2291" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2291" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2291" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2291" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2291" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2291" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2292" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2292" s="4" t="s">
+        <v>2687</v>
+      </c>
+      <c r="B2292" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2292" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2292" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2292" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2292" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2292" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2292" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2293" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2293" s="9" t="s">
+        <v>2688</v>
+      </c>
+      <c r="B2293" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2293" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2293" s="12">
+        <v>882357</v>
+      </c>
+      <c r="E2293" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F2293" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2293" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2293" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2294" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2294" s="4" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B2294" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2294" s="6">
+        <v>45845</v>
+      </c>
+      <c r="D2294" s="7">
+        <v>647291</v>
+      </c>
+      <c r="E2294" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2294" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2294" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2294" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2295" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2295" s="9" t="s">
+        <v>2689</v>
+      </c>
+      <c r="B2295" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2295" s="11">
+        <v>45845</v>
+      </c>
+      <c r="D2295" s="12">
+        <v>875515</v>
+      </c>
+      <c r="E2295" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F2295" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2295" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2295" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/crm_dominus/apps/dados/backlog_ativacao.xlsx
+++ b/crm_dominus/apps/dados/backlog_ativacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387895B8-35C9-4F44-8EE3-93D719AFCEEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74919636-AA89-4A0C-A9CA-188913C27BF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1068BE8-6A04-4046-BF81-1D35DD95EA81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13772" uniqueCount="2694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15248" uniqueCount="2948">
   <si>
     <t>Cliente</t>
   </si>
@@ -8116,6 +8116,768 @@
   </si>
   <si>
     <t>ATN - IAI - ANA LUIZA PITALUGA KLEIN</t>
+  </si>
+  <si>
+    <t>Patrick da Costa Almeida</t>
+  </si>
+  <si>
+    <t>SONIA MARIA PREZENCE</t>
+  </si>
+  <si>
+    <t>WELLIGTON TICIANI</t>
+  </si>
+  <si>
+    <t>RICHARD DANIEL MINOZZO DA SILVA</t>
+  </si>
+  <si>
+    <t>LAURA VITÓRIA JACINTO ALVES CARVALHO</t>
+  </si>
+  <si>
+    <t>Sidnei Gonçalveis de Oliveira</t>
+  </si>
+  <si>
+    <t>JANETE MARIA SANTIN</t>
+  </si>
+  <si>
+    <t>João Miguel Dos Santos Padilha</t>
+  </si>
+  <si>
+    <t>Paulo Sérgio Santos Silva</t>
+  </si>
+  <si>
+    <t>DANIELA LETICIA KUPKA DORR</t>
+  </si>
+  <si>
+    <t>Erika Rosa Mello</t>
+  </si>
+  <si>
+    <t>Jhon Kleiber González Dun</t>
+  </si>
+  <si>
+    <t>FERNANDA PEREZ</t>
+  </si>
+  <si>
+    <t>Maria Cristina Taborda Moreira</t>
+  </si>
+  <si>
+    <t>Patrícia Cilene Turmena</t>
+  </si>
+  <si>
+    <t>LUIS LUSSANI</t>
+  </si>
+  <si>
+    <t>DIEGO MAFIOLETTI PEREIRA</t>
+  </si>
+  <si>
+    <t>MARCO AURELIO DA SILVA</t>
+  </si>
+  <si>
+    <t>Wanessa Martins De oliveira</t>
+  </si>
+  <si>
+    <t>ERICSSON CUNHA DE PAULA ANHAIA</t>
+  </si>
+  <si>
+    <t>Rebeca Norbelys Pina Iaya</t>
+  </si>
+  <si>
+    <t>CAMILA CAMARGO WOLFF</t>
+  </si>
+  <si>
+    <t>Michel Amaral de Queiroz</t>
+  </si>
+  <si>
+    <t>ROSA DE FATIMA SCHEIDT DO PRADO</t>
+  </si>
+  <si>
+    <t>Stefanie Cenilia de Souza</t>
+  </si>
+  <si>
+    <t>Osvaldo Salles</t>
+  </si>
+  <si>
+    <t>TAIANE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Lázaro García Linares</t>
+  </si>
+  <si>
+    <t>IEDA MARIA PUHL</t>
+  </si>
+  <si>
+    <t>LAYANE COSTA SILVA</t>
+  </si>
+  <si>
+    <t>Camila Miranda Pereira</t>
+  </si>
+  <si>
+    <t>Marco Aurélio de Assis Oliveira</t>
+  </si>
+  <si>
+    <t>Tatiane dos Santos Garcia</t>
+  </si>
+  <si>
+    <t>Sirlei Aparecida Padilha</t>
+  </si>
+  <si>
+    <t>Vilson Carvalho de Bastos</t>
+  </si>
+  <si>
+    <t>JOSE CARLOS PAGNUSSAT</t>
+  </si>
+  <si>
+    <t>Igor morais da silva</t>
+  </si>
+  <si>
+    <t>Patrícia de Andrade Espindola</t>
+  </si>
+  <si>
+    <t>Hellen Cristine Domingues</t>
+  </si>
+  <si>
+    <t>Jéssica Raiane Dias Jesuino</t>
+  </si>
+  <si>
+    <t>JORGE PAULO NASCIMENTO MAIA</t>
+  </si>
+  <si>
+    <t>Edmilson Lopes Pinto</t>
+  </si>
+  <si>
+    <t>Mateus de Queiroz</t>
+  </si>
+  <si>
+    <t>Julia Ferrazzo</t>
+  </si>
+  <si>
+    <t>ANDREY ROBERTO TOMASI</t>
+  </si>
+  <si>
+    <t>Nelson de Freitas Schultz</t>
+  </si>
+  <si>
+    <t>Ana Paula Schafranski</t>
+  </si>
+  <si>
+    <t>Leonardo Aparecido Mello Ferreira</t>
+  </si>
+  <si>
+    <t>Jackson Antônio Ramos Facchin</t>
+  </si>
+  <si>
+    <t>Mary Janaína Dorneles palmeira</t>
+  </si>
+  <si>
+    <t>Nicole Ferreira duarte</t>
+  </si>
+  <si>
+    <t>Eugênio Kinach</t>
+  </si>
+  <si>
+    <t>JACIRA DE PAULA MARCANTE</t>
+  </si>
+  <si>
+    <t>Maria Aparecida Lima Dos Santos</t>
+  </si>
+  <si>
+    <t>Fernanda Fernandes da Rosa</t>
+  </si>
+  <si>
+    <t>Vera Lucia Lopes Cordeiro</t>
+  </si>
+  <si>
+    <t>CIRLENE APARECIDA BRILHANTE DA SILVA</t>
+  </si>
+  <si>
+    <t>VALDIZIA PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>moisés de oliveira</t>
+  </si>
+  <si>
+    <t>JIMMY JUNIOR FLORES HERNANDEZ</t>
+  </si>
+  <si>
+    <t>Eliane Cristina de Almeida</t>
+  </si>
+  <si>
+    <t>GODIVA DA APARECIDA DA SILVA GOMES</t>
+  </si>
+  <si>
+    <t>Henrique Alexandre Rebouças</t>
+  </si>
+  <si>
+    <t>Guilherme dos Santos</t>
+  </si>
+  <si>
+    <t>LUCIA FATIMA PCHIBILSKI</t>
+  </si>
+  <si>
+    <t>Leticia facenda policena</t>
+  </si>
+  <si>
+    <t>MARINA OLIVEIRA NEQUES</t>
+  </si>
+  <si>
+    <t>WILMER JOSÉ VALLENILLA GAMBOA</t>
+  </si>
+  <si>
+    <t>Diomara pereira dos santos</t>
+  </si>
+  <si>
+    <t>Zenaida Coromoto vizcaíno Salazar</t>
+  </si>
+  <si>
+    <t>Miguel moraes Siqueira</t>
+  </si>
+  <si>
+    <t>Helio Matilde</t>
+  </si>
+  <si>
+    <t>Rafaela Luísa Martinelli</t>
+  </si>
+  <si>
+    <t>ANTONIO NATALICIO RIBEIRO</t>
+  </si>
+  <si>
+    <t>Lindomar junior de Lima Machado</t>
+  </si>
+  <si>
+    <t>DANIELA APARECIDA OLIVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Lucas Jorge Kawanishi</t>
+  </si>
+  <si>
+    <t>GABRIEL FLORENCIO MARQUES</t>
+  </si>
+  <si>
+    <t>FABIANO SILVA DA ROSA</t>
+  </si>
+  <si>
+    <t>Telma Da Silva</t>
+  </si>
+  <si>
+    <t>DANIELA CRISTIANA DOS SANTOS COSTA</t>
+  </si>
+  <si>
+    <t>MARILDA NORTOCA CORREA</t>
+  </si>
+  <si>
+    <t>Márcio Antunes</t>
+  </si>
+  <si>
+    <t>Franciele Battilana</t>
+  </si>
+  <si>
+    <t>Matheus Luan da Conceição de Paula</t>
+  </si>
+  <si>
+    <t>Vanessa Soares Feijó</t>
+  </si>
+  <si>
+    <t>Lucas Mitsoro Oreon Carvalho</t>
+  </si>
+  <si>
+    <t>EVANIA CRISTINA BERNADO DOS PASSOS</t>
+  </si>
+  <si>
+    <t>JHONATAN DUTRA DIHL</t>
+  </si>
+  <si>
+    <t>João Vitor de Castro</t>
+  </si>
+  <si>
+    <t>GENIR ROBERTO VAZ</t>
+  </si>
+  <si>
+    <t>CATHERINE ESTHEFANI TIRADO AVILA</t>
+  </si>
+  <si>
+    <t>Paola Cristina Almeida fruto</t>
+  </si>
+  <si>
+    <t>ANA PAULA FERREIRA MARQUES</t>
+  </si>
+  <si>
+    <t>Nataly Rodrigues de Oliveira</t>
+  </si>
+  <si>
+    <t>Kathleen Noemi Souza da Silva</t>
+  </si>
+  <si>
+    <t>LUIZA DA SILVA GIRARDI</t>
+  </si>
+  <si>
+    <t>ANA JULIA CONTI DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>JORGE AUGUSTO BRASIL DA SILVA</t>
+  </si>
+  <si>
+    <t>Deivid André Pires da Silva</t>
+  </si>
+  <si>
+    <t>Maurício Schimidt Flores</t>
+  </si>
+  <si>
+    <t>GUILHERME HENRIQUE DE OLIVEIRA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>CONJUNTO RESIDENCIAL OURO PRETO</t>
+  </si>
+  <si>
+    <t>MARTA DA SILVA FERREIRA</t>
+  </si>
+  <si>
+    <t>Marcio José de Oliveira</t>
+  </si>
+  <si>
+    <t>ALNOLIS CHIQUINNQUIRA GALLARDO SALAZAR</t>
+  </si>
+  <si>
+    <t>Maria Inês Dias Pereira</t>
+  </si>
+  <si>
+    <t>MARLENE LUIZA DE SOUZA</t>
+  </si>
+  <si>
+    <t>Anderson dos Santos de Lemos</t>
+  </si>
+  <si>
+    <t>LUANA DA COSTA CARPES</t>
+  </si>
+  <si>
+    <t>ALEXANDRA GRUMINSKI</t>
+  </si>
+  <si>
+    <t>MARCELO AZEVEDO DA SILVA</t>
+  </si>
+  <si>
+    <t>Alexsander Leal Corrêa</t>
+  </si>
+  <si>
+    <t>SABEDINA DA SILVA SOARES</t>
+  </si>
+  <si>
+    <t>Micael Lucas de Oliveira Machado</t>
+  </si>
+  <si>
+    <t>TATIANE DE COUTO FONTANA LOPES DIAS</t>
+  </si>
+  <si>
+    <t>MATHEUS ALFREDO MACEDO</t>
+  </si>
+  <si>
+    <t>Valdemir Andrade Correia</t>
+  </si>
+  <si>
+    <t>Eric Ruan kittel</t>
+  </si>
+  <si>
+    <t>Queila Viviane Da Conceição Gomes</t>
+  </si>
+  <si>
+    <t>FERNANDA BORBA GOETTERT</t>
+  </si>
+  <si>
+    <t>ANGÉLICA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Maria aparecida Lima da Silva</t>
+  </si>
+  <si>
+    <t>Natieli da Rosa Fernandes</t>
+  </si>
+  <si>
+    <t>RAFAEL CUOCHINSKI</t>
+  </si>
+  <si>
+    <t>PAULO HENRIQUE COSTA GREIN</t>
+  </si>
+  <si>
+    <t>Douglas Marinho Da Silva</t>
+  </si>
+  <si>
+    <t>Henry Ruan Carriel Alves</t>
+  </si>
+  <si>
+    <t>VERONICA DA SILVA RAMOS</t>
+  </si>
+  <si>
+    <t>ISMAEL SILVA DA SILVA</t>
+  </si>
+  <si>
+    <t>EDINEIA HEIDRICH</t>
+  </si>
+  <si>
+    <t>ANNY GLEDYS VILLARROEL RUIZ</t>
+  </si>
+  <si>
+    <t>Layara thays Silva de Andrade</t>
+  </si>
+  <si>
+    <t>JHONY CAUE COELHO TENORIO</t>
+  </si>
+  <si>
+    <t>Rosemara Mota marin</t>
+  </si>
+  <si>
+    <t>AMANDA AZEVEDO BENINI</t>
+  </si>
+  <si>
+    <t>Amarildo dos Santos Boeira</t>
+  </si>
+  <si>
+    <t>Dienita Maria Rech</t>
+  </si>
+  <si>
+    <t>CLAIDES LOURDES DECKER</t>
+  </si>
+  <si>
+    <t>EVANDRO RAMOS PACHECO</t>
+  </si>
+  <si>
+    <t>Mara justo facchini</t>
+  </si>
+  <si>
+    <t>Angélica Brizola Schultz</t>
+  </si>
+  <si>
+    <t>MICHEL RADESKI RAMOS DA SILVA</t>
+  </si>
+  <si>
+    <t>VANDERLEI JUNIO DAMACENO</t>
+  </si>
+  <si>
+    <t>VITOR AUGUSTO DOS SANTOS MARTINS</t>
+  </si>
+  <si>
+    <t>TERESINHA CLECI DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>João Paulo Dos Santos</t>
+  </si>
+  <si>
+    <t>romario vieira dos santos</t>
+  </si>
+  <si>
+    <t>Jose Clair Francisco</t>
+  </si>
+  <si>
+    <t>CAROLINE PAULA DO NASCIMENTO GOMES</t>
+  </si>
+  <si>
+    <t>Maicon Mader Da Silva</t>
+  </si>
+  <si>
+    <t>jhonattan David patino amarista</t>
+  </si>
+  <si>
+    <t>Elielson Leivas dos Santos</t>
+  </si>
+  <si>
+    <t>LUIZ CARLOS DUARTE</t>
+  </si>
+  <si>
+    <t>JANAINE RAMOS</t>
+  </si>
+  <si>
+    <t>ROSANGELA DIAS DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>RODRIGO UBIRATAN FAURO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Claudinei Fernandes dos Santos</t>
+  </si>
+  <si>
+    <t>Marianne dos Santos Barroso</t>
+  </si>
+  <si>
+    <t>Marcia Dias Souza Nascimento</t>
+  </si>
+  <si>
+    <t>Claudia Fabiana Vieira Machado</t>
+  </si>
+  <si>
+    <t>Lucas mateus silva da rosa</t>
+  </si>
+  <si>
+    <t>BRUNA SILVEIRA MOREIRA</t>
+  </si>
+  <si>
+    <t>MAGDA YUSVELYS MAITAN DIAZ</t>
+  </si>
+  <si>
+    <t>Maria Elizete de Souza</t>
+  </si>
+  <si>
+    <t>Angel Jesus Tovar Malave</t>
+  </si>
+  <si>
+    <t>Francine rodrigues de souza</t>
+  </si>
+  <si>
+    <t>Lucas Mello da Silva</t>
+  </si>
+  <si>
+    <t>MIRIA INEZ KUSSLER PEDREIRAS</t>
+  </si>
+  <si>
+    <t>MARIANE AUZANI REGHELIM</t>
+  </si>
+  <si>
+    <t>FERNANDO HENRIQUE DOS SANTOS LISBOA</t>
+  </si>
+  <si>
+    <t>Sandra Mara Cavalheiro</t>
+  </si>
+  <si>
+    <t>Josias Rodrigues Ribeiro</t>
+  </si>
+  <si>
+    <t>Gabriel Vinícius da Silva Severino</t>
+  </si>
+  <si>
+    <t>Matheus Felipe De Lima Buriti</t>
+  </si>
+  <si>
+    <t>Marjorie elena bejarano suarez</t>
+  </si>
+  <si>
+    <t>KETLIN APARECIDA MENDES</t>
+  </si>
+  <si>
+    <t>Mauro Rodrigues Dias</t>
+  </si>
+  <si>
+    <t>Juceli Antunes Martins</t>
+  </si>
+  <si>
+    <t>Marllon Gomes Rodrigues</t>
+  </si>
+  <si>
+    <t>ANTONIO CARLOS HORNES</t>
+  </si>
+  <si>
+    <t>ROMAR APARECIDO RIBEIRO</t>
+  </si>
+  <si>
+    <t>Geraldo Ferreira da Costa</t>
+  </si>
+  <si>
+    <t>EVA SYCHOCKI</t>
+  </si>
+  <si>
+    <t>AUREA/RS</t>
+  </si>
+  <si>
+    <t>Audria Janine pascoal madeira</t>
+  </si>
+  <si>
+    <t>MICHEL DOUGLAS SANTOS DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>EMILE COSTA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Tatiane getner meincheim</t>
+  </si>
+  <si>
+    <t>Rafaela Ribeiro</t>
+  </si>
+  <si>
+    <t>Angela da Luz Ferreira</t>
+  </si>
+  <si>
+    <t>Loreta Machado</t>
+  </si>
+  <si>
+    <t>ELTON JOAO CARLOS BATISTA</t>
+  </si>
+  <si>
+    <t>Elis Taiane Da Rosa Andrade</t>
+  </si>
+  <si>
+    <t>SILVANO SCORSATTO</t>
+  </si>
+  <si>
+    <t>Orangel Josué Chourio Cedeno</t>
+  </si>
+  <si>
+    <t>José Nereu dos santos</t>
+  </si>
+  <si>
+    <t>Fernanda Cecília Roso Azambuja De Souza</t>
+  </si>
+  <si>
+    <t>Josaine Marlei Brum</t>
+  </si>
+  <si>
+    <t>CENTENARIO/RS</t>
+  </si>
+  <si>
+    <t>Carla Santos de Andrade</t>
+  </si>
+  <si>
+    <t>PATRICIA AIRES DE LIMA</t>
+  </si>
+  <si>
+    <t>Ilde Juarez Diel</t>
+  </si>
+  <si>
+    <t>Eduardo de Mello de Oliveira</t>
+  </si>
+  <si>
+    <t>Guilherme Diehl Feijo</t>
+  </si>
+  <si>
+    <t>Paula Marieli da Rocha</t>
+  </si>
+  <si>
+    <t>Roger Santos da Silva</t>
+  </si>
+  <si>
+    <t>Gabriele canutto</t>
+  </si>
+  <si>
+    <t>Júlia Prestes Peixoto</t>
+  </si>
+  <si>
+    <t>PREF.MUN.DE MARAVILHA-SEC. EDUCACAO</t>
+  </si>
+  <si>
+    <t>Geizi Dos Santos Correa</t>
+  </si>
+  <si>
+    <t>MAURICIO CARVALHO</t>
+  </si>
+  <si>
+    <t>ALAN ROBERT FOLLE MACIEL</t>
+  </si>
+  <si>
+    <t>Jonatan Willian da Silva ireno Rodrigues</t>
+  </si>
+  <si>
+    <t>Gilberto Junior Kobs</t>
+  </si>
+  <si>
+    <t>Micheli Da Rosa Junqueira</t>
+  </si>
+  <si>
+    <t>ALESSANDRA ANDRESA PEREIRA</t>
+  </si>
+  <si>
+    <t>Evelin Kauane Do Amaral</t>
+  </si>
+  <si>
+    <t>Kauã Rodrigo Rodrigues dos Santos</t>
+  </si>
+  <si>
+    <t>MARLI ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Maria Patene</t>
+  </si>
+  <si>
+    <t>Íris De Conto Ávila</t>
+  </si>
+  <si>
+    <t>Leandro Pawlak de Paula</t>
+  </si>
+  <si>
+    <t>Evaldo De Souza Oliveira</t>
+  </si>
+  <si>
+    <t>Antonia hack</t>
+  </si>
+  <si>
+    <t>MICHELE CABRAL NUNES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Fernanda da Silva Dorneles</t>
+  </si>
+  <si>
+    <t>Deivid Henrique Fidelis Eschtiler</t>
+  </si>
+  <si>
+    <t>Bernardete Maria Loncznski Cieslak</t>
+  </si>
+  <si>
+    <t>CARLOS GOMES/RS</t>
+  </si>
+  <si>
+    <t>Edenir Luiza Siqueira</t>
+  </si>
+  <si>
+    <t>Bruna Melo Da Luz</t>
+  </si>
+  <si>
+    <t>LUIZ SOUZA</t>
+  </si>
+  <si>
+    <t>ARROIO GRANDE EMPREENDIMENTO SPE LTDA</t>
+  </si>
+  <si>
+    <t>Everaldo Moreira da Silva</t>
+  </si>
+  <si>
+    <t>GRAZIELE PACHECO ALVES</t>
+  </si>
+  <si>
+    <t>MARIANA NODARI</t>
+  </si>
+  <si>
+    <t>Emilly Cecília Morais Serafim</t>
+  </si>
+  <si>
+    <t>Sabrina Pereira Dos Santos</t>
+  </si>
+  <si>
+    <t>DIEGO DOS SANTOS PORTO</t>
+  </si>
+  <si>
+    <t>JORGE MEDEIROS LANG</t>
+  </si>
+  <si>
+    <t>Marizabel Nascimento de Almeida</t>
+  </si>
+  <si>
+    <t>Fernando Zanella</t>
+  </si>
+  <si>
+    <t>NOVA ITABERABA/SC</t>
+  </si>
+  <si>
+    <t>Heitor Passos dos santos</t>
+  </si>
+  <si>
+    <t>EZEQUIEL JUNIOR FERREIRA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Henryann Da Silva Pinto</t>
+  </si>
+  <si>
+    <t>PAR - STB - PAP - JOY TELECOM - Breno Henrique Turina</t>
+  </si>
+  <si>
+    <t>MAURICIO DE AZAMBUJA SOARES</t>
+  </si>
+  <si>
+    <t>PAR - PAP - CSL - ALLNET - JEAN CARLO LOPES</t>
+  </si>
+  <si>
+    <t>PAR - COM - JCA - TECNOSERVISOLUÇÕES - DAIANA P. R. COSTA</t>
+  </si>
+  <si>
+    <t>PAR - COM - AUW - VICROSKI ELETRÔNICOS - FRANCIELE T. N. V.</t>
+  </si>
+  <si>
+    <t>COM - SSL - LEANDRO TKACZYK RIBEIRO</t>
+  </si>
+  <si>
+    <t>O&amp;M - PYB - TEC - WELLYNGTON FLAVIO DE VARGAS</t>
   </si>
 </sst>
 </file>
@@ -8539,7 +9301,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBE226-2569-43EF-8B89-51B7526D69A9}">
-  <dimension ref="A1:H2295"/>
+  <dimension ref="A1:H2541"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -68215,6 +68977,6402 @@
         <v>87</v>
       </c>
     </row>
+    <row r="2296" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2296" s="4" t="s">
+        <v>2694</v>
+      </c>
+      <c r="B2296" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2296" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2296" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E2296" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2296" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2296" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2296" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2297" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2297" s="9" t="s">
+        <v>2695</v>
+      </c>
+      <c r="B2297" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2297" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2297" s="12">
+        <v>668472</v>
+      </c>
+      <c r="E2297" s="5" t="s">
+        <v>924</v>
+      </c>
+      <c r="F2297" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2297" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2297" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2298" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2298" s="4" t="s">
+        <v>2696</v>
+      </c>
+      <c r="B2298" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2298" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2298" s="7">
+        <v>647350</v>
+      </c>
+      <c r="E2298" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2298" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2298" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2298" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2299" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2299" s="9" t="s">
+        <v>2697</v>
+      </c>
+      <c r="B2299" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2299" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2299" s="12">
+        <v>46617</v>
+      </c>
+      <c r="E2299" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F2299" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2299" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2299" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2300" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2300" s="4" t="s">
+        <v>2698</v>
+      </c>
+      <c r="B2300" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2300" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2300" s="7">
+        <v>6060</v>
+      </c>
+      <c r="E2300" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F2300" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2300" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2300" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2301" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2301" s="9" t="s">
+        <v>2699</v>
+      </c>
+      <c r="B2301" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C2301" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2301" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2301" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2301" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2301" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2301" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2302" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2302" s="4" t="s">
+        <v>2700</v>
+      </c>
+      <c r="B2302" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2302" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2302" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2302" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2302" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2302" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2302" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2303" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2303" s="9" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B2303" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2303" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2303" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2303" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2303" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2303" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2303" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2304" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2304" s="4" t="s">
+        <v>2702</v>
+      </c>
+      <c r="B2304" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2304" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2304" s="7">
+        <v>883823</v>
+      </c>
+      <c r="E2304" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2304" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2304" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2304" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2305" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2305" s="9" t="s">
+        <v>2703</v>
+      </c>
+      <c r="B2305" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2305" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2305" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E2305" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2305" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2305" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2305" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2306" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2306" s="4" t="s">
+        <v>2704</v>
+      </c>
+      <c r="B2306" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2306" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2306" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2306" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2306" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2306" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2306" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2307" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2307" s="9" t="s">
+        <v>2705</v>
+      </c>
+      <c r="B2307" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2307" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2307" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2307" s="5" t="s">
+        <v>2941</v>
+      </c>
+      <c r="F2307" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2307" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2307" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2308" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2308" s="4" t="s">
+        <v>2706</v>
+      </c>
+      <c r="B2308" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C2308" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2308" s="7">
+        <v>857108</v>
+      </c>
+      <c r="E2308" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F2308" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2308" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2308" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2309" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2309" s="9" t="s">
+        <v>2707</v>
+      </c>
+      <c r="B2309" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2309" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2309" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2309" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2309" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2309" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2309" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2310" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2310" s="4" t="s">
+        <v>2708</v>
+      </c>
+      <c r="B2310" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2310" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2310" s="7">
+        <v>213687</v>
+      </c>
+      <c r="E2310" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2310" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2310" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2310" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2311" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2311" s="9" t="s">
+        <v>2709</v>
+      </c>
+      <c r="B2311" s="10" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C2311" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2311" s="12">
+        <v>353572</v>
+      </c>
+      <c r="E2311" s="5" t="s">
+        <v>1554</v>
+      </c>
+      <c r="F2311" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2311" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2311" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2312" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2312" s="4" t="s">
+        <v>2710</v>
+      </c>
+      <c r="B2312" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2312" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2312" s="7">
+        <v>172141</v>
+      </c>
+      <c r="E2312" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2312" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2312" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2312" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2313" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2313" s="9" t="s">
+        <v>2711</v>
+      </c>
+      <c r="B2313" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2313" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2313" s="12">
+        <v>127424</v>
+      </c>
+      <c r="E2313" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2313" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2313" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2313" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2314" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2314" s="4" t="s">
+        <v>2712</v>
+      </c>
+      <c r="B2314" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2314" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2314" s="7">
+        <v>855523</v>
+      </c>
+      <c r="E2314" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="F2314" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2314" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2314" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2315" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2315" s="9" t="s">
+        <v>2713</v>
+      </c>
+      <c r="B2315" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2315" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2315" s="12">
+        <v>875888</v>
+      </c>
+      <c r="E2315" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F2315" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2315" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2315" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2316" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2316" s="4" t="s">
+        <v>2714</v>
+      </c>
+      <c r="B2316" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2316" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2316" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E2316" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2316" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2316" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2316" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2317" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2317" s="9" t="s">
+        <v>2715</v>
+      </c>
+      <c r="B2317" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2317" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2317" s="12">
+        <v>547570</v>
+      </c>
+      <c r="E2317" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="F2317" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2317" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2317" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2318" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2318" s="4" t="s">
+        <v>2716</v>
+      </c>
+      <c r="B2318" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2318" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2318" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E2318" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2318" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2318" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2318" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2319" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2319" s="9" t="s">
+        <v>2717</v>
+      </c>
+      <c r="B2319" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2319" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2319" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E2319" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2319" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2319" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2319" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2320" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2320" s="4" t="s">
+        <v>2718</v>
+      </c>
+      <c r="B2320" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2320" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2320" s="7">
+        <v>36923</v>
+      </c>
+      <c r="E2320" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2320" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2320" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2320" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2321" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2321" s="9" t="s">
+        <v>2719</v>
+      </c>
+      <c r="B2321" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2321" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2321" s="12">
+        <v>835429</v>
+      </c>
+      <c r="E2321" s="5" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F2321" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2321" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2321" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2322" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2322" s="4" t="s">
+        <v>2720</v>
+      </c>
+      <c r="B2322" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2322" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2322" s="7">
+        <v>818285</v>
+      </c>
+      <c r="E2322" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2322" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2322" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2322" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2323" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2323" s="9" t="s">
+        <v>2721</v>
+      </c>
+      <c r="B2323" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2323" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2323" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2323" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2323" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2323" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2323" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2324" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2324" s="4" t="s">
+        <v>2722</v>
+      </c>
+      <c r="B2324" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2324" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2324" s="7">
+        <v>86784</v>
+      </c>
+      <c r="E2324" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F2324" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2324" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2324" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2325" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2325" s="9" t="s">
+        <v>2723</v>
+      </c>
+      <c r="B2325" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2325" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2325" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2325" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2325" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2325" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2325" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2326" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2326" s="4" t="s">
+        <v>2724</v>
+      </c>
+      <c r="B2326" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2326" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2326" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2326" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2326" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2326" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2326" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2327" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2327" s="9" t="s">
+        <v>2725</v>
+      </c>
+      <c r="B2327" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2327" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2327" s="12">
+        <v>862247</v>
+      </c>
+      <c r="E2327" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F2327" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2327" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2327" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2328" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2328" s="4" t="s">
+        <v>2726</v>
+      </c>
+      <c r="B2328" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2328" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2328" s="7">
+        <v>869886</v>
+      </c>
+      <c r="E2328" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F2328" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2328" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2328" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2329" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2329" s="9" t="s">
+        <v>2727</v>
+      </c>
+      <c r="B2329" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2329" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2329" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2329" s="5" t="s">
+        <v>2941</v>
+      </c>
+      <c r="F2329" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2329" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2329" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2330" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2330" s="4" t="s">
+        <v>2536</v>
+      </c>
+      <c r="B2330" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2330" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2330" s="7">
+        <v>255780</v>
+      </c>
+      <c r="E2330" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2330" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2330" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2330" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2331" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2331" s="9" t="s">
+        <v>2728</v>
+      </c>
+      <c r="B2331" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2331" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2331" s="12">
+        <v>802917</v>
+      </c>
+      <c r="E2331" s="5" t="s">
+        <v>2942</v>
+      </c>
+      <c r="F2331" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2331" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2331" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2332" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2332" s="4" t="s">
+        <v>2729</v>
+      </c>
+      <c r="B2332" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2332" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2332" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2332" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2332" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2332" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2332" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2333" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2333" s="9" t="s">
+        <v>2730</v>
+      </c>
+      <c r="B2333" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2333" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2333" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2333" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2333" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2333" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2333" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2334" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2334" s="4" t="s">
+        <v>2731</v>
+      </c>
+      <c r="B2334" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2334" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2334" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2334" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2334" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2334" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2334" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2335" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2335" s="9" t="s">
+        <v>2732</v>
+      </c>
+      <c r="B2335" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2335" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2335" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2335" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2335" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2335" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2335" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2336" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2336" s="4" t="s">
+        <v>2733</v>
+      </c>
+      <c r="B2336" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2336" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2336" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2336" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2336" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2336" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2336" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2337" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2337" s="9" t="s">
+        <v>2734</v>
+      </c>
+      <c r="B2337" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2337" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2337" s="12">
+        <v>741461</v>
+      </c>
+      <c r="E2337" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2337" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2337" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2337" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2338" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2338" s="4" t="s">
+        <v>2735</v>
+      </c>
+      <c r="B2338" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2338" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2338" s="7">
+        <v>844068</v>
+      </c>
+      <c r="E2338" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2338" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2338" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2338" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2339" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2339" s="9" t="s">
+        <v>2736</v>
+      </c>
+      <c r="B2339" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2339" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2339" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2339" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2339" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2339" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2339" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2340" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2340" s="4" t="s">
+        <v>2737</v>
+      </c>
+      <c r="B2340" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2340" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2340" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2340" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2340" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2340" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2340" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2341" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2341" s="9" t="s">
+        <v>2738</v>
+      </c>
+      <c r="B2341" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2341" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2341" s="12">
+        <v>729970</v>
+      </c>
+      <c r="E2341" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2341" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2341" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2341" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2342" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2342" s="4" t="s">
+        <v>2739</v>
+      </c>
+      <c r="B2342" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2342" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2342" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2342" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2342" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2342" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2342" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2343" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2343" s="9" t="s">
+        <v>2740</v>
+      </c>
+      <c r="B2343" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2343" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2343" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2343" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2343" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2343" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2343" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2344" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2344" s="4" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B2344" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2344" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2344" s="7">
+        <v>623344</v>
+      </c>
+      <c r="E2344" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2344" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2344" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2344" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2345" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2345" s="9" t="s">
+        <v>2742</v>
+      </c>
+      <c r="B2345" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2345" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2345" s="12">
+        <v>380291</v>
+      </c>
+      <c r="E2345" s="5" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F2345" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2345" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2345" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2346" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2346" s="4" t="s">
+        <v>2743</v>
+      </c>
+      <c r="B2346" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2346" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2346" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2346" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2346" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2346" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2346" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2347" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2347" s="9" t="s">
+        <v>2744</v>
+      </c>
+      <c r="B2347" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2347" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2347" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2347" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2347" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2347" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2347" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2348" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2348" s="4" t="s">
+        <v>2745</v>
+      </c>
+      <c r="B2348" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2348" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2348" s="7">
+        <v>40828</v>
+      </c>
+      <c r="E2348" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2348" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2348" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2348" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2349" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2349" s="9" t="s">
+        <v>2746</v>
+      </c>
+      <c r="B2349" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2349" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2349" s="12">
+        <v>674036</v>
+      </c>
+      <c r="E2349" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2349" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2349" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2349" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2350" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2350" s="4" t="s">
+        <v>2747</v>
+      </c>
+      <c r="B2350" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2350" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2350" s="7">
+        <v>780838</v>
+      </c>
+      <c r="E2350" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="F2350" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2350" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2350" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2351" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2351" s="9" t="s">
+        <v>2748</v>
+      </c>
+      <c r="B2351" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2351" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2351" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E2351" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2351" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2351" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2351" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2352" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2352" s="4" t="s">
+        <v>2749</v>
+      </c>
+      <c r="B2352" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2352" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2352" s="7">
+        <v>674036</v>
+      </c>
+      <c r="E2352" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2352" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2352" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2352" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2353" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2353" s="9" t="s">
+        <v>2750</v>
+      </c>
+      <c r="B2353" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C2353" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2353" s="12">
+        <v>485228</v>
+      </c>
+      <c r="E2353" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F2353" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2353" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2353" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2354" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2354" s="4" t="s">
+        <v>2751</v>
+      </c>
+      <c r="B2354" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C2354" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2354" s="7">
+        <v>485228</v>
+      </c>
+      <c r="E2354" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F2354" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2354" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2354" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2355" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2355" s="9" t="s">
+        <v>2752</v>
+      </c>
+      <c r="B2355" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2355" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2355" s="12">
+        <v>883815</v>
+      </c>
+      <c r="E2355" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F2355" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2355" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2355" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2356" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2356" s="4" t="s">
+        <v>2753</v>
+      </c>
+      <c r="B2356" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2356" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2356" s="7">
+        <v>706513</v>
+      </c>
+      <c r="E2356" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F2356" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2356" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2356" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2357" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2357" s="9" t="s">
+        <v>2754</v>
+      </c>
+      <c r="B2357" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2357" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2357" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2357" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2357" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2357" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2357" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2358" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2358" s="4" t="s">
+        <v>2755</v>
+      </c>
+      <c r="B2358" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2358" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2358" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2358" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2358" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2358" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2358" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2359" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2359" s="9" t="s">
+        <v>2756</v>
+      </c>
+      <c r="B2359" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2359" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2359" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E2359" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2359" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2359" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2359" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2360" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2360" s="4" t="s">
+        <v>2757</v>
+      </c>
+      <c r="B2360" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2360" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2360" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2360" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2360" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2360" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2360" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2361" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2361" s="9" t="s">
+        <v>2758</v>
+      </c>
+      <c r="B2361" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2361" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2361" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2361" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2361" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2361" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2361" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2362" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2362" s="4" t="s">
+        <v>2759</v>
+      </c>
+      <c r="B2362" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2362" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2362" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2362" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2362" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2362" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2362" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2363" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2363" s="9" t="s">
+        <v>2760</v>
+      </c>
+      <c r="B2363" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2363" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2363" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2363" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2363" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2363" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2363" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2364" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2364" s="4" t="s">
+        <v>2761</v>
+      </c>
+      <c r="B2364" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2364" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2364" s="7">
+        <v>836541</v>
+      </c>
+      <c r="E2364" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2364" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2364" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2364" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2365" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2365" s="9" t="s">
+        <v>2762</v>
+      </c>
+      <c r="B2365" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2365" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2365" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2365" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2365" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2365" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2365" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2366" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2366" s="4" t="s">
+        <v>2763</v>
+      </c>
+      <c r="B2366" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2366" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2366" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2366" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2366" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2366" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2366" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2367" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2367" s="9" t="s">
+        <v>2764</v>
+      </c>
+      <c r="B2367" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2367" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2367" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2367" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2367" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2367" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2367" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2368" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2368" s="4" t="s">
+        <v>2765</v>
+      </c>
+      <c r="B2368" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2368" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2368" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2368" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2368" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2368" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2368" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2369" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2369" s="9" t="s">
+        <v>2766</v>
+      </c>
+      <c r="B2369" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2369" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2369" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2369" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2369" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2369" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2369" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2370" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2370" s="4" t="s">
+        <v>2767</v>
+      </c>
+      <c r="B2370" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2370" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2370" s="7">
+        <v>608931</v>
+      </c>
+      <c r="E2370" s="5" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F2370" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G2370" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2370" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2371" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2371" s="9" t="s">
+        <v>2768</v>
+      </c>
+      <c r="B2371" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2371" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2371" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2371" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2371" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2371" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2371" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2372" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2372" s="4" t="s">
+        <v>2769</v>
+      </c>
+      <c r="B2372" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2372" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2372" s="7">
+        <v>608931</v>
+      </c>
+      <c r="E2372" s="5" t="s">
+        <v>2347</v>
+      </c>
+      <c r="F2372" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G2372" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2372" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2373" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2373" s="9" t="s">
+        <v>2770</v>
+      </c>
+      <c r="B2373" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2373" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2373" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2373" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2373" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2373" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2373" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2374" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2374" s="4" t="s">
+        <v>2771</v>
+      </c>
+      <c r="B2374" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2374" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2374" s="7">
+        <v>405</v>
+      </c>
+      <c r="E2374" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2374" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2374" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2374" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2375" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2375" s="9" t="s">
+        <v>2772</v>
+      </c>
+      <c r="B2375" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2375" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2375" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2375" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2375" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2375" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2375" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2376" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2376" s="4" t="s">
+        <v>2773</v>
+      </c>
+      <c r="B2376" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2376" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2376" s="7">
+        <v>844068</v>
+      </c>
+      <c r="E2376" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2376" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2376" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2376" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2377" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2377" s="9" t="s">
+        <v>2774</v>
+      </c>
+      <c r="B2377" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2377" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2377" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2377" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2377" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2377" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2377" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2378" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2378" s="4" t="s">
+        <v>2775</v>
+      </c>
+      <c r="B2378" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2378" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2378" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2378" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2378" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2378" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2378" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2379" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2379" s="9" t="s">
+        <v>2776</v>
+      </c>
+      <c r="B2379" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2379" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2379" s="12">
+        <v>862715</v>
+      </c>
+      <c r="E2379" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="F2379" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2379" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2379" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2380" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2380" s="4" t="s">
+        <v>2777</v>
+      </c>
+      <c r="B2380" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2380" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2380" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2380" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2380" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2380" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2380" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2381" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2381" s="9" t="s">
+        <v>2778</v>
+      </c>
+      <c r="B2381" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2381" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2381" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2381" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2381" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2381" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2381" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2382" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2382" s="4" t="s">
+        <v>2779</v>
+      </c>
+      <c r="B2382" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2382" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2382" s="7">
+        <v>576159</v>
+      </c>
+      <c r="E2382" s="5" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F2382" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2382" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2382" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2383" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2383" s="9" t="s">
+        <v>2780</v>
+      </c>
+      <c r="B2383" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2383" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2383" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2383" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2383" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2383" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2383" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2384" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2384" s="4" t="s">
+        <v>2781</v>
+      </c>
+      <c r="B2384" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2384" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2384" s="7">
+        <v>824664</v>
+      </c>
+      <c r="E2384" s="5" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F2384" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2384" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2384" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2385" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2385" s="9" t="s">
+        <v>2782</v>
+      </c>
+      <c r="B2385" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2385" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2385" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2385" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2385" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2385" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2385" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2386" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2386" s="4" t="s">
+        <v>2783</v>
+      </c>
+      <c r="B2386" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2386" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2386" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2386" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2386" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2386" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2386" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2387" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2387" s="9" t="s">
+        <v>2784</v>
+      </c>
+      <c r="B2387" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2387" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2387" s="12">
+        <v>863796</v>
+      </c>
+      <c r="E2387" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="F2387" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2387" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2387" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2388" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2388" s="4" t="s">
+        <v>2785</v>
+      </c>
+      <c r="B2388" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2388" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2388" s="7">
+        <v>883815</v>
+      </c>
+      <c r="E2388" s="5" t="s">
+        <v>905</v>
+      </c>
+      <c r="F2388" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2388" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2388" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2389" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2389" s="9" t="s">
+        <v>2786</v>
+      </c>
+      <c r="B2389" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2389" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2389" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2389" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2389" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2389" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2389" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2390" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2390" s="4" t="s">
+        <v>2787</v>
+      </c>
+      <c r="B2390" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2390" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2390" s="7">
+        <v>873105</v>
+      </c>
+      <c r="E2390" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F2390" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2390" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2390" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2391" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2391" s="9" t="s">
+        <v>2788</v>
+      </c>
+      <c r="B2391" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2391" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2391" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2391" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2391" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2391" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2391" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2392" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2392" s="4" t="s">
+        <v>2789</v>
+      </c>
+      <c r="B2392" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2392" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2392" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2392" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2392" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2392" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2392" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2393" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2393" s="9" t="s">
+        <v>2790</v>
+      </c>
+      <c r="B2393" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2393" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2393" s="12">
+        <v>172141</v>
+      </c>
+      <c r="E2393" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2393" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2393" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2393" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2394" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2394" s="4" t="s">
+        <v>2791</v>
+      </c>
+      <c r="B2394" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2394" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2394" s="7">
+        <v>835429</v>
+      </c>
+      <c r="E2394" s="5" t="s">
+        <v>1561</v>
+      </c>
+      <c r="F2394" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2394" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2394" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2395" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2395" s="9" t="s">
+        <v>2792</v>
+      </c>
+      <c r="B2395" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2395" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2395" s="12">
+        <v>329027</v>
+      </c>
+      <c r="E2395" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2395" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2395" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2395" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2396" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2396" s="4" t="s">
+        <v>2793</v>
+      </c>
+      <c r="B2396" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2396" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2396" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2396" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2396" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2396" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2396" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2397" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2397" s="9" t="s">
+        <v>2794</v>
+      </c>
+      <c r="B2397" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2397" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2397" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2397" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2397" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2397" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2397" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2398" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2398" s="4" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B2398" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2398" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2398" s="7">
+        <v>262147</v>
+      </c>
+      <c r="E2398" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2398" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2398" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2398" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2399" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2399" s="9" t="s">
+        <v>2796</v>
+      </c>
+      <c r="B2399" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2399" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2399" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2399" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2399" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2399" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2399" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2400" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2400" s="4" t="s">
+        <v>2797</v>
+      </c>
+      <c r="B2400" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2400" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2400" s="7">
+        <v>858855</v>
+      </c>
+      <c r="E2400" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F2400" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2400" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2400" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2401" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2401" s="9" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B2401" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2401" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2401" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2401" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2401" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2401" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2401" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2402" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2402" s="4" t="s">
+        <v>2799</v>
+      </c>
+      <c r="B2402" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2402" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2402" s="7">
+        <v>382096</v>
+      </c>
+      <c r="E2402" s="5" t="s">
+        <v>1825</v>
+      </c>
+      <c r="F2402" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2402" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2402" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2403" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2403" s="9" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B2403" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2403" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2403" s="12">
+        <v>680982</v>
+      </c>
+      <c r="E2403" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F2403" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2403" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2403" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2404" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2404" s="4" t="s">
+        <v>2801</v>
+      </c>
+      <c r="B2404" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2404" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2404" s="7">
+        <v>706513</v>
+      </c>
+      <c r="E2404" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F2404" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2404" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2404" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2405" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2405" s="9" t="s">
+        <v>2802</v>
+      </c>
+      <c r="B2405" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2405" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2405" s="12">
+        <v>405</v>
+      </c>
+      <c r="E2405" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2405" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2405" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2405" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2406" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2406" s="4" t="s">
+        <v>2803</v>
+      </c>
+      <c r="B2406" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2406" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2406" s="7">
+        <v>878929</v>
+      </c>
+      <c r="E2406" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F2406" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2406" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2406" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2407" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2407" s="9" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B2407" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2407" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2407" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2407" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2407" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2407" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2407" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2408" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2408" s="4" t="s">
+        <v>2805</v>
+      </c>
+      <c r="B2408" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2408" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2408" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2408" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2408" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2408" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2408" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2409" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2409" s="9" t="s">
+        <v>2806</v>
+      </c>
+      <c r="B2409" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2409" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2409" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2409" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2409" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2409" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2409" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2410" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2410" s="4" t="s">
+        <v>2807</v>
+      </c>
+      <c r="B2410" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C2410" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2410" s="7">
+        <v>119776</v>
+      </c>
+      <c r="E2410" s="5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F2410" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2410" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2410" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2411" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2411" s="9" t="s">
+        <v>2808</v>
+      </c>
+      <c r="B2411" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2411" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2411" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2411" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2411" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2411" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2411" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2412" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2412" s="4" t="s">
+        <v>2809</v>
+      </c>
+      <c r="B2412" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2412" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2412" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2412" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2412" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2412" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2412" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2413" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2413" s="9" t="s">
+        <v>2810</v>
+      </c>
+      <c r="B2413" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2413" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2413" s="12">
+        <v>882296</v>
+      </c>
+      <c r="E2413" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2413" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2413" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2413" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2414" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2414" s="4" t="s">
+        <v>2811</v>
+      </c>
+      <c r="B2414" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2414" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2414" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2414" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2414" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2414" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2414" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2415" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2415" s="9" t="s">
+        <v>2812</v>
+      </c>
+      <c r="B2415" s="10" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2415" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2415" s="12">
+        <v>6060</v>
+      </c>
+      <c r="E2415" s="5" t="s">
+        <v>2692</v>
+      </c>
+      <c r="F2415" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2415" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2415" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2416" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2416" s="4" t="s">
+        <v>2813</v>
+      </c>
+      <c r="B2416" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2416" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2416" s="7">
+        <v>725067</v>
+      </c>
+      <c r="E2416" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2416" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2416" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2416" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2417" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2417" s="9" t="s">
+        <v>2814</v>
+      </c>
+      <c r="B2417" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2417" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2417" s="12">
+        <v>736256</v>
+      </c>
+      <c r="E2417" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F2417" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2417" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2417" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2418" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2418" s="4" t="s">
+        <v>2815</v>
+      </c>
+      <c r="B2418" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2418" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2418" s="7">
+        <v>818285</v>
+      </c>
+      <c r="E2418" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2418" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2418" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2418" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2419" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2419" s="9" t="s">
+        <v>2816</v>
+      </c>
+      <c r="B2419" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2419" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2419" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2419" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2419" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2419" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2419" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2420" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2420" s="4" t="s">
+        <v>2817</v>
+      </c>
+      <c r="B2420" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2420" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2420" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2420" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2420" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2420" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2420" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2421" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2421" s="9" t="s">
+        <v>2818</v>
+      </c>
+      <c r="B2421" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2421" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2421" s="12">
+        <v>255780</v>
+      </c>
+      <c r="E2421" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2421" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2421" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2421" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2422" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2422" s="4" t="s">
+        <v>2819</v>
+      </c>
+      <c r="B2422" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2422" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2422" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2422" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2422" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2422" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2422" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2423" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2423" s="9" t="s">
+        <v>2820</v>
+      </c>
+      <c r="B2423" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2423" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2423" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2423" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2423" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2423" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2423" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2424" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2424" s="4" t="s">
+        <v>2821</v>
+      </c>
+      <c r="B2424" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2424" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2424" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2424" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2424" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2424" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2424" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2425" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2425" s="9" t="s">
+        <v>2822</v>
+      </c>
+      <c r="B2425" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2425" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2425" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E2425" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2425" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2425" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2425" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2426" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2426" s="4" t="s">
+        <v>2823</v>
+      </c>
+      <c r="B2426" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2426" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2426" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2426" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2426" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2426" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2426" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2427" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2427" s="9" t="s">
+        <v>2824</v>
+      </c>
+      <c r="B2427" s="10" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C2427" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2427" s="12">
+        <v>857108</v>
+      </c>
+      <c r="E2427" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F2427" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2427" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2427" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2428" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2428" s="4" t="s">
+        <v>2825</v>
+      </c>
+      <c r="B2428" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2428" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2428" s="7">
+        <v>822704</v>
+      </c>
+      <c r="E2428" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F2428" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2428" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2428" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2429" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2429" s="9" t="s">
+        <v>2826</v>
+      </c>
+      <c r="B2429" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2429" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2429" s="12">
+        <v>637113</v>
+      </c>
+      <c r="E2429" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F2429" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2429" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2429" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2430" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2430" s="4" t="s">
+        <v>2827</v>
+      </c>
+      <c r="B2430" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2430" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2430" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2430" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2430" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2430" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2430" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2431" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2431" s="9" t="s">
+        <v>2828</v>
+      </c>
+      <c r="B2431" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2431" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2431" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2431" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2431" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2431" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2431" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2432" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2432" s="4" t="s">
+        <v>2829</v>
+      </c>
+      <c r="B2432" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2432" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2432" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2432" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2432" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2432" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2432" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2433" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2433" s="9" t="s">
+        <v>2830</v>
+      </c>
+      <c r="B2433" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2433" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2433" s="12">
+        <v>405</v>
+      </c>
+      <c r="E2433" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2433" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2433" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2433" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2434" s="4" t="s">
+        <v>2831</v>
+      </c>
+      <c r="B2434" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2434" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2434" s="7">
+        <v>910</v>
+      </c>
+      <c r="E2434" s="5" t="s">
+        <v>2944</v>
+      </c>
+      <c r="F2434" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2434" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2434" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2435" s="9" t="s">
+        <v>2832</v>
+      </c>
+      <c r="B2435" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2435" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2435" s="12">
+        <v>257754</v>
+      </c>
+      <c r="E2435" s="5" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F2435" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2435" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2435" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2436" s="4" t="s">
+        <v>2833</v>
+      </c>
+      <c r="B2436" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2436" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2436" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2436" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2436" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2436" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2436" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2437" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2437" s="9" t="s">
+        <v>2834</v>
+      </c>
+      <c r="B2437" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2437" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2437" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2437" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2437" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2437" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2437" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2438" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2438" s="4" t="s">
+        <v>2835</v>
+      </c>
+      <c r="B2438" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C2438" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2438" s="7">
+        <v>878787</v>
+      </c>
+      <c r="E2438" s="5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F2438" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2438" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2438" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2439" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2439" s="9" t="s">
+        <v>2836</v>
+      </c>
+      <c r="B2439" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2439" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2439" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2439" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2439" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2439" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2439" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2440" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2440" s="4" t="s">
+        <v>2837</v>
+      </c>
+      <c r="B2440" s="5" t="s">
+        <v>742</v>
+      </c>
+      <c r="C2440" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2440" s="7">
+        <v>452920</v>
+      </c>
+      <c r="E2440" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="F2440" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2440" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2440" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2441" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2441" s="9" t="s">
+        <v>2838</v>
+      </c>
+      <c r="B2441" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2441" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2441" s="12">
+        <v>405</v>
+      </c>
+      <c r="E2441" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2441" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2441" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2441" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2442" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2442" s="4" t="s">
+        <v>2839</v>
+      </c>
+      <c r="B2442" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2442" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2442" s="7">
+        <v>883213</v>
+      </c>
+      <c r="E2442" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F2442" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2442" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2442" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2443" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2443" s="9" t="s">
+        <v>2840</v>
+      </c>
+      <c r="B2443" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2443" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2443" s="12">
+        <v>872155</v>
+      </c>
+      <c r="E2443" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2443" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2443" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2443" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2444" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2444" s="4" t="s">
+        <v>2841</v>
+      </c>
+      <c r="B2444" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2444" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2444" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2444" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2444" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2444" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2444" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2445" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2445" s="9" t="s">
+        <v>2842</v>
+      </c>
+      <c r="B2445" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2445" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2445" s="12">
+        <v>874055</v>
+      </c>
+      <c r="E2445" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="F2445" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2445" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2445" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2446" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2446" s="4" t="s">
+        <v>2843</v>
+      </c>
+      <c r="B2446" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2446" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2446" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2446" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2446" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2446" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2446" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2447" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2447" s="9" t="s">
+        <v>2844</v>
+      </c>
+      <c r="B2447" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2447" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2447" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2447" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2447" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2447" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2447" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2448" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2448" s="4" t="s">
+        <v>2845</v>
+      </c>
+      <c r="B2448" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2448" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2448" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E2448" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2448" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2448" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2448" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2449" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2449" s="9" t="s">
+        <v>2846</v>
+      </c>
+      <c r="B2449" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2449" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2449" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2449" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2449" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2449" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2449" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2450" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2450" s="4" t="s">
+        <v>2847</v>
+      </c>
+      <c r="B2450" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2450" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2450" s="7">
+        <v>837970</v>
+      </c>
+      <c r="E2450" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F2450" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2450" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2450" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2451" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2451" s="9" t="s">
+        <v>2848</v>
+      </c>
+      <c r="B2451" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2451" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2451" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2451" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2451" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2451" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2451" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2452" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2452" s="4" t="s">
+        <v>2849</v>
+      </c>
+      <c r="B2452" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2452" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2452" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2452" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2452" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2452" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2452" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2453" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2453" s="9" t="s">
+        <v>2850</v>
+      </c>
+      <c r="B2453" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2453" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2453" s="12">
+        <v>329027</v>
+      </c>
+      <c r="E2453" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2453" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2453" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2453" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2454" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2454" s="4" t="s">
+        <v>2851</v>
+      </c>
+      <c r="B2454" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C2454" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2454" s="7">
+        <v>878856</v>
+      </c>
+      <c r="E2454" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F2454" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2454" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2454" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2455" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2455" s="9" t="s">
+        <v>2852</v>
+      </c>
+      <c r="B2455" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2455" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2455" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2455" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2455" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2455" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2455" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2456" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2456" s="4" t="s">
+        <v>2853</v>
+      </c>
+      <c r="B2456" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C2456" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2456" s="7">
+        <v>828092</v>
+      </c>
+      <c r="E2456" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F2456" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2456" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2456" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2457" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2457" s="9" t="s">
+        <v>2854</v>
+      </c>
+      <c r="B2457" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2457" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2457" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2457" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2457" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2457" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2457" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2458" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2458" s="4" t="s">
+        <v>2855</v>
+      </c>
+      <c r="B2458" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2458" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2458" s="7">
+        <v>560570</v>
+      </c>
+      <c r="E2458" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2458" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2458" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2458" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2459" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2459" s="9" t="s">
+        <v>2856</v>
+      </c>
+      <c r="B2459" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2459" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2459" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E2459" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2459" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2459" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2459" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2460" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2460" s="4" t="s">
+        <v>2857</v>
+      </c>
+      <c r="B2460" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2460" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2460" s="7">
+        <v>741461</v>
+      </c>
+      <c r="E2460" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2460" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2460" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2460" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2461" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2461" s="9" t="s">
+        <v>2858</v>
+      </c>
+      <c r="B2461" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2461" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2461" s="12">
+        <v>882361</v>
+      </c>
+      <c r="E2461" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F2461" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2461" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2461" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2462" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2462" s="4" t="s">
+        <v>2859</v>
+      </c>
+      <c r="B2462" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2462" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2462" s="7">
+        <v>621514</v>
+      </c>
+      <c r="E2462" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="F2462" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2462" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2462" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2463" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2463" s="9" t="s">
+        <v>2860</v>
+      </c>
+      <c r="B2463" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2463" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2463" s="12">
+        <v>886911</v>
+      </c>
+      <c r="E2463" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F2463" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2463" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2463" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2464" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2464" s="4" t="s">
+        <v>2861</v>
+      </c>
+      <c r="B2464" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2464" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2464" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2464" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2464" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2464" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2464" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2465" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2465" s="9" t="s">
+        <v>2862</v>
+      </c>
+      <c r="B2465" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2465" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2465" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2465" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2465" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2465" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2465" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2466" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2466" s="4" t="s">
+        <v>2863</v>
+      </c>
+      <c r="B2466" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2466" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2466" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E2466" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2466" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2466" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2466" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2467" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2467" s="9" t="s">
+        <v>2864</v>
+      </c>
+      <c r="B2467" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2467" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2467" s="12">
+        <v>555881</v>
+      </c>
+      <c r="E2467" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="F2467" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2467" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2467" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2468" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2468" s="4" t="s">
+        <v>2865</v>
+      </c>
+      <c r="B2468" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2468" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2468" s="7">
+        <v>859994</v>
+      </c>
+      <c r="E2468" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F2468" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2468" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2468" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2469" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2469" s="9" t="s">
+        <v>2866</v>
+      </c>
+      <c r="B2469" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C2469" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2469" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2469" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2469" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2469" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2469" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2470" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2470" s="4" t="s">
+        <v>2867</v>
+      </c>
+      <c r="B2470" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2470" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2470" s="7">
+        <v>729970</v>
+      </c>
+      <c r="E2470" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2470" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2470" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2470" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2471" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2471" s="9" t="s">
+        <v>2868</v>
+      </c>
+      <c r="B2471" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="C2471" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2471" s="12">
+        <v>729970</v>
+      </c>
+      <c r="E2471" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2471" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2471" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2471" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2472" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2472" s="4" t="s">
+        <v>2869</v>
+      </c>
+      <c r="B2472" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2472" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2472" s="7">
+        <v>825670</v>
+      </c>
+      <c r="E2472" s="5" t="s">
+        <v>1271</v>
+      </c>
+      <c r="F2472" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2472" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2472" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2473" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2473" s="9" t="s">
+        <v>2870</v>
+      </c>
+      <c r="B2473" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2473" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2473" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2473" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2473" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2473" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2473" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2474" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2474" s="4" t="s">
+        <v>2871</v>
+      </c>
+      <c r="B2474" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2474" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2474" s="7">
+        <v>883823</v>
+      </c>
+      <c r="E2474" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2474" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2474" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2474" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2475" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2475" s="9" t="s">
+        <v>2872</v>
+      </c>
+      <c r="B2475" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2475" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2475" s="12">
+        <v>882361</v>
+      </c>
+      <c r="E2475" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F2475" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2475" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2475" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2476" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2476" s="4" t="s">
+        <v>2873</v>
+      </c>
+      <c r="B2476" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2476" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2476" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2476" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2476" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2476" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2476" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2477" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2477" s="9" t="s">
+        <v>2874</v>
+      </c>
+      <c r="B2477" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2477" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2477" s="12">
+        <v>811237</v>
+      </c>
+      <c r="E2477" s="5" t="s">
+        <v>894</v>
+      </c>
+      <c r="F2477" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2477" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2477" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2478" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2478" s="4" t="s">
+        <v>2875</v>
+      </c>
+      <c r="B2478" s="5" t="s">
+        <v>2654</v>
+      </c>
+      <c r="C2478" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2478" s="7">
+        <v>336158</v>
+      </c>
+      <c r="E2478" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F2478" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2478" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2478" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2479" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2479" s="9" t="s">
+        <v>2876</v>
+      </c>
+      <c r="B2479" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2479" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2479" s="12">
+        <v>619784</v>
+      </c>
+      <c r="E2479" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2479" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2479" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2479" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2480" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2480" s="4" t="s">
+        <v>2877</v>
+      </c>
+      <c r="B2480" s="5" t="s">
+        <v>2878</v>
+      </c>
+      <c r="C2480" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2480" s="7">
+        <v>383260</v>
+      </c>
+      <c r="E2480" s="5" t="s">
+        <v>2945</v>
+      </c>
+      <c r="F2480" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2480" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2480" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2481" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2481" s="9" t="s">
+        <v>2879</v>
+      </c>
+      <c r="B2481" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2481" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2481" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2481" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2481" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2481" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2481" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2482" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2482" s="4" t="s">
+        <v>2880</v>
+      </c>
+      <c r="B2482" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2482" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2482" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2482" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2482" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2482" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2482" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2483" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2483" s="9" t="s">
+        <v>2881</v>
+      </c>
+      <c r="B2483" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2483" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2483" s="12">
+        <v>683063</v>
+      </c>
+      <c r="E2483" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2483" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2483" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2483" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2484" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2484" s="4" t="s">
+        <v>2882</v>
+      </c>
+      <c r="B2484" s="5" t="s">
+        <v>717</v>
+      </c>
+      <c r="C2484" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2484" s="7">
+        <v>683063</v>
+      </c>
+      <c r="E2484" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2484" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2484" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2484" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2485" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2485" s="9" t="s">
+        <v>2883</v>
+      </c>
+      <c r="B2485" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2485" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2485" s="12">
+        <v>576121</v>
+      </c>
+      <c r="E2485" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2485" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2485" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2485" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2486" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2486" s="4" t="s">
+        <v>2884</v>
+      </c>
+      <c r="B2486" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2486" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2486" s="7">
+        <v>619784</v>
+      </c>
+      <c r="E2486" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2486" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2486" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2486" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2487" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2487" s="9" t="s">
+        <v>2885</v>
+      </c>
+      <c r="B2487" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2487" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2487" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E2487" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2487" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2487" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2487" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2488" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2488" s="4" t="s">
+        <v>2886</v>
+      </c>
+      <c r="B2488" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2488" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2488" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2488" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2488" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2488" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2488" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2489" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2489" s="9" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B2489" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2489" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2489" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2489" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2489" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2489" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2489" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2490" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2490" s="4" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B2490" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2490" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2490" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2490" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2490" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2490" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2490" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2491" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2491" s="9" t="s">
+        <v>2889</v>
+      </c>
+      <c r="B2491" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2491" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2491" s="12">
+        <v>177442</v>
+      </c>
+      <c r="E2491" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2491" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2491" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2491" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2492" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2492" s="4" t="s">
+        <v>2890</v>
+      </c>
+      <c r="B2492" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2492" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2492" s="7">
+        <v>682336</v>
+      </c>
+      <c r="E2492" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="F2492" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2492" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2492" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2493" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2493" s="9" t="s">
+        <v>2891</v>
+      </c>
+      <c r="B2493" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2493" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2493" s="12">
+        <v>725067</v>
+      </c>
+      <c r="E2493" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2493" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2493" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2493" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2494" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2494" s="4" t="s">
+        <v>2892</v>
+      </c>
+      <c r="B2494" s="5" t="s">
+        <v>2893</v>
+      </c>
+      <c r="C2494" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2494" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E2494" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2494" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2494" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2494" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2495" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2495" s="9" t="s">
+        <v>2894</v>
+      </c>
+      <c r="B2495" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2495" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2495" s="12">
+        <v>870012</v>
+      </c>
+      <c r="E2495" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F2495" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2495" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2495" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2496" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2496" s="4" t="s">
+        <v>2895</v>
+      </c>
+      <c r="B2496" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2496" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2496" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2496" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2496" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2496" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2496" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2497" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2497" s="9" t="s">
+        <v>2896</v>
+      </c>
+      <c r="B2497" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2497" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2497" s="12">
+        <v>781646</v>
+      </c>
+      <c r="E2497" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2497" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2497" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2497" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2498" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2498" s="4" t="s">
+        <v>2897</v>
+      </c>
+      <c r="B2498" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2498" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2498" s="7">
+        <v>682336</v>
+      </c>
+      <c r="E2498" s="5" t="s">
+        <v>902</v>
+      </c>
+      <c r="F2498" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2498" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2498" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2499" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2499" s="9" t="s">
+        <v>2898</v>
+      </c>
+      <c r="B2499" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2499" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2499" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2499" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2499" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2499" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2499" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2500" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2500" s="4" t="s">
+        <v>2899</v>
+      </c>
+      <c r="B2500" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2500" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2500" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2500" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2500" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2500" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2500" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2501" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2501" s="9" t="s">
+        <v>2900</v>
+      </c>
+      <c r="B2501" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2501" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2501" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2501" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2501" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2501" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2501" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2502" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2502" s="4" t="s">
+        <v>2901</v>
+      </c>
+      <c r="B2502" s="5" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2502" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2502" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2502" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2502" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2502" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2502" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2503" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2503" s="9" t="s">
+        <v>2902</v>
+      </c>
+      <c r="B2503" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2503" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2503" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E2503" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2503" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2503" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2503" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2504" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2504" s="4" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B2504" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2504" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2504" s="7">
+        <v>242745</v>
+      </c>
+      <c r="E2504" s="5" t="s">
+        <v>1567</v>
+      </c>
+      <c r="F2504" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2504" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2504" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2505" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2505" s="9" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B2505" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2505" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2505" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E2505" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F2505" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2505" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2505" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2506" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2506" s="4" t="s">
+        <v>2905</v>
+      </c>
+      <c r="B2506" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2506" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2506" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2506" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2506" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2506" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2506" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2507" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2507" s="9" t="s">
+        <v>2906</v>
+      </c>
+      <c r="B2507" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2507" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2507" s="12">
+        <v>857350</v>
+      </c>
+      <c r="E2507" s="5" t="s">
+        <v>2098</v>
+      </c>
+      <c r="F2507" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2507" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2507" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2508" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2508" s="4" t="s">
+        <v>2907</v>
+      </c>
+      <c r="B2508" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2508" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2508" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E2508" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2508" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2508" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2508" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2509" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2509" s="9" t="s">
+        <v>1846</v>
+      </c>
+      <c r="B2509" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2509" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2509" s="12">
+        <v>872122</v>
+      </c>
+      <c r="E2509" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2509" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2509" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2509" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2510" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2510" s="4" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B2510" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2510" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2510" s="7">
+        <v>884801</v>
+      </c>
+      <c r="E2510" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F2510" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2510" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2510" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2511" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2511" s="9" t="s">
+        <v>2909</v>
+      </c>
+      <c r="B2511" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2511" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2511" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E2511" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2511" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2511" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2511" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2512" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2512" s="4" t="s">
+        <v>2910</v>
+      </c>
+      <c r="B2512" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2512" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2512" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E2512" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2512" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2512" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2512" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2513" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2513" s="9" t="s">
+        <v>2911</v>
+      </c>
+      <c r="B2513" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2513" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2513" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E2513" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2513" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2513" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2513" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2514" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2514" s="4" t="s">
+        <v>2912</v>
+      </c>
+      <c r="B2514" s="5" t="s">
+        <v>1229</v>
+      </c>
+      <c r="C2514" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2514" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2514" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2514" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2514" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2514" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2515" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2515" s="9" t="s">
+        <v>2913</v>
+      </c>
+      <c r="B2515" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2515" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2515" s="12">
+        <v>785577</v>
+      </c>
+      <c r="E2515" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F2515" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2515" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2515" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2516" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2516" s="4" t="s">
+        <v>2914</v>
+      </c>
+      <c r="B2516" s="5" t="s">
+        <v>828</v>
+      </c>
+      <c r="C2516" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2516" s="7">
+        <v>886633</v>
+      </c>
+      <c r="E2516" s="5" t="s">
+        <v>2946</v>
+      </c>
+      <c r="F2516" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="G2516" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2516" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2517" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2517" s="9" t="s">
+        <v>2915</v>
+      </c>
+      <c r="B2517" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2517" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2517" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E2517" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2517" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2517" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2517" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2518" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2518" s="4" t="s">
+        <v>2916</v>
+      </c>
+      <c r="B2518" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C2518" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2518" s="7">
+        <v>619759</v>
+      </c>
+      <c r="E2518" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F2518" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2518" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2518" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2519" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2519" s="9" t="s">
+        <v>2917</v>
+      </c>
+      <c r="B2519" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2519" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2519" s="12">
+        <v>767508</v>
+      </c>
+      <c r="E2519" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2519" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2519" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2519" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2520" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2520" s="4" t="s">
+        <v>2918</v>
+      </c>
+      <c r="B2520" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2520" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2520" s="7">
+        <v>876183</v>
+      </c>
+      <c r="E2520" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F2520" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2520" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2520" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2521" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2521" s="9" t="s">
+        <v>2919</v>
+      </c>
+      <c r="B2521" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2521" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2521" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2521" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2521" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2521" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2521" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2522" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2522" s="4" t="s">
+        <v>2920</v>
+      </c>
+      <c r="B2522" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2522" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2522" s="7">
+        <v>767508</v>
+      </c>
+      <c r="E2522" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F2522" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2522" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2522" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2523" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2523" s="9" t="s">
+        <v>2921</v>
+      </c>
+      <c r="B2523" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2523" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2523" s="12">
+        <v>880152</v>
+      </c>
+      <c r="E2523" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2523" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2523" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2523" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2524" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2524" s="4" t="s">
+        <v>2922</v>
+      </c>
+      <c r="B2524" s="5" t="s">
+        <v>2923</v>
+      </c>
+      <c r="C2524" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2524" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2524" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2524" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2524" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2524" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2525" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2525" s="9" t="s">
+        <v>2924</v>
+      </c>
+      <c r="B2525" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2525" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2525" s="12">
+        <v>872155</v>
+      </c>
+      <c r="E2525" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F2525" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2525" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2525" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2526" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2526" s="4" t="s">
+        <v>2925</v>
+      </c>
+      <c r="B2526" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2526" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2526" s="7">
+        <v>813618</v>
+      </c>
+      <c r="E2526" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F2526" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2526" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2526" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2527" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2527" s="9" t="s">
+        <v>2926</v>
+      </c>
+      <c r="B2527" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2527" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2527" s="12">
+        <v>864113</v>
+      </c>
+      <c r="E2527" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F2527" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2527" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2527" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2528" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2528" s="4" t="s">
+        <v>2927</v>
+      </c>
+      <c r="B2528" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2528" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2528" s="7">
+        <v>818103</v>
+      </c>
+      <c r="E2528" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2528" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2528" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2528" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2529" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2529" s="9" t="s">
+        <v>2928</v>
+      </c>
+      <c r="B2529" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2529" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2529" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2529" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2529" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2529" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2529" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2530" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2530" s="4" t="s">
+        <v>2929</v>
+      </c>
+      <c r="B2530" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2530" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2530" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2530" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2530" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2530" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2530" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2531" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2531" s="9" t="s">
+        <v>2930</v>
+      </c>
+      <c r="B2531" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2531" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2531" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2531" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2531" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2531" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2531" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2532" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2532" s="4" t="s">
+        <v>2931</v>
+      </c>
+      <c r="B2532" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2532" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2532" s="7">
+        <v>878856</v>
+      </c>
+      <c r="E2532" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F2532" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2532" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2532" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2533" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2533" s="9" t="s">
+        <v>2932</v>
+      </c>
+      <c r="B2533" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2533" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2533" s="12">
+        <v>853036</v>
+      </c>
+      <c r="E2533" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="F2533" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2533" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2533" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2534" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2534" s="4" t="s">
+        <v>2933</v>
+      </c>
+      <c r="B2534" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2534" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2534" s="7">
+        <v>872253</v>
+      </c>
+      <c r="E2534" s="5" t="s">
+        <v>2491</v>
+      </c>
+      <c r="F2534" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2534" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2534" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2535" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2535" s="9" t="s">
+        <v>2934</v>
+      </c>
+      <c r="B2535" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2535" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2535" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E2535" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F2535" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2535" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2535" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2536" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2536" s="4" t="s">
+        <v>2935</v>
+      </c>
+      <c r="B2536" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2536" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2536" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E2536" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2536" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2536" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2536" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2537" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2537" s="9" t="s">
+        <v>2936</v>
+      </c>
+      <c r="B2537" s="10" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C2537" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2537" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2537" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2537" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2537" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2537" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2538" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2538" s="4" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B2538" s="5" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C2538" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2538" s="7">
+        <v>647291</v>
+      </c>
+      <c r="E2538" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F2538" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G2538" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2538" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2539" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2539" s="9" t="s">
+        <v>2938</v>
+      </c>
+      <c r="B2539" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2539" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2539" s="12">
+        <v>876282</v>
+      </c>
+      <c r="E2539" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F2539" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2539" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2539" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2540" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2540" s="4" t="s">
+        <v>2939</v>
+      </c>
+      <c r="B2540" s="5" t="s">
+        <v>2937</v>
+      </c>
+      <c r="C2540" s="6">
+        <v>45846</v>
+      </c>
+      <c r="D2540" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2540" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2540" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2540" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2540" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2541" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2541" s="9" t="s">
+        <v>2940</v>
+      </c>
+      <c r="B2541" s="10" t="s">
+        <v>1501</v>
+      </c>
+      <c r="C2541" s="11">
+        <v>45846</v>
+      </c>
+      <c r="D2541" s="12">
+        <v>629688</v>
+      </c>
+      <c r="E2541" s="5" t="s">
+        <v>2947</v>
+      </c>
+      <c r="F2541" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2541" s="10" t="s">
+        <v>2345</v>
+      </c>
+      <c r="H2541" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/crm_dominus/apps/dados/backlog_ativacao.xlsx
+++ b/crm_dominus/apps/dados/backlog_ativacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1069513-7AE6-4894-8909-73B011CB5DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA75B47-041B-4198-8691-E3BB202A49B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1068BE8-6A04-4046-BF81-1D35DD95EA81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16832" uniqueCount="3221">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18248" uniqueCount="3455">
   <si>
     <t>Cliente</t>
   </si>
@@ -8883,9 +8883,6 @@
     <t>ERENIDES FERRER MOREIRA</t>
   </si>
   <si>
-    <t>Gesiele Aparecida de Oliveira Rosa</t>
-  </si>
-  <si>
     <t>VICENTE JONAS PASQUALOTTO</t>
   </si>
   <si>
@@ -9273,9 +9270,6 @@
     <t>Silvia Jorge Ramos</t>
   </si>
   <si>
-    <t>Valdecir de Medeiros</t>
-  </si>
-  <si>
     <t>JOAO LUIZ BORGES DOS NANTOS</t>
   </si>
   <si>
@@ -9697,6 +9691,714 @@
   </si>
   <si>
     <t>YOHANA DE SOUZA BATISTA</t>
+  </si>
+  <si>
+    <t>Gesiane  Aparecida de Oliveira Rosa</t>
+  </si>
+  <si>
+    <t>Valdicir de Medeiros</t>
+  </si>
+  <si>
+    <t>Everton Bertin</t>
+  </si>
+  <si>
+    <t>Serlei Rodrigue da Silva Ribeiro</t>
+  </si>
+  <si>
+    <t>VANUSA SOUTO</t>
+  </si>
+  <si>
+    <t>RICARDO ELSTOR TOILLIER</t>
+  </si>
+  <si>
+    <t>Yegres Alvarez</t>
+  </si>
+  <si>
+    <t>DERIQUI DOS REIS RAASCH</t>
+  </si>
+  <si>
+    <t>Lucimara Dos Santos</t>
+  </si>
+  <si>
+    <t>ALDO CARNEIRO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Paloma Matulle Machado</t>
+  </si>
+  <si>
+    <t>Leonan matos ferraz</t>
+  </si>
+  <si>
+    <t>Regina De Fátima Fernandes Ricardo</t>
+  </si>
+  <si>
+    <t>Sidney Augusto Lopes</t>
+  </si>
+  <si>
+    <t>PAULO SÉRGIO ZEQUIM</t>
+  </si>
+  <si>
+    <t>Rafael Leonardo Paz Soares</t>
+  </si>
+  <si>
+    <t>Maxine santana anziliero</t>
+  </si>
+  <si>
+    <t>Maristela da Rosa</t>
+  </si>
+  <si>
+    <t>MARINÊS TEDESCO SAVI</t>
+  </si>
+  <si>
+    <t>Luiz Carlos Moureira Dos Santos</t>
+  </si>
+  <si>
+    <t>LUCAS DIAS CAMARGO</t>
+  </si>
+  <si>
+    <t>Maiara Dos Santos Rodrigues</t>
+  </si>
+  <si>
+    <t>ARIANE CHAVES MACHADO</t>
+  </si>
+  <si>
+    <t>TALITA VITORIA PONTES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>MIRIAM HATSUE TAKEMOTO</t>
+  </si>
+  <si>
+    <t>Eliane Teresinha Bueno</t>
+  </si>
+  <si>
+    <t>Graziela Souza Da Luz</t>
+  </si>
+  <si>
+    <t>Brendha da silva Camargo</t>
+  </si>
+  <si>
+    <t>Flavio Boeira Silva</t>
+  </si>
+  <si>
+    <t>Diogo do roncio ramos</t>
+  </si>
+  <si>
+    <t>Anderson da Silva Capela</t>
+  </si>
+  <si>
+    <t>Ademir Cavalheiro da Silva</t>
+  </si>
+  <si>
+    <t>VERA LUCIA FALKEMBACH</t>
+  </si>
+  <si>
+    <t>MANOELA ZAMBIASI</t>
+  </si>
+  <si>
+    <t>TEREZINHA RICCI</t>
+  </si>
+  <si>
+    <t>SALETE VERRONICA DALMORA</t>
+  </si>
+  <si>
+    <t>CB - LUCAS FELIPE TEIXEIRA ROSA</t>
+  </si>
+  <si>
+    <t>URSULA VINCKEL</t>
+  </si>
+  <si>
+    <t>ALESON NEURI DE LIMA</t>
+  </si>
+  <si>
+    <t>ANDREZA MORAES BRANCO</t>
+  </si>
+  <si>
+    <t>Odete De Fátima Brilhante</t>
+  </si>
+  <si>
+    <t>LUIS ANTONIO BARETA DE AGUIAR</t>
+  </si>
+  <si>
+    <t>B&amp;B COMERCIO DE PRODUTOS ALIMENTICIOS LTDA</t>
+  </si>
+  <si>
+    <t>Régis Machado Cardoso</t>
+  </si>
+  <si>
+    <t>ELIEZER ALVES FAGUNDES</t>
+  </si>
+  <si>
+    <t>Milena De Oliveira</t>
+  </si>
+  <si>
+    <t>Marise Cristina Rodrigues Foganholo</t>
+  </si>
+  <si>
+    <t>JARDEL MALDANER SCHENK</t>
+  </si>
+  <si>
+    <t>Meiry Cardoso</t>
+  </si>
+  <si>
+    <t>Rosana de los ángeles guzman pino</t>
+  </si>
+  <si>
+    <t>CLEOMAR LAURINDO DA SILVA</t>
+  </si>
+  <si>
+    <t>ANA MARIA SIQUEIRA MUNIZ</t>
+  </si>
+  <si>
+    <t>EVA BORGES DA ROSA</t>
+  </si>
+  <si>
+    <t>Flávio Luís Kristen</t>
+  </si>
+  <si>
+    <t>Rita Aparecida Barbosa</t>
+  </si>
+  <si>
+    <t>GERALDO HONORATO DE PAULA</t>
+  </si>
+  <si>
+    <t>Leonardo Nunes Pereira</t>
+  </si>
+  <si>
+    <t>SOELI DIAS DA LUZ</t>
+  </si>
+  <si>
+    <t>JULIO CESAR WALTER</t>
+  </si>
+  <si>
+    <t>Cleysson Michael Soares da Silva</t>
+  </si>
+  <si>
+    <t>Maria Eduarda da Costa Oliveira</t>
+  </si>
+  <si>
+    <t>CARINA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>Ingrid Pacheco Guimarães</t>
+  </si>
+  <si>
+    <t>Michell de los angeles choez Zambrano</t>
+  </si>
+  <si>
+    <t>Alan Floss Peter</t>
+  </si>
+  <si>
+    <t>Pablo Henrique Pavan</t>
+  </si>
+  <si>
+    <t>Silvia Mara Vaz Das Neves</t>
+  </si>
+  <si>
+    <t>Cláudio Cesar Burgardt</t>
+  </si>
+  <si>
+    <t>Veridiane Gonçalves dos Santos</t>
+  </si>
+  <si>
+    <t>Marli Eva Rodrigues</t>
+  </si>
+  <si>
+    <t>Clarissa Molossi</t>
+  </si>
+  <si>
+    <t>AYMEE PINHEIRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ANA NATALLY GALLIANI</t>
+  </si>
+  <si>
+    <t>Juraci Nunes</t>
+  </si>
+  <si>
+    <t>SARAH MARCIELLA ROGUS</t>
+  </si>
+  <si>
+    <t>Sthefani Kauana Kochenski Cavallini</t>
+  </si>
+  <si>
+    <t>Paulo Rogério Gonçalves Dos Santos</t>
+  </si>
+  <si>
+    <t>UILIAM INACIO CAVRUCOV</t>
+  </si>
+  <si>
+    <t>Nathalia Gomes Rosa</t>
+  </si>
+  <si>
+    <t>Setembrino lemes</t>
+  </si>
+  <si>
+    <t>Mateus Henrique Dos Santos Mendes</t>
+  </si>
+  <si>
+    <t>Elis Regina Alchieri dos Santos</t>
+  </si>
+  <si>
+    <t>Ana Paula Pereira</t>
+  </si>
+  <si>
+    <t>DIRCEU KUHN</t>
+  </si>
+  <si>
+    <t>FABIO FERREIRA</t>
+  </si>
+  <si>
+    <t>Maria De Graça Da Silva</t>
+  </si>
+  <si>
+    <t>LUANA FERNANDES GONÇALVES BELO</t>
+  </si>
+  <si>
+    <t>IND DOS TRAB NAS IND METALURG MECANICA E MATERIAL ELET</t>
+  </si>
+  <si>
+    <t>Gilmar kerppers</t>
+  </si>
+  <si>
+    <t>ISMAEL DOS SANTOS ROSA</t>
+  </si>
+  <si>
+    <t>VILSON PAIDA</t>
+  </si>
+  <si>
+    <t>Luiz Henrique Constâncio Borges</t>
+  </si>
+  <si>
+    <t>ADRIANE MARQUES RIBEIRO</t>
+  </si>
+  <si>
+    <t>Renê Domingues</t>
+  </si>
+  <si>
+    <t>MARIA DAS DORES CRUZ</t>
+  </si>
+  <si>
+    <t>Enson Daniel luces cortez</t>
+  </si>
+  <si>
+    <t>Amanda Aparecida Batista Siebre</t>
+  </si>
+  <si>
+    <t>Conselho de Desenvolvimento de Erechim - Coder</t>
+  </si>
+  <si>
+    <t>Patrícia Da Silva Flores Moraes Dias</t>
+  </si>
+  <si>
+    <t>Schaiane Dietzmann Torres</t>
+  </si>
+  <si>
+    <t>Lúcia Nebikailo de Oliveira</t>
+  </si>
+  <si>
+    <t>Janete leguica dos santos</t>
+  </si>
+  <si>
+    <t>Isabel de Freitas Silveira</t>
+  </si>
+  <si>
+    <t>Victoria Lorenzetti Vidal</t>
+  </si>
+  <si>
+    <t>Sthefani Machado Leal</t>
+  </si>
+  <si>
+    <t>TATIELE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>PRISCILA GIRARDI CAMARGO</t>
+  </si>
+  <si>
+    <t>TAIS CRISTINA CORREA BONFIN</t>
+  </si>
+  <si>
+    <t>BIGUACU/SC</t>
+  </si>
+  <si>
+    <t>CLENIO MOREIRA CASTANON</t>
+  </si>
+  <si>
+    <t>carlos alberto martins</t>
+  </si>
+  <si>
+    <t>ADRIANI CRISTIANI STANGA</t>
+  </si>
+  <si>
+    <t>Cláudio João da Silva</t>
+  </si>
+  <si>
+    <t>Alexandre Rafael Mendes Ferreira</t>
+  </si>
+  <si>
+    <t>ERIQUE FABRICIOS CAMARGO COSTA</t>
+  </si>
+  <si>
+    <t>MICKAELE CORREA</t>
+  </si>
+  <si>
+    <t>Silvana Alves rocha</t>
+  </si>
+  <si>
+    <t>Kauã Gonçalves Lucas</t>
+  </si>
+  <si>
+    <t>KELLY SABRINA DA MAIA</t>
+  </si>
+  <si>
+    <t>ADRIANA ANTONINHA GEDES</t>
+  </si>
+  <si>
+    <t>Franciele dos Santos myszka</t>
+  </si>
+  <si>
+    <t>Rudinei paulo negrini</t>
+  </si>
+  <si>
+    <t>MARLI PAULA DA SILVA</t>
+  </si>
+  <si>
+    <t>DANUZA FATIMA ZANROSSO</t>
+  </si>
+  <si>
+    <t>JULIANO ZINN KETZER</t>
+  </si>
+  <si>
+    <t>Jéssica Rodrigues</t>
+  </si>
+  <si>
+    <t>Elisabete Schardosim Porto Brum</t>
+  </si>
+  <si>
+    <t>Damares Ayres Santos</t>
+  </si>
+  <si>
+    <t>Kauan Wilkem De Andrade Pinheiro</t>
+  </si>
+  <si>
+    <t>Eduardo dos santos zanata</t>
+  </si>
+  <si>
+    <t>SAMANTA DE SOUZA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Domingos Alves Pereira</t>
+  </si>
+  <si>
+    <t>Tinamara Nogueira Santolin</t>
+  </si>
+  <si>
+    <t>Estevão Gonçalves Falero</t>
+  </si>
+  <si>
+    <t>Jovane vitoria de Avila</t>
+  </si>
+  <si>
+    <t>Elias dos Santos</t>
+  </si>
+  <si>
+    <t>Gabriela Corrêa Assunção</t>
+  </si>
+  <si>
+    <t>Dalila Barbosa De Oliveira</t>
+  </si>
+  <si>
+    <t>LEONARDO DOS SANTOS NUNES</t>
+  </si>
+  <si>
+    <t>PAOLA ALINE ARMILIATO MELOTTO</t>
+  </si>
+  <si>
+    <t>Elvira Lima Novaes</t>
+  </si>
+  <si>
+    <t>Carla Adriane De Andrade</t>
+  </si>
+  <si>
+    <t>EVELIN VIANEXIS MARTINEZ HERNANDES</t>
+  </si>
+  <si>
+    <t>Thalya Emanuele dos Anjos</t>
+  </si>
+  <si>
+    <t>Cristiano Tedesco</t>
+  </si>
+  <si>
+    <t>José Benjamin Meza</t>
+  </si>
+  <si>
+    <t>Cleide De Fátima Silva Maciel</t>
+  </si>
+  <si>
+    <t>LUCIANA SALETE CABRAL</t>
+  </si>
+  <si>
+    <t>Terezinha Vargas Seifert</t>
+  </si>
+  <si>
+    <t>Luciene Alves Rodrigues</t>
+  </si>
+  <si>
+    <t>ELIANE DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>RONI FOGAÇA DE LIMA</t>
+  </si>
+  <si>
+    <t>CASSIANO ALEF DA SILVA</t>
+  </si>
+  <si>
+    <t>Paula Amaral de Alencar</t>
+  </si>
+  <si>
+    <t>Patricia da Silva Alves</t>
+  </si>
+  <si>
+    <t>Alessandro Biedermann Do Amaral</t>
+  </si>
+  <si>
+    <t>IZABEL BRUNETTO</t>
+  </si>
+  <si>
+    <t>Adriane Aparecida Da Silva</t>
+  </si>
+  <si>
+    <t>Denise Fernandes Barbosa</t>
+  </si>
+  <si>
+    <t>CLAUDIR ANTONIO CEQUIN</t>
+  </si>
+  <si>
+    <t>Nilton Mendes</t>
+  </si>
+  <si>
+    <t>Gabriel Camargo da Silva</t>
+  </si>
+  <si>
+    <t>Michele Caroline dos Santos Oliveira</t>
+  </si>
+  <si>
+    <t>Jorge Luis Viegas Costa Junior</t>
+  </si>
+  <si>
+    <t>MEIRA DE SANTOS COMERCIO DE EXTINTORES LTD</t>
+  </si>
+  <si>
+    <t>Evelise Da Silveira</t>
+  </si>
+  <si>
+    <t>Maikon brayan Mendes da silva</t>
+  </si>
+  <si>
+    <t>Karem Sabrina Schmitt Martins</t>
+  </si>
+  <si>
+    <t>Stefani da Silva alves</t>
+  </si>
+  <si>
+    <t>Selma Nazaré De Oliveira</t>
+  </si>
+  <si>
+    <t>JOSIANE DE AZEVEDO ALVES</t>
+  </si>
+  <si>
+    <t>VIVIANE RAMOS</t>
+  </si>
+  <si>
+    <t>MARIA APARECIDA DA SILVA MORAES</t>
+  </si>
+  <si>
+    <t>LUIZ FERNANDO ALMEIDA BAIRROS</t>
+  </si>
+  <si>
+    <t>vitor igor do nascimento torri</t>
+  </si>
+  <si>
+    <t>LEONICE DE OLIVEIRA DE LIMA</t>
+  </si>
+  <si>
+    <t>EVERTON DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>Otilia Pacheco Rodrigues</t>
+  </si>
+  <si>
+    <t>RODRIGO SBARDELOTTO PEGORARO</t>
+  </si>
+  <si>
+    <t>Enoir Assunção</t>
+  </si>
+  <si>
+    <t>Camila Martins</t>
+  </si>
+  <si>
+    <t>Ritieli Da Silva</t>
+  </si>
+  <si>
+    <t>Jacson Aloísio priebe</t>
+  </si>
+  <si>
+    <t>Ederson Plate de Souza</t>
+  </si>
+  <si>
+    <t>Alfredo José Borrego Espin</t>
+  </si>
+  <si>
+    <t>Suelen Gabriele Dos Santos Teixeira</t>
+  </si>
+  <si>
+    <t>Breno Moraes Souza</t>
+  </si>
+  <si>
+    <t>MARIA ROSERIA PEREIRA</t>
+  </si>
+  <si>
+    <t>Socorro Aparecida Antônia</t>
+  </si>
+  <si>
+    <t>ADAIR JUNIOR TEIXEIRA</t>
+  </si>
+  <si>
+    <t>DIENIFER DA SILVA CORREA CARDOSO</t>
+  </si>
+  <si>
+    <t>Juciana Luiz Mendes</t>
+  </si>
+  <si>
+    <t>MP POSTO E LOGISTICA LTDA</t>
+  </si>
+  <si>
+    <t>JOAO ADEILDO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Vitória Nilza da Silva dornelles</t>
+  </si>
+  <si>
+    <t>C &amp; C CLINICA MEDICA LTDA</t>
+  </si>
+  <si>
+    <t>Gabriel Roberto Rizzo Koch Lopes</t>
+  </si>
+  <si>
+    <t>Rafael Ceolim Braganholo</t>
+  </si>
+  <si>
+    <t>JOSNEY PEREIRA</t>
+  </si>
+  <si>
+    <t>ODERVAL POSSIDONIO</t>
+  </si>
+  <si>
+    <t>IRACEMINHA/SC</t>
+  </si>
+  <si>
+    <t>Paula Roberta bugs</t>
+  </si>
+  <si>
+    <t>ALEXANDRE DA ROCHA BORGES</t>
+  </si>
+  <si>
+    <t>Ana Julia Nogueira Borges</t>
+  </si>
+  <si>
+    <t>SAO CARLOS/SC</t>
+  </si>
+  <si>
+    <t>Géssica Maria Carvalho Souza</t>
+  </si>
+  <si>
+    <t>Guilherme Farias Zahner</t>
+  </si>
+  <si>
+    <t>MATHEUS DEBASTIANI ZANINI</t>
+  </si>
+  <si>
+    <t>Elivelion da Silva Alemar</t>
+  </si>
+  <si>
+    <t>Camila vitoria batalha de almeida</t>
+  </si>
+  <si>
+    <t>MARIA EDUARDA HICKMANN</t>
+  </si>
+  <si>
+    <t>Leni De Fátima Nunes De Mello</t>
+  </si>
+  <si>
+    <t>NATALIA COLOMBO DA SILVA</t>
+  </si>
+  <si>
+    <t>ALESSANDRA KUFNER VIEIRA</t>
+  </si>
+  <si>
+    <t>Jéssica de Fátima pacheco alves</t>
+  </si>
+  <si>
+    <t>Rangel Mosises Kist</t>
+  </si>
+  <si>
+    <t>Naira Bloss</t>
+  </si>
+  <si>
+    <t>Viviany Freitas Battisti</t>
+  </si>
+  <si>
+    <t>LARISSA PRESTE WIEBBELLING</t>
+  </si>
+  <si>
+    <t>Tânia Gabriel de Brito</t>
+  </si>
+  <si>
+    <t>LILIAN CANELLO</t>
+  </si>
+  <si>
+    <t>Odenir Souza dos Santos</t>
+  </si>
+  <si>
+    <t>MR - FARMA LTDA</t>
+  </si>
+  <si>
+    <t>Joel Saavedra Tabares</t>
+  </si>
+  <si>
+    <t>JEAN MARCOS DOS SANTOS LONGO</t>
+  </si>
+  <si>
+    <t>ALCIDES ALVES BATISTA</t>
+  </si>
+  <si>
+    <t>Gabriela Cardoso De Abreu</t>
+  </si>
+  <si>
+    <t>WHB PUBLICIDADE E PROPAGANDA LTDA</t>
+  </si>
+  <si>
+    <t>RUDINEI LUIS TRENTIN RUBAS</t>
+  </si>
+  <si>
+    <t>Fatima Terezinha M Cardoso</t>
+  </si>
+  <si>
+    <t>Patrícia grefenhagen</t>
+  </si>
+  <si>
+    <t>Dirceu Lemes de Paula</t>
+  </si>
+  <si>
+    <t>VALDIR OSMAR ROTHER</t>
+  </si>
+  <si>
+    <t>O&amp;M - CCO - ATN - LUCAS DE ZORZI</t>
+  </si>
+  <si>
+    <t>COM - UMR - ANA CAROLINA EVANGELISTA</t>
+  </si>
+  <si>
+    <t>PAR - INTE - IRH - INDEL INFORMATICA - TEYLOR NYLAND</t>
   </si>
 </sst>
 </file>
@@ -10120,7 +10822,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBE226-2569-43EF-8B89-51B7526D69A9}">
-  <dimension ref="A1:H2805"/>
+  <dimension ref="A1:H3041"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -76220,7 +76922,7 @@
     </row>
     <row r="2543" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2543" s="9" t="s">
-        <v>2949</v>
+        <v>3219</v>
       </c>
       <c r="B2543" s="10" t="s">
         <v>10</v>
@@ -76246,7 +76948,7 @@
     </row>
     <row r="2544" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2544" s="4" t="s">
-        <v>2950</v>
+        <v>2949</v>
       </c>
       <c r="B2544" s="5" t="s">
         <v>1205</v>
@@ -76272,7 +76974,7 @@
     </row>
     <row r="2545" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2545" s="9" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
       <c r="B2545" s="10" t="s">
         <v>67</v>
@@ -76298,7 +77000,7 @@
     </row>
     <row r="2546" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2546" s="4" t="s">
-        <v>2952</v>
+        <v>2951</v>
       </c>
       <c r="B2546" s="5" t="s">
         <v>34</v>
@@ -76324,7 +77026,7 @@
     </row>
     <row r="2547" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2547" s="9" t="s">
-        <v>2953</v>
+        <v>2952</v>
       </c>
       <c r="B2547" s="10" t="s">
         <v>22</v>
@@ -76350,7 +77052,7 @@
     </row>
     <row r="2548" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2548" s="4" t="s">
-        <v>2954</v>
+        <v>2953</v>
       </c>
       <c r="B2548" s="5" t="s">
         <v>34</v>
@@ -76376,7 +77078,7 @@
     </row>
     <row r="2549" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2549" s="9" t="s">
-        <v>2955</v>
+        <v>2954</v>
       </c>
       <c r="B2549" s="10" t="s">
         <v>34</v>
@@ -76402,7 +77104,7 @@
     </row>
     <row r="2550" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2550" s="4" t="s">
-        <v>2956</v>
+        <v>2955</v>
       </c>
       <c r="B2550" s="5" t="s">
         <v>722</v>
@@ -76428,7 +77130,7 @@
     </row>
     <row r="2551" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2551" s="9" t="s">
-        <v>2957</v>
+        <v>2956</v>
       </c>
       <c r="B2551" s="10" t="s">
         <v>17</v>
@@ -76454,7 +77156,7 @@
     </row>
     <row r="2552" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2552" s="4" t="s">
-        <v>2958</v>
+        <v>2957</v>
       </c>
       <c r="B2552" s="5" t="s">
         <v>8</v>
@@ -76480,7 +77182,7 @@
     </row>
     <row r="2553" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2553" s="9" t="s">
-        <v>2959</v>
+        <v>2958</v>
       </c>
       <c r="B2553" s="10" t="s">
         <v>22</v>
@@ -76506,7 +77208,7 @@
     </row>
     <row r="2554" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2554" s="4" t="s">
-        <v>2960</v>
+        <v>2959</v>
       </c>
       <c r="B2554" s="5" t="s">
         <v>1085</v>
@@ -76532,7 +77234,7 @@
     </row>
     <row r="2555" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2555" s="9" t="s">
-        <v>2961</v>
+        <v>2960</v>
       </c>
       <c r="B2555" s="10" t="s">
         <v>28</v>
@@ -76558,7 +77260,7 @@
     </row>
     <row r="2556" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2556" s="4" t="s">
-        <v>2962</v>
+        <v>2961</v>
       </c>
       <c r="B2556" s="5" t="s">
         <v>19</v>
@@ -76584,7 +77286,7 @@
     </row>
     <row r="2557" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2557" s="9" t="s">
-        <v>2963</v>
+        <v>2962</v>
       </c>
       <c r="B2557" s="10" t="s">
         <v>22</v>
@@ -76610,7 +77312,7 @@
     </row>
     <row r="2558" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2558" s="4" t="s">
-        <v>2964</v>
+        <v>2963</v>
       </c>
       <c r="B2558" s="5" t="s">
         <v>16</v>
@@ -76636,7 +77338,7 @@
     </row>
     <row r="2559" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2559" s="9" t="s">
-        <v>2965</v>
+        <v>2964</v>
       </c>
       <c r="B2559" s="10" t="s">
         <v>35</v>
@@ -76662,7 +77364,7 @@
     </row>
     <row r="2560" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2560" s="4" t="s">
-        <v>2966</v>
+        <v>2965</v>
       </c>
       <c r="B2560" s="5" t="s">
         <v>54</v>
@@ -76688,7 +77390,7 @@
     </row>
     <row r="2561" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2561" s="9" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="B2561" s="10" t="s">
         <v>17</v>
@@ -76714,7 +77416,7 @@
     </row>
     <row r="2562" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2562" s="4" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="B2562" s="5" t="s">
         <v>22</v>
@@ -76726,7 +77428,7 @@
         <v>556838</v>
       </c>
       <c r="E2562" s="5" t="s">
-        <v>3213</v>
+        <v>3211</v>
       </c>
       <c r="F2562" s="5" t="s">
         <v>89</v>
@@ -76740,7 +77442,7 @@
     </row>
     <row r="2563" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2563" s="9" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
       <c r="B2563" s="10" t="s">
         <v>16</v>
@@ -76766,7 +77468,7 @@
     </row>
     <row r="2564" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2564" s="4" t="s">
-        <v>2949</v>
+        <v>3219</v>
       </c>
       <c r="B2564" s="5" t="s">
         <v>10</v>
@@ -76792,7 +77494,7 @@
     </row>
     <row r="2565" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2565" s="9" t="s">
-        <v>2970</v>
+        <v>2969</v>
       </c>
       <c r="B2565" s="10" t="s">
         <v>17</v>
@@ -76818,7 +77520,7 @@
     </row>
     <row r="2566" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2566" s="4" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="B2566" s="5" t="s">
         <v>28</v>
@@ -76844,7 +77546,7 @@
     </row>
     <row r="2567" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2567" s="9" t="s">
-        <v>2972</v>
+        <v>2971</v>
       </c>
       <c r="B2567" s="10" t="s">
         <v>32</v>
@@ -76870,7 +77572,7 @@
     </row>
     <row r="2568" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2568" s="4" t="s">
-        <v>2973</v>
+        <v>2972</v>
       </c>
       <c r="B2568" s="5" t="s">
         <v>29</v>
@@ -76896,7 +77598,7 @@
     </row>
     <row r="2569" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2569" s="9" t="s">
-        <v>2974</v>
+        <v>2973</v>
       </c>
       <c r="B2569" s="10" t="s">
         <v>9</v>
@@ -76922,7 +77624,7 @@
     </row>
     <row r="2570" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2570" s="4" t="s">
-        <v>2975</v>
+        <v>2974</v>
       </c>
       <c r="B2570" s="5" t="s">
         <v>43</v>
@@ -76948,7 +77650,7 @@
     </row>
     <row r="2571" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2571" s="9" t="s">
-        <v>2976</v>
+        <v>2975</v>
       </c>
       <c r="B2571" s="10" t="s">
         <v>22</v>
@@ -76974,7 +77676,7 @@
     </row>
     <row r="2572" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2572" s="4" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="B2572" s="5" t="s">
         <v>43</v>
@@ -77000,7 +77702,7 @@
     </row>
     <row r="2573" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2573" s="9" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="B2573" s="10" t="s">
         <v>16</v>
@@ -77026,7 +77728,7 @@
     </row>
     <row r="2574" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2574" s="4" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
       <c r="B2574" s="5" t="s">
         <v>35</v>
@@ -77052,7 +77754,7 @@
     </row>
     <row r="2575" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2575" s="9" t="s">
-        <v>2980</v>
+        <v>2979</v>
       </c>
       <c r="B2575" s="10" t="s">
         <v>52</v>
@@ -77078,7 +77780,7 @@
     </row>
     <row r="2576" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2576" s="4" t="s">
-        <v>2981</v>
+        <v>2980</v>
       </c>
       <c r="B2576" s="5" t="s">
         <v>51</v>
@@ -77104,7 +77806,7 @@
     </row>
     <row r="2577" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2577" s="9" t="s">
-        <v>2982</v>
+        <v>2981</v>
       </c>
       <c r="B2577" s="10" t="s">
         <v>19</v>
@@ -77130,7 +77832,7 @@
     </row>
     <row r="2578" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2578" s="4" t="s">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="B2578" s="5" t="s">
         <v>58</v>
@@ -77142,7 +77844,7 @@
         <v>771857</v>
       </c>
       <c r="E2578" s="5" t="s">
-        <v>3214</v>
+        <v>3212</v>
       </c>
       <c r="F2578" s="5" t="s">
         <v>126</v>
@@ -77156,7 +77858,7 @@
     </row>
     <row r="2579" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2579" s="9" t="s">
-        <v>2984</v>
+        <v>2983</v>
       </c>
       <c r="B2579" s="10" t="s">
         <v>689</v>
@@ -77182,7 +77884,7 @@
     </row>
     <row r="2580" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2580" s="4" t="s">
-        <v>2985</v>
+        <v>2984</v>
       </c>
       <c r="B2580" s="5" t="s">
         <v>22</v>
@@ -77208,7 +77910,7 @@
     </row>
     <row r="2581" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2581" s="9" t="s">
-        <v>2986</v>
+        <v>2985</v>
       </c>
       <c r="B2581" s="10" t="s">
         <v>23</v>
@@ -77234,7 +77936,7 @@
     </row>
     <row r="2582" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2582" s="4" t="s">
-        <v>2987</v>
+        <v>2986</v>
       </c>
       <c r="B2582" s="5" t="s">
         <v>34</v>
@@ -77260,7 +77962,7 @@
     </row>
     <row r="2583" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2583" s="9" t="s">
-        <v>2988</v>
+        <v>2987</v>
       </c>
       <c r="B2583" s="10" t="s">
         <v>9</v>
@@ -77286,7 +77988,7 @@
     </row>
     <row r="2584" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2584" s="4" t="s">
-        <v>2989</v>
+        <v>2988</v>
       </c>
       <c r="B2584" s="5" t="s">
         <v>17</v>
@@ -77312,7 +78014,7 @@
     </row>
     <row r="2585" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2585" s="9" t="s">
-        <v>2990</v>
+        <v>2989</v>
       </c>
       <c r="B2585" s="10" t="s">
         <v>19</v>
@@ -77338,7 +78040,7 @@
     </row>
     <row r="2586" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2586" s="4" t="s">
-        <v>2991</v>
+        <v>2990</v>
       </c>
       <c r="B2586" s="5" t="s">
         <v>16</v>
@@ -77364,7 +78066,7 @@
     </row>
     <row r="2587" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2587" s="9" t="s">
-        <v>2992</v>
+        <v>2991</v>
       </c>
       <c r="B2587" s="10" t="s">
         <v>54</v>
@@ -77390,7 +78092,7 @@
     </row>
     <row r="2588" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2588" s="4" t="s">
-        <v>2993</v>
+        <v>2992</v>
       </c>
       <c r="B2588" s="5" t="s">
         <v>10</v>
@@ -77416,7 +78118,7 @@
     </row>
     <row r="2589" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2589" s="9" t="s">
-        <v>2994</v>
+        <v>2993</v>
       </c>
       <c r="B2589" s="10" t="s">
         <v>16</v>
@@ -77442,7 +78144,7 @@
     </row>
     <row r="2590" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2590" s="4" t="s">
-        <v>2995</v>
+        <v>2994</v>
       </c>
       <c r="B2590" s="5" t="s">
         <v>22</v>
@@ -77468,7 +78170,7 @@
     </row>
     <row r="2591" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2591" s="9" t="s">
-        <v>2996</v>
+        <v>2995</v>
       </c>
       <c r="B2591" s="10" t="s">
         <v>34</v>
@@ -77494,7 +78196,7 @@
     </row>
     <row r="2592" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2592" s="4" t="s">
-        <v>2997</v>
+        <v>2996</v>
       </c>
       <c r="B2592" s="5" t="s">
         <v>22</v>
@@ -77520,7 +78222,7 @@
     </row>
     <row r="2593" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2593" s="9" t="s">
-        <v>2998</v>
+        <v>2997</v>
       </c>
       <c r="B2593" s="10" t="s">
         <v>1501</v>
@@ -77546,7 +78248,7 @@
     </row>
     <row r="2594" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2594" s="4" t="s">
-        <v>2999</v>
+        <v>2998</v>
       </c>
       <c r="B2594" s="5" t="s">
         <v>11</v>
@@ -77572,7 +78274,7 @@
     </row>
     <row r="2595" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2595" s="9" t="s">
-        <v>3000</v>
+        <v>2999</v>
       </c>
       <c r="B2595" s="10" t="s">
         <v>16</v>
@@ -77598,7 +78300,7 @@
     </row>
     <row r="2596" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2596" s="4" t="s">
-        <v>3001</v>
+        <v>3000</v>
       </c>
       <c r="B2596" s="5" t="s">
         <v>28</v>
@@ -77610,7 +78312,7 @@
         <v>214794</v>
       </c>
       <c r="E2596" s="5" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="F2596" s="5" t="s">
         <v>2347</v>
@@ -77624,7 +78326,7 @@
     </row>
     <row r="2597" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2597" s="9" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="B2597" s="10" t="s">
         <v>67</v>
@@ -77650,7 +78352,7 @@
     </row>
     <row r="2598" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2598" s="4" t="s">
-        <v>3003</v>
+        <v>3002</v>
       </c>
       <c r="B2598" s="5" t="s">
         <v>722</v>
@@ -77676,7 +78378,7 @@
     </row>
     <row r="2599" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2599" s="9" t="s">
-        <v>3004</v>
+        <v>3003</v>
       </c>
       <c r="B2599" s="10" t="s">
         <v>19</v>
@@ -77702,7 +78404,7 @@
     </row>
     <row r="2600" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2600" s="4" t="s">
-        <v>3005</v>
+        <v>3004</v>
       </c>
       <c r="B2600" s="5" t="s">
         <v>1471</v>
@@ -77728,7 +78430,7 @@
     </row>
     <row r="2601" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2601" s="9" t="s">
-        <v>3006</v>
+        <v>3005</v>
       </c>
       <c r="B2601" s="10" t="s">
         <v>632</v>
@@ -77754,7 +78456,7 @@
     </row>
     <row r="2602" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2602" s="4" t="s">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="B2602" s="5" t="s">
         <v>806</v>
@@ -77780,7 +78482,7 @@
     </row>
     <row r="2603" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2603" s="9" t="s">
-        <v>3008</v>
+        <v>3007</v>
       </c>
       <c r="B2603" s="10" t="s">
         <v>22</v>
@@ -77806,7 +78508,7 @@
     </row>
     <row r="2604" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2604" s="4" t="s">
-        <v>3009</v>
+        <v>3008</v>
       </c>
       <c r="B2604" s="5" t="s">
         <v>34</v>
@@ -77832,7 +78534,7 @@
     </row>
     <row r="2605" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2605" s="9" t="s">
-        <v>3010</v>
+        <v>3009</v>
       </c>
       <c r="B2605" s="10" t="s">
         <v>804</v>
@@ -77858,7 +78560,7 @@
     </row>
     <row r="2606" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2606" s="4" t="s">
-        <v>3011</v>
+        <v>3010</v>
       </c>
       <c r="B2606" s="5" t="s">
         <v>9</v>
@@ -77884,7 +78586,7 @@
     </row>
     <row r="2607" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2607" s="9" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="B2607" s="10" t="s">
         <v>1535</v>
@@ -77910,7 +78612,7 @@
     </row>
     <row r="2608" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2608" s="4" t="s">
-        <v>3013</v>
+        <v>3012</v>
       </c>
       <c r="B2608" s="5" t="s">
         <v>34</v>
@@ -77936,7 +78638,7 @@
     </row>
     <row r="2609" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2609" s="9" t="s">
-        <v>3014</v>
+        <v>3013</v>
       </c>
       <c r="B2609" s="10" t="s">
         <v>22</v>
@@ -77962,7 +78664,7 @@
     </row>
     <row r="2610" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2610" s="4" t="s">
-        <v>3015</v>
+        <v>3014</v>
       </c>
       <c r="B2610" s="5" t="s">
         <v>10</v>
@@ -77988,7 +78690,7 @@
     </row>
     <row r="2611" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2611" s="9" t="s">
-        <v>3016</v>
+        <v>3015</v>
       </c>
       <c r="B2611" s="10" t="s">
         <v>10</v>
@@ -78014,7 +78716,7 @@
     </row>
     <row r="2612" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2612" s="4" t="s">
-        <v>3017</v>
+        <v>3016</v>
       </c>
       <c r="B2612" s="5" t="s">
         <v>23</v>
@@ -78040,7 +78742,7 @@
     </row>
     <row r="2613" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2613" s="9" t="s">
-        <v>3018</v>
+        <v>3017</v>
       </c>
       <c r="B2613" s="10" t="s">
         <v>16</v>
@@ -78066,7 +78768,7 @@
     </row>
     <row r="2614" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2614" s="4" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="B2614" s="5" t="s">
         <v>34</v>
@@ -78092,7 +78794,7 @@
     </row>
     <row r="2615" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2615" s="9" t="s">
-        <v>3020</v>
+        <v>3019</v>
       </c>
       <c r="B2615" s="10" t="s">
         <v>16</v>
@@ -78118,7 +78820,7 @@
     </row>
     <row r="2616" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2616" s="4" t="s">
-        <v>3021</v>
+        <v>3020</v>
       </c>
       <c r="B2616" s="5" t="s">
         <v>34</v>
@@ -78144,7 +78846,7 @@
     </row>
     <row r="2617" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2617" s="9" t="s">
-        <v>3022</v>
+        <v>3021</v>
       </c>
       <c r="B2617" s="10" t="s">
         <v>10</v>
@@ -78170,7 +78872,7 @@
     </row>
     <row r="2618" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2618" s="4" t="s">
-        <v>3023</v>
+        <v>3022</v>
       </c>
       <c r="B2618" s="5" t="s">
         <v>11</v>
@@ -78196,7 +78898,7 @@
     </row>
     <row r="2619" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2619" s="9" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="B2619" s="10" t="s">
         <v>28</v>
@@ -78222,7 +78924,7 @@
     </row>
     <row r="2620" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2620" s="4" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="B2620" s="5" t="s">
         <v>16</v>
@@ -78248,7 +78950,7 @@
     </row>
     <row r="2621" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2621" s="9" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
       <c r="B2621" s="10" t="s">
         <v>17</v>
@@ -78274,7 +78976,7 @@
     </row>
     <row r="2622" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2622" s="4" t="s">
-        <v>3027</v>
+        <v>3026</v>
       </c>
       <c r="B2622" s="5" t="s">
         <v>19</v>
@@ -78300,7 +79002,7 @@
     </row>
     <row r="2623" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2623" s="9" t="s">
-        <v>3028</v>
+        <v>3027</v>
       </c>
       <c r="B2623" s="10" t="s">
         <v>8</v>
@@ -78326,7 +79028,7 @@
     </row>
     <row r="2624" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2624" s="4" t="s">
-        <v>3029</v>
+        <v>3028</v>
       </c>
       <c r="B2624" s="5" t="s">
         <v>20</v>
@@ -78352,7 +79054,7 @@
     </row>
     <row r="2625" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2625" s="9" t="s">
-        <v>3030</v>
+        <v>3029</v>
       </c>
       <c r="B2625" s="10" t="s">
         <v>44</v>
@@ -78378,7 +79080,7 @@
     </row>
     <row r="2626" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2626" s="4" t="s">
-        <v>3031</v>
+        <v>3030</v>
       </c>
       <c r="B2626" s="5" t="s">
         <v>804</v>
@@ -78404,7 +79106,7 @@
     </row>
     <row r="2627" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2627" s="9" t="s">
-        <v>3032</v>
+        <v>3031</v>
       </c>
       <c r="B2627" s="10" t="s">
         <v>20</v>
@@ -78430,7 +79132,7 @@
     </row>
     <row r="2628" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2628" s="4" t="s">
-        <v>3033</v>
+        <v>3032</v>
       </c>
       <c r="B2628" s="5" t="s">
         <v>22</v>
@@ -78456,7 +79158,7 @@
     </row>
     <row r="2629" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2629" s="9" t="s">
-        <v>3034</v>
+        <v>3033</v>
       </c>
       <c r="B2629" s="10" t="s">
         <v>30</v>
@@ -78482,7 +79184,7 @@
     </row>
     <row r="2630" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2630" s="4" t="s">
-        <v>3035</v>
+        <v>3034</v>
       </c>
       <c r="B2630" s="5" t="s">
         <v>19</v>
@@ -78508,7 +79210,7 @@
     </row>
     <row r="2631" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2631" s="9" t="s">
-        <v>3036</v>
+        <v>3035</v>
       </c>
       <c r="B2631" s="10" t="s">
         <v>33</v>
@@ -78534,7 +79236,7 @@
     </row>
     <row r="2632" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2632" s="4" t="s">
-        <v>3037</v>
+        <v>3036</v>
       </c>
       <c r="B2632" s="5" t="s">
         <v>56</v>
@@ -78560,7 +79262,7 @@
     </row>
     <row r="2633" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2633" s="9" t="s">
-        <v>3038</v>
+        <v>3037</v>
       </c>
       <c r="B2633" s="10" t="s">
         <v>22</v>
@@ -78586,7 +79288,7 @@
     </row>
     <row r="2634" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2634" s="4" t="s">
-        <v>3039</v>
+        <v>3038</v>
       </c>
       <c r="B2634" s="5" t="s">
         <v>48</v>
@@ -78598,7 +79300,7 @@
         <v>872366</v>
       </c>
       <c r="E2634" s="5" t="s">
-        <v>3216</v>
+        <v>3214</v>
       </c>
       <c r="F2634" s="5" t="s">
         <v>94</v>
@@ -78612,7 +79314,7 @@
     </row>
     <row r="2635" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2635" s="9" t="s">
-        <v>3040</v>
+        <v>3039</v>
       </c>
       <c r="B2635" s="10" t="s">
         <v>22</v>
@@ -78638,7 +79340,7 @@
     </row>
     <row r="2636" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2636" s="4" t="s">
-        <v>3041</v>
+        <v>3040</v>
       </c>
       <c r="B2636" s="5" t="s">
         <v>55</v>
@@ -78664,7 +79366,7 @@
     </row>
     <row r="2637" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2637" s="9" t="s">
-        <v>3042</v>
+        <v>3041</v>
       </c>
       <c r="B2637" s="10" t="s">
         <v>22</v>
@@ -78690,7 +79392,7 @@
     </row>
     <row r="2638" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2638" s="4" t="s">
-        <v>3043</v>
+        <v>3042</v>
       </c>
       <c r="B2638" s="5" t="s">
         <v>15</v>
@@ -78716,7 +79418,7 @@
     </row>
     <row r="2639" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2639" s="9" t="s">
-        <v>3044</v>
+        <v>3043</v>
       </c>
       <c r="B2639" s="10" t="s">
         <v>22</v>
@@ -78742,7 +79444,7 @@
     </row>
     <row r="2640" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2640" s="4" t="s">
-        <v>3045</v>
+        <v>3044</v>
       </c>
       <c r="B2640" s="5" t="s">
         <v>31</v>
@@ -78768,7 +79470,7 @@
     </row>
     <row r="2641" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2641" s="9" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
       <c r="B2641" s="10" t="s">
         <v>49</v>
@@ -78794,7 +79496,7 @@
     </row>
     <row r="2642" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2642" s="4" t="s">
-        <v>3047</v>
+        <v>3046</v>
       </c>
       <c r="B2642" s="5" t="s">
         <v>28</v>
@@ -78820,7 +79522,7 @@
     </row>
     <row r="2643" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2643" s="9" t="s">
-        <v>3048</v>
+        <v>3047</v>
       </c>
       <c r="B2643" s="10" t="s">
         <v>16</v>
@@ -78846,7 +79548,7 @@
     </row>
     <row r="2644" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2644" s="4" t="s">
-        <v>3049</v>
+        <v>3048</v>
       </c>
       <c r="B2644" s="5" t="s">
         <v>28</v>
@@ -78872,7 +79574,7 @@
     </row>
     <row r="2645" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2645" s="9" t="s">
-        <v>3050</v>
+        <v>3049</v>
       </c>
       <c r="B2645" s="10" t="s">
         <v>32</v>
@@ -78898,7 +79600,7 @@
     </row>
     <row r="2646" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2646" s="4" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="B2646" s="5" t="s">
         <v>35</v>
@@ -78924,7 +79626,7 @@
     </row>
     <row r="2647" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2647" s="9" t="s">
-        <v>3052</v>
+        <v>3051</v>
       </c>
       <c r="B2647" s="10" t="s">
         <v>18</v>
@@ -78950,7 +79652,7 @@
     </row>
     <row r="2648" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2648" s="4" t="s">
-        <v>3053</v>
+        <v>3052</v>
       </c>
       <c r="B2648" s="5" t="s">
         <v>16</v>
@@ -78976,7 +79678,7 @@
     </row>
     <row r="2649" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2649" s="9" t="s">
-        <v>3054</v>
+        <v>3053</v>
       </c>
       <c r="B2649" s="10" t="s">
         <v>8</v>
@@ -79002,7 +79704,7 @@
     </row>
     <row r="2650" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2650" s="4" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="B2650" s="5" t="s">
         <v>18</v>
@@ -79028,7 +79730,7 @@
     </row>
     <row r="2651" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2651" s="9" t="s">
-        <v>3056</v>
+        <v>3055</v>
       </c>
       <c r="B2651" s="10" t="s">
         <v>28</v>
@@ -79040,7 +79742,7 @@
         <v>214794</v>
       </c>
       <c r="E2651" s="5" t="s">
-        <v>3215</v>
+        <v>3213</v>
       </c>
       <c r="F2651" s="5" t="s">
         <v>2347</v>
@@ -79054,7 +79756,7 @@
     </row>
     <row r="2652" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2652" s="4" t="s">
-        <v>3057</v>
+        <v>3056</v>
       </c>
       <c r="B2652" s="5" t="s">
         <v>22</v>
@@ -79080,7 +79782,7 @@
     </row>
     <row r="2653" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2653" s="9" t="s">
-        <v>3058</v>
+        <v>3057</v>
       </c>
       <c r="B2653" s="10" t="s">
         <v>19</v>
@@ -79106,7 +79808,7 @@
     </row>
     <row r="2654" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2654" s="4" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="B2654" s="5" t="s">
         <v>45</v>
@@ -79132,7 +79834,7 @@
     </row>
     <row r="2655" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2655" s="9" t="s">
-        <v>3060</v>
+        <v>3059</v>
       </c>
       <c r="B2655" s="10" t="s">
         <v>47</v>
@@ -79158,7 +79860,7 @@
     </row>
     <row r="2656" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2656" s="4" t="s">
-        <v>3061</v>
+        <v>3060</v>
       </c>
       <c r="B2656" s="5" t="s">
         <v>632</v>
@@ -79184,7 +79886,7 @@
     </row>
     <row r="2657" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2657" s="9" t="s">
-        <v>3062</v>
+        <v>3061</v>
       </c>
       <c r="B2657" s="10" t="s">
         <v>10</v>
@@ -79210,7 +79912,7 @@
     </row>
     <row r="2658" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2658" s="4" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="B2658" s="5" t="s">
         <v>19</v>
@@ -79236,7 +79938,7 @@
     </row>
     <row r="2659" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2659" s="9" t="s">
-        <v>3064</v>
+        <v>3063</v>
       </c>
       <c r="B2659" s="10" t="s">
         <v>44</v>
@@ -79262,7 +79964,7 @@
     </row>
     <row r="2660" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2660" s="4" t="s">
-        <v>3065</v>
+        <v>3064</v>
       </c>
       <c r="B2660" s="5" t="s">
         <v>25</v>
@@ -79288,7 +79990,7 @@
     </row>
     <row r="2661" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2661" s="9" t="s">
-        <v>3066</v>
+        <v>3065</v>
       </c>
       <c r="B2661" s="10" t="s">
         <v>18</v>
@@ -79314,7 +80016,7 @@
     </row>
     <row r="2662" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2662" s="4" t="s">
-        <v>3067</v>
+        <v>3066</v>
       </c>
       <c r="B2662" s="5" t="s">
         <v>13</v>
@@ -79340,7 +80042,7 @@
     </row>
     <row r="2663" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2663" s="9" t="s">
-        <v>3068</v>
+        <v>3067</v>
       </c>
       <c r="B2663" s="10" t="s">
         <v>15</v>
@@ -79366,7 +80068,7 @@
     </row>
     <row r="2664" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2664" s="4" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
       <c r="B2664" s="5" t="s">
         <v>13</v>
@@ -79392,7 +80094,7 @@
     </row>
     <row r="2665" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2665" s="9" t="s">
-        <v>3070</v>
+        <v>3069</v>
       </c>
       <c r="B2665" s="10" t="s">
         <v>45</v>
@@ -79418,7 +80120,7 @@
     </row>
     <row r="2666" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2666" s="4" t="s">
-        <v>3071</v>
+        <v>3070</v>
       </c>
       <c r="B2666" s="5" t="s">
         <v>33</v>
@@ -79444,7 +80146,7 @@
     </row>
     <row r="2667" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2667" s="9" t="s">
-        <v>3072</v>
+        <v>3071</v>
       </c>
       <c r="B2667" s="10" t="s">
         <v>9</v>
@@ -79470,7 +80172,7 @@
     </row>
     <row r="2668" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2668" s="4" t="s">
-        <v>3073</v>
+        <v>3072</v>
       </c>
       <c r="B2668" s="5" t="s">
         <v>34</v>
@@ -79496,7 +80198,7 @@
     </row>
     <row r="2669" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2669" s="9" t="s">
-        <v>3074</v>
+        <v>3073</v>
       </c>
       <c r="B2669" s="10" t="s">
         <v>16</v>
@@ -79522,7 +80224,7 @@
     </row>
     <row r="2670" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2670" s="4" t="s">
-        <v>3075</v>
+        <v>3074</v>
       </c>
       <c r="B2670" s="5" t="s">
         <v>17</v>
@@ -79548,7 +80250,7 @@
     </row>
     <row r="2671" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2671" s="9" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="B2671" s="10" t="s">
         <v>13</v>
@@ -79574,7 +80276,7 @@
     </row>
     <row r="2672" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2672" s="4" t="s">
-        <v>3077</v>
+        <v>3076</v>
       </c>
       <c r="B2672" s="5" t="s">
         <v>63</v>
@@ -79586,7 +80288,7 @@
         <v>889186</v>
       </c>
       <c r="E2672" s="5" t="s">
-        <v>3217</v>
+        <v>3215</v>
       </c>
       <c r="F2672" s="5" t="s">
         <v>2347</v>
@@ -79600,7 +80302,7 @@
     </row>
     <row r="2673" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2673" s="9" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
       <c r="B2673" s="10" t="s">
         <v>33</v>
@@ -79626,7 +80328,7 @@
     </row>
     <row r="2674" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2674" s="4" t="s">
-        <v>3079</v>
+        <v>3220</v>
       </c>
       <c r="B2674" s="5" t="s">
         <v>33</v>
@@ -79652,7 +80354,7 @@
     </row>
     <row r="2675" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2675" s="9" t="s">
-        <v>3080</v>
+        <v>3078</v>
       </c>
       <c r="B2675" s="10" t="s">
         <v>22</v>
@@ -79678,7 +80380,7 @@
     </row>
     <row r="2676" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2676" s="4" t="s">
-        <v>3081</v>
+        <v>3079</v>
       </c>
       <c r="B2676" s="5" t="s">
         <v>22</v>
@@ -79704,7 +80406,7 @@
     </row>
     <row r="2677" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2677" s="9" t="s">
-        <v>3082</v>
+        <v>3080</v>
       </c>
       <c r="B2677" s="10" t="s">
         <v>44</v>
@@ -79730,7 +80432,7 @@
     </row>
     <row r="2678" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2678" s="4" t="s">
-        <v>3083</v>
+        <v>3081</v>
       </c>
       <c r="B2678" s="5" t="s">
         <v>49</v>
@@ -79756,7 +80458,7 @@
     </row>
     <row r="2679" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2679" s="9" t="s">
-        <v>3084</v>
+        <v>3082</v>
       </c>
       <c r="B2679" s="10" t="s">
         <v>44</v>
@@ -79782,7 +80484,7 @@
     </row>
     <row r="2680" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2680" s="4" t="s">
-        <v>3085</v>
+        <v>3083</v>
       </c>
       <c r="B2680" s="5" t="s">
         <v>31</v>
@@ -79808,7 +80510,7 @@
     </row>
     <row r="2681" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2681" s="9" t="s">
-        <v>3086</v>
+        <v>3084</v>
       </c>
       <c r="B2681" s="10" t="s">
         <v>40</v>
@@ -79834,7 +80536,7 @@
     </row>
     <row r="2682" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2682" s="4" t="s">
-        <v>3087</v>
+        <v>3085</v>
       </c>
       <c r="B2682" s="5" t="s">
         <v>34</v>
@@ -79860,7 +80562,7 @@
     </row>
     <row r="2683" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2683" s="9" t="s">
-        <v>3088</v>
+        <v>3086</v>
       </c>
       <c r="B2683" s="10" t="s">
         <v>13</v>
@@ -79886,7 +80588,7 @@
     </row>
     <row r="2684" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2684" s="4" t="s">
-        <v>3089</v>
+        <v>3087</v>
       </c>
       <c r="B2684" s="5" t="s">
         <v>35</v>
@@ -79912,7 +80614,7 @@
     </row>
     <row r="2685" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2685" s="9" t="s">
-        <v>3090</v>
+        <v>3088</v>
       </c>
       <c r="B2685" s="10" t="s">
         <v>22</v>
@@ -79938,7 +80640,7 @@
     </row>
     <row r="2686" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2686" s="4" t="s">
-        <v>3091</v>
+        <v>3089</v>
       </c>
       <c r="B2686" s="5" t="s">
         <v>19</v>
@@ -79964,7 +80666,7 @@
     </row>
     <row r="2687" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2687" s="9" t="s">
-        <v>3092</v>
+        <v>3090</v>
       </c>
       <c r="B2687" s="10" t="s">
         <v>45</v>
@@ -79990,7 +80692,7 @@
     </row>
     <row r="2688" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2688" s="4" t="s">
-        <v>3093</v>
+        <v>3091</v>
       </c>
       <c r="B2688" s="5" t="s">
         <v>44</v>
@@ -80016,7 +80718,7 @@
     </row>
     <row r="2689" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2689" s="9" t="s">
-        <v>3094</v>
+        <v>3092</v>
       </c>
       <c r="B2689" s="10" t="s">
         <v>23</v>
@@ -80042,7 +80744,7 @@
     </row>
     <row r="2690" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2690" s="4" t="s">
-        <v>3095</v>
+        <v>3093</v>
       </c>
       <c r="B2690" s="5" t="s">
         <v>59</v>
@@ -80068,7 +80770,7 @@
     </row>
     <row r="2691" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2691" s="9" t="s">
-        <v>3096</v>
+        <v>3094</v>
       </c>
       <c r="B2691" s="10" t="s">
         <v>1471</v>
@@ -80094,7 +80796,7 @@
     </row>
     <row r="2692" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2692" s="4" t="s">
-        <v>3097</v>
+        <v>3095</v>
       </c>
       <c r="B2692" s="5" t="s">
         <v>822</v>
@@ -80120,7 +80822,7 @@
     </row>
     <row r="2693" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2693" s="9" t="s">
-        <v>3098</v>
+        <v>3096</v>
       </c>
       <c r="B2693" s="10" t="s">
         <v>22</v>
@@ -80146,7 +80848,7 @@
     </row>
     <row r="2694" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2694" s="4" t="s">
-        <v>3099</v>
+        <v>3097</v>
       </c>
       <c r="B2694" s="5" t="s">
         <v>56</v>
@@ -80172,7 +80874,7 @@
     </row>
     <row r="2695" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2695" s="9" t="s">
-        <v>3100</v>
+        <v>3098</v>
       </c>
       <c r="B2695" s="10" t="s">
         <v>46</v>
@@ -80198,7 +80900,7 @@
     </row>
     <row r="2696" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2696" s="4" t="s">
-        <v>3101</v>
+        <v>3099</v>
       </c>
       <c r="B2696" s="5" t="s">
         <v>13</v>
@@ -80224,7 +80926,7 @@
     </row>
     <row r="2697" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2697" s="9" t="s">
-        <v>3102</v>
+        <v>3100</v>
       </c>
       <c r="B2697" s="10" t="s">
         <v>37</v>
@@ -80250,7 +80952,7 @@
     </row>
     <row r="2698" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2698" s="4" t="s">
-        <v>3103</v>
+        <v>3101</v>
       </c>
       <c r="B2698" s="5" t="s">
         <v>49</v>
@@ -80276,7 +80978,7 @@
     </row>
     <row r="2699" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2699" s="9" t="s">
-        <v>3104</v>
+        <v>3102</v>
       </c>
       <c r="B2699" s="10" t="s">
         <v>13</v>
@@ -80302,7 +81004,7 @@
     </row>
     <row r="2700" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2700" s="4" t="s">
-        <v>3105</v>
+        <v>3103</v>
       </c>
       <c r="B2700" s="5" t="s">
         <v>10</v>
@@ -80328,7 +81030,7 @@
     </row>
     <row r="2701" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2701" s="9" t="s">
-        <v>3106</v>
+        <v>3104</v>
       </c>
       <c r="B2701" s="10" t="s">
         <v>19</v>
@@ -80354,7 +81056,7 @@
     </row>
     <row r="2702" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2702" s="4" t="s">
-        <v>3107</v>
+        <v>3105</v>
       </c>
       <c r="B2702" s="5" t="s">
         <v>8</v>
@@ -80380,7 +81082,7 @@
     </row>
     <row r="2703" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2703" s="9" t="s">
-        <v>3108</v>
+        <v>3106</v>
       </c>
       <c r="B2703" s="10" t="s">
         <v>34</v>
@@ -80406,7 +81108,7 @@
     </row>
     <row r="2704" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2704" s="4" t="s">
-        <v>3109</v>
+        <v>3107</v>
       </c>
       <c r="B2704" s="5" t="s">
         <v>29</v>
@@ -80432,7 +81134,7 @@
     </row>
     <row r="2705" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2705" s="9" t="s">
-        <v>3110</v>
+        <v>3108</v>
       </c>
       <c r="B2705" s="10" t="s">
         <v>632</v>
@@ -80458,7 +81160,7 @@
     </row>
     <row r="2706" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2706" s="4" t="s">
-        <v>3111</v>
+        <v>3109</v>
       </c>
       <c r="B2706" s="5" t="s">
         <v>17</v>
@@ -80484,7 +81186,7 @@
     </row>
     <row r="2707" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2707" s="9" t="s">
-        <v>3112</v>
+        <v>3110</v>
       </c>
       <c r="B2707" s="10" t="s">
         <v>17</v>
@@ -80510,7 +81212,7 @@
     </row>
     <row r="2708" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2708" s="4" t="s">
-        <v>3113</v>
+        <v>3111</v>
       </c>
       <c r="B2708" s="5" t="s">
         <v>43</v>
@@ -80536,7 +81238,7 @@
     </row>
     <row r="2709" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2709" s="9" t="s">
-        <v>3114</v>
+        <v>3112</v>
       </c>
       <c r="B2709" s="10" t="s">
         <v>43</v>
@@ -80562,7 +81264,7 @@
     </row>
     <row r="2710" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2710" s="4" t="s">
-        <v>3115</v>
+        <v>3113</v>
       </c>
       <c r="B2710" s="5" t="s">
         <v>793</v>
@@ -80588,7 +81290,7 @@
     </row>
     <row r="2711" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2711" s="9" t="s">
-        <v>3116</v>
+        <v>3114</v>
       </c>
       <c r="B2711" s="10" t="s">
         <v>35</v>
@@ -80614,7 +81316,7 @@
     </row>
     <row r="2712" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2712" s="4" t="s">
-        <v>3117</v>
+        <v>3115</v>
       </c>
       <c r="B2712" s="5" t="s">
         <v>63</v>
@@ -80626,7 +81328,7 @@
         <v>879212</v>
       </c>
       <c r="E2712" s="5" t="s">
-        <v>3218</v>
+        <v>3216</v>
       </c>
       <c r="F2712" s="5" t="s">
         <v>89</v>
@@ -80640,7 +81342,7 @@
     </row>
     <row r="2713" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2713" s="9" t="s">
-        <v>3118</v>
+        <v>3116</v>
       </c>
       <c r="B2713" s="10" t="s">
         <v>1643</v>
@@ -80666,7 +81368,7 @@
     </row>
     <row r="2714" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2714" s="4" t="s">
-        <v>3119</v>
+        <v>3117</v>
       </c>
       <c r="B2714" s="5" t="s">
         <v>43</v>
@@ -80692,7 +81394,7 @@
     </row>
     <row r="2715" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2715" s="9" t="s">
-        <v>3120</v>
+        <v>3118</v>
       </c>
       <c r="B2715" s="10" t="s">
         <v>17</v>
@@ -80718,7 +81420,7 @@
     </row>
     <row r="2716" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2716" s="4" t="s">
-        <v>3121</v>
+        <v>3119</v>
       </c>
       <c r="B2716" s="5" t="s">
         <v>43</v>
@@ -80744,7 +81446,7 @@
     </row>
     <row r="2717" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2717" s="9" t="s">
-        <v>3122</v>
+        <v>3120</v>
       </c>
       <c r="B2717" s="10" t="s">
         <v>11</v>
@@ -80770,7 +81472,7 @@
     </row>
     <row r="2718" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2718" s="4" t="s">
-        <v>3123</v>
+        <v>3121</v>
       </c>
       <c r="B2718" s="5" t="s">
         <v>46</v>
@@ -80796,7 +81498,7 @@
     </row>
     <row r="2719" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2719" s="9" t="s">
-        <v>3124</v>
+        <v>3122</v>
       </c>
       <c r="B2719" s="10" t="s">
         <v>22</v>
@@ -80822,7 +81524,7 @@
     </row>
     <row r="2720" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2720" s="4" t="s">
-        <v>3125</v>
+        <v>3123</v>
       </c>
       <c r="B2720" s="5" t="s">
         <v>19</v>
@@ -80848,7 +81550,7 @@
     </row>
     <row r="2721" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2721" s="9" t="s">
-        <v>3126</v>
+        <v>3124</v>
       </c>
       <c r="B2721" s="10" t="s">
         <v>26</v>
@@ -80874,7 +81576,7 @@
     </row>
     <row r="2722" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2722" s="4" t="s">
-        <v>3127</v>
+        <v>3125</v>
       </c>
       <c r="B2722" s="5" t="s">
         <v>17</v>
@@ -80900,7 +81602,7 @@
     </row>
     <row r="2723" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2723" s="9" t="s">
-        <v>3128</v>
+        <v>3126</v>
       </c>
       <c r="B2723" s="10" t="s">
         <v>19</v>
@@ -80926,7 +81628,7 @@
     </row>
     <row r="2724" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2724" s="4" t="s">
-        <v>3129</v>
+        <v>3127</v>
       </c>
       <c r="B2724" s="5" t="s">
         <v>15</v>
@@ -80952,7 +81654,7 @@
     </row>
     <row r="2725" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2725" s="9" t="s">
-        <v>3130</v>
+        <v>3128</v>
       </c>
       <c r="B2725" s="10" t="s">
         <v>59</v>
@@ -80978,7 +81680,7 @@
     </row>
     <row r="2726" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2726" s="4" t="s">
-        <v>3131</v>
+        <v>3129</v>
       </c>
       <c r="B2726" s="5" t="s">
         <v>46</v>
@@ -81004,7 +81706,7 @@
     </row>
     <row r="2727" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2727" s="9" t="s">
-        <v>3132</v>
+        <v>3130</v>
       </c>
       <c r="B2727" s="10" t="s">
         <v>52</v>
@@ -81030,7 +81732,7 @@
     </row>
     <row r="2728" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2728" s="4" t="s">
-        <v>3133</v>
+        <v>3131</v>
       </c>
       <c r="B2728" s="5" t="s">
         <v>28</v>
@@ -81056,10 +81758,10 @@
     </row>
     <row r="2729" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2729" s="9" t="s">
-        <v>3134</v>
+        <v>3132</v>
       </c>
       <c r="B2729" s="10" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="C2729" s="11">
         <v>45847</v>
@@ -81082,7 +81784,7 @@
     </row>
     <row r="2730" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2730" s="4" t="s">
-        <v>3136</v>
+        <v>3134</v>
       </c>
       <c r="B2730" s="5" t="s">
         <v>10</v>
@@ -81108,7 +81810,7 @@
     </row>
     <row r="2731" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2731" s="9" t="s">
-        <v>3137</v>
+        <v>3135</v>
       </c>
       <c r="B2731" s="10" t="s">
         <v>49</v>
@@ -81120,7 +81822,7 @@
         <v>654312</v>
       </c>
       <c r="E2731" s="5" t="s">
-        <v>3219</v>
+        <v>3217</v>
       </c>
       <c r="F2731" s="5" t="s">
         <v>89</v>
@@ -81134,7 +81836,7 @@
     </row>
     <row r="2732" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2732" s="4" t="s">
-        <v>3138</v>
+        <v>3136</v>
       </c>
       <c r="B2732" s="5" t="s">
         <v>24</v>
@@ -81160,7 +81862,7 @@
     </row>
     <row r="2733" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2733" s="9" t="s">
-        <v>3139</v>
+        <v>3137</v>
       </c>
       <c r="B2733" s="10" t="s">
         <v>29</v>
@@ -81186,7 +81888,7 @@
     </row>
     <row r="2734" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2734" s="4" t="s">
-        <v>3140</v>
+        <v>3138</v>
       </c>
       <c r="B2734" s="5" t="s">
         <v>22</v>
@@ -81212,7 +81914,7 @@
     </row>
     <row r="2735" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2735" s="9" t="s">
-        <v>3141</v>
+        <v>3139</v>
       </c>
       <c r="B2735" s="10" t="s">
         <v>15</v>
@@ -81238,7 +81940,7 @@
     </row>
     <row r="2736" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2736" s="4" t="s">
-        <v>3142</v>
+        <v>3140</v>
       </c>
       <c r="B2736" s="5" t="s">
         <v>9</v>
@@ -81264,7 +81966,7 @@
     </row>
     <row r="2737" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2737" s="9" t="s">
-        <v>3143</v>
+        <v>3141</v>
       </c>
       <c r="B2737" s="10" t="s">
         <v>38</v>
@@ -81290,7 +81992,7 @@
     </row>
     <row r="2738" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2738" s="4" t="s">
-        <v>3144</v>
+        <v>3142</v>
       </c>
       <c r="B2738" s="5" t="s">
         <v>30</v>
@@ -81316,7 +82018,7 @@
     </row>
     <row r="2739" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2739" s="9" t="s">
-        <v>3145</v>
+        <v>3143</v>
       </c>
       <c r="B2739" s="10" t="s">
         <v>30</v>
@@ -81342,7 +82044,7 @@
     </row>
     <row r="2740" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2740" s="4" t="s">
-        <v>3146</v>
+        <v>3144</v>
       </c>
       <c r="B2740" s="5" t="s">
         <v>49</v>
@@ -81368,7 +82070,7 @@
     </row>
     <row r="2741" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2741" s="9" t="s">
-        <v>3147</v>
+        <v>3145</v>
       </c>
       <c r="B2741" s="10" t="s">
         <v>1727</v>
@@ -81394,7 +82096,7 @@
     </row>
     <row r="2742" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2742" s="4" t="s">
-        <v>3148</v>
+        <v>3146</v>
       </c>
       <c r="B2742" s="5" t="s">
         <v>19</v>
@@ -81420,10 +82122,10 @@
     </row>
     <row r="2743" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2743" s="9" t="s">
-        <v>3149</v>
+        <v>3147</v>
       </c>
       <c r="B2743" s="10" t="s">
-        <v>3150</v>
+        <v>3148</v>
       </c>
       <c r="C2743" s="11">
         <v>45847</v>
@@ -81446,7 +82148,7 @@
     </row>
     <row r="2744" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2744" s="4" t="s">
-        <v>3151</v>
+        <v>3149</v>
       </c>
       <c r="B2744" s="5" t="s">
         <v>10</v>
@@ -81472,7 +82174,7 @@
     </row>
     <row r="2745" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2745" s="9" t="s">
-        <v>3152</v>
+        <v>3150</v>
       </c>
       <c r="B2745" s="10" t="s">
         <v>31</v>
@@ -81498,7 +82200,7 @@
     </row>
     <row r="2746" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2746" s="4" t="s">
-        <v>3153</v>
+        <v>3151</v>
       </c>
       <c r="B2746" s="5" t="s">
         <v>38</v>
@@ -81524,7 +82226,7 @@
     </row>
     <row r="2747" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2747" s="9" t="s">
-        <v>3154</v>
+        <v>3152</v>
       </c>
       <c r="B2747" s="10" t="s">
         <v>38</v>
@@ -81550,7 +82252,7 @@
     </row>
     <row r="2748" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2748" s="4" t="s">
-        <v>3155</v>
+        <v>3153</v>
       </c>
       <c r="B2748" s="5" t="s">
         <v>27</v>
@@ -81576,7 +82278,7 @@
     </row>
     <row r="2749" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2749" s="9" t="s">
-        <v>3156</v>
+        <v>3154</v>
       </c>
       <c r="B2749" s="10" t="s">
         <v>31</v>
@@ -81602,7 +82304,7 @@
     </row>
     <row r="2750" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2750" s="4" t="s">
-        <v>3157</v>
+        <v>3155</v>
       </c>
       <c r="B2750" s="5" t="s">
         <v>33</v>
@@ -81628,7 +82330,7 @@
     </row>
     <row r="2751" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2751" s="9" t="s">
-        <v>3158</v>
+        <v>3156</v>
       </c>
       <c r="B2751" s="10" t="s">
         <v>47</v>
@@ -81654,7 +82356,7 @@
     </row>
     <row r="2752" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2752" s="4" t="s">
-        <v>3159</v>
+        <v>3157</v>
       </c>
       <c r="B2752" s="5" t="s">
         <v>43</v>
@@ -81680,7 +82382,7 @@
     </row>
     <row r="2753" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2753" s="9" t="s">
-        <v>3160</v>
+        <v>3158</v>
       </c>
       <c r="B2753" s="10" t="s">
         <v>17</v>
@@ -81706,7 +82408,7 @@
     </row>
     <row r="2754" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2754" s="4" t="s">
-        <v>3161</v>
+        <v>3159</v>
       </c>
       <c r="B2754" s="5" t="s">
         <v>11</v>
@@ -81732,7 +82434,7 @@
     </row>
     <row r="2755" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2755" s="9" t="s">
-        <v>3162</v>
+        <v>3160</v>
       </c>
       <c r="B2755" s="10" t="s">
         <v>18</v>
@@ -81758,7 +82460,7 @@
     </row>
     <row r="2756" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2756" s="4" t="s">
-        <v>3163</v>
+        <v>3161</v>
       </c>
       <c r="B2756" s="5" t="s">
         <v>24</v>
@@ -81784,7 +82486,7 @@
     </row>
     <row r="2757" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2757" s="9" t="s">
-        <v>3164</v>
+        <v>3162</v>
       </c>
       <c r="B2757" s="10" t="s">
         <v>24</v>
@@ -81810,7 +82512,7 @@
     </row>
     <row r="2758" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2758" s="4" t="s">
-        <v>3165</v>
+        <v>3163</v>
       </c>
       <c r="B2758" s="5" t="s">
         <v>53</v>
@@ -81836,7 +82538,7 @@
     </row>
     <row r="2759" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2759" s="9" t="s">
-        <v>3166</v>
+        <v>3164</v>
       </c>
       <c r="B2759" s="10" t="s">
         <v>15</v>
@@ -81862,7 +82564,7 @@
     </row>
     <row r="2760" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2760" s="4" t="s">
-        <v>3167</v>
+        <v>3165</v>
       </c>
       <c r="B2760" s="5" t="s">
         <v>30</v>
@@ -81888,7 +82590,7 @@
     </row>
     <row r="2761" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2761" s="9" t="s">
-        <v>3168</v>
+        <v>3166</v>
       </c>
       <c r="B2761" s="10" t="s">
         <v>27</v>
@@ -81914,7 +82616,7 @@
     </row>
     <row r="2762" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2762" s="4" t="s">
-        <v>3169</v>
+        <v>3167</v>
       </c>
       <c r="B2762" s="5" t="s">
         <v>30</v>
@@ -81940,7 +82642,7 @@
     </row>
     <row r="2763" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2763" s="9" t="s">
-        <v>3170</v>
+        <v>3168</v>
       </c>
       <c r="B2763" s="10" t="s">
         <v>14</v>
@@ -81966,7 +82668,7 @@
     </row>
     <row r="2764" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2764" s="4" t="s">
-        <v>3171</v>
+        <v>3169</v>
       </c>
       <c r="B2764" s="5" t="s">
         <v>22</v>
@@ -81992,7 +82694,7 @@
     </row>
     <row r="2765" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2765" s="9" t="s">
-        <v>3172</v>
+        <v>3170</v>
       </c>
       <c r="B2765" s="10" t="s">
         <v>28</v>
@@ -82018,7 +82720,7 @@
     </row>
     <row r="2766" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2766" s="4" t="s">
-        <v>3173</v>
+        <v>3171</v>
       </c>
       <c r="B2766" s="5" t="s">
         <v>45</v>
@@ -82044,7 +82746,7 @@
     </row>
     <row r="2767" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2767" s="9" t="s">
-        <v>3174</v>
+        <v>3172</v>
       </c>
       <c r="B2767" s="10" t="s">
         <v>27</v>
@@ -82070,7 +82772,7 @@
     </row>
     <row r="2768" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2768" s="4" t="s">
-        <v>3175</v>
+        <v>3173</v>
       </c>
       <c r="B2768" s="5" t="s">
         <v>1194</v>
@@ -82096,7 +82798,7 @@
     </row>
     <row r="2769" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2769" s="9" t="s">
-        <v>3176</v>
+        <v>3174</v>
       </c>
       <c r="B2769" s="10" t="s">
         <v>1548</v>
@@ -82122,7 +82824,7 @@
     </row>
     <row r="2770" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2770" s="4" t="s">
-        <v>3177</v>
+        <v>3175</v>
       </c>
       <c r="B2770" s="5" t="s">
         <v>32</v>
@@ -82148,7 +82850,7 @@
     </row>
     <row r="2771" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2771" s="9" t="s">
-        <v>3178</v>
+        <v>3176</v>
       </c>
       <c r="B2771" s="10" t="s">
         <v>16</v>
@@ -82160,7 +82862,7 @@
         <v>581014</v>
       </c>
       <c r="E2771" s="5" t="s">
-        <v>3220</v>
+        <v>3218</v>
       </c>
       <c r="F2771" s="5" t="s">
         <v>89</v>
@@ -82174,7 +82876,7 @@
     </row>
     <row r="2772" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2772" s="4" t="s">
-        <v>3179</v>
+        <v>3177</v>
       </c>
       <c r="B2772" s="5" t="s">
         <v>18</v>
@@ -82200,7 +82902,7 @@
     </row>
     <row r="2773" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2773" s="9" t="s">
-        <v>3180</v>
+        <v>3178</v>
       </c>
       <c r="B2773" s="10" t="s">
         <v>30</v>
@@ -82226,7 +82928,7 @@
     </row>
     <row r="2774" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2774" s="4" t="s">
-        <v>3181</v>
+        <v>3179</v>
       </c>
       <c r="B2774" s="5" t="s">
         <v>17</v>
@@ -82252,7 +82954,7 @@
     </row>
     <row r="2775" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2775" s="9" t="s">
-        <v>3182</v>
+        <v>3180</v>
       </c>
       <c r="B2775" s="10" t="s">
         <v>15</v>
@@ -82278,7 +82980,7 @@
     </row>
     <row r="2776" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2776" s="4" t="s">
-        <v>3183</v>
+        <v>3181</v>
       </c>
       <c r="B2776" s="5" t="s">
         <v>27</v>
@@ -82304,10 +83006,10 @@
     </row>
     <row r="2777" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2777" s="9" t="s">
-        <v>3184</v>
+        <v>3182</v>
       </c>
       <c r="B2777" s="10" t="s">
-        <v>3135</v>
+        <v>3133</v>
       </c>
       <c r="C2777" s="11">
         <v>45847</v>
@@ -82330,7 +83032,7 @@
     </row>
     <row r="2778" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2778" s="4" t="s">
-        <v>3185</v>
+        <v>3183</v>
       </c>
       <c r="B2778" s="5" t="s">
         <v>15</v>
@@ -82356,7 +83058,7 @@
     </row>
     <row r="2779" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2779" s="9" t="s">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="B2779" s="10" t="s">
         <v>840</v>
@@ -82382,7 +83084,7 @@
     </row>
     <row r="2780" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2780" s="4" t="s">
-        <v>3187</v>
+        <v>3185</v>
       </c>
       <c r="B2780" s="5" t="s">
         <v>717</v>
@@ -82408,7 +83110,7 @@
     </row>
     <row r="2781" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2781" s="9" t="s">
-        <v>3188</v>
+        <v>3186</v>
       </c>
       <c r="B2781" s="10" t="s">
         <v>15</v>
@@ -82434,7 +83136,7 @@
     </row>
     <row r="2782" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2782" s="4" t="s">
-        <v>3189</v>
+        <v>3187</v>
       </c>
       <c r="B2782" s="5" t="s">
         <v>15</v>
@@ -82460,7 +83162,7 @@
     </row>
     <row r="2783" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2783" s="9" t="s">
-        <v>3190</v>
+        <v>3188</v>
       </c>
       <c r="B2783" s="10" t="s">
         <v>15</v>
@@ -82486,7 +83188,7 @@
     </row>
     <row r="2784" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2784" s="4" t="s">
-        <v>3191</v>
+        <v>3189</v>
       </c>
       <c r="B2784" s="5" t="s">
         <v>43</v>
@@ -82512,7 +83214,7 @@
     </row>
     <row r="2785" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2785" s="9" t="s">
-        <v>3192</v>
+        <v>3190</v>
       </c>
       <c r="B2785" s="10" t="s">
         <v>56</v>
@@ -82538,7 +83240,7 @@
     </row>
     <row r="2786" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2786" s="4" t="s">
-        <v>3193</v>
+        <v>3191</v>
       </c>
       <c r="B2786" s="5" t="s">
         <v>27</v>
@@ -82564,7 +83266,7 @@
     </row>
     <row r="2787" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2787" s="9" t="s">
-        <v>3194</v>
+        <v>3192</v>
       </c>
       <c r="B2787" s="10" t="s">
         <v>37</v>
@@ -82590,7 +83292,7 @@
     </row>
     <row r="2788" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2788" s="4" t="s">
-        <v>3195</v>
+        <v>3193</v>
       </c>
       <c r="B2788" s="5" t="s">
         <v>22</v>
@@ -82616,7 +83318,7 @@
     </row>
     <row r="2789" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2789" s="9" t="s">
-        <v>3196</v>
+        <v>3194</v>
       </c>
       <c r="B2789" s="10" t="s">
         <v>37</v>
@@ -82642,7 +83344,7 @@
     </row>
     <row r="2790" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2790" s="4" t="s">
-        <v>3197</v>
+        <v>3195</v>
       </c>
       <c r="B2790" s="5" t="s">
         <v>27</v>
@@ -82668,7 +83370,7 @@
     </row>
     <row r="2791" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2791" s="9" t="s">
-        <v>3198</v>
+        <v>3196</v>
       </c>
       <c r="B2791" s="10" t="s">
         <v>15</v>
@@ -82694,7 +83396,7 @@
     </row>
     <row r="2792" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2792" s="4" t="s">
-        <v>3199</v>
+        <v>3197</v>
       </c>
       <c r="B2792" s="5" t="s">
         <v>22</v>
@@ -82720,7 +83422,7 @@
     </row>
     <row r="2793" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2793" s="9" t="s">
-        <v>3200</v>
+        <v>3198</v>
       </c>
       <c r="B2793" s="10" t="s">
         <v>1288</v>
@@ -82746,7 +83448,7 @@
     </row>
     <row r="2794" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2794" s="4" t="s">
-        <v>3201</v>
+        <v>3199</v>
       </c>
       <c r="B2794" s="5" t="s">
         <v>8</v>
@@ -82772,7 +83474,7 @@
     </row>
     <row r="2795" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2795" s="9" t="s">
-        <v>3202</v>
+        <v>3200</v>
       </c>
       <c r="B2795" s="10" t="s">
         <v>19</v>
@@ -82798,7 +83500,7 @@
     </row>
     <row r="2796" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2796" s="4" t="s">
-        <v>3203</v>
+        <v>3201</v>
       </c>
       <c r="B2796" s="5" t="s">
         <v>34</v>
@@ -82824,7 +83526,7 @@
     </row>
     <row r="2797" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2797" s="9" t="s">
-        <v>3204</v>
+        <v>3202</v>
       </c>
       <c r="B2797" s="10" t="s">
         <v>14</v>
@@ -82850,7 +83552,7 @@
     </row>
     <row r="2798" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2798" s="4" t="s">
-        <v>3205</v>
+        <v>3203</v>
       </c>
       <c r="B2798" s="5" t="s">
         <v>39</v>
@@ -82876,7 +83578,7 @@
     </row>
     <row r="2799" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2799" s="9" t="s">
-        <v>3206</v>
+        <v>3204</v>
       </c>
       <c r="B2799" s="10" t="s">
         <v>840</v>
@@ -82902,7 +83604,7 @@
     </row>
     <row r="2800" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2800" s="4" t="s">
-        <v>3207</v>
+        <v>3205</v>
       </c>
       <c r="B2800" s="5" t="s">
         <v>15</v>
@@ -82928,7 +83630,7 @@
     </row>
     <row r="2801" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2801" s="9" t="s">
-        <v>3208</v>
+        <v>3206</v>
       </c>
       <c r="B2801" s="10" t="s">
         <v>38</v>
@@ -82954,7 +83656,7 @@
     </row>
     <row r="2802" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2802" s="4" t="s">
-        <v>3209</v>
+        <v>3207</v>
       </c>
       <c r="B2802" s="5" t="s">
         <v>39</v>
@@ -82980,7 +83682,7 @@
     </row>
     <row r="2803" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2803" s="9" t="s">
-        <v>3210</v>
+        <v>3208</v>
       </c>
       <c r="B2803" s="10" t="s">
         <v>1288</v>
@@ -83006,7 +83708,7 @@
     </row>
     <row r="2804" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2804" s="4" t="s">
-        <v>3211</v>
+        <v>3209</v>
       </c>
       <c r="B2804" s="5" t="s">
         <v>1471</v>
@@ -83032,7 +83734,7 @@
     </row>
     <row r="2805" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2805" s="9" t="s">
-        <v>3212</v>
+        <v>3210</v>
       </c>
       <c r="B2805" s="10" t="s">
         <v>30</v>
@@ -83053,6 +83755,6142 @@
         <v>86</v>
       </c>
       <c r="H2805" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2806" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2806" s="4" t="s">
+        <v>3221</v>
+      </c>
+      <c r="B2806" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2806" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2806" s="7">
+        <v>560570</v>
+      </c>
+      <c r="E2806" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2806" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2806" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2806" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2807" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2807" s="9" t="s">
+        <v>3222</v>
+      </c>
+      <c r="B2807" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2807" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2807" s="12">
+        <v>817</v>
+      </c>
+      <c r="E2807" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F2807" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2807" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2807" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2808" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2808" s="4" t="s">
+        <v>3223</v>
+      </c>
+      <c r="B2808" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2808" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2808" s="7">
+        <v>556838</v>
+      </c>
+      <c r="E2808" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F2808" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2808" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2808" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2809" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2809" s="9" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B2809" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2809" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2809" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E2809" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2809" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2809" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2809" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2810" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2810" s="4" t="s">
+        <v>3225</v>
+      </c>
+      <c r="B2810" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2810" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2810" s="7">
+        <v>380291</v>
+      </c>
+      <c r="E2810" s="5" t="s">
+        <v>2090</v>
+      </c>
+      <c r="F2810" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2810" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2810" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2811" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2811" s="9" t="s">
+        <v>3226</v>
+      </c>
+      <c r="B2811" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C2811" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2811" s="12">
+        <v>127424</v>
+      </c>
+      <c r="E2811" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F2811" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2811" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2811" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2812" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2812" s="4" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B2812" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2812" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2812" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2812" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2812" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2812" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2812" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2813" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2813" s="9" t="s">
+        <v>3228</v>
+      </c>
+      <c r="B2813" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2813" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2813" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E2813" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2813" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2813" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2813" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2814" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2814" s="4" t="s">
+        <v>3229</v>
+      </c>
+      <c r="B2814" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2814" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2814" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2814" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2814" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2814" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2814" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2815" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2815" s="9" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B2815" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2815" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2815" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2815" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2815" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2815" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2815" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2816" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2816" s="4" t="s">
+        <v>3231</v>
+      </c>
+      <c r="B2816" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2816" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2816" s="7">
+        <v>40828</v>
+      </c>
+      <c r="E2816" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2816" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2816" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2816" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2817" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2817" s="9" t="s">
+        <v>3232</v>
+      </c>
+      <c r="B2817" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2817" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2817" s="12">
+        <v>674036</v>
+      </c>
+      <c r="E2817" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2817" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2817" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2817" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2818" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2818" s="4" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B2818" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C2818" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2818" s="7">
+        <v>810976</v>
+      </c>
+      <c r="E2818" s="5" t="s">
+        <v>1260</v>
+      </c>
+      <c r="F2818" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2818" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2818" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2819" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2819" s="9" t="s">
+        <v>3234</v>
+      </c>
+      <c r="B2819" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2819" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2819" s="12">
+        <v>825133</v>
+      </c>
+      <c r="E2819" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="F2819" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2819" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2819" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2820" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2820" s="4" t="s">
+        <v>3235</v>
+      </c>
+      <c r="B2820" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2820" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2820" s="7">
+        <v>827985</v>
+      </c>
+      <c r="E2820" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2820" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2820" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2820" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2821" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2821" s="9" t="s">
+        <v>3236</v>
+      </c>
+      <c r="B2821" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2821" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2821" s="12">
+        <v>200543</v>
+      </c>
+      <c r="E2821" s="5" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F2821" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2821" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2821" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2822" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2822" s="4" t="s">
+        <v>3237</v>
+      </c>
+      <c r="B2822" s="5" t="s">
+        <v>722</v>
+      </c>
+      <c r="C2822" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2822" s="7">
+        <v>6060</v>
+      </c>
+      <c r="E2822" s="5" t="s">
+        <v>2691</v>
+      </c>
+      <c r="F2822" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2822" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2822" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2823" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2823" s="9" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B2823" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2823" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2823" s="12">
+        <v>860321</v>
+      </c>
+      <c r="E2823" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="F2823" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2823" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2823" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2824" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2824" s="4" t="s">
+        <v>3239</v>
+      </c>
+      <c r="B2824" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2824" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2824" s="7">
+        <v>459336</v>
+      </c>
+      <c r="E2824" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2824" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2824" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2824" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2825" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2825" s="9" t="s">
+        <v>3240</v>
+      </c>
+      <c r="B2825" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2825" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2825" s="12">
+        <v>576159</v>
+      </c>
+      <c r="E2825" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2825" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2825" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2825" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2826" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2826" s="4" t="s">
+        <v>3241</v>
+      </c>
+      <c r="B2826" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2826" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2826" s="7">
+        <v>860321</v>
+      </c>
+      <c r="E2826" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="F2826" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2826" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2826" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2827" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2827" s="9" t="s">
+        <v>3242</v>
+      </c>
+      <c r="B2827" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2827" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2827" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2827" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2827" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2827" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2827" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2828" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2828" s="4" t="s">
+        <v>3243</v>
+      </c>
+      <c r="B2828" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2828" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2828" s="7">
+        <v>556838</v>
+      </c>
+      <c r="E2828" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F2828" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2828" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2828" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2829" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2829" s="9" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B2829" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2829" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2829" s="12">
+        <v>878787</v>
+      </c>
+      <c r="E2829" s="5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="F2829" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2829" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2829" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2830" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2830" s="4" t="s">
+        <v>3245</v>
+      </c>
+      <c r="B2830" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2830" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2830" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2830" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2830" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2830" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2830" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2831" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2831" s="9" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B2831" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2831" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2831" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2831" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2831" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2831" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2831" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2832" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2832" s="4" t="s">
+        <v>3247</v>
+      </c>
+      <c r="B2832" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2832" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2832" s="7">
+        <v>827985</v>
+      </c>
+      <c r="E2832" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2832" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2832" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2832" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2833" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2833" s="9" t="s">
+        <v>3248</v>
+      </c>
+      <c r="B2833" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2833" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2833" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2833" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2833" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2833" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2833" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2834" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2834" s="4" t="s">
+        <v>3249</v>
+      </c>
+      <c r="B2834" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2834" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2834" s="7">
+        <v>868672</v>
+      </c>
+      <c r="E2834" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2834" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2834" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2834" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2835" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2835" s="9" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B2835" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2835" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2835" s="12">
+        <v>817</v>
+      </c>
+      <c r="E2835" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F2835" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2835" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2835" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2836" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2836" s="4" t="s">
+        <v>3251</v>
+      </c>
+      <c r="B2836" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2836" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2836" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E2836" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2836" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2836" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2836" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2837" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2837" s="9" t="s">
+        <v>3252</v>
+      </c>
+      <c r="B2837" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2837" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2837" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2837" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2837" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2837" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2837" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2838" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2838" s="4" t="s">
+        <v>2795</v>
+      </c>
+      <c r="B2838" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2838" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2838" s="7">
+        <v>525458</v>
+      </c>
+      <c r="E2838" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2838" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2838" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2838" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2839" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2839" s="9" t="s">
+        <v>3253</v>
+      </c>
+      <c r="B2839" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2839" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2839" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2839" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2839" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2839" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2839" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2840" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2840" s="4" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B2840" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2840" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2840" s="7">
+        <v>875521</v>
+      </c>
+      <c r="E2840" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F2840" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2840" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2840" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2841" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2841" s="9" t="s">
+        <v>3255</v>
+      </c>
+      <c r="B2841" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2841" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2841" s="12">
+        <v>873643</v>
+      </c>
+      <c r="E2841" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F2841" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2841" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2841" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2842" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2842" s="4" t="s">
+        <v>3256</v>
+      </c>
+      <c r="B2842" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2842" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2842" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2842" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2842" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2842" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2842" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2843" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2843" s="9" t="s">
+        <v>3219</v>
+      </c>
+      <c r="B2843" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2843" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2843" s="12">
+        <v>862247</v>
+      </c>
+      <c r="E2843" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F2843" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2843" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2843" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2844" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2844" s="4" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B2844" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2844" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2844" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2844" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2844" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2844" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2844" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2845" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2845" s="9" t="s">
+        <v>3258</v>
+      </c>
+      <c r="B2845" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2845" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2845" s="12">
+        <v>36923</v>
+      </c>
+      <c r="E2845" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="F2845" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2845" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2845" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2846" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2846" s="4" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B2846" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2846" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2846" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2846" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2846" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2846" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2846" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2847" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2847" s="9" t="s">
+        <v>3260</v>
+      </c>
+      <c r="B2847" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2847" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2847" s="12">
+        <v>399149</v>
+      </c>
+      <c r="E2847" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2847" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2847" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2847" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2848" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2848" s="4" t="s">
+        <v>3261</v>
+      </c>
+      <c r="B2848" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2848" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2848" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2848" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2848" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2848" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2848" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2849" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2849" s="9" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B2849" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2849" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2849" s="12">
+        <v>556838</v>
+      </c>
+      <c r="E2849" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F2849" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2849" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2849" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2850" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2850" s="4" t="s">
+        <v>3263</v>
+      </c>
+      <c r="B2850" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2850" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2850" s="7">
+        <v>110</v>
+      </c>
+      <c r="E2850" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2850" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2850" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2850" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2851" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2851" s="9" t="s">
+        <v>3264</v>
+      </c>
+      <c r="B2851" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2851" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2851" s="12">
+        <v>860321</v>
+      </c>
+      <c r="E2851" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="F2851" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2851" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2851" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2852" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2852" s="4" t="s">
+        <v>3265</v>
+      </c>
+      <c r="B2852" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2852" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2852" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E2852" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2852" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2852" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2852" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2853" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2853" s="9" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B2853" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2853" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2853" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2853" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2853" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2853" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2853" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2854" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2854" s="4" t="s">
+        <v>3267</v>
+      </c>
+      <c r="B2854" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2854" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2854" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2854" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2854" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2854" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2854" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2855" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2855" s="9" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B2855" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2855" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2855" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2855" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2855" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2855" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2855" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2856" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2856" s="4" t="s">
+        <v>3269</v>
+      </c>
+      <c r="B2856" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2856" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2856" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2856" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2856" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2856" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2856" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2857" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2857" s="9" t="s">
+        <v>3270</v>
+      </c>
+      <c r="B2857" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2857" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2857" s="12">
+        <v>637113</v>
+      </c>
+      <c r="E2857" s="5" t="s">
+        <v>1558</v>
+      </c>
+      <c r="F2857" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2857" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2857" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2858" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2858" s="4" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B2858" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2858" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2858" s="7">
+        <v>560570</v>
+      </c>
+      <c r="E2858" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2858" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2858" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2858" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2859" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2859" s="9" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B2859" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2859" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2859" s="12">
+        <v>876282</v>
+      </c>
+      <c r="E2859" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F2859" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2859" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2859" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2860" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2860" s="4" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B2860" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2860" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2860" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2860" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2860" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2860" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2860" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2861" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2861" s="9" t="s">
+        <v>3272</v>
+      </c>
+      <c r="B2861" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2861" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2861" s="12">
+        <v>876282</v>
+      </c>
+      <c r="E2861" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F2861" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2861" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2861" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2862" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2862" s="4" t="s">
+        <v>3274</v>
+      </c>
+      <c r="B2862" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2862" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2862" s="7">
+        <v>459336</v>
+      </c>
+      <c r="E2862" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2862" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2862" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2862" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2863" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2863" s="9" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B2863" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2863" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2863" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2863" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2863" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2863" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2863" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2864" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2864" s="4" t="s">
+        <v>3276</v>
+      </c>
+      <c r="B2864" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2864" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2864" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E2864" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2864" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2864" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2864" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2865" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2865" s="9" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B2865" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2865" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2865" s="12">
+        <v>666428</v>
+      </c>
+      <c r="E2865" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F2865" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2865" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2865" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2866" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2866" s="4" t="s">
+        <v>3278</v>
+      </c>
+      <c r="B2866" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2866" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2866" s="7">
+        <v>858855</v>
+      </c>
+      <c r="E2866" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F2866" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2866" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2866" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2867" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2867" s="9" t="s">
+        <v>3279</v>
+      </c>
+      <c r="B2867" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2867" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2867" s="12">
+        <v>576121</v>
+      </c>
+      <c r="E2867" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2867" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2867" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2867" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2868" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2868" s="4" t="s">
+        <v>3280</v>
+      </c>
+      <c r="B2868" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2868" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2868" s="7">
+        <v>683063</v>
+      </c>
+      <c r="E2868" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2868" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2868" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2868" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2869" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2869" s="9" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B2869" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2869" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2869" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2869" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2869" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2869" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2869" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2870" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2870" s="4" t="s">
+        <v>3282</v>
+      </c>
+      <c r="B2870" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2870" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2870" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2870" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2870" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2870" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2870" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2871" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2871" s="9" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B2871" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2871" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2871" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2871" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2871" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2871" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2871" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2872" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2872" s="4" t="s">
+        <v>3284</v>
+      </c>
+      <c r="B2872" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2872" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2872" s="7">
+        <v>885298</v>
+      </c>
+      <c r="E2872" s="5" t="s">
+        <v>2486</v>
+      </c>
+      <c r="F2872" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2872" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2872" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2873" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2873" s="9" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B2873" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2873" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2873" s="12">
+        <v>876149</v>
+      </c>
+      <c r="E2873" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F2873" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2873" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2873" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2874" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2874" s="4" t="s">
+        <v>3286</v>
+      </c>
+      <c r="B2874" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2874" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2874" s="7">
+        <v>863796</v>
+      </c>
+      <c r="E2874" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="F2874" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2874" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2874" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2875" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2875" s="9" t="s">
+        <v>3287</v>
+      </c>
+      <c r="B2875" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2875" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2875" s="12">
+        <v>860321</v>
+      </c>
+      <c r="E2875" s="5" t="s">
+        <v>890</v>
+      </c>
+      <c r="F2875" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2875" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2875" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2876" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2876" s="4" t="s">
+        <v>3288</v>
+      </c>
+      <c r="B2876" s="5" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C2876" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2876" s="7">
+        <v>216565</v>
+      </c>
+      <c r="E2876" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2876" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2876" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2876" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2877" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2877" s="9" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B2877" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2877" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2877" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E2877" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2877" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2877" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2877" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2878" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2878" s="4" t="s">
+        <v>3290</v>
+      </c>
+      <c r="B2878" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2878" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2878" s="7">
+        <v>837970</v>
+      </c>
+      <c r="E2878" s="5" t="s">
+        <v>1278</v>
+      </c>
+      <c r="F2878" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2878" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2878" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2879" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2879" s="9" t="s">
+        <v>3291</v>
+      </c>
+      <c r="B2879" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2879" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2879" s="12">
+        <v>795531</v>
+      </c>
+      <c r="E2879" s="5" t="s">
+        <v>1571</v>
+      </c>
+      <c r="F2879" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2879" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2879" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2880" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2880" s="4" t="s">
+        <v>3292</v>
+      </c>
+      <c r="B2880" s="5" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C2880" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2880" s="7">
+        <v>216565</v>
+      </c>
+      <c r="E2880" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F2880" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2880" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2880" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2881" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2881" s="9" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B2881" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2881" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2881" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E2881" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F2881" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2881" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2881" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2882" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2882" s="4" t="s">
+        <v>3294</v>
+      </c>
+      <c r="B2882" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2882" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2882" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2882" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2882" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2882" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2882" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2883" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2883" s="9" t="s">
+        <v>3295</v>
+      </c>
+      <c r="B2883" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2883" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2883" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2883" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2883" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2883" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2883" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2884" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2884" s="4" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B2884" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2884" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2884" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2884" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2884" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2884" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2884" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2885" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2885" s="9" t="s">
+        <v>3297</v>
+      </c>
+      <c r="B2885" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2885" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2885" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2885" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2885" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2885" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2885" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2886" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2886" s="4" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B2886" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2886" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2886" s="7">
+        <v>262147</v>
+      </c>
+      <c r="E2886" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2886" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2886" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2886" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2887" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2887" s="9" t="s">
+        <v>3299</v>
+      </c>
+      <c r="B2887" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2887" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2887" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E2887" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2887" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2887" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2887" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2888" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2888" s="4" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B2888" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C2888" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2888" s="7">
+        <v>399007</v>
+      </c>
+      <c r="E2888" s="5" t="s">
+        <v>1559</v>
+      </c>
+      <c r="F2888" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2888" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2888" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2889" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2889" s="9" t="s">
+        <v>3301</v>
+      </c>
+      <c r="B2889" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2889" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2889" s="12">
+        <v>872122</v>
+      </c>
+      <c r="E2889" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2889" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2889" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2889" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2890" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2890" s="4" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B2890" s="5" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C2890" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2890" s="7">
+        <v>38153</v>
+      </c>
+      <c r="E2890" s="5" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F2890" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2890" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2890" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2891" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2891" s="9" t="s">
+        <v>3303</v>
+      </c>
+      <c r="B2891" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2891" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2891" s="12">
+        <v>377654</v>
+      </c>
+      <c r="E2891" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2891" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2891" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2891" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2892" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2892" s="4" t="s">
+        <v>3304</v>
+      </c>
+      <c r="B2892" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2892" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2892" s="7">
+        <v>576159</v>
+      </c>
+      <c r="E2892" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2892" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2892" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2892" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2893" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2893" s="9" t="s">
+        <v>3305</v>
+      </c>
+      <c r="B2893" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2893" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2893" s="12">
+        <v>683063</v>
+      </c>
+      <c r="E2893" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2893" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2893" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2893" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2894" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2894" s="4" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B2894" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2894" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2894" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E2894" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2894" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2894" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2894" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2895" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2895" s="9" t="s">
+        <v>3307</v>
+      </c>
+      <c r="B2895" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2895" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2895" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E2895" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2895" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2895" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2895" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2896" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2896" s="4" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B2896" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2896" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2896" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2896" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2896" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2896" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2896" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2897" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2897" s="9" t="s">
+        <v>3309</v>
+      </c>
+      <c r="B2897" s="10" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C2897" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2897" s="12">
+        <v>883580</v>
+      </c>
+      <c r="E2897" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F2897" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2897" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2897" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2898" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2898" s="4" t="s">
+        <v>3310</v>
+      </c>
+      <c r="B2898" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2898" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2898" s="7">
+        <v>569000</v>
+      </c>
+      <c r="E2898" s="5" t="s">
+        <v>3452</v>
+      </c>
+      <c r="F2898" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2898" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2898" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2899" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2899" s="9" t="s">
+        <v>3311</v>
+      </c>
+      <c r="B2899" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2899" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2899" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2899" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2899" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2899" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2899" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2900" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2900" s="4" t="s">
+        <v>3312</v>
+      </c>
+      <c r="B2900" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2900" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2900" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2900" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2900" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2900" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2900" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2901" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2901" s="9" t="s">
+        <v>3313</v>
+      </c>
+      <c r="B2901" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2901" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2901" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2901" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2901" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2901" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2901" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2902" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2902" s="4" t="s">
+        <v>3314</v>
+      </c>
+      <c r="B2902" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2902" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2902" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2902" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2902" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2902" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2902" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2903" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2903" s="9" t="s">
+        <v>3315</v>
+      </c>
+      <c r="B2903" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2903" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2903" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E2903" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2903" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2903" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2903" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2904" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2904" s="4" t="s">
+        <v>3316</v>
+      </c>
+      <c r="B2904" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2904" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2904" s="7">
+        <v>377654</v>
+      </c>
+      <c r="E2904" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2904" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2904" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2904" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2905" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2905" s="9" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B2905" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2905" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2905" s="12">
+        <v>781646</v>
+      </c>
+      <c r="E2905" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2905" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2905" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2905" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2906" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2906" s="4" t="s">
+        <v>3318</v>
+      </c>
+      <c r="B2906" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2906" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2906" s="7">
+        <v>576159</v>
+      </c>
+      <c r="E2906" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2906" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2906" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2906" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2907" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2907" s="9" t="s">
+        <v>3319</v>
+      </c>
+      <c r="B2907" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2907" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2907" s="12">
+        <v>562578</v>
+      </c>
+      <c r="E2907" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2907" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2907" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2907" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2908" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2908" s="4" t="s">
+        <v>3320</v>
+      </c>
+      <c r="B2908" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2908" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2908" s="7">
+        <v>882296</v>
+      </c>
+      <c r="E2908" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F2908" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2908" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2908" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2909" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2909" s="9" t="s">
+        <v>3321</v>
+      </c>
+      <c r="B2909" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2909" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2909" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2909" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2909" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2909" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2909" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2910" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2910" s="4" t="s">
+        <v>3322</v>
+      </c>
+      <c r="B2910" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2910" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2910" s="7">
+        <v>729970</v>
+      </c>
+      <c r="E2910" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2910" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2910" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2910" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2911" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2911" s="9" t="s">
+        <v>3323</v>
+      </c>
+      <c r="B2911" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2911" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2911" s="12">
+        <v>576159</v>
+      </c>
+      <c r="E2911" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F2911" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2911" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2911" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2912" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2912" s="4" t="s">
+        <v>3324</v>
+      </c>
+      <c r="B2912" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2912" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2912" s="7">
+        <v>262147</v>
+      </c>
+      <c r="E2912" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2912" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2912" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2912" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2913" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2913" s="9" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B2913" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2913" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2913" s="12">
+        <v>172141</v>
+      </c>
+      <c r="E2913" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2913" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2913" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2913" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2914" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2914" s="4" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B2914" s="5" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C2914" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2914" s="7">
+        <v>833948</v>
+      </c>
+      <c r="E2914" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2914" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2914" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2914" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2915" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2915" s="9" t="s">
+        <v>3326</v>
+      </c>
+      <c r="B2915" s="10" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C2915" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2915" s="12">
+        <v>833948</v>
+      </c>
+      <c r="E2915" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2915" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2915" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2915" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2916" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2916" s="4" t="s">
+        <v>3328</v>
+      </c>
+      <c r="B2916" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2916" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2916" s="7">
+        <v>872122</v>
+      </c>
+      <c r="E2916" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2916" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2916" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2916" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2917" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2917" s="9" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B2917" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C2917" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2917" s="12">
+        <v>873652</v>
+      </c>
+      <c r="E2917" s="5" t="s">
+        <v>1826</v>
+      </c>
+      <c r="F2917" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2917" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2917" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2918" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2918" s="4" t="s">
+        <v>3330</v>
+      </c>
+      <c r="B2918" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2918" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2918" s="7">
+        <v>875521</v>
+      </c>
+      <c r="E2918" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F2918" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2918" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2918" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2919" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2919" s="9" t="s">
+        <v>3331</v>
+      </c>
+      <c r="B2919" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C2919" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2919" s="12">
+        <v>683063</v>
+      </c>
+      <c r="E2919" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F2919" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2919" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2919" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2920" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2920" s="4" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B2920" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2920" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2920" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2920" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2920" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2920" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2920" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2921" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2921" s="9" t="s">
+        <v>3333</v>
+      </c>
+      <c r="B2921" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2921" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2921" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E2921" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2921" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2921" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2921" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2922" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2922" s="4" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B2922" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2922" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2922" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2922" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2922" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2922" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2922" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2923" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2923" s="9" t="s">
+        <v>3335</v>
+      </c>
+      <c r="B2923" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2923" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2923" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E2923" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F2923" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2923" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2923" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2924" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2924" s="4" t="s">
+        <v>3336</v>
+      </c>
+      <c r="B2924" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2924" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2924" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2924" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2924" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2924" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2924" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2925" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2925" s="9" t="s">
+        <v>3337</v>
+      </c>
+      <c r="B2925" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2925" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2925" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E2925" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F2925" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2925" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2925" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2926" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2926" s="4" t="s">
+        <v>3338</v>
+      </c>
+      <c r="B2926" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2926" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2926" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E2926" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2926" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2926" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2926" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2927" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2927" s="9" t="s">
+        <v>3339</v>
+      </c>
+      <c r="B2927" s="10" t="s">
+        <v>822</v>
+      </c>
+      <c r="C2927" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2927" s="12">
+        <v>872122</v>
+      </c>
+      <c r="E2927" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2927" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2927" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2927" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2928" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2928" s="4" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B2928" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2928" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2928" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2928" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2928" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2928" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2928" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2929" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2929" s="9" t="s">
+        <v>3341</v>
+      </c>
+      <c r="B2929" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2929" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2929" s="12">
+        <v>262147</v>
+      </c>
+      <c r="E2929" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F2929" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2929" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2929" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2930" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2930" s="4" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B2930" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2930" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2930" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E2930" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F2930" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2930" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2930" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2931" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2931" s="9" t="s">
+        <v>3343</v>
+      </c>
+      <c r="B2931" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2931" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2931" s="12">
+        <v>741456</v>
+      </c>
+      <c r="E2931" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F2931" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2931" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2931" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2932" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2932" s="4" t="s">
+        <v>3344</v>
+      </c>
+      <c r="B2932" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2932" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2932" s="7">
+        <v>844068</v>
+      </c>
+      <c r="E2932" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F2932" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2932" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2932" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2933" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2933" s="9" t="s">
+        <v>3345</v>
+      </c>
+      <c r="B2933" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2933" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2933" s="12">
+        <v>560570</v>
+      </c>
+      <c r="E2933" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F2933" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2933" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2933" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2934" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2934" s="4" t="s">
+        <v>3346</v>
+      </c>
+      <c r="B2934" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2934" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2934" s="7">
+        <v>883827</v>
+      </c>
+      <c r="E2934" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F2934" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2934" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2934" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2935" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2935" s="9" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B2935" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2935" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2935" s="12">
+        <v>239381</v>
+      </c>
+      <c r="E2935" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2935" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2935" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2935" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2936" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2936" s="4" t="s">
+        <v>3348</v>
+      </c>
+      <c r="B2936" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2936" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2936" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2936" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2936" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2936" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2936" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2937" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2937" s="9" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B2937" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2937" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2937" s="12">
+        <v>780838</v>
+      </c>
+      <c r="E2937" s="5" t="s">
+        <v>2942</v>
+      </c>
+      <c r="F2937" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2937" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2937" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2938" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2938" s="4" t="s">
+        <v>3350</v>
+      </c>
+      <c r="B2938" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2938" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2938" s="7">
+        <v>405</v>
+      </c>
+      <c r="E2938" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F2938" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2938" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2938" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2939" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2939" s="9" t="s">
+        <v>3351</v>
+      </c>
+      <c r="B2939" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2939" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2939" s="12">
+        <v>843026</v>
+      </c>
+      <c r="E2939" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2939" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2939" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2939" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2940" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2940" s="4" t="s">
+        <v>3352</v>
+      </c>
+      <c r="B2940" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2940" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2940" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2940" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2940" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2940" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2940" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2941" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2941" s="9" t="s">
+        <v>3353</v>
+      </c>
+      <c r="B2941" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2941" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2941" s="12">
+        <v>883823</v>
+      </c>
+      <c r="E2941" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F2941" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2941" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2941" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2942" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2942" s="4" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B2942" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2942" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2942" s="7">
+        <v>619784</v>
+      </c>
+      <c r="E2942" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="F2942" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2942" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2942" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2943" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2943" s="9" t="s">
+        <v>3355</v>
+      </c>
+      <c r="B2943" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2943" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2943" s="12">
+        <v>829353</v>
+      </c>
+      <c r="E2943" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F2943" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2943" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2943" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2944" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2944" s="4" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B2944" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2944" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2944" s="7">
+        <v>239381</v>
+      </c>
+      <c r="E2944" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F2944" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G2944" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2944" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2945" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2945" s="9" t="s">
+        <v>3357</v>
+      </c>
+      <c r="B2945" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2945" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2945" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E2945" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2945" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2945" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2945" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2946" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2946" s="4" t="s">
+        <v>3358</v>
+      </c>
+      <c r="B2946" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2946" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2946" s="7">
+        <v>172141</v>
+      </c>
+      <c r="E2946" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2946" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2946" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2946" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2947" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2947" s="9" t="s">
+        <v>3359</v>
+      </c>
+      <c r="B2947" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2947" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2947" s="12">
+        <v>623344</v>
+      </c>
+      <c r="E2947" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2947" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2947" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2947" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2948" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2948" s="4" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B2948" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2948" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2948" s="7">
+        <v>40828</v>
+      </c>
+      <c r="E2948" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F2948" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2948" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2948" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2949" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2949" s="9" t="s">
+        <v>3361</v>
+      </c>
+      <c r="B2949" s="10" t="s">
+        <v>853</v>
+      </c>
+      <c r="C2949" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2949" s="12">
+        <v>482494</v>
+      </c>
+      <c r="E2949" s="5" t="s">
+        <v>3453</v>
+      </c>
+      <c r="F2949" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2949" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2949" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2950" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2950" s="4" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B2950" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2950" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2950" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2950" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2950" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2950" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2950" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2951" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2951" s="9" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B2951" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2951" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2951" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2951" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2951" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2951" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2951" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2952" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2952" s="4" t="s">
+        <v>3363</v>
+      </c>
+      <c r="B2952" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2952" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2952" s="7">
+        <v>177442</v>
+      </c>
+      <c r="E2952" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2952" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2952" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2952" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2953" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2953" s="9" t="s">
+        <v>3364</v>
+      </c>
+      <c r="B2953" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2953" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2953" s="12">
+        <v>827985</v>
+      </c>
+      <c r="E2953" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="F2953" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2953" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2953" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2954" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2954" s="4" t="s">
+        <v>3365</v>
+      </c>
+      <c r="B2954" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2954" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2954" s="7">
+        <v>653931</v>
+      </c>
+      <c r="E2954" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F2954" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2954" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2954" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2955" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2955" s="9" t="s">
+        <v>3366</v>
+      </c>
+      <c r="B2955" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2955" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2955" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2955" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2955" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2955" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2955" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2956" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2956" s="4" t="s">
+        <v>3367</v>
+      </c>
+      <c r="B2956" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2956" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2956" s="7">
+        <v>862247</v>
+      </c>
+      <c r="E2956" s="5" t="s">
+        <v>1266</v>
+      </c>
+      <c r="F2956" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2956" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2956" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2957" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2957" s="9" t="s">
+        <v>3368</v>
+      </c>
+      <c r="B2957" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2957" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2957" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E2957" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2957" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2957" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2957" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2958" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2958" s="4" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B2958" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2958" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2958" s="7">
+        <v>883819</v>
+      </c>
+      <c r="E2958" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2958" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2958" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2958" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2959" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2959" s="9" t="s">
+        <v>3370</v>
+      </c>
+      <c r="B2959" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2959" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2959" s="12">
+        <v>843508</v>
+      </c>
+      <c r="E2959" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="F2959" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2959" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2959" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2960" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2960" s="4" t="s">
+        <v>3371</v>
+      </c>
+      <c r="B2960" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2960" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2960" s="7">
+        <v>878685</v>
+      </c>
+      <c r="E2960" s="5" t="s">
+        <v>1555</v>
+      </c>
+      <c r="F2960" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2960" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2960" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2961" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2961" s="9" t="s">
+        <v>3372</v>
+      </c>
+      <c r="B2961" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2961" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2961" s="12">
+        <v>710727</v>
+      </c>
+      <c r="E2961" s="5" t="s">
+        <v>1273</v>
+      </c>
+      <c r="F2961" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2961" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2961" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2962" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2962" s="4" t="s">
+        <v>3373</v>
+      </c>
+      <c r="B2962" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2962" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2962" s="7">
+        <v>787456</v>
+      </c>
+      <c r="E2962" s="5" t="s">
+        <v>927</v>
+      </c>
+      <c r="F2962" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2962" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2962" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2963" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2963" s="9" t="s">
+        <v>3374</v>
+      </c>
+      <c r="B2963" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2963" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2963" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2963" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2963" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2963" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2963" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2964" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2964" s="4" t="s">
+        <v>3375</v>
+      </c>
+      <c r="B2964" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2964" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2964" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E2964" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F2964" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2964" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2964" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2965" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2965" s="9" t="s">
+        <v>3376</v>
+      </c>
+      <c r="B2965" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C2965" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2965" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E2965" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2965" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2965" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2965" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2966" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2966" s="4" t="s">
+        <v>3377</v>
+      </c>
+      <c r="B2966" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2966" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2966" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2966" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2966" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2966" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2966" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="2967" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2967" s="9" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B2967" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2967" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2967" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E2967" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2967" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2967" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2967" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2968" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2968" s="4" t="s">
+        <v>3379</v>
+      </c>
+      <c r="B2968" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C2968" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2968" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2968" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2968" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2968" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2968" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2969" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2969" s="9" t="s">
+        <v>3380</v>
+      </c>
+      <c r="B2969" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2969" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2969" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E2969" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2969" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2969" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H2969" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2970" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2970" s="4" t="s">
+        <v>3381</v>
+      </c>
+      <c r="B2970" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2970" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2970" s="7">
+        <v>880152</v>
+      </c>
+      <c r="E2970" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2970" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2970" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2970" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2971" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2971" s="9" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B2971" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2971" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2971" s="12">
+        <v>880152</v>
+      </c>
+      <c r="E2971" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2971" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2971" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2971" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2972" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2972" s="4" t="s">
+        <v>3383</v>
+      </c>
+      <c r="B2972" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2972" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2972" s="7">
+        <v>878918</v>
+      </c>
+      <c r="E2972" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2972" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2972" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2972" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2973" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2973" s="9" t="s">
+        <v>3384</v>
+      </c>
+      <c r="B2973" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2973" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2973" s="12">
+        <v>781646</v>
+      </c>
+      <c r="E2973" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F2973" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2973" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2973" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2974" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2974" s="4" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B2974" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2974" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2974" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2974" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2974" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2974" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2974" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2975" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2975" s="9" t="s">
+        <v>3386</v>
+      </c>
+      <c r="B2975" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2975" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2975" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E2975" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2975" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2975" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2975" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2976" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2976" s="4" t="s">
+        <v>3387</v>
+      </c>
+      <c r="B2976" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2976" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2976" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2976" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2976" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2976" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2976" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2977" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2977" s="9" t="s">
+        <v>3388</v>
+      </c>
+      <c r="B2977" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2977" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2977" s="12">
+        <v>881485</v>
+      </c>
+      <c r="E2977" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F2977" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2977" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2977" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2978" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2978" s="4" t="s">
+        <v>3389</v>
+      </c>
+      <c r="B2978" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2978" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2978" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E2978" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F2978" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G2978" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2978" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2979" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2979" s="9" t="s">
+        <v>3390</v>
+      </c>
+      <c r="B2979" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2979" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2979" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2979" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2979" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2979" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2979" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2980" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2980" s="4" t="s">
+        <v>3391</v>
+      </c>
+      <c r="B2980" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2980" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2980" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E2980" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F2980" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2980" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2980" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2981" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2981" s="9" t="s">
+        <v>3392</v>
+      </c>
+      <c r="B2981" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2981" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2981" s="12">
+        <v>859311</v>
+      </c>
+      <c r="E2981" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F2981" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2981" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2981" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2982" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2982" s="4" t="s">
+        <v>3393</v>
+      </c>
+      <c r="B2982" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2982" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2982" s="7">
+        <v>886911</v>
+      </c>
+      <c r="E2982" s="5" t="s">
+        <v>600</v>
+      </c>
+      <c r="F2982" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2982" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2982" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2983" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2983" s="9" t="s">
+        <v>3394</v>
+      </c>
+      <c r="B2983" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2983" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2983" s="12">
+        <v>836541</v>
+      </c>
+      <c r="E2983" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="F2983" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2983" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2983" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2984" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2984" s="4" t="s">
+        <v>3395</v>
+      </c>
+      <c r="B2984" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2984" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2984" s="7">
+        <v>177442</v>
+      </c>
+      <c r="E2984" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F2984" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2984" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2984" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2985" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2985" s="9" t="s">
+        <v>3396</v>
+      </c>
+      <c r="B2985" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2985" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2985" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E2985" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F2985" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2985" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2985" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2986" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2986" s="4" t="s">
+        <v>3397</v>
+      </c>
+      <c r="B2986" s="5" t="s">
+        <v>1548</v>
+      </c>
+      <c r="C2986" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2986" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E2986" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2986" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2986" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2986" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="2987" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2987" s="9" t="s">
+        <v>3398</v>
+      </c>
+      <c r="B2987" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2987" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2987" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E2987" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2987" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2987" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2987" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2988" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2988" s="4" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B2988" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2988" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2988" s="7">
+        <v>878249</v>
+      </c>
+      <c r="E2988" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="F2988" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2988" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2988" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2989" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2989" s="9" t="s">
+        <v>3400</v>
+      </c>
+      <c r="B2989" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2989" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2989" s="12">
+        <v>869886</v>
+      </c>
+      <c r="E2989" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F2989" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G2989" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H2989" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2990" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2990" s="4" t="s">
+        <v>3401</v>
+      </c>
+      <c r="B2990" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2990" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2990" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E2990" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F2990" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2990" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2990" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2991" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2991" s="9" t="s">
+        <v>3402</v>
+      </c>
+      <c r="B2991" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2991" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2991" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2991" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2991" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2991" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2991" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2992" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2992" s="4" t="s">
+        <v>3403</v>
+      </c>
+      <c r="B2992" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2992" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2992" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E2992" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F2992" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2992" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2992" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2993" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2993" s="9" t="s">
+        <v>3404</v>
+      </c>
+      <c r="B2993" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2993" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2993" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2993" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2993" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2993" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2993" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2994" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2994" s="4" t="s">
+        <v>3405</v>
+      </c>
+      <c r="B2994" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2994" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2994" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E2994" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F2994" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2994" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2994" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2995" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2995" s="9" t="s">
+        <v>3406</v>
+      </c>
+      <c r="B2995" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2995" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2995" s="12">
+        <v>788656</v>
+      </c>
+      <c r="E2995" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2995" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2995" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2995" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2996" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2996" s="4" t="s">
+        <v>3407</v>
+      </c>
+      <c r="B2996" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C2996" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2996" s="7">
+        <v>729970</v>
+      </c>
+      <c r="E2996" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F2996" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2996" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H2996" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2997" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2997" s="9" t="s">
+        <v>3408</v>
+      </c>
+      <c r="B2997" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2997" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2997" s="12">
+        <v>818103</v>
+      </c>
+      <c r="E2997" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2997" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G2997" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2997" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2998" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2998" s="4" t="s">
+        <v>3409</v>
+      </c>
+      <c r="B2998" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2998" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D2998" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E2998" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2998" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G2998" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H2998" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2999" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2999" s="9" t="s">
+        <v>3410</v>
+      </c>
+      <c r="B2999" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C2999" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D2999" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E2999" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F2999" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G2999" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H2999" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3000" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3000" s="4" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B3000" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3000" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3000" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E3000" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3000" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3000" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3000" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3001" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3001" s="9" t="s">
+        <v>3412</v>
+      </c>
+      <c r="B3001" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3001" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3001" s="12">
+        <v>529843</v>
+      </c>
+      <c r="E3001" s="5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="F3001" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3001" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3001" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3002" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3002" s="4" t="s">
+        <v>3413</v>
+      </c>
+      <c r="B3002" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3002" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3002" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E3002" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3002" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3002" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3002" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3003" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3003" s="9" t="s">
+        <v>3414</v>
+      </c>
+      <c r="B3003" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3003" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3003" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E3003" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3003" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3003" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3003" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3004" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3004" s="4" t="s">
+        <v>3415</v>
+      </c>
+      <c r="B3004" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3004" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3004" s="7">
+        <v>405</v>
+      </c>
+      <c r="E3004" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3004" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3004" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3004" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3005" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3005" s="9" t="s">
+        <v>3416</v>
+      </c>
+      <c r="B3005" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3005" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3005" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E3005" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3005" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3005" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3005" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3006" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3006" s="4" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B3006" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3006" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3006" s="7">
+        <v>619759</v>
+      </c>
+      <c r="E3006" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F3006" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3006" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3006" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3007" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3007" s="9" t="s">
+        <v>3418</v>
+      </c>
+      <c r="B3007" s="10" t="s">
+        <v>3419</v>
+      </c>
+      <c r="C3007" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3007" s="12">
+        <v>198483</v>
+      </c>
+      <c r="E3007" s="5" t="s">
+        <v>3454</v>
+      </c>
+      <c r="F3007" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3007" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3007" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3008" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3008" s="4" t="s">
+        <v>3420</v>
+      </c>
+      <c r="B3008" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3008" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3008" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E3008" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3008" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3008" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3008" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3009" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3009" s="9" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B3009" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3009" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3009" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E3009" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3009" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3009" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3009" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3010" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3010" s="4" t="s">
+        <v>3422</v>
+      </c>
+      <c r="B3010" s="5" t="s">
+        <v>3423</v>
+      </c>
+      <c r="C3010" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3010" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E3010" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3010" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3010" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3010" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3011" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3011" s="9" t="s">
+        <v>3424</v>
+      </c>
+      <c r="B3011" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3011" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3011" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E3011" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3011" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3011" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3011" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3012" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3012" s="4" t="s">
+        <v>3425</v>
+      </c>
+      <c r="B3012" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3012" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3012" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3012" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3012" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3012" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3012" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3013" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3013" s="9" t="s">
+        <v>3426</v>
+      </c>
+      <c r="B3013" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3013" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3013" s="12">
+        <v>399149</v>
+      </c>
+      <c r="E3013" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3013" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3013" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3013" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3014" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3014" s="4" t="s">
+        <v>3427</v>
+      </c>
+      <c r="B3014" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3014" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3014" s="7">
+        <v>843112</v>
+      </c>
+      <c r="E3014" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="F3014" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3014" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3014" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3015" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3015" s="9" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B3015" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3015" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3015" s="12">
+        <v>882331</v>
+      </c>
+      <c r="E3015" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3015" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3015" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3015" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3016" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3016" s="4" t="s">
+        <v>3429</v>
+      </c>
+      <c r="B3016" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3016" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3016" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E3016" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3016" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3016" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3016" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3017" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3017" s="9" t="s">
+        <v>3430</v>
+      </c>
+      <c r="B3017" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3017" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3017" s="12">
+        <v>876183</v>
+      </c>
+      <c r="E3017" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="F3017" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3017" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3017" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3018" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3018" s="4" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B3018" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3018" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3018" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3018" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3018" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3018" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3018" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3019" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3019" s="9" t="s">
+        <v>3432</v>
+      </c>
+      <c r="B3019" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3019" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3019" s="12">
+        <v>888374</v>
+      </c>
+      <c r="E3019" s="5" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F3019" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3019" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3019" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3020" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3020" s="4" t="s">
+        <v>2389</v>
+      </c>
+      <c r="B3020" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3020" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3020" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E3020" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3020" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3020" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3020" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3021" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3021" s="9" t="s">
+        <v>3433</v>
+      </c>
+      <c r="B3021" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3021" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3021" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E3021" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3021" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3021" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3021" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3022" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3022" s="4" t="s">
+        <v>3434</v>
+      </c>
+      <c r="B3022" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3022" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3022" s="7">
+        <v>736256</v>
+      </c>
+      <c r="E3022" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3022" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3022" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3022" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3023" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3023" s="9" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B3023" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3023" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3023" s="12">
+        <v>547683</v>
+      </c>
+      <c r="E3023" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3023" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3023" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3023" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3024" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3024" s="4" t="s">
+        <v>3436</v>
+      </c>
+      <c r="B3024" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3024" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3024" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E3024" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3024" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3024" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3024" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3025" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3025" s="9" t="s">
+        <v>3437</v>
+      </c>
+      <c r="B3025" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3025" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3025" s="12">
+        <v>884801</v>
+      </c>
+      <c r="E3025" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F3025" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3025" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3025" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3026" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3026" s="4" t="s">
+        <v>3438</v>
+      </c>
+      <c r="B3026" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C3026" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3026" s="7">
+        <v>878249</v>
+      </c>
+      <c r="E3026" s="5" t="s">
+        <v>892</v>
+      </c>
+      <c r="F3026" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3026" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3026" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3027" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3027" s="9" t="s">
+        <v>3439</v>
+      </c>
+      <c r="B3027" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3027" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3027" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E3027" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3027" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3027" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3027" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3028" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3028" s="4" t="s">
+        <v>3440</v>
+      </c>
+      <c r="B3028" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3028" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3028" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3028" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3028" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3028" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3028" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3029" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3029" s="9" t="s">
+        <v>3441</v>
+      </c>
+      <c r="B3029" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3029" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3029" s="12">
+        <v>785577</v>
+      </c>
+      <c r="E3029" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F3029" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3029" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3029" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3030" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3030" s="4" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B3030" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3030" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3030" s="7">
+        <v>830617</v>
+      </c>
+      <c r="E3030" s="5" t="s">
+        <v>2354</v>
+      </c>
+      <c r="F3030" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3030" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3030" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3031" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3031" s="9" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B3031" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3031" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3031" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E3031" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3031" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3031" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3031" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3032" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3032" s="4" t="s">
+        <v>3443</v>
+      </c>
+      <c r="B3032" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3032" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3032" s="7">
+        <v>216565</v>
+      </c>
+      <c r="E3032" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="F3032" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3032" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3032" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3033" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3033" s="9" t="s">
+        <v>3444</v>
+      </c>
+      <c r="B3033" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3033" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3033" s="12">
+        <v>619759</v>
+      </c>
+      <c r="E3033" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F3033" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3033" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3033" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3034" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3034" s="4" t="s">
+        <v>3445</v>
+      </c>
+      <c r="B3034" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3034" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3034" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3034" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3034" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3034" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3034" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3035" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3035" s="9" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B3035" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3035" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3035" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E3035" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3035" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3035" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3035" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3036" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3036" s="4" t="s">
+        <v>3447</v>
+      </c>
+      <c r="B3036" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3036" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3036" s="7">
+        <v>213687</v>
+      </c>
+      <c r="E3036" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3036" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3036" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3036" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3037" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3037" s="9" t="s">
+        <v>616</v>
+      </c>
+      <c r="B3037" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3037" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3037" s="12">
+        <v>781646</v>
+      </c>
+      <c r="E3037" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="F3037" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3037" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3037" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3038" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3038" s="4" t="s">
+        <v>3448</v>
+      </c>
+      <c r="B3038" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3038" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3038" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3038" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3038" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3038" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3038" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3039" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3039" s="9" t="s">
+        <v>3449</v>
+      </c>
+      <c r="B3039" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C3039" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3039" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E3039" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3039" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3039" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3039" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3040" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3040" s="4" t="s">
+        <v>3450</v>
+      </c>
+      <c r="B3040" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3040" s="6">
+        <v>45848</v>
+      </c>
+      <c r="D3040" s="7">
+        <v>729970</v>
+      </c>
+      <c r="E3040" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="F3040" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3040" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3040" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3041" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3041" s="9" t="s">
+        <v>3451</v>
+      </c>
+      <c r="B3041" s="10" t="s">
+        <v>1580</v>
+      </c>
+      <c r="C3041" s="11">
+        <v>45848</v>
+      </c>
+      <c r="D3041" s="12">
+        <v>38153</v>
+      </c>
+      <c r="E3041" s="5" t="s">
+        <v>1816</v>
+      </c>
+      <c r="F3041" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3041" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3041" s="13" t="s">
         <v>87</v>
       </c>
     </row>

--- a/crm_dominus/apps/dados/backlog_ativacao.xlsx
+++ b/crm_dominus/apps/dados/backlog_ativacao.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PME-COM-02740\Desktop\V2-crm-dominus\crm_dominus\apps\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BA75B47-041B-4198-8691-E3BB202A49B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7591FE07-3420-4A0F-9E25-98332BDA995A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F1068BE8-6A04-4046-BF81-1D35DD95EA81}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18248" uniqueCount="3455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19730" uniqueCount="3702">
   <si>
     <t>Cliente</t>
   </si>
@@ -10399,6 +10399,747 @@
   </si>
   <si>
     <t>PAR - INTE - IRH - INDEL INFORMATICA - TEYLOR NYLAND</t>
+  </si>
+  <si>
+    <t>FERNANDO DA SILVA</t>
+  </si>
+  <si>
+    <t>LAURA SILVA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Elizangela de Jesus Vicoli</t>
+  </si>
+  <si>
+    <t>DANIELLE RAQUEL MAHLE</t>
+  </si>
+  <si>
+    <t>EDIVAN BONDAN</t>
+  </si>
+  <si>
+    <t>Elisandra Dorneles Soares</t>
+  </si>
+  <si>
+    <t>Ana claudia de Siqueira</t>
+  </si>
+  <si>
+    <t>Ketlyn costa da silva</t>
+  </si>
+  <si>
+    <t>Patrick Almeida dos Santos</t>
+  </si>
+  <si>
+    <t>Janete Aparecida welter</t>
+  </si>
+  <si>
+    <t>Luis Guilherme Amaral de Barros</t>
+  </si>
+  <si>
+    <t>Neuton Diego Carriel</t>
+  </si>
+  <si>
+    <t>Solange Rute de Senna</t>
+  </si>
+  <si>
+    <t>JONATAN ROSA ESPINDOLA</t>
+  </si>
+  <si>
+    <t>RAYANA FRIGO PAIVA</t>
+  </si>
+  <si>
+    <t>RODRIGO MOESCH WELTER</t>
+  </si>
+  <si>
+    <t>kimberli neves gomes</t>
+  </si>
+  <si>
+    <t>Silmara Padilha Varella</t>
+  </si>
+  <si>
+    <t>Priscila Pinto</t>
+  </si>
+  <si>
+    <t>Joao Paulo Barbosa</t>
+  </si>
+  <si>
+    <t>SAMARA PADILHA TIMOTEO</t>
+  </si>
+  <si>
+    <t>Juliane Alves da luz de Jesus</t>
+  </si>
+  <si>
+    <t>BRENDA RENATA LEMES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Patrícia Abril Puchal</t>
+  </si>
+  <si>
+    <t>CLAUDETE NEGRI</t>
+  </si>
+  <si>
+    <t>Mário José Rodrigues da Silva</t>
+  </si>
+  <si>
+    <t>Ana Maria Ribeiro</t>
+  </si>
+  <si>
+    <t>Hayla Camila de Oliveira</t>
+  </si>
+  <si>
+    <t>Rute Santana dos Santos Pires</t>
+  </si>
+  <si>
+    <t>LUCIENE CARVALHO DA SILVA GANGORRA</t>
+  </si>
+  <si>
+    <t>SHEILA CRISTINA BAZZI</t>
+  </si>
+  <si>
+    <t>ITA/SC</t>
+  </si>
+  <si>
+    <t>KLEVERTON RODRIGO ROSA DA ROSA</t>
+  </si>
+  <si>
+    <t>Priscila Meirelles de Oliveira</t>
+  </si>
+  <si>
+    <t>Raissa Vitoria Vargas dos Santos</t>
+  </si>
+  <si>
+    <t>Edison Alexander Hereira Gomez</t>
+  </si>
+  <si>
+    <t>LEANDRO VESELY DE SOUZA</t>
+  </si>
+  <si>
+    <t>Loise de Fátima Ribas</t>
+  </si>
+  <si>
+    <t>Everton Carlos Palermo Rovida</t>
+  </si>
+  <si>
+    <t>ELISEU GRDEN</t>
+  </si>
+  <si>
+    <t>Sueli Duarte De Oliveira Assis</t>
+  </si>
+  <si>
+    <t>Valdeci romanini</t>
+  </si>
+  <si>
+    <t>Maria de lourdes de oliveira</t>
+  </si>
+  <si>
+    <t>Alisson Machado de Almeida</t>
+  </si>
+  <si>
+    <t>ANDRIGO DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>Arisson Rafael Do Nascimento Lima</t>
+  </si>
+  <si>
+    <t>LUIZ ROQUE TRENTIN DE ANDRADE</t>
+  </si>
+  <si>
+    <t>Fabrício dos Santos Mendes</t>
+  </si>
+  <si>
+    <t>JONATAS DUTRA FIORENTIN</t>
+  </si>
+  <si>
+    <t>ADRIANA FATIMA DUARTE</t>
+  </si>
+  <si>
+    <t>ERISSON RONALDO DURANS ALVES</t>
+  </si>
+  <si>
+    <t>Diego Trindade Garcia</t>
+  </si>
+  <si>
+    <t>Francini da Silveira Narciso</t>
+  </si>
+  <si>
+    <t>FAGNER CONTE</t>
+  </si>
+  <si>
+    <t>Jair Gonçalves Silveira</t>
+  </si>
+  <si>
+    <t>Robert Christian Welter</t>
+  </si>
+  <si>
+    <t>DAIANA SILVEIRA</t>
+  </si>
+  <si>
+    <t>Jonathan Henrique Maia machado</t>
+  </si>
+  <si>
+    <t>Dalvalina Aparecida da Silva Oliveira</t>
+  </si>
+  <si>
+    <t>Cesar Augusto Ferreira</t>
+  </si>
+  <si>
+    <t>Michael Padilha Santos</t>
+  </si>
+  <si>
+    <t>Letícia de Menezes Bueno</t>
+  </si>
+  <si>
+    <t>Aline Cristiane Scheibler</t>
+  </si>
+  <si>
+    <t>Franyeni Diaz</t>
+  </si>
+  <si>
+    <t>JULIO CESAR DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Vanessa Tavares da luz</t>
+  </si>
+  <si>
+    <t>EZEQUIEL MICHEL</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA RODRIGUES</t>
+  </si>
+  <si>
+    <t>MONIKI JUKOSKI</t>
+  </si>
+  <si>
+    <t>Ana Rosa dos Santos Marques</t>
+  </si>
+  <si>
+    <t>Adlineser patricia Pereira dos Santos</t>
+  </si>
+  <si>
+    <t>Carlos Alexandre Narcizo Paz</t>
+  </si>
+  <si>
+    <t>ELIZANGELA DOS SANTOS DA SILVA</t>
+  </si>
+  <si>
+    <t>Claudiangela Alves Pereira</t>
+  </si>
+  <si>
+    <t>SOLANGE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Raquel Mirian da Costa</t>
+  </si>
+  <si>
+    <t>Alexandre De Jesus Santos</t>
+  </si>
+  <si>
+    <t>Valquíria De Campos</t>
+  </si>
+  <si>
+    <t>ROGERIO ANTONIO VANIN</t>
+  </si>
+  <si>
+    <t>Glauber Basso</t>
+  </si>
+  <si>
+    <t>Marcelo Antônio Medeiros</t>
+  </si>
+  <si>
+    <t>MARCIO ALESCINDRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>AMANDA BARBOSA GOERITZ</t>
+  </si>
+  <si>
+    <t>Anderson Maia Dos Santos</t>
+  </si>
+  <si>
+    <t>Vitória De Oliveira Cândido</t>
+  </si>
+  <si>
+    <t>Antônio Agadir Corrêa</t>
+  </si>
+  <si>
+    <t>BENJAMIM NATANIEL DIMER FERNANDEZ</t>
+  </si>
+  <si>
+    <t>ANDERSON DE SOUZA MARCELINO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Joelson nespollo</t>
+  </si>
+  <si>
+    <t>Rafael Lemann Valim</t>
+  </si>
+  <si>
+    <t>Otávio Augusto de Almeida</t>
+  </si>
+  <si>
+    <t>Ana Clara Mendes</t>
+  </si>
+  <si>
+    <t>Weder Martins De Paula</t>
+  </si>
+  <si>
+    <t>NADIA APARECIDA CHAIM DA SILVA</t>
+  </si>
+  <si>
+    <t>Antônio Marlon Milani</t>
+  </si>
+  <si>
+    <t>Paula Gabriely Gomes</t>
+  </si>
+  <si>
+    <t>Patrícia de Meira Cavalheiro</t>
+  </si>
+  <si>
+    <t>CAMILY VITORIA MACHADO</t>
+  </si>
+  <si>
+    <t>JOSELIO DE OLIVEIRA PIRES JUNIOR</t>
+  </si>
+  <si>
+    <t>LETICIA SCHEFFER</t>
+  </si>
+  <si>
+    <t>Alvino Souza Da Conceição</t>
+  </si>
+  <si>
+    <t>ALEX DE OLIVEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>Gabriel Vinicius dos Santos Rodrigues</t>
+  </si>
+  <si>
+    <t>ALBERI FERREIRA DE CASTRO</t>
+  </si>
+  <si>
+    <t>Josevaldo Augusto</t>
+  </si>
+  <si>
+    <t>João Valdir De Oliveira De Paula</t>
+  </si>
+  <si>
+    <t>Juliano Adamski</t>
+  </si>
+  <si>
+    <t>Taina Santos Camargo</t>
+  </si>
+  <si>
+    <t>André da Silva Petry</t>
+  </si>
+  <si>
+    <t>Carlos Alexandre Maciel De Oliveira</t>
+  </si>
+  <si>
+    <t>Alaíde Jerônimo Rodrigues</t>
+  </si>
+  <si>
+    <t>THYEINI PAOLA PRADO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Rafael da Silva Ferreira</t>
+  </si>
+  <si>
+    <t>Priscila Da Rocha</t>
+  </si>
+  <si>
+    <t>Luis Elieser de Oliveira Viana</t>
+  </si>
+  <si>
+    <t>Julia Graciela Alves Do Carmo</t>
+  </si>
+  <si>
+    <t>Alessandra Amaral Queiroz</t>
+  </si>
+  <si>
+    <t>VANESSA OLIVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Luan Felipe Borges Camargo</t>
+  </si>
+  <si>
+    <t>Yesiree Yusmery Martínez Páez</t>
+  </si>
+  <si>
+    <t>Bruno Silva da Cruz</t>
+  </si>
+  <si>
+    <t>Pamela vitória Queiroz de Oliveira</t>
+  </si>
+  <si>
+    <t>ALEX SANDRA BARCELLOS DE ARAUJO</t>
+  </si>
+  <si>
+    <t>PEDRO FRANDOLOSO</t>
+  </si>
+  <si>
+    <t>KELIS CATIANE PERIN</t>
+  </si>
+  <si>
+    <t>YASMIM EVELLYN PEREIRA VIEIRA</t>
+  </si>
+  <si>
+    <t>Joselina Mary de Proença</t>
+  </si>
+  <si>
+    <t>INSTITUTO UNIWORK - VALENCIO E FARIA LTDA</t>
+  </si>
+  <si>
+    <t>STEFANIE CAUANE ALLEBRAND</t>
+  </si>
+  <si>
+    <t>LUANDSON SOARES AMARAL</t>
+  </si>
+  <si>
+    <t>FHILLIPI MIRANDA AGNE</t>
+  </si>
+  <si>
+    <t>Luciana Mara Tronco</t>
+  </si>
+  <si>
+    <t>Glamirvis Karine Verde Guerra</t>
+  </si>
+  <si>
+    <t>DANIEL CEZAR ZANG</t>
+  </si>
+  <si>
+    <t>Everton Maciel</t>
+  </si>
+  <si>
+    <t>ALLAN HENRIQUE LANGE FERREIRA</t>
+  </si>
+  <si>
+    <t>JOHNNY JESUS SALAZAR REYES</t>
+  </si>
+  <si>
+    <t>Dirlene Rodrigues Ignácio Kretschmer</t>
+  </si>
+  <si>
+    <t>VALDECIR DAVID DANDOLINI</t>
+  </si>
+  <si>
+    <t>CAPITANIO &amp; CIA LTDA</t>
+  </si>
+  <si>
+    <t>Carlos Daniel Stumpf</t>
+  </si>
+  <si>
+    <t>HIAGO TRINDADE DE LIMA</t>
+  </si>
+  <si>
+    <t>FERNANDO LUCAS</t>
+  </si>
+  <si>
+    <t>Marlon Filipe Da Rosa Balhejo</t>
+  </si>
+  <si>
+    <t>ANDREI LOPES MELNIK</t>
+  </si>
+  <si>
+    <t>Elza Casagrande Oltramari</t>
+  </si>
+  <si>
+    <t>Andressa Cristina Remoaldo dos Santos</t>
+  </si>
+  <si>
+    <t>Rogério americano de Freitas</t>
+  </si>
+  <si>
+    <t>MARCIA COELHO RODRIGUES BARA</t>
+  </si>
+  <si>
+    <t>José Douglas Pilar</t>
+  </si>
+  <si>
+    <t>AURI JOSE FERREIRA MENDONCA</t>
+  </si>
+  <si>
+    <t>ASSOCIACAO COMUNITARIA DO BAIRRO ALVORADA</t>
+  </si>
+  <si>
+    <t>CARLOS ALBERTO CANTELLI</t>
+  </si>
+  <si>
+    <t>Cleonice Azeredo Alves</t>
+  </si>
+  <si>
+    <t>CLARA TETERYCZ</t>
+  </si>
+  <si>
+    <t>ELIS ROXANA RUBIO MARQUEZ</t>
+  </si>
+  <si>
+    <t>Nadia Sanchez Rodrigues</t>
+  </si>
+  <si>
+    <t>Camila Souza Ribeiro</t>
+  </si>
+  <si>
+    <t>Terezinha Melo De Oliveira</t>
+  </si>
+  <si>
+    <t>Jeniffer Cristiane Quevedo Teixeira</t>
+  </si>
+  <si>
+    <t>RESIDENCIAL BOM PASTOR</t>
+  </si>
+  <si>
+    <t>Loraini Candida Bueno Leal Assunção</t>
+  </si>
+  <si>
+    <t>ANDREY FIDELIS CARDOSO VIANA</t>
+  </si>
+  <si>
+    <t>PABLO DAVID DA SILVA RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>Sandro Bertinatto</t>
+  </si>
+  <si>
+    <t>HENRIQUE MATEUS SOARES PAIVA</t>
+  </si>
+  <si>
+    <t>MATEUS CORREA GUZATTI</t>
+  </si>
+  <si>
+    <t>Ermelina dos Santos</t>
+  </si>
+  <si>
+    <t>Wesley Crecencio Oliveira ribeiro</t>
+  </si>
+  <si>
+    <t>Andrielli dos santos Pacheco</t>
+  </si>
+  <si>
+    <t>Rhuan Pablo da Silva dos Santos</t>
+  </si>
+  <si>
+    <t>ELISEU FRUZINDA</t>
+  </si>
+  <si>
+    <t>ROMELANDIA/SC</t>
+  </si>
+  <si>
+    <t>FELIPE GOMES DA ROCHA</t>
+  </si>
+  <si>
+    <t>UILIAM SILVA DA SILVA</t>
+  </si>
+  <si>
+    <t>Caetano Oliveira da Silva</t>
+  </si>
+  <si>
+    <t>RAFAEL FERREIRA DORDETTI</t>
+  </si>
+  <si>
+    <t>LUIS GROSS</t>
+  </si>
+  <si>
+    <t>KEILER JOSÉ REQUENA GONZÁLES</t>
+  </si>
+  <si>
+    <t>Ronsagela Beatriz de Moraes</t>
+  </si>
+  <si>
+    <t>BRUNA DIAS COELHO</t>
+  </si>
+  <si>
+    <t>Bruno Santos Oliveira</t>
+  </si>
+  <si>
+    <t>Leticia Zorzi Martins da Silva</t>
+  </si>
+  <si>
+    <t>Lucia Baldin</t>
+  </si>
+  <si>
+    <t>MAREMA/SC</t>
+  </si>
+  <si>
+    <t>Diego Mateus Pavoski</t>
+  </si>
+  <si>
+    <t>Rosane Helena Schwingel</t>
+  </si>
+  <si>
+    <t>Isabela Barbosa Santos Da Silva</t>
+  </si>
+  <si>
+    <t>ADRIANA DE SENA VIEIRA ENGEL</t>
+  </si>
+  <si>
+    <t>RAFAELA FERNANDES GUALBERTO</t>
+  </si>
+  <si>
+    <t>Alexandre Da Silva Macedo</t>
+  </si>
+  <si>
+    <t>EVERTON JAIR DA ROSA</t>
+  </si>
+  <si>
+    <t>Silvia maria baumgratz</t>
+  </si>
+  <si>
+    <t>Jair Marques Nascimento</t>
+  </si>
+  <si>
+    <t>Bruna Gonçalves pereira</t>
+  </si>
+  <si>
+    <t>Alni Pedro Farias</t>
+  </si>
+  <si>
+    <t>MARCOS ANTONIO DOS SANTOS AVELAR</t>
+  </si>
+  <si>
+    <t>Wilson Francisco Alves</t>
+  </si>
+  <si>
+    <t>Tania Maria Dias De Souza Santos</t>
+  </si>
+  <si>
+    <t>MIGUEL ARCANJO MACHADO SOBRINHO</t>
+  </si>
+  <si>
+    <t>Sandra Fernandes</t>
+  </si>
+  <si>
+    <t>Neymar Do Prado Felicio</t>
+  </si>
+  <si>
+    <t>ANGELICA ALVES DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>Audiceia Cardoso Dos Santos</t>
+  </si>
+  <si>
+    <t>Fabio Junio Ambrosio</t>
+  </si>
+  <si>
+    <t>Mario zan de toffol</t>
+  </si>
+  <si>
+    <t>MATHEUS LOPES DA SILVA</t>
+  </si>
+  <si>
+    <t>JULIANA RIOS</t>
+  </si>
+  <si>
+    <t>JOSELAINE PONCIO BARBOSA</t>
+  </si>
+  <si>
+    <t>Jonevaldo Soares</t>
+  </si>
+  <si>
+    <t>NAIR RODRIGUES</t>
+  </si>
+  <si>
+    <t>JANEMAR CHAVES DOMINGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>ALVARO MANICA</t>
+  </si>
+  <si>
+    <t>BRUNO SILVIO ROVERSI</t>
+  </si>
+  <si>
+    <t>Suelen da Rosa Junqueira</t>
+  </si>
+  <si>
+    <t>LUANA APARECIDA DE CAMPOS</t>
+  </si>
+  <si>
+    <t>Rosicleia Aparecida De Macedo Ferreira</t>
+  </si>
+  <si>
+    <t>Vanderson Luiz de Almeida</t>
+  </si>
+  <si>
+    <t>RAQUEL CAMPOS</t>
+  </si>
+  <si>
+    <t>Ana Augusta Dos Santos</t>
+  </si>
+  <si>
+    <t>GENESIO GIOCONDO</t>
+  </si>
+  <si>
+    <t>CASSIANE  POSTAL</t>
+  </si>
+  <si>
+    <t>GESSICA ALVES FERREIRA</t>
+  </si>
+  <si>
+    <t>Stefani Caroline Hahn Ramos</t>
+  </si>
+  <si>
+    <t>Luís Maita</t>
+  </si>
+  <si>
+    <t>Angélica Dos Santos Teixeira</t>
+  </si>
+  <si>
+    <t>FERNANDA REGINA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ROSELI TEREZINHA HAHN DIEDRICH</t>
+  </si>
+  <si>
+    <t>Leandra Christiane Da Silva</t>
+  </si>
+  <si>
+    <t>Luiz Guiomar Rocha</t>
+  </si>
+  <si>
+    <t>João Sisnei Escobar</t>
+  </si>
+  <si>
+    <t>Patricia Escasban</t>
+  </si>
+  <si>
+    <t>Cleverson Ferraz Do Carmo Ribeiro</t>
+  </si>
+  <si>
+    <t>ELISA GABRIELA DA SILVEIRA DA MOTTA</t>
+  </si>
+  <si>
+    <t>CLAUDIO DOS SANTOS RODRIGUES</t>
+  </si>
+  <si>
+    <t>EMERSON OLIVEIRA D'AVILA</t>
+  </si>
+  <si>
+    <t>Camila depromocena oliveira</t>
+  </si>
+  <si>
+    <t>Priscila de fatima miranda</t>
+  </si>
+  <si>
+    <t>Rubnei dos Santos Silva</t>
+  </si>
+  <si>
+    <t>Rogério Tormem</t>
+  </si>
+  <si>
+    <t>Edson Webler</t>
+  </si>
+  <si>
+    <t>Lourena Aparecida Galvão nunes</t>
+  </si>
+  <si>
+    <t>Luciano Ferreira da rocha</t>
+  </si>
+  <si>
+    <t>COM - TOO - GABRIELLY VAZQUES DE LIMA</t>
+  </si>
+  <si>
+    <t>COM - FRL - CRISTIANE POLO</t>
+  </si>
+  <si>
+    <t>COM - PAS - ANTONY ALEXANDER DA SILVA RIBEIRO</t>
+  </si>
+  <si>
+    <t>PAR - INTE - RMD - INFORMATICA PERONDI - IVANIR PERONDI</t>
   </si>
 </sst>
 </file>
@@ -10822,7 +11563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EBE226-2569-43EF-8B89-51B7526D69A9}">
-  <dimension ref="A1:H3041"/>
+  <dimension ref="A1:H3288"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="10.5546875" bestFit="1" customWidth="1"/>
@@ -89894,6 +90635,6428 @@
         <v>87</v>
       </c>
     </row>
+    <row r="3042" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3042" s="4" t="s">
+        <v>3455</v>
+      </c>
+      <c r="B3042" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3042" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3042" s="7">
+        <v>775845</v>
+      </c>
+      <c r="E3042" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3042" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3042" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3042" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3043" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3043" s="9" t="s">
+        <v>3456</v>
+      </c>
+      <c r="B3043" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C3043" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3043" s="12">
+        <v>127424</v>
+      </c>
+      <c r="E3043" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3043" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3043" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3043" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3044" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3044" s="4" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B3044" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3044" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3044" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3044" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3044" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3044" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3044" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3045" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3045" s="9" t="s">
+        <v>3458</v>
+      </c>
+      <c r="B3045" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3045" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3045" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E3045" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3045" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3045" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3045" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3046" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3046" s="4" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B3046" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3046" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3046" s="7">
+        <v>706513</v>
+      </c>
+      <c r="E3046" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F3046" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3046" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3046" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3047" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3047" s="9" t="s">
+        <v>3460</v>
+      </c>
+      <c r="B3047" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3047" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3047" s="12">
+        <v>576159</v>
+      </c>
+      <c r="E3047" s="5" t="s">
+        <v>2690</v>
+      </c>
+      <c r="F3047" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3047" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3047" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3048" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3048" s="4" t="s">
+        <v>3461</v>
+      </c>
+      <c r="B3048" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3048" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3048" s="7">
+        <v>683063</v>
+      </c>
+      <c r="E3048" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F3048" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3048" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3048" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3049" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3049" s="9" t="s">
+        <v>3462</v>
+      </c>
+      <c r="B3049" s="10" t="s">
+        <v>806</v>
+      </c>
+      <c r="C3049" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3049" s="12">
+        <v>811004</v>
+      </c>
+      <c r="E3049" s="5" t="s">
+        <v>3698</v>
+      </c>
+      <c r="F3049" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3049" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3049" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3050" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3050" s="4" t="s">
+        <v>3463</v>
+      </c>
+      <c r="B3050" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3050" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3050" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3050" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3050" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3050" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3050" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3051" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3051" s="9" t="s">
+        <v>3464</v>
+      </c>
+      <c r="B3051" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C3051" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3051" s="12">
+        <v>86784</v>
+      </c>
+      <c r="E3051" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3051" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3051" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3051" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3052" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3052" s="4" t="s">
+        <v>3465</v>
+      </c>
+      <c r="B3052" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3052" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3052" s="7">
+        <v>866752</v>
+      </c>
+      <c r="E3052" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3052" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3052" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3052" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3053" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3053" s="9" t="s">
+        <v>3466</v>
+      </c>
+      <c r="B3053" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3053" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3053" s="12">
+        <v>556838</v>
+      </c>
+      <c r="E3053" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F3053" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3053" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3053" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3054" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3054" s="4" t="s">
+        <v>3467</v>
+      </c>
+      <c r="B3054" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="C3054" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3054" s="7">
+        <v>867522</v>
+      </c>
+      <c r="E3054" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3054" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3054" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3054" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3055" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3055" s="9" t="s">
+        <v>3468</v>
+      </c>
+      <c r="B3055" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3055" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3055" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E3055" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3055" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3055" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3055" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3056" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3056" s="4" t="s">
+        <v>3469</v>
+      </c>
+      <c r="B3056" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3056" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3056" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E3056" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3056" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3056" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3056" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3057" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3057" s="9" t="s">
+        <v>3470</v>
+      </c>
+      <c r="B3057" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3057" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3057" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E3057" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3057" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3057" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3057" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3058" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3058" s="4" t="s">
+        <v>3471</v>
+      </c>
+      <c r="B3058" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3058" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3058" s="7">
+        <v>882296</v>
+      </c>
+      <c r="E3058" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3058" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3058" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3058" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3059" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3059" s="9" t="s">
+        <v>3472</v>
+      </c>
+      <c r="B3059" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3059" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3059" s="12">
+        <v>882331</v>
+      </c>
+      <c r="E3059" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3059" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3059" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3059" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3060" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3060" s="4" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B3060" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3060" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3060" s="7">
+        <v>834515</v>
+      </c>
+      <c r="E3060" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F3060" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3060" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3060" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3061" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3061" s="9" t="s">
+        <v>3473</v>
+      </c>
+      <c r="B3061" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3061" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3061" s="12">
+        <v>868672</v>
+      </c>
+      <c r="E3061" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3061" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3061" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3061" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3062" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3062" s="4" t="s">
+        <v>3474</v>
+      </c>
+      <c r="B3062" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3062" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3062" s="7">
+        <v>368409</v>
+      </c>
+      <c r="E3062" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="F3062" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3062" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3062" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3063" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3063" s="9" t="s">
+        <v>3475</v>
+      </c>
+      <c r="B3063" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3063" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3063" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E3063" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3063" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3063" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3063" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3064" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3064" s="4" t="s">
+        <v>3476</v>
+      </c>
+      <c r="B3064" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3064" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3064" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E3064" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3064" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3064" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3064" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3065" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3065" s="9" t="s">
+        <v>3477</v>
+      </c>
+      <c r="B3065" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3065" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3065" s="12">
+        <v>213687</v>
+      </c>
+      <c r="E3065" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="F3065" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3065" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3065" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3066" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3066" s="4" t="s">
+        <v>3478</v>
+      </c>
+      <c r="B3066" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3066" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3066" s="7">
+        <v>875888</v>
+      </c>
+      <c r="E3066" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F3066" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3066" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3066" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3067" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3067" s="9" t="s">
+        <v>3479</v>
+      </c>
+      <c r="B3067" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3067" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3067" s="12">
+        <v>235841</v>
+      </c>
+      <c r="E3067" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3067" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3067" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3067" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3068" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3068" s="4" t="s">
+        <v>3480</v>
+      </c>
+      <c r="B3068" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3068" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3068" s="7">
+        <v>864414</v>
+      </c>
+      <c r="E3068" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F3068" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3068" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3068" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3069" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3069" s="9" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B3069" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3069" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3069" s="12">
+        <v>828092</v>
+      </c>
+      <c r="E3069" s="5" t="s">
+        <v>1569</v>
+      </c>
+      <c r="F3069" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3069" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3069" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3070" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3070" s="4" t="s">
+        <v>3481</v>
+      </c>
+      <c r="B3070" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3070" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3070" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E3070" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3070" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3070" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3070" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3071" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3071" s="9" t="s">
+        <v>3482</v>
+      </c>
+      <c r="B3071" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3071" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3071" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E3071" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3071" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3071" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3071" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3072" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3072" s="4" t="s">
+        <v>3483</v>
+      </c>
+      <c r="B3072" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3072" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3072" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E3072" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3072" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3072" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3072" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3073" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3073" s="9" t="s">
+        <v>3484</v>
+      </c>
+      <c r="B3073" s="10" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C3073" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3073" s="12">
+        <v>382796</v>
+      </c>
+      <c r="E3073" s="5" t="s">
+        <v>917</v>
+      </c>
+      <c r="F3073" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3073" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3073" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3074" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3074" s="4" t="s">
+        <v>3485</v>
+      </c>
+      <c r="B3074" s="5" t="s">
+        <v>3486</v>
+      </c>
+      <c r="C3074" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3074" s="7">
+        <v>77299</v>
+      </c>
+      <c r="E3074" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F3074" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3074" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3074" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3075" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3075" s="9" t="s">
+        <v>3487</v>
+      </c>
+      <c r="B3075" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3075" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3075" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E3075" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3075" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3075" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3075" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3076" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3076" s="4" t="s">
+        <v>3488</v>
+      </c>
+      <c r="B3076" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3076" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3076" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E3076" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3076" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3076" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3076" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3077" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3077" s="9" t="s">
+        <v>3489</v>
+      </c>
+      <c r="B3077" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3077" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3077" s="12">
+        <v>574996</v>
+      </c>
+      <c r="E3077" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="F3077" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3077" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3077" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3078" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3078" s="4" t="s">
+        <v>3490</v>
+      </c>
+      <c r="B3078" s="5" t="s">
+        <v>1535</v>
+      </c>
+      <c r="C3078" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3078" s="7">
+        <v>822704</v>
+      </c>
+      <c r="E3078" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3078" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3078" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3078" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3079" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3079" s="9" t="s">
+        <v>3491</v>
+      </c>
+      <c r="B3079" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3079" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3079" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E3079" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3079" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3079" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3079" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3080" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3080" s="4" t="s">
+        <v>3492</v>
+      </c>
+      <c r="B3080" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3080" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3080" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E3080" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3080" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3080" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3080" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3081" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3081" s="9" t="s">
+        <v>3493</v>
+      </c>
+      <c r="B3081" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3081" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3081" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E3081" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3081" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3081" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3081" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3082" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3082" s="4" t="s">
+        <v>3494</v>
+      </c>
+      <c r="B3082" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3082" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3082" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3082" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3082" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3082" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3082" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3083" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3083" s="9" t="s">
+        <v>3495</v>
+      </c>
+      <c r="B3083" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3083" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3083" s="12">
+        <v>881485</v>
+      </c>
+      <c r="E3083" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F3083" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3083" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3083" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3084" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3084" s="4" t="s">
+        <v>3496</v>
+      </c>
+      <c r="B3084" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3084" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3084" s="7">
+        <v>883823</v>
+      </c>
+      <c r="E3084" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="F3084" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3084" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3084" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3085" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3085" s="9" t="s">
+        <v>3497</v>
+      </c>
+      <c r="B3085" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3085" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3085" s="12">
+        <v>829353</v>
+      </c>
+      <c r="E3085" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3085" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3085" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3085" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3086" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3086" s="4" t="s">
+        <v>3498</v>
+      </c>
+      <c r="B3086" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3086" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3086" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E3086" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3086" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3086" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3086" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3087" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3087" s="9" t="s">
+        <v>3499</v>
+      </c>
+      <c r="B3087" s="10" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3087" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3087" s="12">
+        <v>862715</v>
+      </c>
+      <c r="E3087" s="5" t="s">
+        <v>912</v>
+      </c>
+      <c r="F3087" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3087" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3087" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3088" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3088" s="4" t="s">
+        <v>3500</v>
+      </c>
+      <c r="B3088" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3088" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3088" s="7">
+        <v>817</v>
+      </c>
+      <c r="E3088" s="5" t="s">
+        <v>1263</v>
+      </c>
+      <c r="F3088" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3088" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3088" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3089" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3089" s="9" t="s">
+        <v>3501</v>
+      </c>
+      <c r="B3089" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3089" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3089" s="12">
+        <v>172141</v>
+      </c>
+      <c r="E3089" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3089" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3089" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3089" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3090" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3090" s="4" t="s">
+        <v>3502</v>
+      </c>
+      <c r="B3090" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3090" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3090" s="7">
+        <v>875888</v>
+      </c>
+      <c r="E3090" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F3090" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3090" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3090" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3091" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3091" s="9" t="s">
+        <v>3503</v>
+      </c>
+      <c r="B3091" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3091" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3091" s="12">
+        <v>844442</v>
+      </c>
+      <c r="E3091" s="5" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F3091" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3091" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3091" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3092" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3092" s="4" t="s">
+        <v>3504</v>
+      </c>
+      <c r="B3092" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3092" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3092" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E3092" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F3092" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3092" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3092" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3093" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3093" s="9" t="s">
+        <v>3505</v>
+      </c>
+      <c r="B3093" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3093" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3093" s="12">
+        <v>864414</v>
+      </c>
+      <c r="E3093" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F3093" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3093" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3093" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3094" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3094" s="4" t="s">
+        <v>3506</v>
+      </c>
+      <c r="B3094" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3094" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3094" s="7">
+        <v>780838</v>
+      </c>
+      <c r="E3094" s="5" t="s">
+        <v>2942</v>
+      </c>
+      <c r="F3094" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3094" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3094" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3095" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3095" s="9" t="s">
+        <v>3507</v>
+      </c>
+      <c r="B3095" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3095" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3095" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E3095" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3095" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3095" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3095" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3096" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3096" s="4" t="s">
+        <v>3508</v>
+      </c>
+      <c r="B3096" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3096" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3096" s="7">
+        <v>785577</v>
+      </c>
+      <c r="E3096" s="5" t="s">
+        <v>601</v>
+      </c>
+      <c r="F3096" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3096" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3096" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3097" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3097" s="9" t="s">
+        <v>3509</v>
+      </c>
+      <c r="B3097" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3097" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3097" s="12">
+        <v>875521</v>
+      </c>
+      <c r="E3097" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F3097" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3097" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3097" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3098" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3098" s="4" t="s">
+        <v>3510</v>
+      </c>
+      <c r="B3098" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3098" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3098" s="7">
+        <v>437804</v>
+      </c>
+      <c r="E3098" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3098" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3098" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3098" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3099" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3099" s="9" t="s">
+        <v>3511</v>
+      </c>
+      <c r="B3099" s="10" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C3099" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3099" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E3099" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3099" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3099" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3099" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3100" s="4" t="s">
+        <v>3512</v>
+      </c>
+      <c r="B3100" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3100" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3100" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E3100" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3100" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3100" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3100" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3101" s="9" t="s">
+        <v>3513</v>
+      </c>
+      <c r="B3101" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3101" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3101" s="12">
+        <v>683349</v>
+      </c>
+      <c r="E3101" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3101" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3101" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3101" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3102" s="4" t="s">
+        <v>3514</v>
+      </c>
+      <c r="B3102" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3102" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3102" s="7">
+        <v>556838</v>
+      </c>
+      <c r="E3102" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F3102" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3102" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3102" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3103" s="9" t="s">
+        <v>3515</v>
+      </c>
+      <c r="B3103" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3103" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3103" s="12">
+        <v>882296</v>
+      </c>
+      <c r="E3103" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3103" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3103" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3103" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3104" s="4" t="s">
+        <v>3516</v>
+      </c>
+      <c r="B3104" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3104" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3104" s="7">
+        <v>882296</v>
+      </c>
+      <c r="E3104" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3104" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3104" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3104" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3105" s="9" t="s">
+        <v>3517</v>
+      </c>
+      <c r="B3105" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3105" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3105" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E3105" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3105" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3105" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3105" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3106" s="4" t="s">
+        <v>3518</v>
+      </c>
+      <c r="B3106" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3106" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3106" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E3106" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3106" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3106" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3106" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3107" s="9" t="s">
+        <v>3519</v>
+      </c>
+      <c r="B3107" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3107" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3107" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E3107" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3107" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3107" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3107" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3108" s="4" t="s">
+        <v>3520</v>
+      </c>
+      <c r="B3108" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3108" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3108" s="7">
+        <v>262147</v>
+      </c>
+      <c r="E3108" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="F3108" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3108" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3108" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3109" s="9" t="s">
+        <v>3521</v>
+      </c>
+      <c r="B3109" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3109" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3109" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3109" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3109" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3109" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3109" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3110" s="4" t="s">
+        <v>3522</v>
+      </c>
+      <c r="B3110" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3110" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3110" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E3110" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3110" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3110" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3110" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3111" s="9" t="s">
+        <v>3523</v>
+      </c>
+      <c r="B3111" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3111" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3111" s="12">
+        <v>653931</v>
+      </c>
+      <c r="E3111" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3111" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3111" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3111" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3112" s="4" t="s">
+        <v>3524</v>
+      </c>
+      <c r="B3112" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3112" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3112" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E3112" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3112" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3112" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3112" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3113" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3113" s="9" t="s">
+        <v>3525</v>
+      </c>
+      <c r="B3113" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3113" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3113" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3113" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3113" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3113" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3113" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3114" s="4" t="s">
+        <v>3526</v>
+      </c>
+      <c r="B3114" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3114" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3114" s="7">
+        <v>861705</v>
+      </c>
+      <c r="E3114" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3114" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3114" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3114" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3115" s="9" t="s">
+        <v>3527</v>
+      </c>
+      <c r="B3115" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3115" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3115" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E3115" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3115" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3115" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3115" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3116" s="4" t="s">
+        <v>3528</v>
+      </c>
+      <c r="B3116" s="5" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C3116" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3116" s="7">
+        <v>114283</v>
+      </c>
+      <c r="E3116" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F3116" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3116" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3116" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3117" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3117" s="9" t="s">
+        <v>3529</v>
+      </c>
+      <c r="B3117" s="10" t="s">
+        <v>2076</v>
+      </c>
+      <c r="C3117" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3117" s="12">
+        <v>857108</v>
+      </c>
+      <c r="E3117" s="5" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F3117" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3117" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3117" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3118" s="4" t="s">
+        <v>3530</v>
+      </c>
+      <c r="B3118" s="5" t="s">
+        <v>840</v>
+      </c>
+      <c r="C3118" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3118" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E3118" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3118" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3118" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3118" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3119" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3119" s="9" t="s">
+        <v>3531</v>
+      </c>
+      <c r="B3119" s="10" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3119" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3119" s="12">
+        <v>843112</v>
+      </c>
+      <c r="E3119" s="5" t="s">
+        <v>913</v>
+      </c>
+      <c r="F3119" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3119" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3119" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3120" s="4" t="s">
+        <v>3532</v>
+      </c>
+      <c r="B3120" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3120" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3120" s="7">
+        <v>829353</v>
+      </c>
+      <c r="E3120" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F3120" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3120" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3120" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3121" s="9" t="s">
+        <v>3533</v>
+      </c>
+      <c r="B3121" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3121" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3121" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E3121" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3121" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3121" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3121" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3122" s="4" t="s">
+        <v>3534</v>
+      </c>
+      <c r="B3122" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3122" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3122" s="7">
+        <v>863796</v>
+      </c>
+      <c r="E3122" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="F3122" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3122" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3122" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3123" s="9" t="s">
+        <v>3535</v>
+      </c>
+      <c r="B3123" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3123" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3123" s="12">
+        <v>882357</v>
+      </c>
+      <c r="E3123" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3123" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3123" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3123" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3124" s="4" t="s">
+        <v>3536</v>
+      </c>
+      <c r="B3124" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C3124" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3124" s="7">
+        <v>485228</v>
+      </c>
+      <c r="E3124" s="5" t="s">
+        <v>1262</v>
+      </c>
+      <c r="F3124" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3124" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3124" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3125" s="9" t="s">
+        <v>3537</v>
+      </c>
+      <c r="B3125" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3125" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3125" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E3125" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3125" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3125" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3125" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3126" s="4" t="s">
+        <v>3538</v>
+      </c>
+      <c r="B3126" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3126" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3126" s="7">
+        <v>559912</v>
+      </c>
+      <c r="E3126" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3126" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3126" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3126" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3127" s="9" t="s">
+        <v>3539</v>
+      </c>
+      <c r="B3127" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3127" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3127" s="12">
+        <v>878848</v>
+      </c>
+      <c r="E3127" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F3127" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3127" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3127" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3128" s="4" t="s">
+        <v>3540</v>
+      </c>
+      <c r="B3128" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3128" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3128" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E3128" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3128" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3128" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3128" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3129" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3129" s="9" t="s">
+        <v>3541</v>
+      </c>
+      <c r="B3129" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3129" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3129" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E3129" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3129" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3129" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3129" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3130" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3130" s="4" t="s">
+        <v>3542</v>
+      </c>
+      <c r="B3130" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3130" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3130" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3130" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3130" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3130" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3130" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3131" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3131" s="9" t="s">
+        <v>3543</v>
+      </c>
+      <c r="B3131" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3131" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3131" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3131" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3131" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3131" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3131" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3132" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3132" s="4" t="s">
+        <v>3544</v>
+      </c>
+      <c r="B3132" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3132" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3132" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E3132" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3132" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3132" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3132" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3133" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3133" s="9" t="s">
+        <v>3545</v>
+      </c>
+      <c r="B3133" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3133" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3133" s="12">
+        <v>237623</v>
+      </c>
+      <c r="E3133" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="F3133" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3133" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3133" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3134" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3134" s="4" t="s">
+        <v>3546</v>
+      </c>
+      <c r="B3134" s="5" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3134" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3134" s="7">
+        <v>790437</v>
+      </c>
+      <c r="E3134" s="5" t="s">
+        <v>1565</v>
+      </c>
+      <c r="F3134" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3134" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3134" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3135" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3135" s="9" t="s">
+        <v>3547</v>
+      </c>
+      <c r="B3135" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3135" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3135" s="12">
+        <v>827465</v>
+      </c>
+      <c r="E3135" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3135" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3135" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3135" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3136" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3136" s="4" t="s">
+        <v>3548</v>
+      </c>
+      <c r="B3136" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3136" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3136" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3136" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3136" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3136" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3136" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3137" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3137" s="9" t="s">
+        <v>3549</v>
+      </c>
+      <c r="B3137" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C3137" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3137" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3137" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3137" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3137" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3137" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3138" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3138" s="4" t="s">
+        <v>3550</v>
+      </c>
+      <c r="B3138" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3138" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3138" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3138" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3138" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3138" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3138" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3139" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3139" s="9" t="s">
+        <v>3551</v>
+      </c>
+      <c r="B3139" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3139" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3139" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E3139" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3139" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3139" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3139" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3140" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3140" s="4" t="s">
+        <v>3552</v>
+      </c>
+      <c r="B3140" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3140" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3140" s="7">
+        <v>738880</v>
+      </c>
+      <c r="E3140" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3140" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3140" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3140" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3141" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3141" s="9" t="s">
+        <v>3553</v>
+      </c>
+      <c r="B3141" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3141" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3141" s="12">
+        <v>525458</v>
+      </c>
+      <c r="E3141" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F3141" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3141" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3141" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3142" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3142" s="4" t="s">
+        <v>3554</v>
+      </c>
+      <c r="B3142" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3142" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3142" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E3142" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3142" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3142" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3142" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3143" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3143" s="9" t="s">
+        <v>3555</v>
+      </c>
+      <c r="B3143" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3143" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3143" s="12">
+        <v>653931</v>
+      </c>
+      <c r="E3143" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F3143" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3143" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3143" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3144" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3144" s="4" t="s">
+        <v>3556</v>
+      </c>
+      <c r="B3144" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3144" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3144" s="7">
+        <v>837937</v>
+      </c>
+      <c r="E3144" s="5" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F3144" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3144" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3144" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3145" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3145" s="9" t="s">
+        <v>3557</v>
+      </c>
+      <c r="B3145" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3145" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3145" s="12">
+        <v>382799</v>
+      </c>
+      <c r="E3145" s="5" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F3145" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3145" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3145" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3146" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3146" s="4" t="s">
+        <v>3558</v>
+      </c>
+      <c r="B3146" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3146" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3146" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E3146" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3146" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3146" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3146" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3147" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3147" s="9" t="s">
+        <v>3559</v>
+      </c>
+      <c r="B3147" s="10" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C3147" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3147" s="12">
+        <v>833948</v>
+      </c>
+      <c r="E3147" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3147" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3147" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3147" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3148" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3148" s="4" t="s">
+        <v>3559</v>
+      </c>
+      <c r="B3148" s="5" t="s">
+        <v>1471</v>
+      </c>
+      <c r="C3148" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3148" s="7">
+        <v>833948</v>
+      </c>
+      <c r="E3148" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3148" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3148" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3148" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3149" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3149" s="9" t="s">
+        <v>3560</v>
+      </c>
+      <c r="B3149" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3149" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3149" s="12">
+        <v>40828</v>
+      </c>
+      <c r="E3149" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="F3149" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3149" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3149" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3150" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3150" s="4" t="s">
+        <v>3561</v>
+      </c>
+      <c r="B3150" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3150" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3150" s="7">
+        <v>873688</v>
+      </c>
+      <c r="E3150" s="5" t="s">
+        <v>1557</v>
+      </c>
+      <c r="F3150" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3150" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3150" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3151" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3151" s="9" t="s">
+        <v>3562</v>
+      </c>
+      <c r="B3151" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3151" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3151" s="12">
+        <v>594578</v>
+      </c>
+      <c r="E3151" s="5" t="s">
+        <v>3699</v>
+      </c>
+      <c r="F3151" s="5" t="s">
+        <v>2347</v>
+      </c>
+      <c r="G3151" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3151" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3152" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3152" s="4" t="s">
+        <v>3563</v>
+      </c>
+      <c r="B3152" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3152" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3152" s="7">
+        <v>556838</v>
+      </c>
+      <c r="E3152" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F3152" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3152" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3152" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3153" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3153" s="9" t="s">
+        <v>3564</v>
+      </c>
+      <c r="B3153" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3153" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3153" s="12">
+        <v>868672</v>
+      </c>
+      <c r="E3153" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3153" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3153" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3153" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3154" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3154" s="4" t="s">
+        <v>3565</v>
+      </c>
+      <c r="B3154" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="C3154" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3154" s="7">
+        <v>683063</v>
+      </c>
+      <c r="E3154" s="5" t="s">
+        <v>891</v>
+      </c>
+      <c r="F3154" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3154" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3154" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3155" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3155" s="9" t="s">
+        <v>3566</v>
+      </c>
+      <c r="B3155" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3155" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3155" s="12">
+        <v>868672</v>
+      </c>
+      <c r="E3155" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3155" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3155" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3155" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3156" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3156" s="4" t="s">
+        <v>3567</v>
+      </c>
+      <c r="B3156" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3156" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3156" s="7">
+        <v>882296</v>
+      </c>
+      <c r="E3156" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F3156" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3156" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3156" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3157" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3157" s="9" t="s">
+        <v>3568</v>
+      </c>
+      <c r="B3157" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3157" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3157" s="12">
+        <v>767508</v>
+      </c>
+      <c r="E3157" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3157" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3157" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3157" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3158" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3158" s="4" t="s">
+        <v>3569</v>
+      </c>
+      <c r="B3158" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3158" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3158" s="7">
+        <v>556838</v>
+      </c>
+      <c r="E3158" s="5" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F3158" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3158" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3158" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3159" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3159" s="9" t="s">
+        <v>3570</v>
+      </c>
+      <c r="B3159" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3159" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3159" s="12">
+        <v>882357</v>
+      </c>
+      <c r="E3159" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F3159" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3159" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3159" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3160" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3160" s="4" t="s">
+        <v>3571</v>
+      </c>
+      <c r="B3160" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3160" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3160" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E3160" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3160" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3160" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3160" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3161" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3161" s="9" t="s">
+        <v>3572</v>
+      </c>
+      <c r="B3161" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="C3161" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3161" s="12">
+        <v>819069</v>
+      </c>
+      <c r="E3161" s="5" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F3161" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3161" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3161" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3162" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3162" s="4" t="s">
+        <v>3573</v>
+      </c>
+      <c r="B3162" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3162" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3162" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3162" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3162" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3162" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3162" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3163" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3163" s="9" t="s">
+        <v>3574</v>
+      </c>
+      <c r="B3163" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3163" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3163" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E3163" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3163" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3163" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3163" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3164" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3164" s="4" t="s">
+        <v>3575</v>
+      </c>
+      <c r="B3164" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3164" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3164" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3164" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3164" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3164" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3164" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3165" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3165" s="9" t="s">
+        <v>3576</v>
+      </c>
+      <c r="B3165" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3165" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3165" s="12">
+        <v>610972</v>
+      </c>
+      <c r="E3165" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="F3165" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3165" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3165" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3166" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3166" s="4" t="s">
+        <v>3577</v>
+      </c>
+      <c r="B3166" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3166" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3166" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3166" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3166" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3166" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3166" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3167" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3167" s="9" t="s">
+        <v>3578</v>
+      </c>
+      <c r="B3167" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3167" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3167" s="12">
+        <v>864414</v>
+      </c>
+      <c r="E3167" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F3167" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3167" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3167" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3168" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3168" s="4" t="s">
+        <v>3579</v>
+      </c>
+      <c r="B3168" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3168" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3168" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E3168" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3168" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3168" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3168" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3169" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3169" s="9" t="s">
+        <v>3580</v>
+      </c>
+      <c r="B3169" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3169" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3169" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E3169" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3169" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3169" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3169" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3170" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3170" s="4" t="s">
+        <v>3581</v>
+      </c>
+      <c r="B3170" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3170" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3170" s="7">
+        <v>576121</v>
+      </c>
+      <c r="E3170" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3170" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3170" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3170" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3171" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3171" s="9" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B3171" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3171" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3171" s="12">
+        <v>870268</v>
+      </c>
+      <c r="E3171" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="F3171" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3171" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3171" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3172" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3172" s="4" t="s">
+        <v>3582</v>
+      </c>
+      <c r="B3172" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3172" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3172" s="7">
+        <v>870268</v>
+      </c>
+      <c r="E3172" s="5" t="s">
+        <v>907</v>
+      </c>
+      <c r="F3172" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3172" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3172" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3173" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3173" s="9" t="s">
+        <v>3583</v>
+      </c>
+      <c r="B3173" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3173" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3173" s="12">
+        <v>818285</v>
+      </c>
+      <c r="E3173" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F3173" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3173" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3173" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3174" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3174" s="4" t="s">
+        <v>3584</v>
+      </c>
+      <c r="B3174" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3174" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3174" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E3174" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3174" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3174" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3174" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3175" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3175" s="9" t="s">
+        <v>3585</v>
+      </c>
+      <c r="B3175" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3175" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3175" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E3175" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3175" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3175" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3175" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3176" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3176" s="4" t="s">
+        <v>3586</v>
+      </c>
+      <c r="B3176" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3176" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3176" s="7">
+        <v>889181</v>
+      </c>
+      <c r="E3176" s="5" t="s">
+        <v>3700</v>
+      </c>
+      <c r="F3176" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3176" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3176" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3177" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3177" s="9" t="s">
+        <v>3587</v>
+      </c>
+      <c r="B3177" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3177" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3177" s="12">
+        <v>780589</v>
+      </c>
+      <c r="E3177" s="5" t="s">
+        <v>1824</v>
+      </c>
+      <c r="F3177" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3177" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3177" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3178" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3178" s="4" t="s">
+        <v>3588</v>
+      </c>
+      <c r="B3178" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3178" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3178" s="7">
+        <v>617463</v>
+      </c>
+      <c r="E3178" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3178" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3178" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3178" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3179" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3179" s="9" t="s">
+        <v>3589</v>
+      </c>
+      <c r="B3179" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3179" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3179" s="12">
+        <v>864414</v>
+      </c>
+      <c r="E3179" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F3179" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3179" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3179" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3180" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3180" s="4" t="s">
+        <v>3590</v>
+      </c>
+      <c r="B3180" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3180" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3180" s="7">
+        <v>600710</v>
+      </c>
+      <c r="E3180" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3180" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3180" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3180" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3181" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3181" s="9" t="s">
+        <v>3591</v>
+      </c>
+      <c r="B3181" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3181" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3181" s="12">
+        <v>666428</v>
+      </c>
+      <c r="E3181" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F3181" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3181" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3181" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3182" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3182" s="4" t="s">
+        <v>3592</v>
+      </c>
+      <c r="B3182" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3182" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3182" s="7">
+        <v>877649</v>
+      </c>
+      <c r="E3182" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3182" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3182" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3182" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3183" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3183" s="9" t="s">
+        <v>3593</v>
+      </c>
+      <c r="B3183" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3183" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3183" s="12">
+        <v>843026</v>
+      </c>
+      <c r="E3183" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3183" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3183" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3183" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3184" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3184" s="4" t="s">
+        <v>3594</v>
+      </c>
+      <c r="B3184" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3184" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3184" s="7">
+        <v>869886</v>
+      </c>
+      <c r="E3184" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F3184" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3184" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3184" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3185" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3185" s="9" t="s">
+        <v>3595</v>
+      </c>
+      <c r="B3185" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3185" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3185" s="12">
+        <v>875521</v>
+      </c>
+      <c r="E3185" s="5" t="s">
+        <v>2355</v>
+      </c>
+      <c r="F3185" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3185" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3185" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3186" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3186" s="4" t="s">
+        <v>3596</v>
+      </c>
+      <c r="B3186" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3186" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3186" s="7">
+        <v>608355</v>
+      </c>
+      <c r="E3186" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="F3186" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3186" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3186" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3187" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3187" s="9" t="s">
+        <v>3597</v>
+      </c>
+      <c r="B3187" s="10" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C3187" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3187" s="12">
+        <v>77299</v>
+      </c>
+      <c r="E3187" s="5" t="s">
+        <v>1265</v>
+      </c>
+      <c r="F3187" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3187" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3187" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3188" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3188" s="4" t="s">
+        <v>3598</v>
+      </c>
+      <c r="B3188" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3188" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3188" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3188" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3188" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3188" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3188" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3189" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3189" s="9" t="s">
+        <v>3599</v>
+      </c>
+      <c r="B3189" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3189" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3189" s="12">
+        <v>674036</v>
+      </c>
+      <c r="E3189" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3189" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3189" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3189" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3190" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3190" s="4" t="s">
+        <v>3600</v>
+      </c>
+      <c r="B3190" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3190" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3190" s="7">
+        <v>882331</v>
+      </c>
+      <c r="E3190" s="5" t="s">
+        <v>215</v>
+      </c>
+      <c r="F3190" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3190" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3190" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3191" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3191" s="9" t="s">
+        <v>3601</v>
+      </c>
+      <c r="B3191" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3191" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3191" s="12">
+        <v>197832</v>
+      </c>
+      <c r="E3191" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3191" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3191" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3191" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3192" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3192" s="4" t="s">
+        <v>3602</v>
+      </c>
+      <c r="B3192" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3192" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3192" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3192" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3192" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3192" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3192" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3193" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3193" s="9" t="s">
+        <v>3603</v>
+      </c>
+      <c r="B3193" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C3193" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3193" s="12">
+        <v>880349</v>
+      </c>
+      <c r="E3193" s="5" t="s">
+        <v>2352</v>
+      </c>
+      <c r="F3193" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3193" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3193" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3194" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3194" s="4" t="s">
+        <v>3594</v>
+      </c>
+      <c r="B3194" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3194" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3194" s="7">
+        <v>869886</v>
+      </c>
+      <c r="E3194" s="5" t="s">
+        <v>1264</v>
+      </c>
+      <c r="F3194" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3194" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3194" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3195" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3195" s="9" t="s">
+        <v>3604</v>
+      </c>
+      <c r="B3195" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3195" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3195" s="12">
+        <v>559912</v>
+      </c>
+      <c r="E3195" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3195" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3195" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3195" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3196" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3196" s="4" t="s">
+        <v>3605</v>
+      </c>
+      <c r="B3196" s="5" t="s">
+        <v>804</v>
+      </c>
+      <c r="C3196" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3196" s="7">
+        <v>883580</v>
+      </c>
+      <c r="E3196" s="5" t="s">
+        <v>1820</v>
+      </c>
+      <c r="F3196" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3196" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3196" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3197" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3197" s="9" t="s">
+        <v>3606</v>
+      </c>
+      <c r="B3197" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3197" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3197" s="12">
+        <v>666428</v>
+      </c>
+      <c r="E3197" s="5" t="s">
+        <v>1261</v>
+      </c>
+      <c r="F3197" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3197" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3197" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3198" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3198" s="4" t="s">
+        <v>3607</v>
+      </c>
+      <c r="B3198" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3198" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3198" s="7">
+        <v>680982</v>
+      </c>
+      <c r="E3198" s="5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="F3198" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3198" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3198" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3199" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3199" s="9" t="s">
+        <v>3608</v>
+      </c>
+      <c r="B3199" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3199" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3199" s="12">
+        <v>177442</v>
+      </c>
+      <c r="E3199" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F3199" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3199" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3199" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3200" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3200" s="4" t="s">
+        <v>3609</v>
+      </c>
+      <c r="B3200" s="5" t="s">
+        <v>2877</v>
+      </c>
+      <c r="C3200" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3200" s="7">
+        <v>383260</v>
+      </c>
+      <c r="E3200" s="5" t="s">
+        <v>2944</v>
+      </c>
+      <c r="F3200" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3200" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3200" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3201" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3201" s="9" t="s">
+        <v>3610</v>
+      </c>
+      <c r="B3201" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3201" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3201" s="12">
+        <v>706513</v>
+      </c>
+      <c r="E3201" s="5" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F3201" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3201" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3201" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3202" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3202" s="4" t="s">
+        <v>3611</v>
+      </c>
+      <c r="B3202" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3202" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3202" s="7">
+        <v>767508</v>
+      </c>
+      <c r="E3202" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3202" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3202" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3202" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3203" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3203" s="9" t="s">
+        <v>3612</v>
+      </c>
+      <c r="B3203" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3203" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3203" s="12">
+        <v>794227</v>
+      </c>
+      <c r="E3203" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3203" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3203" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3203" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3204" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3204" s="4" t="s">
+        <v>3613</v>
+      </c>
+      <c r="B3204" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3204" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3204" s="7">
+        <v>876162</v>
+      </c>
+      <c r="E3204" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3204" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3204" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3204" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3205" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3205" s="9" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B3205" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3205" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3205" s="12">
+        <v>647291</v>
+      </c>
+      <c r="E3205" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3205" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3205" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3205" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3206" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3206" s="4" t="s">
+        <v>3614</v>
+      </c>
+      <c r="B3206" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3206" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3206" s="7">
+        <v>828645</v>
+      </c>
+      <c r="E3206" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="F3206" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3206" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3206" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3207" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3207" s="9" t="s">
+        <v>3615</v>
+      </c>
+      <c r="B3207" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3207" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3207" s="12">
+        <v>377654</v>
+      </c>
+      <c r="E3207" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F3207" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3207" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3207" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3208" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3208" s="4" t="s">
+        <v>3616</v>
+      </c>
+      <c r="B3208" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3208" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3208" s="7">
+        <v>239381</v>
+      </c>
+      <c r="E3208" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F3208" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G3208" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3208" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3209" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3209" s="9" t="s">
+        <v>3617</v>
+      </c>
+      <c r="B3209" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3209" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3209" s="12">
+        <v>600710</v>
+      </c>
+      <c r="E3209" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3209" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3209" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3209" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3210" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3210" s="4" t="s">
+        <v>3618</v>
+      </c>
+      <c r="B3210" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3210" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3210" s="7">
+        <v>685657</v>
+      </c>
+      <c r="E3210" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F3210" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3210" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3210" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3211" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3211" s="9" t="s">
+        <v>3619</v>
+      </c>
+      <c r="B3211" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3211" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3211" s="12">
+        <v>868672</v>
+      </c>
+      <c r="E3211" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F3211" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3211" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3211" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3212" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3212" s="4" t="s">
+        <v>3620</v>
+      </c>
+      <c r="B3212" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3212" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3212" s="7">
+        <v>165769</v>
+      </c>
+      <c r="E3212" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3212" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3212" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3212" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3213" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3213" s="9" t="s">
+        <v>3621</v>
+      </c>
+      <c r="B3213" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3213" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3213" s="12">
+        <v>775845</v>
+      </c>
+      <c r="E3213" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3213" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3213" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3213" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3214" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3214" s="4" t="s">
+        <v>3622</v>
+      </c>
+      <c r="B3214" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3214" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3214" s="7">
+        <v>233138</v>
+      </c>
+      <c r="E3214" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3214" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3214" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3214" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3215" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3215" s="9" t="s">
+        <v>3623</v>
+      </c>
+      <c r="B3215" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3215" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3215" s="12">
+        <v>777905</v>
+      </c>
+      <c r="E3215" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3215" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3215" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3215" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3216" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3216" s="4" t="s">
+        <v>3624</v>
+      </c>
+      <c r="B3216" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3216" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3216" s="7">
+        <v>235841</v>
+      </c>
+      <c r="E3216" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="F3216" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3216" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3216" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3217" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3217" s="9" t="s">
+        <v>3625</v>
+      </c>
+      <c r="B3217" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3217" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3217" s="12">
+        <v>405</v>
+      </c>
+      <c r="E3217" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3217" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3217" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3217" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3218" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3218" s="4" t="s">
+        <v>3626</v>
+      </c>
+      <c r="B3218" s="5" t="s">
+        <v>3627</v>
+      </c>
+      <c r="C3218" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3218" s="7">
+        <v>74491</v>
+      </c>
+      <c r="E3218" s="5" t="s">
+        <v>3701</v>
+      </c>
+      <c r="F3218" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3218" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3218" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3219" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3219" s="9" t="s">
+        <v>3628</v>
+      </c>
+      <c r="B3219" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3219" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3219" s="12">
+        <v>689070</v>
+      </c>
+      <c r="E3219" s="5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F3219" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3219" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3219" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3220" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3220" s="4" t="s">
+        <v>3629</v>
+      </c>
+      <c r="B3220" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3220" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3220" s="7">
+        <v>777905</v>
+      </c>
+      <c r="E3220" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="F3220" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3220" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3220" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3221" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3221" s="9" t="s">
+        <v>3630</v>
+      </c>
+      <c r="B3221" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3221" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3221" s="12">
+        <v>883819</v>
+      </c>
+      <c r="E3221" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3221" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3221" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3221" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3222" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3222" s="4" t="s">
+        <v>3631</v>
+      </c>
+      <c r="B3222" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3222" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3222" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3222" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3222" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3222" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3222" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3223" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3223" s="9" t="s">
+        <v>3632</v>
+      </c>
+      <c r="B3223" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3223" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3223" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E3223" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3223" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3223" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3223" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3224" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3224" s="4" t="s">
+        <v>3633</v>
+      </c>
+      <c r="B3224" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3224" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3224" s="7">
+        <v>399149</v>
+      </c>
+      <c r="E3224" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F3224" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3224" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3224" s="8" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3225" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3225" s="9" t="s">
+        <v>3634</v>
+      </c>
+      <c r="B3225" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3225" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3225" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3225" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3225" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3225" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3225" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3226" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3226" s="4" t="s">
+        <v>3635</v>
+      </c>
+      <c r="B3226" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3226" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3226" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E3226" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3226" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3226" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3226" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3227" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3227" s="9" t="s">
+        <v>3636</v>
+      </c>
+      <c r="B3227" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3227" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3227" s="12">
+        <v>674036</v>
+      </c>
+      <c r="E3227" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3227" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3227" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3227" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3228" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3228" s="4" t="s">
+        <v>3637</v>
+      </c>
+      <c r="B3228" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3228" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3228" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E3228" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3228" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3228" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3228" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3229" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3229" s="9" t="s">
+        <v>3638</v>
+      </c>
+      <c r="B3229" s="10" t="s">
+        <v>3639</v>
+      </c>
+      <c r="C3229" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3229" s="12">
+        <v>177442</v>
+      </c>
+      <c r="E3229" s="5" t="s">
+        <v>923</v>
+      </c>
+      <c r="F3229" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3229" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3229" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3230" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3230" s="4" t="s">
+        <v>3640</v>
+      </c>
+      <c r="B3230" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3230" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3230" s="7">
+        <v>556579</v>
+      </c>
+      <c r="E3230" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3230" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3230" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3230" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3231" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3231" s="9" t="s">
+        <v>3641</v>
+      </c>
+      <c r="B3231" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3231" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3231" s="12">
+        <v>736256</v>
+      </c>
+      <c r="E3231" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F3231" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3231" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3231" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3232" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3232" s="4" t="s">
+        <v>3642</v>
+      </c>
+      <c r="B3232" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3232" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3232" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E3232" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3232" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3232" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3232" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3233" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3233" s="9" t="s">
+        <v>3643</v>
+      </c>
+      <c r="B3233" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3233" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3233" s="12">
+        <v>818285</v>
+      </c>
+      <c r="E3233" s="5" t="s">
+        <v>2689</v>
+      </c>
+      <c r="F3233" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3233" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3233" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3234" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3234" s="4" t="s">
+        <v>3644</v>
+      </c>
+      <c r="B3234" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3234" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3234" s="7">
+        <v>883819</v>
+      </c>
+      <c r="E3234" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="F3234" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3234" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3234" s="8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3235" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3235" s="9" t="s">
+        <v>3645</v>
+      </c>
+      <c r="B3235" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3235" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3235" s="12">
+        <v>872155</v>
+      </c>
+      <c r="E3235" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="F3235" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3235" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3235" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3236" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3236" s="4" t="s">
+        <v>3646</v>
+      </c>
+      <c r="B3236" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3236" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3236" s="7">
+        <v>694166</v>
+      </c>
+      <c r="E3236" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3236" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3236" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3236" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3237" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3237" s="9" t="s">
+        <v>3647</v>
+      </c>
+      <c r="B3237" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3237" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3237" s="12">
+        <v>878929</v>
+      </c>
+      <c r="E3237" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F3237" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3237" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3237" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3238" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3238" s="4" t="s">
+        <v>3648</v>
+      </c>
+      <c r="B3238" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3238" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3238" s="7">
+        <v>46617</v>
+      </c>
+      <c r="E3238" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="F3238" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3238" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3238" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3239" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3239" s="9" t="s">
+        <v>3649</v>
+      </c>
+      <c r="B3239" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3239" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3239" s="12">
+        <v>233138</v>
+      </c>
+      <c r="E3239" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3239" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3239" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3239" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3240" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3240" s="4" t="s">
+        <v>3650</v>
+      </c>
+      <c r="B3240" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3240" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3240" s="7">
+        <v>876282</v>
+      </c>
+      <c r="E3240" s="5" t="s">
+        <v>925</v>
+      </c>
+      <c r="F3240" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3240" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3240" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3241" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3241" s="9" t="s">
+        <v>3651</v>
+      </c>
+      <c r="B3241" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3241" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3241" s="12">
+        <v>822704</v>
+      </c>
+      <c r="E3241" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3241" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3241" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3241" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3242" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3242" s="4" t="s">
+        <v>3652</v>
+      </c>
+      <c r="B3242" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3242" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3242" s="7">
+        <v>867522</v>
+      </c>
+      <c r="E3242" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3242" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3242" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3242" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3243" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3243" s="9" t="s">
+        <v>3653</v>
+      </c>
+      <c r="B3243" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3243" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3243" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E3243" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3243" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3243" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3243" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3244" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3244" s="4" t="s">
+        <v>3654</v>
+      </c>
+      <c r="B3244" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3244" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3244" s="7">
+        <v>867522</v>
+      </c>
+      <c r="E3244" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="F3244" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3244" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3244" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3245" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3245" s="9" t="s">
+        <v>3655</v>
+      </c>
+      <c r="B3245" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3245" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3245" s="12">
+        <v>617463</v>
+      </c>
+      <c r="E3245" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="F3245" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3245" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3245" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3246" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3246" s="4" t="s">
+        <v>3656</v>
+      </c>
+      <c r="B3246" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3246" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3246" s="7">
+        <v>559912</v>
+      </c>
+      <c r="E3246" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3246" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3246" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3246" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3247" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3247" s="9" t="s">
+        <v>3657</v>
+      </c>
+      <c r="B3247" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3247" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3247" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E3247" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3247" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3247" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3247" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3248" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3248" s="4" t="s">
+        <v>3658</v>
+      </c>
+      <c r="B3248" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3248" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3248" s="7">
+        <v>559912</v>
+      </c>
+      <c r="E3248" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F3248" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3248" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3248" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3249" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3249" s="9" t="s">
+        <v>3659</v>
+      </c>
+      <c r="B3249" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3249" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3249" s="12">
+        <v>792341</v>
+      </c>
+      <c r="E3249" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3249" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3249" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3249" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3250" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3250" s="4" t="s">
+        <v>3660</v>
+      </c>
+      <c r="B3250" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3250" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3250" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3250" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3250" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3250" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3250" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3251" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3251" s="9" t="s">
+        <v>3661</v>
+      </c>
+      <c r="B3251" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3251" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3251" s="12">
+        <v>165769</v>
+      </c>
+      <c r="E3251" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3251" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3251" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3251" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3252" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3252" s="4" t="s">
+        <v>3662</v>
+      </c>
+      <c r="B3252" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3252" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3252" s="7">
+        <v>165769</v>
+      </c>
+      <c r="E3252" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="F3252" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3252" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3252" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3253" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3253" s="9" t="s">
+        <v>3663</v>
+      </c>
+      <c r="B3253" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3253" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3253" s="12">
+        <v>878918</v>
+      </c>
+      <c r="E3253" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3253" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3253" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3253" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3254" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3254" s="4" t="s">
+        <v>3664</v>
+      </c>
+      <c r="B3254" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3254" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3254" s="7">
+        <v>716615</v>
+      </c>
+      <c r="E3254" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3254" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3254" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3254" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3255" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3255" s="9" t="s">
+        <v>3665</v>
+      </c>
+      <c r="B3255" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3255" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3255" s="12">
+        <v>864414</v>
+      </c>
+      <c r="E3255" s="5" t="s">
+        <v>906</v>
+      </c>
+      <c r="F3255" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3255" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3255" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3256" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3256" s="4" t="s">
+        <v>3666</v>
+      </c>
+      <c r="B3256" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3256" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3256" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E3256" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3256" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3256" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3256" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3257" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3257" s="9" t="s">
+        <v>3667</v>
+      </c>
+      <c r="B3257" s="10" t="s">
+        <v>1488</v>
+      </c>
+      <c r="C3257" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3257" s="12">
+        <v>114283</v>
+      </c>
+      <c r="E3257" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="F3257" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3257" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3257" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3258" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3258" s="4" t="s">
+        <v>3668</v>
+      </c>
+      <c r="B3258" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3258" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3258" s="7">
+        <v>875515</v>
+      </c>
+      <c r="E3258" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="F3258" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3258" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3258" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3259" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3259" s="9" t="s">
+        <v>3669</v>
+      </c>
+      <c r="B3259" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3259" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3259" s="12">
+        <v>876162</v>
+      </c>
+      <c r="E3259" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="F3259" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3259" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3259" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3260" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3260" s="4" t="s">
+        <v>3670</v>
+      </c>
+      <c r="B3260" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3260" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3260" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3260" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3260" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3260" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3260" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3261" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3261" s="9" t="s">
+        <v>3671</v>
+      </c>
+      <c r="B3261" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3261" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3261" s="12">
+        <v>687168</v>
+      </c>
+      <c r="E3261" s="5" t="s">
+        <v>1572</v>
+      </c>
+      <c r="F3261" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3261" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3261" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3262" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3262" s="4" t="s">
+        <v>3672</v>
+      </c>
+      <c r="B3262" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3262" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3262" s="7">
+        <v>792341</v>
+      </c>
+      <c r="E3262" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="F3262" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3262" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3262" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3263" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3263" s="9" t="s">
+        <v>3673</v>
+      </c>
+      <c r="B3263" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3263" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3263" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E3263" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3263" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3263" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3263" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3264" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3264" s="4" t="s">
+        <v>3674</v>
+      </c>
+      <c r="B3264" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3264" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3264" s="7">
+        <v>716615</v>
+      </c>
+      <c r="E3264" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3264" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3264" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3264" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3265" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3265" s="9" t="s">
+        <v>3675</v>
+      </c>
+      <c r="B3265" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C3265" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3265" s="12">
+        <v>619759</v>
+      </c>
+      <c r="E3265" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F3265" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3265" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3265" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3266" s="4" t="s">
+        <v>3676</v>
+      </c>
+      <c r="B3266" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3266" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3266" s="7">
+        <v>683349</v>
+      </c>
+      <c r="E3266" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3266" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3266" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3266" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3267" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3267" s="9" t="s">
+        <v>3677</v>
+      </c>
+      <c r="B3267" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C3267" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3267" s="12">
+        <v>556579</v>
+      </c>
+      <c r="E3267" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3267" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3267" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3267" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3268" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3268" s="4" t="s">
+        <v>3678</v>
+      </c>
+      <c r="B3268" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3268" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3268" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E3268" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3268" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3268" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3268" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3269" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3269" s="9" t="s">
+        <v>3679</v>
+      </c>
+      <c r="B3269" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3269" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3269" s="12">
+        <v>844068</v>
+      </c>
+      <c r="E3269" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F3269" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3269" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="H3269" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3270" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3270" s="4" t="s">
+        <v>3680</v>
+      </c>
+      <c r="B3270" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3270" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3270" s="7">
+        <v>877649</v>
+      </c>
+      <c r="E3270" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F3270" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3270" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3270" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3271" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3271" s="9" t="s">
+        <v>3681</v>
+      </c>
+      <c r="B3271" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3271" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3271" s="12">
+        <v>694166</v>
+      </c>
+      <c r="E3271" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3271" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3271" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3271" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="3272" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3272" s="4" t="s">
+        <v>3682</v>
+      </c>
+      <c r="B3272" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3272" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3272" s="7">
+        <v>827465</v>
+      </c>
+      <c r="E3272" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="F3272" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G3272" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3272" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3273" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3273" s="9" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B3273" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3273" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3273" s="12">
+        <v>878638</v>
+      </c>
+      <c r="E3273" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="F3273" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3273" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3273" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3274" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3274" s="4" t="s">
+        <v>3684</v>
+      </c>
+      <c r="B3274" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3274" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3274" s="7">
+        <v>716615</v>
+      </c>
+      <c r="E3274" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3274" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3274" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3274" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3275" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3275" s="9" t="s">
+        <v>3685</v>
+      </c>
+      <c r="B3275" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3275" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3275" s="12">
+        <v>716615</v>
+      </c>
+      <c r="E3275" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="F3275" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3275" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3275" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3276" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3276" s="4" t="s">
+        <v>3686</v>
+      </c>
+      <c r="B3276" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3276" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3276" s="7">
+        <v>197832</v>
+      </c>
+      <c r="E3276" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="F3276" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G3276" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3276" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3277" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3277" s="9" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B3277" s="10" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3277" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3277" s="12">
+        <v>674036</v>
+      </c>
+      <c r="E3277" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F3277" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G3277" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3277" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3278" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3278" s="4" t="s">
+        <v>3688</v>
+      </c>
+      <c r="B3278" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3278" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3278" s="7">
+        <v>794227</v>
+      </c>
+      <c r="E3278" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3278" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="G3278" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3278" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3279" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3279" s="9" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B3279" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3279" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3279" s="12">
+        <v>738880</v>
+      </c>
+      <c r="E3279" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3279" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3279" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3279" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3280" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3280" s="4" t="s">
+        <v>3690</v>
+      </c>
+      <c r="B3280" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3280" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3280" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E3280" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3280" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3280" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="H3280" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3281" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3281" s="9" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B3281" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3281" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3281" s="12">
+        <v>880152</v>
+      </c>
+      <c r="E3281" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3281" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3281" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3281" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3282" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3282" s="4" t="s">
+        <v>3692</v>
+      </c>
+      <c r="B3282" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3282" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3282" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E3282" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3282" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3282" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="H3282" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3283" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3283" s="9" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B3283" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3283" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3283" s="12">
+        <v>861705</v>
+      </c>
+      <c r="E3283" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F3283" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="G3283" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3283" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3284" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3284" s="4" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B3284" s="5" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C3284" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3284" s="7">
+        <v>647291</v>
+      </c>
+      <c r="E3284" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="F3284" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G3284" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3284" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3285" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3285" s="9" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B3285" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3285" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3285" s="12">
+        <v>647350</v>
+      </c>
+      <c r="E3285" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3285" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3285" s="10" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3285" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3286" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3286" s="4" t="s">
+        <v>3695</v>
+      </c>
+      <c r="B3286" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3286" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3286" s="7">
+        <v>788656</v>
+      </c>
+      <c r="E3286" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="F3286" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="G3286" s="5" t="s">
+        <v>2344</v>
+      </c>
+      <c r="H3286" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3287" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3287" s="9" t="s">
+        <v>3696</v>
+      </c>
+      <c r="B3287" s="10" t="s">
+        <v>840</v>
+      </c>
+      <c r="C3287" s="11">
+        <v>45849</v>
+      </c>
+      <c r="D3287" s="12">
+        <v>773535</v>
+      </c>
+      <c r="E3287" s="5" t="s">
+        <v>926</v>
+      </c>
+      <c r="F3287" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3287" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3287" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3288" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3288" s="4" t="s">
+        <v>3697</v>
+      </c>
+      <c r="B3288" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3288" s="6">
+        <v>45849</v>
+      </c>
+      <c r="D3288" s="7">
+        <v>880152</v>
+      </c>
+      <c r="E3288" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="F3288" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G3288" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3288" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
